--- a/docs/resultados.xlsx
+++ b/docs/resultados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I101"/>
+  <dimension ref="A1:I100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -489,7 +489,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0004979-20.2017.8.16.0056</t>
+          <t>0000022-19.1988.8.16.0047</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -499,27 +499,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Locação de Imóvel</t>
+          <t>Bancários</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>19/08/2024</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>05/08/2026 16:53</t>
+          <t>17/08/2026 13:03</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>05/08/2026 16:53</t>
+          <t>17/08/2026 13:03</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>20/08/2026 22:45</t>
+          <t>19/08/2026 00:42</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -536,7 +536,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0021603-50.2020.8.16.0021</t>
+          <t>0000033-52.2025.8.16.0079</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -546,27 +546,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Locação de Imóvel</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>10/12/2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>17/08/2026 14:53</t>
+          <t>17/08/2026 13:13</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17/08/2026 14:53</t>
+          <t>17/08/2026 13:13</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>20/08/2026 22:45</t>
+          <t>18/08/2026 16:46</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -583,37 +583,37 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0088421-71.2025.8.16.0000</t>
+          <t>0000163-85.2024.8.16.0173</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Crimes de Trânsito</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>13/08/2026 18:23</t>
+          <t>14/08/2026 17:13</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>13/08/2026 18:23</t>
+          <t>14/08/2026 17:13</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>20/08/2026 22:45</t>
+          <t>18/08/2026 13:38</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,7 +630,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0001893-39.2022.8.16.0097</t>
+          <t>0000174-98.2020.8.16.0062</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -640,27 +640,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Crimes de Trânsito</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>18/08/2026 16:13</t>
+          <t>17/08/2026 18:03</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>18/08/2026 16:13</t>
+          <t>17/08/2026 18:03</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>19/08/2026 03:41</t>
+          <t>18/08/2026 23:33</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -677,37 +677,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0038454-62.2022.8.16.0000</t>
+          <t>0000272-47.2009.8.16.0037</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Direitos / Deveres do Condômino</t>
+          <t>Homicídio Qualificado</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>03/10/2023</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>14/08/2026 13:03</t>
+          <t>13/08/2026 20:43</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>14/08/2026 13:03</t>
+          <t>13/08/2026 20:43</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>19/08/2026 04:12</t>
+          <t>18/08/2026 11:31</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -724,37 +724,37 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0028518-34.2023.8.16.0014</t>
+          <t>0000470-27.2018.8.16.0051</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Usucapião Extraordinária</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>19/08/2025</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>13/08/2026 16:43</t>
+          <t>14/08/2026 14:24</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>13/08/2026 16:43</t>
+          <t>14/08/2026 14:24</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>19/08/2026 03:21</t>
+          <t>18/08/2026 22:23</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -771,7 +771,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0068467-73.2024.8.16.0000</t>
+          <t>0000521-43.2023.8.16.0122</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -781,27 +781,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>24/10/2025</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>05/08/2026 18:53</t>
+          <t>14/08/2026 21:43</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>05/08/2026 18:53</t>
+          <t>14/08/2026 21:43</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>19/08/2026 03:21</t>
+          <t>18/08/2026 13:13</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -818,37 +818,37 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0037335-61.2025.8.16.0000</t>
+          <t>0000579-95.2025.8.16.0083</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Limitação de Juros</t>
+          <t>Furto Qualificado</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12/08/2026 15:03</t>
+          <t>14/08/2026 15:13</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>12/08/2026 15:03</t>
+          <t>14/08/2026 15:13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>19/08/2026 03:21</t>
+          <t>18/08/2026 10:42</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -865,7 +865,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0002976-93.2025.8.16.0159</t>
+          <t>0000625-04.2023.8.16.0100</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -875,27 +875,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dano Qualificado contra a Administração Pública</t>
+          <t>Usucapião Ordinária</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>13/08/2026 20:53</t>
+          <t>14/08/2026 20:33</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>13/08/2026 20:53</t>
+          <t>14/08/2026 20:33</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>19/08/2026 03:21</t>
+          <t>18/08/2026 10:44</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -912,12 +912,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0001236-59.2021.8.16.0024</t>
+          <t>0000706-08.2025.8.16.0156</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -927,22 +927,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>18/08/2026 10:52</t>
+          <t>13/08/2026 14:03</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>18/08/2026 10:52</t>
+          <t>13/08/2026 14:03</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>19/08/2026 02:47</t>
+          <t>18/08/2026 13:26</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -959,12 +959,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0050711-80.2026.8.16.0000</t>
+          <t>0001042-23.2024.8.16.0196</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -974,22 +974,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>13/08/2026 17:13</t>
+          <t>14/08/2026 13:43</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>13/08/2026 17:13</t>
+          <t>14/08/2026 13:43</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>19/08/2026 02:47</t>
+          <t>19/08/2026 00:37</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1006,37 +1006,37 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0001373-33.2019.8.16.0017</t>
+          <t>0001125-91.2024.8.16.0114</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Crimes de Trânsito</t>
+          <t>Tráfico de Drogas e Condutas Afins | Receptação | Adulteração de Sinal Identificador de Veículo Automotor</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>19/09/2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>13/08/2026 20:53</t>
+          <t>13/08/2026 20:43</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>13/08/2026 20:53</t>
+          <t>13/08/2026 20:43</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>19/08/2026 02:47</t>
+          <t>19/08/2026 02:36</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1053,7 +1053,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0026752-14.2021.8.16.0014</t>
+          <t>0001165-69.2023.8.16.0159</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1063,27 +1063,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Pagamento</t>
+          <t>Fornecimento</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>21/08/2024</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>14/08/2026 15:43</t>
+          <t>14/08/2026 19:43</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>14/08/2026 15:43</t>
+          <t>14/08/2026 19:43</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>19/08/2026 02:48</t>
+          <t>18/08/2026 13:44</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0016776-75.2024.8.16.0014</t>
+          <t>0001236-59.2021.8.16.0024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1110,27 +1110,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Plano de Saúde</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>12/08/2026 14:03</t>
+          <t>18/08/2026 10:52</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>12/08/2026 14:03</t>
+          <t>18/08/2026 10:52</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>19/08/2026 02:48</t>
+          <t>19/08/2026 02:47</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1147,7 +1147,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0009710-10.2025.8.16.0014</t>
+          <t>0001373-33.2019.8.16.0017</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1157,27 +1157,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Duplicata</t>
+          <t>Crimes de Trânsito</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>13/08/2026 18:33</t>
+          <t>13/08/2026 20:53</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>13/08/2026 18:33</t>
+          <t>13/08/2026 20:53</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>19/08/2026 02:48</t>
+          <t>19/08/2026 02:47</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1194,7 +1194,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0046048-25.2025.8.16.0000</t>
+          <t>0001556-88.2013.8.16.0154</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1204,27 +1204,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Seguro | Multa de 10% | Cumprimento Provisório de Sentença</t>
+          <t>Anulação de Débito Fiscal | Prescrição</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>05/08/2026 18:53</t>
+          <t>14/08/2026 17:43</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>05/08/2026 18:53</t>
+          <t>14/08/2026 17:43</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>19/08/2026 02:49</t>
+          <t>18/08/2026 12:52</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1241,7 +1241,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0117203-25.2024.8.16.0000</t>
+          <t>0001593-15.2020.8.16.0108</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1251,27 +1251,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Nota Promissória</t>
+          <t>Erro Médico | Erro Médico</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>03/02/2026</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>05/08/2026 14:53</t>
+          <t>13/08/2026 16:43</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>05/08/2026 14:53</t>
+          <t>13/08/2026 16:43</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>19/08/2026 02:49</t>
+          <t>19/08/2026 00:37</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1288,37 +1288,37 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0019003-57.2023.8.16.0019</t>
+          <t>0001652-58.2024.8.16.0109</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Desclassificação</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>02/10/2025</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>17/08/2026 18:53</t>
+          <t>12/08/2026 13:23</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>17/08/2026 18:53</t>
+          <t>12/08/2026 13:23</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>19/08/2026 03:12</t>
+          <t>18/08/2026 11:48</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1335,7 +1335,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0029761-52.2023.8.16.0001</t>
+          <t>0001849-73.2024.8.16.0089</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1345,27 +1345,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Dívida Ativa (Execução Fiscal)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>22/10/2025</t>
+          <t>24/04/2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>05/08/2026 15:53</t>
+          <t>14/08/2026 20:53</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>05/08/2026 15:53</t>
+          <t>14/08/2026 20:53</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>19/08/2026 02:22</t>
+          <t>18/08/2026 20:48</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1382,7 +1382,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0016302-44.2023.8.16.0013</t>
+          <t>0001893-39.2022.8.16.0097</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1397,22 +1397,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>17/08/2026 18:33</t>
+          <t>18/08/2026 16:13</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>17/08/2026 18:33</t>
+          <t>18/08/2026 16:13</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>19/08/2026 02:36</t>
+          <t>19/08/2026 03:41</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1429,7 +1429,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0014865-07.2023.8.16.0000</t>
+          <t>0001965-03.2025.8.16.0006</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1439,27 +1439,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Seguro | Práticas Abusivas | Indenização por Dano Moral | Repetição do Indébito</t>
+          <t>Homicídio Qualificado</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>29/05/2024</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>05/08/2026 17:13</t>
+          <t>14/08/2026 14:33</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>05/08/2026 17:13</t>
+          <t>14/08/2026 14:33</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>19/08/2026 02:36</t>
+          <t>18/08/2026 16:27</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1476,37 +1476,37 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0001125-91.2024.8.16.0114</t>
+          <t>0002360-70.2019.8.16.0146</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Receptação | Adulteração de Sinal Identificador de Veículo Automotor</t>
+          <t>Arrendamento Rural | Perdas e Danos</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>19/09/2025</t>
+          <t>22/05/2024</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>13/08/2026 20:43</t>
+          <t>14/08/2026 21:03</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>13/08/2026 20:43</t>
+          <t>14/08/2026 21:03</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>19/08/2026 02:36</t>
+          <t>18/08/2026 15:28</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1523,37 +1523,37 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0049454-20.2026.8.16.0000</t>
+          <t>0002525-63.2015.8.16.0080</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Prisão Preventiva | Tráfico de Drogas e Condutas Afins</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>13/08/2026 17:33</t>
+          <t>14/08/2026 18:33</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>13/08/2026 17:33</t>
+          <t>14/08/2026 18:33</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>19/08/2026 02:36</t>
+          <t>18/08/2026 17:14</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1570,7 +1570,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0008467-81.2013.8.16.0004</t>
+          <t>0002719-60.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1580,27 +1580,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Devolução de contribuições previdenciárias pagas além do teto</t>
+          <t>Acidente de Trânsito</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>18/02/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>07/08/2026 14:13</t>
+          <t>14/08/2026 19:53</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>07/08/2026 14:13</t>
+          <t>14/08/2026 19:53</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>19/08/2026 02:44</t>
+          <t>18/08/2026 16:14</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1617,37 +1617,37 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0011351-39.2006.8.16.0001</t>
+          <t>0002961-64.2022.8.16.0019</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Espécies de Títulos de Crédito</t>
+          <t>Crimes do Sistema Nacional de Armas</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>28/04/2021</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>05/08/2026 15:33</t>
+          <t>12/08/2026 13:43</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>05/08/2026 15:33</t>
+          <t>12/08/2026 13:43</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>19/08/2026 01:36</t>
+          <t>18/08/2026 11:32</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1664,37 +1664,37 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0032218-94.2023.8.16.0021</t>
+          <t>0002974-73.2012.8.16.0129</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Crimes do Sistema Nacional de Armas | Receptação</t>
+          <t>Indenização por Dano Material | Honorários Advocatícios | Pagamento do Débito | Cumprimento Provisório de Sentença</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>13/08/2026 16:33</t>
+          <t>14/08/2026 16:13</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>13/08/2026 16:33</t>
+          <t>14/08/2026 16:13</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>19/08/2026 02:14</t>
+          <t>18/08/2026 23:34</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>4002176-24.2025.8.16.4321</t>
+          <t>0002976-93.2025.8.16.0159</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1721,27 +1721,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Progressão de Regime</t>
+          <t>Dano Qualificado contra a Administração Pública</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>18/08/2026 16:03</t>
+          <t>13/08/2026 20:53</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>18/08/2026 16:03</t>
+          <t>13/08/2026 20:53</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>19/08/2026 02:18</t>
+          <t>19/08/2026 03:21</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1758,37 +1758,37 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0109747-58.2023.8.16.0000</t>
+          <t>0003154-89.2025.8.16.0014</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>14/08/2026 18:33</t>
+          <t>13/08/2026 21:53</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>14/08/2026 18:33</t>
+          <t>13/08/2026 21:53</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>19/08/2026 02:20</t>
+          <t>18/08/2026 21:05</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1805,37 +1805,37 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0010998-38.2022.8.16.0033</t>
+          <t>0003260-92.2022.8.16.0196</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tratamento médico-hospitalar</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>04/12/2025</t>
+          <t>27/11/2024</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>14/08/2026 20:03</t>
+          <t>17/08/2026 17:43</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>14/08/2026 20:03</t>
+          <t>17/08/2026 17:43</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>19/08/2026 02:20</t>
+          <t>18/08/2026 16:29</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1852,37 +1852,37 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0127459-90.2025.8.16.0000</t>
+          <t>0003825-94.2025.8.16.0117</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins | Prisão Preventiva</t>
+          <t>Corrupção passiva</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>13/08/2026 20:53</t>
+          <t>13/08/2026 20:33</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>13/08/2026 20:53</t>
+          <t>13/08/2026 20:33</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>19/08/2026 02:20</t>
+          <t>18/08/2026 14:32</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1899,7 +1899,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0015822-25.2021.8.16.0017</t>
+          <t>0004067-08.2022.8.16.0069</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1909,27 +1909,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Comissão</t>
+          <t>Defeito, nulidade ou anulação | Prescrição e Decadência</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>17/12/2025</t>
+          <t>30/01/2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>14/08/2026 14:43</t>
+          <t>14/08/2026 15:03</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>14/08/2026 14:43</t>
+          <t>14/08/2026 15:03</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>19/08/2026 02:20</t>
+          <t>18/08/2026 12:27</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1946,37 +1946,37 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0009011-73.2016.8.16.0001</t>
+          <t>0004410-05.2022.8.16.0004</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Previdência privada</t>
+          <t>Equilíbrio Financeiro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>19/03/2025</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>07/08/2026 14:33</t>
+          <t>17/08/2026 14:43</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>07/08/2026 14:33</t>
+          <t>17/08/2026 14:43</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>19/08/2026 00:06</t>
+          <t>18/08/2026 12:55</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1993,37 +1993,37 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0005392-93.2012.8.16.0028</t>
+          <t>0004744-04.2024.8.16.0090</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Indenização por Dano Ambiental</t>
+          <t>Tráfico de Drogas e Condutas Afins | Aplicação da Pena</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>05/08/2026 15:33</t>
+          <t>13/08/2026 15:43</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>05/08/2026 15:33</t>
+          <t>13/08/2026 15:43</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>19/08/2026 00:16</t>
+          <t>18/08/2026 11:44</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2040,7 +2040,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0028981-20.2017.8.16.0035</t>
+          <t>0004820-79.2022.8.16.0031</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2050,27 +2050,27 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Roubo Majorado</t>
+          <t>Posse</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>13/08/2026 21:53</t>
+          <t>17/08/2026 15:03</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>13/08/2026 21:53</t>
+          <t>17/08/2026 15:03</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>19/08/2026 00:16</t>
+          <t>18/08/2026 11:03</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2087,7 +2087,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0012287-20.2023.8.16.0017</t>
+          <t>0005192-20.2021.8.16.0045</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2097,27 +2097,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Nomeação</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>18/11/2025</t>
+          <t>06/08/2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>14/08/2026 20:53</t>
+          <t>14/08/2026 15:33</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>14/08/2026 20:53</t>
+          <t>14/08/2026 15:33</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>19/08/2026 00:25</t>
+          <t>18/08/2026 16:48</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2134,7 +2134,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0001227-62.2023.8.16.0110</t>
+          <t>0005407-05.2019.8.16.0194</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2144,27 +2144,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Competência Tributária</t>
+          <t>Locação de Imóvel</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>06/08/2026 14:13</t>
+          <t>14/08/2026 13:33</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>06/08/2026 14:13</t>
+          <t>14/08/2026 13:33</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>19/08/2026 00:25</t>
+          <t>18/08/2026 13:44</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2181,7 +2181,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0001593-15.2020.8.16.0108</t>
+          <t>0006707-23.2024.8.16.0098</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2191,27 +2191,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Erro Médico | Erro Médico</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>13/08/2026 16:43</t>
+          <t>13/08/2026 17:13</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>13/08/2026 16:43</t>
+          <t>13/08/2026 17:13</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>19/08/2026 00:37</t>
+          <t>18/08/2026 14:57</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2228,37 +2228,37 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0126623-54.2024.8.16.0000</t>
+          <t>0007668-63.2023.8.16.0044</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>17/08/2026 15:13</t>
+          <t>13/08/2026 17:13</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>17/08/2026 15:13</t>
+          <t>13/08/2026 17:13</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>19/08/2026 00:37</t>
+          <t>18/08/2026 17:06</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2275,37 +2275,37 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0001042-23.2024.8.16.0196</t>
+          <t>0007716-78.2022.8.16.0069</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Alienação Fiduciária</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>13/01/2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>14/08/2026 13:43</t>
+          <t>14/08/2026 20:03</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>14/08/2026 13:43</t>
+          <t>14/08/2026 20:03</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>19/08/2026 00:37</t>
+          <t>18/08/2026 13:42</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2322,37 +2322,37 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0060424-79.2026.8.16.0000</t>
+          <t>0007773-25.2020.8.16.0083</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Furto</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>12/08/2026 09:26</t>
+          <t>13/08/2026 19:13</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>12/08/2026 09:26</t>
+          <t>13/08/2026 19:13</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>19/08/2026 00:37</t>
+          <t>18/08/2026 14:32</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2369,37 +2369,37 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0000393-84.2024.8.16.0155</t>
+          <t>0008905-80.2017.8.16.0000</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Pagamento Atrasado / Correção Monetária</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>12/03/2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>07/08/2026 13:23</t>
+          <t>13/08/2026 15:43</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>07/08/2026 13:23</t>
+          <t>13/08/2026 15:43</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>19/08/2026 00:37</t>
+          <t>18/08/2026 13:38</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2416,7 +2416,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0000022-19.1988.8.16.0047</t>
+          <t>0009238-08.2024.8.16.0058</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2426,27 +2426,27 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bancários</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>19/08/2024</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>17/08/2026 13:03</t>
+          <t>13/08/2026 21:03</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>17/08/2026 13:03</t>
+          <t>13/08/2026 21:03</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>19/08/2026 00:42</t>
+          <t>18/08/2026 12:05</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2463,7 +2463,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0016802-20.2021.8.16.0001</t>
+          <t>0009710-10.2025.8.16.0014</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2473,27 +2473,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Duplicata</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>17/07/2024</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>05/08/2026 19:03</t>
+          <t>13/08/2026 18:33</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>05/08/2026 19:03</t>
+          <t>13/08/2026 18:33</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>19/08/2026 00:50</t>
+          <t>19/08/2026 02:48</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2510,7 +2510,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0000470-27.2018.8.16.0051</t>
+          <t>0010296-65.2020.8.16.0194</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2520,27 +2520,27 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Usucapião Extraordinária</t>
+          <t>Práticas Abusivas | Rescisão do contrato e devolução do dinheiro | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>14/08/2026 14:24</t>
+          <t>17/08/2026 14:23</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>14/08/2026 14:24</t>
+          <t>17/08/2026 14:23</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>18/08/2026 22:23</t>
+          <t>18/08/2026 16:41</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2557,37 +2557,37 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0093139-77.2026.8.16.0000</t>
+          <t>0010323-40.2023.8.16.0001</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Seqüestro e cárcere privado | Crimes de Tortura | Lesão Cometida em Razão da Condição de Mulher | Ameaça</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>17/08/2026 17:23</t>
+          <t>12/08/2026 14:53</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>17/08/2026 17:23</t>
+          <t>12/08/2026 14:53</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>18/08/2026 22:58</t>
+          <t>18/08/2026 14:24</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2604,7 +2604,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0000174-98.2020.8.16.0062</t>
+          <t>0010998-38.2022.8.16.0033</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2614,27 +2614,27 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Tratamento médico-hospitalar</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>04/12/2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>17/08/2026 18:03</t>
+          <t>14/08/2026 20:03</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>17/08/2026 18:03</t>
+          <t>14/08/2026 20:03</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>18/08/2026 23:33</t>
+          <t>19/08/2026 02:20</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2651,7 +2651,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0002974-73.2012.8.16.0129</t>
+          <t>0011077-65.2022.8.16.0017</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2661,27 +2661,27 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Honorários Advocatícios | Pagamento do Débito | Cumprimento Provisório de Sentença</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>15/01/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>14/08/2026 16:13</t>
+          <t>13/08/2026 14:33</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>14/08/2026 16:13</t>
+          <t>13/08/2026 14:33</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>18/08/2026 23:34</t>
+          <t>18/08/2026 14:43</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2698,7 +2698,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0025658-39.2023.8.16.0021</t>
+          <t>0011811-63.2021.8.16.0045</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2708,27 +2708,27 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Crimes do Sistema Nacional de Armas</t>
+          <t>Crimes Previstos no Estatuto do Idoso</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>14/08/2026 14:33</t>
+          <t>13/08/2026 17:13</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>14/08/2026 14:33</t>
+          <t>13/08/2026 17:13</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>18/08/2026 23:34</t>
+          <t>18/08/2026 21:37</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2745,7 +2745,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0122142-48.2024.8.16.0000</t>
+          <t>0012180-37.2017.8.16.0194</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2755,27 +2755,27 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Desapropriação | Imissão na Posse</t>
+          <t>Indenização por Dano Moral | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>24/09/2025</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>12/08/2026 13:13</t>
+          <t>17/08/2026 13:03</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>12/08/2026 13:13</t>
+          <t>17/08/2026 13:03</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>18/08/2026 23:47</t>
+          <t>18/08/2026 19:20</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2792,37 +2792,37 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0003154-89.2025.8.16.0014</t>
+          <t>0012196-10.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Abuso de Poder | Defeito, nulidade ou anulação | Tutela de Evidência | Violação dos Princípios Administrativos | Cumprimento Provisório de Sentença | Legitimidade Ativa e Passiva</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>13/08/2026 21:53</t>
+          <t>14/08/2026 16:33</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>13/08/2026 21:53</t>
+          <t>14/08/2026 16:33</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>18/08/2026 21:05</t>
+          <t>18/08/2026 21:37</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2839,7 +2839,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0035638-22.2019.8.16.0030</t>
+          <t>0012287-20.2023.8.16.0017</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2849,27 +2849,27 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Receptação Qualificada</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>13/11/2025</t>
+          <t>18/11/2025</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>13/08/2026 16:43</t>
+          <t>14/08/2026 20:53</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>13/08/2026 16:43</t>
+          <t>14/08/2026 20:53</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>18/08/2026 21:37</t>
+          <t>19/08/2026 00:25</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2886,7 +2886,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0011811-63.2021.8.16.0045</t>
+          <t>0012621-37.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2896,27 +2896,27 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Crimes Previstos no Estatuto do Idoso</t>
+          <t>Despesas Condominiais</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>13/08/2026 17:13</t>
+          <t>14/08/2026 14:33</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>13/08/2026 17:13</t>
+          <t>14/08/2026 14:33</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>18/08/2026 21:37</t>
+          <t>18/08/2026 14:27</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2933,7 +2933,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0012196-10.2025.8.16.0000</t>
+          <t>0015822-25.2021.8.16.0017</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2943,27 +2943,27 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Abuso de Poder | Defeito, nulidade ou anulação | Tutela de Evidência | Violação dos Princípios Administrativos | Cumprimento Provisório de Sentença | Legitimidade Ativa e Passiva</t>
+          <t>Comissão</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>17/12/2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>14/08/2026 16:33</t>
+          <t>14/08/2026 14:43</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>14/08/2026 16:33</t>
+          <t>14/08/2026 14:43</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>18/08/2026 21:37</t>
+          <t>19/08/2026 02:20</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2980,7 +2980,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0128332-27.2024.8.16.0000</t>
+          <t>0016302-44.2023.8.16.0013</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2990,27 +2990,27 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Pagamento com Sub-rogação</t>
+          <t>Crimes de Trânsito</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>27/01/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>05/08/2026 13:23</t>
+          <t>17/08/2026 18:33</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>05/08/2026 13:23</t>
+          <t>17/08/2026 18:33</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>18/08/2026 20:20</t>
+          <t>19/08/2026 02:36</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3027,7 +3027,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0001849-73.2024.8.16.0089</t>
+          <t>0016776-75.2024.8.16.0014</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3037,27 +3037,27 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>Plano de Saúde</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>24/04/2025</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>14/08/2026 20:53</t>
+          <t>12/08/2026 14:03</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>14/08/2026 20:53</t>
+          <t>12/08/2026 14:03</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>18/08/2026 20:48</t>
+          <t>19/08/2026 02:48</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3074,7 +3074,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0023966-78.2018.8.16.0021</t>
+          <t>0018604-92.2023.8.16.0030</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3084,27 +3084,27 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Inclusão Indevida em Cadastro de Inadimplentes</t>
+          <t>Dever de Informação</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>25/08/2025</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>14/08/2026 16:43</t>
+          <t>12/08/2026 13:13</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>14/08/2026 16:43</t>
+          <t>12/08/2026 13:13</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>18/08/2026 20:48</t>
+          <t>18/08/2026 13:44</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3121,37 +3121,37 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0001449-20.2024.8.16.0102</t>
+          <t>0019003-57.2023.8.16.0019</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tarifas</t>
+          <t>Tráfico de Drogas e Condutas Afins | Desclassificação</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>02/10/2025</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>07/08/2026 13:03</t>
+          <t>17/08/2026 18:53</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>07/08/2026 13:03</t>
+          <t>17/08/2026 18:53</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>18/08/2026 20:48</t>
+          <t>19/08/2026 03:12</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3168,7 +3168,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0124840-27.2024.8.16.0000</t>
+          <t>0021603-50.2020.8.16.0021</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3178,27 +3178,27 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação</t>
+          <t>Locação de Imóvel</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>02/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>14/08/2026 07:29</t>
+          <t>17/08/2026 14:53</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>14/08/2026 07:29</t>
+          <t>17/08/2026 14:53</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>18/08/2026 20:48</t>
+          <t>20/08/2026 22:45</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3215,7 +3215,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0030427-19.2020.8.16.0014</t>
+          <t>0023731-33.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3225,27 +3225,27 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Duplicata | Cédula de Produto Rural</t>
+          <t>Indenização por Dano Moral | Liminar | Adequação da Ação / Procedimento</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>11/08/2025</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>14/08/2026 19:43</t>
+          <t>17/08/2026 14:53</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>14/08/2026 19:43</t>
+          <t>17/08/2026 14:53</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>18/08/2026 18:18</t>
+          <t>18/08/2026 13:02</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3262,7 +3262,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0027023-26.2025.8.16.0000</t>
+          <t>0023966-78.2018.8.16.0021</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3272,27 +3272,27 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Homicídio Qualificado | Destruição / Subração / Ocultação de Cadáver</t>
+          <t>Inclusão Indevida em Cadastro de Inadimplentes</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>25/08/2025</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>06/08/2026 12:21</t>
+          <t>14/08/2026 16:43</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>06/08/2026 12:21</t>
+          <t>14/08/2026 16:43</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>18/08/2026 18:32</t>
+          <t>18/08/2026 20:48</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3309,7 +3309,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0029973-10.2022.8.16.0001</t>
+          <t>0024261-64.2025.8.16.0185</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3319,27 +3319,27 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Previdência privada</t>
+          <t>Dívida Ativa (Execução Fiscal)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>17/08/2026 15:13</t>
+          <t>14/08/2026 19:23</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>17/08/2026 15:13</t>
+          <t>14/08/2026 19:23</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>18/08/2026 19:09</t>
+          <t>18/08/2026 13:56</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3356,7 +3356,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0012180-37.2017.8.16.0194</t>
+          <t>0025658-39.2023.8.16.0021</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3366,27 +3366,27 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Indenização por Dano Material</t>
+          <t>Crimes do Sistema Nacional de Armas</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>24/09/2025</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>17/08/2026 13:03</t>
+          <t>14/08/2026 14:33</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>17/08/2026 13:03</t>
+          <t>14/08/2026 14:33</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>18/08/2026 19:20</t>
+          <t>18/08/2026 23:34</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3403,7 +3403,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0002525-63.2015.8.16.0080</t>
+          <t>0026752-14.2021.8.16.0014</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3413,27 +3413,27 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Pagamento</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>21/08/2024</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>14/08/2026 18:33</t>
+          <t>14/08/2026 15:43</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>14/08/2026 18:33</t>
+          <t>14/08/2026 15:43</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>18/08/2026 17:14</t>
+          <t>19/08/2026 02:48</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3450,37 +3450,37 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0009922-20.2018.8.16.0194</t>
+          <t>0028518-34.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Serviços Profissionais | Indenização por Dano Moral</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>02/10/2025</t>
+          <t>19/08/2025</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>05/08/2026 18:23</t>
+          <t>13/08/2026 16:43</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>05/08/2026 18:23</t>
+          <t>13/08/2026 16:43</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>18/08/2026 17:14</t>
+          <t>19/08/2026 03:21</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3497,7 +3497,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0027523-29.2024.8.16.0000</t>
+          <t>0028981-20.2017.8.16.0035</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3507,27 +3507,27 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Roubo Majorado</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>26/03/2025</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>05/08/2026 17:43</t>
+          <t>13/08/2026 21:53</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>05/08/2026 17:43</t>
+          <t>13/08/2026 21:53</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>18/08/2026 17:14</t>
+          <t>19/08/2026 00:16</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3544,37 +3544,37 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0002719-60.2025.8.16.0000</t>
+          <t>0030192-26.2018.8.16.0013</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Embargos de Divergência em Recurso Especial</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Acidente de Trânsito</t>
+          <t>Roubo Majorado</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>13/10/2022</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>14/08/2026 19:53</t>
+          <t>17/08/2026 13:23</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>14/08/2026 19:53</t>
+          <t>17/08/2026 13:23</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>18/08/2026 16:14</t>
+          <t>18/08/2026 03:55</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3591,7 +3591,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0042997-32.2023.8.16.0014</t>
+          <t>0032218-94.2023.8.16.0021</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3601,27 +3601,27 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Roubo Majorado</t>
+          <t>Crimes do Sistema Nacional de Armas | Receptação</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>13/08/2026 13:58</t>
+          <t>13/08/2026 16:33</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>13/08/2026 13:58</t>
+          <t>13/08/2026 16:33</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>18/08/2026 16:14</t>
+          <t>19/08/2026 02:14</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3638,37 +3638,37 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0000142-12.2019.8.16.0165</t>
+          <t>0032747-79.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Extorsão</t>
+          <t>Bens Públicos</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>21/06/2024</t>
+          <t>14/10/2025</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>06/08/2026 09:55</t>
+          <t>13/08/2026 18:03</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>06/08/2026 09:55</t>
+          <t>13/08/2026 18:03</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>18/08/2026 16:27</t>
+          <t>18/08/2026 11:43</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3685,7 +3685,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0041319-84.2024.8.16.0001</t>
+          <t>0035638-22.2019.8.16.0030</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3695,27 +3695,27 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ingresso e Exclusão dos Sócios na Sociedade</t>
+          <t>Receptação Qualificada</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>26/05/2025</t>
+          <t>13/11/2025</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>17/08/2026 13:13</t>
+          <t>13/08/2026 16:43</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>17/08/2026 13:13</t>
+          <t>13/08/2026 16:43</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>18/08/2026 16:27</t>
+          <t>18/08/2026 21:37</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3732,7 +3732,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0001965-03.2025.8.16.0006</t>
+          <t>0036039-38.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3742,27 +3742,27 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Homicídio Qualificado</t>
+          <t>Servidão Administrativa</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>14/08/2026 14:33</t>
+          <t>12/08/2026 14:23</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>14/08/2026 14:33</t>
+          <t>12/08/2026 14:23</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>18/08/2026 16:27</t>
+          <t>18/08/2026 11:03</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3779,7 +3779,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0088933-88.2024.8.16.0000</t>
+          <t>0037335-61.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3789,27 +3789,27 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Multas e demais Sanções</t>
+          <t>Limitação de Juros</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>14/08/2026 20:33</t>
+          <t>12/08/2026 15:03</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>14/08/2026 20:33</t>
+          <t>12/08/2026 15:03</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>18/08/2026 16:27</t>
+          <t>19/08/2026 03:21</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3826,7 +3826,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0003260-92.2022.8.16.0196</t>
+          <t>0038454-62.2022.8.16.0000</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3836,27 +3836,27 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Direitos / Deveres do Condômino</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>27/11/2024</t>
+          <t>03/10/2023</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>17/08/2026 17:43</t>
+          <t>14/08/2026 13:03</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>17/08/2026 17:43</t>
+          <t>14/08/2026 13:03</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>18/08/2026 16:29</t>
+          <t>19/08/2026 04:12</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3873,37 +3873,37 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0117282-67.2025.8.16.0000</t>
+          <t>0039374-82.2012.8.16.0001</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Crimes do Sistema Nacional de Armas | Associação para a Produção e Tráfico e Condutas Afins</t>
+          <t>Auxílio-Doença Acidentário</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>05/06/2025</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>05/08/2026 13:13</t>
+          <t>14/08/2026 15:03</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>05/08/2026 13:13</t>
+          <t>14/08/2026 15:03</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>18/08/2026 16:38</t>
+          <t>18/08/2026 12:55</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3920,7 +3920,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0022577-43.2022.8.16.0013</t>
+          <t>0041319-84.2024.8.16.0001</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3930,27 +3930,27 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Furto Qualificado</t>
+          <t>Ingresso e Exclusão dos Sócios na Sociedade</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>08/01/2026</t>
+          <t>26/05/2025</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>06/08/2026 12:20</t>
+          <t>17/08/2026 13:13</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>06/08/2026 12:21</t>
+          <t>17/08/2026 13:13</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>18/08/2026 16:41</t>
+          <t>18/08/2026 16:27</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3967,37 +3967,37 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0016694-74.2016.8.16.0030</t>
+          <t>0042997-32.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
+          <t>Roubo Majorado</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>07/08/2026 13:03</t>
+          <t>13/08/2026 13:58</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>07/08/2026 13:03</t>
+          <t>13/08/2026 13:58</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>18/08/2026 16:41</t>
+          <t>18/08/2026 16:14</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -4014,37 +4014,37 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0010296-65.2020.8.16.0194</t>
+          <t>0046238-58.2024.8.16.0182</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Pedido de Uniformização de Interpretação de Lei Criminal</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Práticas Abusivas | Rescisão do contrato e devolução do dinheiro | Indenização por Dano Moral</t>
+          <t>Residência Médica | Programas de Bolsas e Financiamento Estudantil com Recursos Públicos</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>03/04/2025</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>17/08/2026 14:23</t>
+          <t>18/08/2026 01:57</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>17/08/2026 14:23</t>
+          <t>18/08/2026 01:57</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>18/08/2026 16:41</t>
+          <t>18/08/2026 14:27</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4061,37 +4061,37 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0000033-52.2025.8.16.0079</t>
+          <t>0049454-20.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação</t>
+          <t>Prisão Preventiva | Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>10/12/2025</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>17/08/2026 13:13</t>
+          <t>13/08/2026 17:33</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>17/08/2026 13:13</t>
+          <t>13/08/2026 17:33</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>18/08/2026 16:46</t>
+          <t>19/08/2026 02:36</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -4108,37 +4108,37 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0005192-20.2021.8.16.0045</t>
+          <t>0050711-80.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Nomeação</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>06/08/2025</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>14/08/2026 15:33</t>
+          <t>13/08/2026 17:13</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>14/08/2026 15:33</t>
+          <t>13/08/2026 17:13</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>18/08/2026 16:48</t>
+          <t>19/08/2026 02:47</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4155,7 +4155,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0007668-63.2023.8.16.0044</t>
+          <t>0059258-46.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4165,27 +4165,27 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Descontos Indevidos</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>13/08/2026 17:13</t>
+          <t>13/08/2026 19:33</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>13/08/2026 17:13</t>
+          <t>13/08/2026 19:33</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>18/08/2026 17:06</t>
+          <t>18/08/2026 03:55</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4202,37 +4202,37 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0001537-89.2023.8.16.0006</t>
+          <t>0060424-79.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Homicídio Qualificado</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>07/08/2026 06:36</t>
+          <t>12/08/2026 09:26</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>07/08/2026 06:36</t>
+          <t>12/08/2026 09:26</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>18/08/2026 17:07</t>
+          <t>19/08/2026 00:37</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4249,37 +4249,37 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0013864-16.2025.8.16.0000</t>
+          <t>0064158-64.2024.8.16.0014</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Cédula de Produto Rural</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>05/08/2026 17:03</t>
+          <t>13/08/2026 14:33</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>05/08/2026 17:03</t>
+          <t>13/08/2026 14:33</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>18/08/2026 15:54</t>
+          <t>18/08/2026 11:03</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4296,7 +4296,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0002552-28.2015.8.16.0183</t>
+          <t>0064838-91.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4306,27 +4306,27 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Servidores Inativos | Requisição de Pequeno Valor - RPV</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>23/02/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>05/08/2026 17:23</t>
+          <t>17/08/2026 14:03</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>05/08/2026 17:23</t>
+          <t>17/08/2026 14:03</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>18/08/2026 15:54</t>
+          <t>18/08/2026 13:13</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4343,37 +4343,37 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0000518-84.2009.8.16.0185</t>
+          <t>0065092-93.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Prestação de Serviços | Concurso de Credores | Duplicata</t>
+          <t>Homicídio Qualificado | Crime Tentado</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>29/05/2024</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>05/08/2026 18:53</t>
+          <t>17/08/2026 18:43</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>05/08/2026 18:53</t>
+          <t>17/08/2026 18:43</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>18/08/2026 16:00</t>
+          <t>18/08/2026 10:25</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4390,7 +4390,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0010537-63.2021.8.16.0013</t>
+          <t>0065469-61.2022.8.16.0014</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4400,27 +4400,27 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Furto Qualificado</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>05/08/2026 18:13</t>
+          <t>12/08/2026 13:53</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>05/08/2026 18:13</t>
+          <t>12/08/2026 13:53</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>18/08/2026 15:15</t>
+          <t>18/08/2026 15:43</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4437,37 +4437,37 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0002360-70.2019.8.16.0146</t>
+          <t>0066120-96.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Arrendamento Rural | Perdas e Danos</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>22/05/2024</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>14/08/2026 21:03</t>
+          <t>17/08/2026 17:13</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>14/08/2026 21:03</t>
+          <t>17/08/2026 17:13</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>18/08/2026 15:28</t>
+          <t>18/08/2026 11:44</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4484,7 +4484,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0032040-60.2013.8.16.0001</t>
+          <t>0068649-22.2021.8.16.0014</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4494,27 +4494,27 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Práticas Abusivas | Indenização por Dano Moral | Indenização por Dano Material</t>
+          <t>Inventário e Partilha | Bem de Família Legal</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>01/04/2025</t>
+          <t>14/10/2025</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>05/08/2026 17:03</t>
+          <t>17/08/2026 13:33</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>05/08/2026 17:03</t>
+          <t>17/08/2026 13:33</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>18/08/2026 15:28</t>
+          <t>18/08/2026 13:38</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4531,7 +4531,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0065469-61.2022.8.16.0014</t>
+          <t>0070705-31.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4541,27 +4541,27 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação</t>
+          <t>Condomínio</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>12/08/2026 13:53</t>
+          <t>14/08/2026 18:03</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>12/08/2026 13:53</t>
+          <t>14/08/2026 18:03</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>18/08/2026 15:43</t>
+          <t>18/08/2026 10:26</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4578,7 +4578,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0011077-65.2022.8.16.0017</t>
+          <t>0088421-71.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4593,22 +4593,22 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>15/01/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>13/08/2026 14:33</t>
+          <t>13/08/2026 18:23</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>13/08/2026 14:33</t>
+          <t>13/08/2026 18:23</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>18/08/2026 14:43</t>
+          <t>20/08/2026 22:45</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4625,7 +4625,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0006707-23.2024.8.16.0098</t>
+          <t>0088933-88.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4635,27 +4635,27 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Multas e demais Sanções</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>13/08/2026 17:13</t>
+          <t>14/08/2026 20:33</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>13/08/2026 17:13</t>
+          <t>14/08/2026 20:33</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>18/08/2026 14:57</t>
+          <t>18/08/2026 16:27</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4672,37 +4672,37 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0094754-39.2025.8.16.0000</t>
+          <t>0093139-77.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Peculato</t>
+          <t>Seqüestro e cárcere privado | Crimes de Tortura | Lesão Cometida em Razão da Condição de Mulher | Ameaça</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>17/08/2026 15:53</t>
+          <t>17/08/2026 17:23</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>17/08/2026 15:53</t>
+          <t>17/08/2026 17:23</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>18/08/2026 15:11</t>
+          <t>18/08/2026 22:58</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4719,37 +4719,37 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0046238-58.2024.8.16.0182</t>
+          <t>0094754-39.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Pedido de Uniformização de Interpretação de Lei Criminal</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Residência Médica | Programas de Bolsas e Financiamento Estudantil com Recursos Públicos</t>
+          <t>Peculato</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>03/04/2025</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>18/08/2026 01:57</t>
+          <t>17/08/2026 15:53</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>18/08/2026 01:57</t>
+          <t>17/08/2026 15:53</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>18/08/2026 14:27</t>
+          <t>18/08/2026 15:11</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4766,7 +4766,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0003825-94.2025.8.16.0117</t>
+          <t>0109747-58.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4776,27 +4776,27 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Corrupção passiva</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>29/09/2025</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>13/08/2026 20:33</t>
+          <t>14/08/2026 18:33</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>13/08/2026 20:33</t>
+          <t>14/08/2026 18:33</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>18/08/2026 14:32</t>
+          <t>19/08/2026 02:20</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4813,7 +4813,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0000889-98.2013.8.16.0026</t>
+          <t>0122142-48.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4823,27 +4823,27 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Resgate de Contribuição | Provas | Indenização por Dano Moral</t>
+          <t>Desapropriação | Imissão na Posse</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>05/08/2026 18:33</t>
+          <t>12/08/2026 13:13</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>05/08/2026 18:33</t>
+          <t>12/08/2026 13:13</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>18/08/2026 08:14</t>
+          <t>18/08/2026 23:47</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4860,37 +4860,37 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0009080-35.2020.8.16.0173</t>
+          <t>0124840-27.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>15/10/2025</t>
+          <t>02/03/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>14/08/2026 18:23</t>
+          <t>14/08/2026 07:29</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>14/08/2026 18:23</t>
+          <t>14/08/2026 07:29</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>18/08/2026 08:14</t>
+          <t>18/08/2026 20:48</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4907,7 +4907,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0005818-14.2020.8.16.0194</t>
+          <t>0126623-54.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4917,27 +4917,27 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Abatimento proporcional do preço</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>14/08/2026 19:33</t>
+          <t>17/08/2026 15:13</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>14/08/2026 19:33</t>
+          <t>17/08/2026 15:13</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>18/08/2026 08:14</t>
+          <t>19/08/2026 00:37</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4954,37 +4954,37 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0026663-11.2023.8.16.0017</t>
+          <t>0127459-90.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins</t>
+          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins | Prisão Preventiva</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>18/09/2025</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>05/08/2026 14:11</t>
+          <t>13/08/2026 20:53</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>05/08/2026 18:00</t>
+          <t>13/08/2026 20:53</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>18/08/2026 08:45</t>
+          <t>19/08/2026 02:20</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -5001,37 +5001,37 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0013715-90.2017.8.16.0035</t>
+          <t>0131195-19.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Usucapião Extraordinária</t>
+          <t>Associação para a Produção e Tráfico e Condutas Afins | Prisão Preventiva</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>07/08/2026 14:13</t>
+          <t>13/08/2026 21:53</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>07/08/2026 14:13</t>
+          <t>13/08/2026 21:53</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>18/08/2026 08:47</t>
+          <t>18/08/2026 12:05</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -5048,7 +5048,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0025178-22.2026.8.16.0000</t>
+          <t>0152011-22.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -5058,27 +5058,27 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Promoção, constituição, financiamento ou integração de Organização Criminosa</t>
+          <t>Decorrente de Violência Doméstica | Injúria | Dano | Ameaça</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>05/08/2026 13:03</t>
+          <t>13/08/2026 21:03</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>05/08/2026 13:03</t>
+          <t>13/08/2026 21:03</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>18/08/2026 08:47</t>
+          <t>18/08/2026 11:17</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -5095,37 +5095,37 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0109806-12.2024.8.16.0000</t>
+          <t>4002176-24.2025.8.16.4321</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Invalidez Permanente</t>
+          <t>Progressão de Regime</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>13/08/2026 21:53</t>
+          <t>18/08/2026 16:03</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>13/08/2026 21:53</t>
+          <t>18/08/2026 16:03</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>18/08/2026 09:05</t>
+          <t>19/08/2026 02:18</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -5134,53 +5134,6 @@
         </is>
       </c>
       <c r="I100" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>0068216-55.2024.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Cobrança | Obrigação de Fazer / Não Fazer</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>02/02/2026</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>14/08/2026 20:33</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>14/08/2026 20:33</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>18/08/2026 09:16</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>

--- a/docs/resultados.xlsx
+++ b/docs/resultados.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I100"/>
+  <dimension ref="A1:I96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
@@ -536,7 +536,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0000033-52.2025.8.16.0079</t>
+          <t>0000174-98.2020.8.16.0062</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -546,27 +546,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>10/12/2025</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>17/08/2026 13:13</t>
+          <t>17/08/2026 18:03</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17/08/2026 13:13</t>
+          <t>17/08/2026 18:03</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>18/08/2026 16:46</t>
+          <t>18/08/2026 23:33</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -583,37 +583,37 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0000163-85.2024.8.16.0173</t>
+          <t>0000272-47.2009.8.16.0037</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Crimes de Trânsito</t>
+          <t>Homicídio Qualificado</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>14/08/2026 17:13</t>
+          <t>13/08/2026 20:43</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>14/08/2026 17:13</t>
+          <t>13/08/2026 20:43</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>18/08/2026 13:38</t>
+          <t>18/08/2026 11:31</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,7 +630,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0000174-98.2020.8.16.0062</t>
+          <t>0000470-27.2018.8.16.0051</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -640,27 +640,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Usucapião Extraordinária</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17/08/2026 18:03</t>
+          <t>14/08/2026 14:24</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>17/08/2026 18:03</t>
+          <t>14/08/2026 14:24</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>18/08/2026 23:33</t>
+          <t>18/08/2026 22:23</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -677,37 +677,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0000272-47.2009.8.16.0037</t>
+          <t>0000579-95.2025.8.16.0083</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Homicídio Qualificado</t>
+          <t>Furto Qualificado</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>13/08/2026 20:43</t>
+          <t>14/08/2026 15:13</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>13/08/2026 20:43</t>
+          <t>14/08/2026 15:13</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>18/08/2026 11:31</t>
+          <t>18/08/2026 10:42</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -724,7 +724,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0000470-27.2018.8.16.0051</t>
+          <t>0000625-04.2023.8.16.0100</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -734,27 +734,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Usucapião Extraordinária</t>
+          <t>Usucapião Ordinária</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>14/08/2026 14:24</t>
+          <t>14/08/2026 20:33</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>14/08/2026 14:24</t>
+          <t>14/08/2026 20:33</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>18/08/2026 22:23</t>
+          <t>18/08/2026 10:44</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -771,37 +771,37 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0000521-43.2023.8.16.0122</t>
+          <t>0000627-67.2022.8.16.0048</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>02/09/2024</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>14/08/2026 21:43</t>
+          <t>17/08/2026 13:53</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>14/08/2026 21:43</t>
+          <t>17/08/2026 13:53</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>18/08/2026 13:13</t>
+          <t>18/08/2026 05:35</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -818,37 +818,37 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0000579-95.2025.8.16.0083</t>
+          <t>0000855-53.2024.8.16.0151</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Furto Qualificado</t>
+          <t>Roubo Majorado</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>14/08/2026 15:13</t>
+          <t>17/08/2026 15:53</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>14/08/2026 15:13</t>
+          <t>17/08/2026 15:53</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>18/08/2026 10:42</t>
+          <t>18/08/2026 07:13</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -865,37 +865,37 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0000625-04.2023.8.16.0100</t>
+          <t>0001042-23.2024.8.16.0196</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Usucapião Ordinária</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>14/08/2026 20:33</t>
+          <t>14/08/2026 13:43</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>14/08/2026 20:33</t>
+          <t>14/08/2026 13:43</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>18/08/2026 10:44</t>
+          <t>19/08/2026 00:37</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -912,7 +912,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0000706-08.2025.8.16.0156</t>
+          <t>0001125-91.2024.8.16.0114</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -922,27 +922,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Tráfico de Drogas e Condutas Afins | Receptação | Adulteração de Sinal Identificador de Veículo Automotor</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>19/09/2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>13/08/2026 14:03</t>
+          <t>13/08/2026 20:43</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>13/08/2026 14:03</t>
+          <t>13/08/2026 20:43</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>18/08/2026 13:26</t>
+          <t>19/08/2026 02:36</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -959,12 +959,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0001042-23.2024.8.16.0196</t>
+          <t>0001236-59.2021.8.16.0024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -974,22 +974,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>14/08/2026 13:43</t>
+          <t>18/08/2026 10:52</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>14/08/2026 13:43</t>
+          <t>18/08/2026 10:52</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>19/08/2026 00:37</t>
+          <t>19/08/2026 02:47</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1006,37 +1006,37 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0001125-91.2024.8.16.0114</t>
+          <t>0001373-33.2019.8.16.0017</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Receptação | Adulteração de Sinal Identificador de Veículo Automotor</t>
+          <t>Crimes de Trânsito</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>19/09/2025</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>13/08/2026 20:43</t>
+          <t>13/08/2026 20:53</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>13/08/2026 20:43</t>
+          <t>13/08/2026 20:53</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>19/08/2026 02:36</t>
+          <t>19/08/2026 02:47</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1053,7 +1053,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0001165-69.2023.8.16.0159</t>
+          <t>0001556-88.2013.8.16.0154</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1063,27 +1063,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Fornecimento</t>
+          <t>Anulação de Débito Fiscal | Prescrição</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>14/08/2026 19:43</t>
+          <t>14/08/2026 17:43</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>14/08/2026 19:43</t>
+          <t>14/08/2026 17:43</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>18/08/2026 13:44</t>
+          <t>18/08/2026 12:52</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0001236-59.2021.8.16.0024</t>
+          <t>0001593-15.2020.8.16.0108</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1110,27 +1110,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Erro Médico | Erro Médico</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>18/08/2026 10:52</t>
+          <t>13/08/2026 16:43</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>18/08/2026 10:52</t>
+          <t>13/08/2026 16:43</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>19/08/2026 02:47</t>
+          <t>19/08/2026 00:37</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1147,7 +1147,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0001373-33.2019.8.16.0017</t>
+          <t>0001652-58.2024.8.16.0109</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1157,27 +1157,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Crimes de Trânsito</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>13/08/2026 20:53</t>
+          <t>12/08/2026 13:23</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>13/08/2026 20:53</t>
+          <t>12/08/2026 13:23</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>19/08/2026 02:47</t>
+          <t>18/08/2026 11:48</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1194,7 +1194,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0001556-88.2013.8.16.0154</t>
+          <t>0001713-48.2023.8.16.0045</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1204,27 +1204,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Anulação de Débito Fiscal | Prescrição</t>
+          <t>Crimes Previstos no Estatuto da criança e do adolescente</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>14/08/2026 17:43</t>
+          <t>13/08/2026 21:13</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>14/08/2026 17:43</t>
+          <t>13/08/2026 21:13</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>18/08/2026 12:52</t>
+          <t>18/08/2026 07:46</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1241,7 +1241,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0001593-15.2020.8.16.0108</t>
+          <t>0001849-73.2024.8.16.0089</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1251,27 +1251,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Erro Médico | Erro Médico</t>
+          <t>Dívida Ativa (Execução Fiscal)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>24/04/2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>13/08/2026 16:43</t>
+          <t>14/08/2026 20:53</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>13/08/2026 16:43</t>
+          <t>14/08/2026 20:53</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>19/08/2026 00:37</t>
+          <t>18/08/2026 20:48</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1288,7 +1288,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0001652-58.2024.8.16.0109</t>
+          <t>0001893-39.2022.8.16.0097</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1298,27 +1298,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Crimes de Trânsito</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>12/08/2026 13:23</t>
+          <t>18/08/2026 16:13</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>12/08/2026 13:23</t>
+          <t>18/08/2026 16:13</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>18/08/2026 11:48</t>
+          <t>19/08/2026 03:41</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1335,7 +1335,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0001849-73.2024.8.16.0089</t>
+          <t>0002768-46.2025.8.16.0083</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1345,27 +1345,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>24/04/2025</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>14/08/2026 20:53</t>
+          <t>12/08/2026 14:43</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>14/08/2026 20:53</t>
+          <t>12/08/2026 14:43</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>18/08/2026 20:48</t>
+          <t>18/08/2026 04:24</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1382,7 +1382,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0001893-39.2022.8.16.0097</t>
+          <t>0002961-64.2022.8.16.0019</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1392,27 +1392,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Crimes de Trânsito</t>
+          <t>Crimes do Sistema Nacional de Armas</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>18/08/2026 16:13</t>
+          <t>12/08/2026 13:43</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>18/08/2026 16:13</t>
+          <t>12/08/2026 13:43</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>19/08/2026 03:41</t>
+          <t>18/08/2026 11:32</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1429,7 +1429,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0001965-03.2025.8.16.0006</t>
+          <t>0002974-73.2012.8.16.0129</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1439,27 +1439,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Homicídio Qualificado</t>
+          <t>Indenização por Dano Material | Honorários Advocatícios | Pagamento do Débito | Cumprimento Provisório de Sentença</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>14/08/2026 14:33</t>
+          <t>14/08/2026 16:13</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>14/08/2026 14:33</t>
+          <t>14/08/2026 16:13</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>18/08/2026 16:27</t>
+          <t>18/08/2026 23:34</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1476,7 +1476,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0002360-70.2019.8.16.0146</t>
+          <t>0002976-93.2025.8.16.0159</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1486,27 +1486,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Arrendamento Rural | Perdas e Danos</t>
+          <t>Dano Qualificado contra a Administração Pública</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>22/05/2024</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>14/08/2026 21:03</t>
+          <t>13/08/2026 20:53</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>14/08/2026 21:03</t>
+          <t>13/08/2026 20:53</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>18/08/2026 15:28</t>
+          <t>19/08/2026 03:21</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1523,37 +1523,37 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0002525-63.2015.8.16.0080</t>
+          <t>0003154-89.2025.8.16.0014</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>14/08/2026 18:33</t>
+          <t>13/08/2026 21:53</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>14/08/2026 18:33</t>
+          <t>13/08/2026 21:53</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>18/08/2026 17:14</t>
+          <t>18/08/2026 21:05</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1570,37 +1570,37 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0002719-60.2025.8.16.0000</t>
+          <t>0003523-75.2025.8.16.0146</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Acidente de Trânsito</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>14/08/2026 19:53</t>
+          <t>17/08/2026 20:03</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>14/08/2026 19:53</t>
+          <t>17/08/2026 20:03</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>18/08/2026 16:14</t>
+          <t>18/08/2026 04:49</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1617,7 +1617,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0002961-64.2022.8.16.0019</t>
+          <t>0004067-08.2022.8.16.0069</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1627,27 +1627,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Crimes do Sistema Nacional de Armas</t>
+          <t>Defeito, nulidade ou anulação | Prescrição e Decadência</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>30/01/2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>12/08/2026 13:43</t>
+          <t>14/08/2026 15:03</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>12/08/2026 13:43</t>
+          <t>14/08/2026 15:03</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>18/08/2026 11:32</t>
+          <t>18/08/2026 12:27</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1664,7 +1664,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0002974-73.2012.8.16.0129</t>
+          <t>0004410-05.2022.8.16.0004</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1674,27 +1674,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Honorários Advocatícios | Pagamento do Débito | Cumprimento Provisório de Sentença</t>
+          <t>Equilíbrio Financeiro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>14/08/2026 16:13</t>
+          <t>17/08/2026 14:43</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>14/08/2026 16:13</t>
+          <t>17/08/2026 14:43</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>18/08/2026 23:34</t>
+          <t>18/08/2026 12:55</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1711,37 +1711,37 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0002976-93.2025.8.16.0159</t>
+          <t>0004744-04.2024.8.16.0090</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dano Qualificado contra a Administração Pública</t>
+          <t>Tráfico de Drogas e Condutas Afins | Aplicação da Pena</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>13/08/2026 20:53</t>
+          <t>13/08/2026 15:43</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>13/08/2026 20:53</t>
+          <t>13/08/2026 15:43</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>19/08/2026 03:21</t>
+          <t>18/08/2026 11:44</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1758,37 +1758,37 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0003154-89.2025.8.16.0014</t>
+          <t>0004820-79.2022.8.16.0031</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Posse</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>13/08/2026 21:53</t>
+          <t>17/08/2026 15:03</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>13/08/2026 21:53</t>
+          <t>17/08/2026 15:03</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>18/08/2026 21:05</t>
+          <t>18/08/2026 11:03</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1805,37 +1805,37 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0003260-92.2022.8.16.0196</t>
+          <t>0004855-37.2019.8.16.0001</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>27/11/2024</t>
+          <t>30/01/2024</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>17/08/2026 17:43</t>
+          <t>14/08/2026 14:33</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>17/08/2026 17:43</t>
+          <t>14/08/2026 14:33</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>18/08/2026 16:29</t>
+          <t>18/08/2026 07:28</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1852,7 +1852,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0003825-94.2025.8.16.0117</t>
+          <t>0004943-61.2022.8.16.0004</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1862,27 +1862,27 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Corrupção passiva</t>
+          <t>ISS/ Imposto sobre Serviços</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>13/08/2026 20:33</t>
+          <t>17/08/2026 15:25</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>13/08/2026 20:33</t>
+          <t>17/08/2026 15:25</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>18/08/2026 14:32</t>
+          <t>18/08/2026 05:23</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1899,7 +1899,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0004067-08.2022.8.16.0069</t>
+          <t>0005206-31.2024.8.16.0196</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1909,27 +1909,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação | Prescrição e Decadência</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>30/01/2025</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>14/08/2026 15:03</t>
+          <t>13/08/2026 13:23</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>14/08/2026 15:03</t>
+          <t>13/08/2026 13:23</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>18/08/2026 12:27</t>
+          <t>18/08/2026 04:01</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1946,7 +1946,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0004410-05.2022.8.16.0004</t>
+          <t>0005407-05.2019.8.16.0194</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1956,27 +1956,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Equilíbrio Financeiro</t>
+          <t>Locação de Imóvel</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>17/08/2026 14:43</t>
+          <t>14/08/2026 13:33</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>17/08/2026 14:43</t>
+          <t>14/08/2026 13:33</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>18/08/2026 12:55</t>
+          <t>18/08/2026 13:44</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1993,37 +1993,37 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0004744-04.2024.8.16.0090</t>
+          <t>0005523-98.2017.8.16.0026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Aplicação da Pena</t>
+          <t>Multas e demais Sanções | Violação dos Princípios Administrativos | Termo de Ajustamento de Conduta - TAC | Ônus da Prova | Obrigação de Fazer / Não Fazer | Desvio de Função</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>17/10/2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>13/08/2026 15:43</t>
+          <t>14/08/2026 13:23</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>13/08/2026 15:43</t>
+          <t>14/08/2026 13:23</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>18/08/2026 11:44</t>
+          <t>18/08/2026 04:35</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2040,7 +2040,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0004820-79.2022.8.16.0031</t>
+          <t>0005818-14.2020.8.16.0194</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2050,27 +2050,27 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Posse</t>
+          <t>Abatimento proporcional do preço</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>17/08/2026 15:03</t>
+          <t>14/08/2026 19:33</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>17/08/2026 15:03</t>
+          <t>14/08/2026 19:33</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>18/08/2026 11:03</t>
+          <t>18/08/2026 08:14</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2087,7 +2087,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0005192-20.2021.8.16.0045</t>
+          <t>0005981-44.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2097,27 +2097,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Nomeação</t>
+          <t>Compra e Venda</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>06/08/2025</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>14/08/2026 15:33</t>
+          <t>17/08/2026 14:43</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>14/08/2026 15:33</t>
+          <t>17/08/2026 14:43</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>18/08/2026 16:48</t>
+          <t>18/08/2026 04:01</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2134,7 +2134,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0005407-05.2019.8.16.0194</t>
+          <t>0007189-69.2024.8.16.0130</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2144,27 +2144,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Locação de Imóvel</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>14/08/2026 13:33</t>
+          <t>14/08/2026 16:23</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>14/08/2026 13:33</t>
+          <t>14/08/2026 16:23</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>18/08/2026 13:44</t>
+          <t>18/08/2026 04:01</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2181,7 +2181,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0006707-23.2024.8.16.0098</t>
+          <t>0007559-88.2023.8.16.0031</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2191,27 +2191,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Práticas Abusivas</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>13/08/2026 17:13</t>
+          <t>14/08/2026 19:43</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>13/08/2026 17:13</t>
+          <t>14/08/2026 19:43</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>18/08/2026 14:57</t>
+          <t>18/08/2026 08:00</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2228,12 +2228,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0007668-63.2023.8.16.0044</t>
+          <t>0008081-09.2023.8.16.0034</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2243,22 +2243,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>13/08/2026 17:13</t>
+          <t>14/08/2026 16:53</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>13/08/2026 17:13</t>
+          <t>14/08/2026 16:53</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>18/08/2026 17:06</t>
+          <t>18/08/2026 05:36</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2275,37 +2275,37 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0007716-78.2022.8.16.0069</t>
+          <t>0009080-35.2020.8.16.0173</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Alienação Fiduciária</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>13/01/2025</t>
+          <t>15/10/2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>14/08/2026 20:03</t>
+          <t>14/08/2026 18:23</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>14/08/2026 20:03</t>
+          <t>14/08/2026 18:23</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>18/08/2026 13:42</t>
+          <t>18/08/2026 08:14</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2322,7 +2322,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0007773-25.2020.8.16.0083</t>
+          <t>0009238-08.2024.8.16.0058</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2332,27 +2332,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Furto</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>13/08/2026 19:13</t>
+          <t>13/08/2026 21:03</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>13/08/2026 19:13</t>
+          <t>13/08/2026 21:03</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>18/08/2026 14:32</t>
+          <t>18/08/2026 12:05</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2369,37 +2369,37 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0008905-80.2017.8.16.0000</t>
+          <t>0009710-10.2025.8.16.0014</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Pagamento Atrasado / Correção Monetária</t>
+          <t>Duplicata</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>12/03/2025</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>13/08/2026 15:43</t>
+          <t>13/08/2026 18:33</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>13/08/2026 15:43</t>
+          <t>13/08/2026 18:33</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>18/08/2026 13:38</t>
+          <t>19/08/2026 02:48</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2416,7 +2416,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0009238-08.2024.8.16.0058</t>
+          <t>0010998-38.2022.8.16.0033</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2426,27 +2426,27 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Tratamento médico-hospitalar</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>04/12/2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>13/08/2026 21:03</t>
+          <t>14/08/2026 20:03</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>13/08/2026 21:03</t>
+          <t>14/08/2026 20:03</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>18/08/2026 12:05</t>
+          <t>19/08/2026 02:20</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2463,7 +2463,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0009710-10.2025.8.16.0014</t>
+          <t>0011811-63.2021.8.16.0045</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2473,27 +2473,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Duplicata</t>
+          <t>Crimes Previstos no Estatuto do Idoso</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>13/08/2026 18:33</t>
+          <t>13/08/2026 17:13</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>13/08/2026 18:33</t>
+          <t>13/08/2026 17:13</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>19/08/2026 02:48</t>
+          <t>18/08/2026 21:37</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2510,7 +2510,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0010296-65.2020.8.16.0194</t>
+          <t>0012196-10.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2520,27 +2520,27 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Práticas Abusivas | Rescisão do contrato e devolução do dinheiro | Indenização por Dano Moral</t>
+          <t>Abuso de Poder | Defeito, nulidade ou anulação | Tutela de Evidência | Violação dos Princípios Administrativos | Cumprimento Provisório de Sentença | Legitimidade Ativa e Passiva</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>17/08/2026 14:23</t>
+          <t>14/08/2026 16:33</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>17/08/2026 14:23</t>
+          <t>14/08/2026 16:33</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>18/08/2026 16:41</t>
+          <t>18/08/2026 21:37</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2557,7 +2557,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0010323-40.2023.8.16.0001</t>
+          <t>0012287-20.2023.8.16.0017</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2567,27 +2567,27 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>18/11/2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>12/08/2026 14:53</t>
+          <t>14/08/2026 20:53</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>12/08/2026 14:53</t>
+          <t>14/08/2026 20:53</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>18/08/2026 14:24</t>
+          <t>19/08/2026 00:25</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2604,37 +2604,37 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0010998-38.2022.8.16.0033</t>
+          <t>0015241-62.2025.8.16.0019</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tratamento médico-hospitalar</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>04/12/2025</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>14/08/2026 20:03</t>
+          <t>13/08/2026 18:33</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>14/08/2026 20:03</t>
+          <t>13/08/2026 18:33</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>19/08/2026 02:20</t>
+          <t>18/08/2026 06:25</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2651,7 +2651,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0011077-65.2022.8.16.0017</t>
+          <t>0015297-55.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2661,27 +2661,27 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Prestação de Serviços | Honorários Advocatícios</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>15/01/2026</t>
+          <t>08/07/2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>13/08/2026 14:33</t>
+          <t>14/08/2026 18:33</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>13/08/2026 14:33</t>
+          <t>14/08/2026 18:33</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>18/08/2026 14:43</t>
+          <t>18/08/2026 07:57</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2698,7 +2698,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0011811-63.2021.8.16.0045</t>
+          <t>0015822-25.2021.8.16.0017</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2708,27 +2708,27 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Crimes Previstos no Estatuto do Idoso</t>
+          <t>Comissão</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>17/12/2025</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>13/08/2026 17:13</t>
+          <t>14/08/2026 14:43</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>13/08/2026 17:13</t>
+          <t>14/08/2026 14:43</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>18/08/2026 21:37</t>
+          <t>19/08/2026 02:20</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2745,7 +2745,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0012180-37.2017.8.16.0194</t>
+          <t>0016302-44.2023.8.16.0013</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2755,27 +2755,27 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Indenização por Dano Material</t>
+          <t>Crimes de Trânsito</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>24/09/2025</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>17/08/2026 13:03</t>
+          <t>17/08/2026 18:33</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>17/08/2026 13:03</t>
+          <t>17/08/2026 18:33</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>18/08/2026 19:20</t>
+          <t>19/08/2026 02:36</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2792,7 +2792,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0012196-10.2025.8.16.0000</t>
+          <t>0016776-75.2024.8.16.0014</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2802,27 +2802,27 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Abuso de Poder | Defeito, nulidade ou anulação | Tutela de Evidência | Violação dos Princípios Administrativos | Cumprimento Provisório de Sentença | Legitimidade Ativa e Passiva</t>
+          <t>Plano de Saúde</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>14/08/2026 16:33</t>
+          <t>12/08/2026 14:03</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>14/08/2026 16:33</t>
+          <t>12/08/2026 14:03</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>18/08/2026 21:37</t>
+          <t>19/08/2026 02:48</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2839,37 +2839,37 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0012287-20.2023.8.16.0017</t>
+          <t>0018929-14.2006.8.16.0014</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>18/11/2025</t>
+          <t>23/05/2025</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>14/08/2026 20:53</t>
+          <t>17/08/2026 13:53</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>14/08/2026 20:53</t>
+          <t>17/08/2026 13:53</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>19/08/2026 00:25</t>
+          <t>18/08/2026 07:57</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2886,37 +2886,37 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0012621-37.2025.8.16.0000</t>
+          <t>0019003-57.2023.8.16.0019</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Despesas Condominiais</t>
+          <t>Tráfico de Drogas e Condutas Afins | Desclassificação</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/10/2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>14/08/2026 14:33</t>
+          <t>17/08/2026 18:53</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>14/08/2026 14:33</t>
+          <t>17/08/2026 18:53</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>18/08/2026 14:27</t>
+          <t>19/08/2026 03:12</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2933,7 +2933,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0015822-25.2021.8.16.0017</t>
+          <t>0021603-50.2020.8.16.0021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2943,27 +2943,27 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Comissão</t>
+          <t>Locação de Imóvel</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>17/12/2025</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>14/08/2026 14:43</t>
+          <t>17/08/2026 14:53</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>14/08/2026 14:43</t>
+          <t>17/08/2026 14:53</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>19/08/2026 02:20</t>
+          <t>20/08/2026 22:45</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2980,7 +2980,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0016302-44.2023.8.16.0013</t>
+          <t>0023731-33.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2990,27 +2990,27 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Crimes de Trânsito</t>
+          <t>Indenização por Dano Moral | Liminar | Adequação da Ação / Procedimento</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>17/08/2026 18:33</t>
+          <t>17/08/2026 14:53</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>17/08/2026 18:33</t>
+          <t>17/08/2026 14:53</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>19/08/2026 02:36</t>
+          <t>18/08/2026 13:02</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3027,7 +3027,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0016776-75.2024.8.16.0014</t>
+          <t>0023966-78.2018.8.16.0021</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3037,27 +3037,27 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Plano de Saúde</t>
+          <t>Inclusão Indevida em Cadastro de Inadimplentes</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>25/08/2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>12/08/2026 14:03</t>
+          <t>14/08/2026 16:43</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>12/08/2026 14:03</t>
+          <t>14/08/2026 16:43</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>19/08/2026 02:48</t>
+          <t>18/08/2026 20:48</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3074,7 +3074,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0018604-92.2023.8.16.0030</t>
+          <t>0025658-39.2023.8.16.0021</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3084,27 +3084,27 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Dever de Informação</t>
+          <t>Crimes do Sistema Nacional de Armas</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>12/08/2026 13:13</t>
+          <t>14/08/2026 14:33</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>12/08/2026 13:13</t>
+          <t>14/08/2026 14:33</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>18/08/2026 13:44</t>
+          <t>18/08/2026 23:34</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3121,37 +3121,37 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0019003-57.2023.8.16.0019</t>
+          <t>0026752-14.2021.8.16.0014</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Desclassificação</t>
+          <t>Pagamento</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>02/10/2025</t>
+          <t>21/08/2024</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>17/08/2026 18:53</t>
+          <t>14/08/2026 15:43</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>17/08/2026 18:53</t>
+          <t>14/08/2026 15:43</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>19/08/2026 03:12</t>
+          <t>19/08/2026 02:48</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3168,37 +3168,37 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0021603-50.2020.8.16.0021</t>
+          <t>0027175-86.2016.8.16.0001</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Locação de Imóvel</t>
+          <t>Previdência privada</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>23/02/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>17/08/2026 14:53</t>
+          <t>12/08/2026 11:39</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>17/08/2026 14:53</t>
+          <t>12/08/2026 11:39</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20/08/2026 22:45</t>
+          <t>18/08/2026 06:23</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3215,37 +3215,37 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0023731-33.2025.8.16.0000</t>
+          <t>0028518-34.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Liminar | Adequação da Ação / Procedimento</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>19/08/2025</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>17/08/2026 14:53</t>
+          <t>13/08/2026 16:43</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>17/08/2026 14:53</t>
+          <t>13/08/2026 16:43</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>18/08/2026 13:02</t>
+          <t>19/08/2026 03:21</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3262,7 +3262,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0023966-78.2018.8.16.0021</t>
+          <t>0028981-20.2017.8.16.0035</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3272,27 +3272,27 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Inclusão Indevida em Cadastro de Inadimplentes</t>
+          <t>Roubo Majorado</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>25/08/2025</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>14/08/2026 16:43</t>
+          <t>13/08/2026 21:53</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>14/08/2026 16:43</t>
+          <t>13/08/2026 21:53</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>18/08/2026 20:48</t>
+          <t>19/08/2026 00:16</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3309,7 +3309,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0024261-64.2025.8.16.0185</t>
+          <t>0029973-10.2022.8.16.0001</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3319,27 +3319,27 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>Previdência privada</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>14/08/2026 19:23</t>
+          <t>17/08/2026 15:13</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>14/08/2026 19:23</t>
+          <t>17/08/2026 15:13</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>18/08/2026 13:56</t>
+          <t>18/08/2026 19:09</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3356,7 +3356,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0025658-39.2023.8.16.0021</t>
+          <t>0030427-19.2020.8.16.0014</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3366,27 +3366,27 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Crimes do Sistema Nacional de Armas</t>
+          <t>Duplicata | Cédula de Produto Rural</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>11/08/2025</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>14/08/2026 14:33</t>
+          <t>14/08/2026 19:43</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>14/08/2026 14:33</t>
+          <t>14/08/2026 19:43</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>18/08/2026 23:34</t>
+          <t>18/08/2026 18:18</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3403,37 +3403,37 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0026752-14.2021.8.16.0014</t>
+          <t>0032218-94.2023.8.16.0021</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Pagamento</t>
+          <t>Crimes do Sistema Nacional de Armas | Receptação</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>21/08/2024</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>14/08/2026 15:43</t>
+          <t>13/08/2026 16:33</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>14/08/2026 15:43</t>
+          <t>13/08/2026 16:33</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>19/08/2026 02:48</t>
+          <t>19/08/2026 02:14</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3450,37 +3450,37 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0028518-34.2023.8.16.0014</t>
+          <t>0032747-79.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Bens Públicos</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>19/08/2025</t>
+          <t>14/10/2025</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>13/08/2026 16:43</t>
+          <t>13/08/2026 18:03</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>13/08/2026 16:43</t>
+          <t>13/08/2026 18:03</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>19/08/2026 03:21</t>
+          <t>18/08/2026 11:43</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3497,7 +3497,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0028981-20.2017.8.16.0035</t>
+          <t>0033095-34.2023.8.16.0021</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3507,27 +3507,27 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Roubo Majorado</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>13/08/2026 21:53</t>
+          <t>13/08/2026 20:23</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>13/08/2026 21:53</t>
+          <t>13/08/2026 20:23</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>19/08/2026 00:16</t>
+          <t>18/08/2026 04:03</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3544,37 +3544,37 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0030192-26.2018.8.16.0013</t>
+          <t>0035638-22.2019.8.16.0030</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Embargos de Divergência em Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Roubo Majorado</t>
+          <t>Receptação Qualificada</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>13/10/2022</t>
+          <t>13/11/2025</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>17/08/2026 13:23</t>
+          <t>13/08/2026 16:43</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>17/08/2026 13:23</t>
+          <t>13/08/2026 16:43</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>18/08/2026 03:55</t>
+          <t>18/08/2026 21:37</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3591,37 +3591,37 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0032218-94.2023.8.16.0021</t>
+          <t>0036039-38.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Crimes do Sistema Nacional de Armas | Receptação</t>
+          <t>Servidão Administrativa</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>13/08/2026 16:33</t>
+          <t>12/08/2026 14:23</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>13/08/2026 16:33</t>
+          <t>12/08/2026 14:23</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>19/08/2026 02:14</t>
+          <t>18/08/2026 11:03</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3638,7 +3638,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0032747-79.2023.8.16.0000</t>
+          <t>0037335-61.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3648,27 +3648,27 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bens Públicos</t>
+          <t>Limitação de Juros</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>14/10/2025</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>13/08/2026 18:03</t>
+          <t>12/08/2026 15:03</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>13/08/2026 18:03</t>
+          <t>12/08/2026 15:03</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>18/08/2026 11:43</t>
+          <t>19/08/2026 03:21</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3685,37 +3685,37 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0035638-22.2019.8.16.0030</t>
+          <t>0038454-62.2022.8.16.0000</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Receptação Qualificada</t>
+          <t>Direitos / Deveres do Condômino</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>13/11/2025</t>
+          <t>03/10/2023</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>13/08/2026 16:43</t>
+          <t>14/08/2026 13:03</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>13/08/2026 16:43</t>
+          <t>14/08/2026 13:03</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>18/08/2026 21:37</t>
+          <t>19/08/2026 04:12</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3732,7 +3732,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0036039-38.2024.8.16.0000</t>
+          <t>0039374-82.2012.8.16.0001</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3742,27 +3742,27 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Servidão Administrativa</t>
+          <t>Auxílio-Doença Acidentário</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>05/06/2025</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>12/08/2026 14:23</t>
+          <t>14/08/2026 15:03</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>12/08/2026 14:23</t>
+          <t>14/08/2026 15:03</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>18/08/2026 11:03</t>
+          <t>18/08/2026 12:55</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3779,7 +3779,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0037335-61.2025.8.16.0000</t>
+          <t>0040465-59.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3789,27 +3789,27 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Limitação de Juros</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>12/08/2026 15:03</t>
+          <t>13/08/2026 21:33</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>12/08/2026 15:03</t>
+          <t>13/08/2026 21:33</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>19/08/2026 03:21</t>
+          <t>18/08/2026 07:46</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3826,37 +3826,37 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0038454-62.2022.8.16.0000</t>
+          <t>0042134-16.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Direitos / Deveres do Condômino</t>
+          <t>Furto Qualificado</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>03/10/2023</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>14/08/2026 13:03</t>
+          <t>13/08/2026 19:53</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>14/08/2026 13:03</t>
+          <t>13/08/2026 19:53</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>19/08/2026 04:12</t>
+          <t>18/08/2026 04:24</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3873,7 +3873,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0039374-82.2012.8.16.0001</t>
+          <t>0046203-28.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3883,27 +3883,27 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Auxílio-Doença Acidentário</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>05/06/2025</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>14/08/2026 15:03</t>
+          <t>12/08/2026 14:23</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>14/08/2026 15:03</t>
+          <t>12/08/2026 14:23</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>18/08/2026 12:55</t>
+          <t>18/08/2026 07:46</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3920,37 +3920,37 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0041319-84.2024.8.16.0001</t>
+          <t>0049454-20.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Ingresso e Exclusão dos Sócios na Sociedade</t>
+          <t>Prisão Preventiva | Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>26/05/2025</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>17/08/2026 13:13</t>
+          <t>13/08/2026 17:33</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>17/08/2026 13:13</t>
+          <t>13/08/2026 17:33</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>18/08/2026 16:27</t>
+          <t>19/08/2026 02:36</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3967,37 +3967,37 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0042997-32.2023.8.16.0014</t>
+          <t>0050711-80.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Roubo Majorado</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>13/08/2026 13:58</t>
+          <t>13/08/2026 17:13</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>13/08/2026 13:58</t>
+          <t>13/08/2026 17:13</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>18/08/2026 16:14</t>
+          <t>19/08/2026 02:47</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -4014,37 +4014,37 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0046238-58.2024.8.16.0182</t>
+          <t>0058234-17.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Pedido de Uniformização de Interpretação de Lei Criminal</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Residência Médica | Programas de Bolsas e Financiamento Estudantil com Recursos Públicos</t>
+          <t>Ato Lesivo ao Patrimônio Artístico, Estético, Histórico ou Turístico</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>03/04/2025</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>18/08/2026 01:57</t>
+          <t>14/08/2026 16:23</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>18/08/2026 01:57</t>
+          <t>14/08/2026 16:23</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>18/08/2026 14:27</t>
+          <t>18/08/2026 09:19</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4061,7 +4061,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0049454-20.2026.8.16.0000</t>
+          <t>0060424-79.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4071,27 +4071,27 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Prisão Preventiva | Tráfico de Drogas e Condutas Afins</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>13/08/2026 17:33</t>
+          <t>12/08/2026 09:26</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>13/08/2026 17:33</t>
+          <t>12/08/2026 09:26</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>19/08/2026 02:36</t>
+          <t>19/08/2026 00:37</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -4108,12 +4108,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0050711-80.2026.8.16.0000</t>
+          <t>0064158-64.2024.8.16.0014</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4123,22 +4123,22 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>13/08/2026 17:13</t>
+          <t>13/08/2026 14:33</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>13/08/2026 17:13</t>
+          <t>13/08/2026 14:33</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>19/08/2026 02:47</t>
+          <t>18/08/2026 11:03</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4155,37 +4155,37 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0059258-46.2025.8.16.0000</t>
+          <t>0064838-91.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Descontos Indevidos</t>
+          <t>Servidores Inativos | Requisição de Pequeno Valor - RPV</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>23/02/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>13/08/2026 19:33</t>
+          <t>17/08/2026 14:03</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>13/08/2026 19:33</t>
+          <t>17/08/2026 14:03</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>18/08/2026 03:55</t>
+          <t>18/08/2026 13:13</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4202,7 +4202,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0060424-79.2026.8.16.0000</t>
+          <t>0065092-93.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Homicídio Qualificado | Crime Tentado</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4222,17 +4222,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>12/08/2026 09:26</t>
+          <t>17/08/2026 18:43</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>12/08/2026 09:26</t>
+          <t>17/08/2026 18:43</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>19/08/2026 00:37</t>
+          <t>18/08/2026 10:25</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4249,12 +4249,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0064158-64.2024.8.16.0014</t>
+          <t>0066120-96.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4264,22 +4264,22 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>13/08/2026 14:33</t>
+          <t>17/08/2026 17:13</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>13/08/2026 14:33</t>
+          <t>17/08/2026 17:13</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>18/08/2026 11:03</t>
+          <t>18/08/2026 11:44</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4296,7 +4296,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0064838-91.2024.8.16.0000</t>
+          <t>0068216-55.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4306,27 +4306,27 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Servidores Inativos | Requisição de Pequeno Valor - RPV</t>
+          <t>Cobrança | Obrigação de Fazer / Não Fazer</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>23/02/2026</t>
+          <t>02/02/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>17/08/2026 14:03</t>
+          <t>14/08/2026 20:33</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>17/08/2026 14:03</t>
+          <t>14/08/2026 20:33</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>18/08/2026 13:13</t>
+          <t>18/08/2026 09:16</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4343,37 +4343,37 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0065092-93.2026.8.16.0000</t>
+          <t>0070705-31.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Homicídio Qualificado | Crime Tentado</t>
+          <t>Condomínio</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>17/08/2026 18:43</t>
+          <t>14/08/2026 18:03</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>17/08/2026 18:43</t>
+          <t>14/08/2026 18:03</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>18/08/2026 10:25</t>
+          <t>18/08/2026 10:26</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4390,7 +4390,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0065469-61.2022.8.16.0014</t>
+          <t>0088421-71.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4400,27 +4400,27 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>12/08/2026 13:53</t>
+          <t>13/08/2026 18:23</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>12/08/2026 13:53</t>
+          <t>13/08/2026 18:23</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>18/08/2026 15:43</t>
+          <t>20/08/2026 22:45</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4437,7 +4437,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0066120-96.2026.8.16.0000</t>
+          <t>0093139-77.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4447,27 +4447,27 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Seqüestro e cárcere privado | Crimes de Tortura | Lesão Cometida em Razão da Condição de Mulher | Ameaça</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>17/08/2026 17:13</t>
+          <t>17/08/2026 17:23</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>17/08/2026 17:13</t>
+          <t>17/08/2026 17:23</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>18/08/2026 11:44</t>
+          <t>18/08/2026 22:58</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4484,7 +4484,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0068649-22.2021.8.16.0014</t>
+          <t>0109747-58.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4494,27 +4494,27 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Inventário e Partilha | Bem de Família Legal</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>14/10/2025</t>
+          <t>29/09/2025</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>17/08/2026 13:33</t>
+          <t>14/08/2026 18:33</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>17/08/2026 13:33</t>
+          <t>14/08/2026 18:33</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>18/08/2026 13:38</t>
+          <t>19/08/2026 02:20</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4531,37 +4531,37 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0070705-31.2025.8.16.0000</t>
+          <t>0109806-12.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Condomínio</t>
+          <t>Invalidez Permanente</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>14/08/2026 18:03</t>
+          <t>13/08/2026 21:53</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>14/08/2026 18:03</t>
+          <t>13/08/2026 21:53</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>18/08/2026 10:26</t>
+          <t>18/08/2026 09:05</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4578,7 +4578,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0088421-71.2025.8.16.0000</t>
+          <t>0122142-48.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4588,27 +4588,27 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Desapropriação | Imissão na Posse</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>13/08/2026 18:23</t>
+          <t>12/08/2026 13:13</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>13/08/2026 18:23</t>
+          <t>12/08/2026 13:13</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20/08/2026 22:45</t>
+          <t>18/08/2026 23:47</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4625,7 +4625,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0088933-88.2024.8.16.0000</t>
+          <t>0124840-27.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4635,27 +4635,27 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Multas e demais Sanções</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>02/03/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>14/08/2026 20:33</t>
+          <t>14/08/2026 07:29</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>14/08/2026 20:33</t>
+          <t>14/08/2026 07:29</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>18/08/2026 16:27</t>
+          <t>18/08/2026 20:48</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4672,37 +4672,37 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0093139-77.2026.8.16.0000</t>
+          <t>0126623-54.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Seqüestro e cárcere privado | Crimes de Tortura | Lesão Cometida em Razão da Condição de Mulher | Ameaça</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>17/08/2026 17:23</t>
+          <t>17/08/2026 15:13</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>17/08/2026 17:23</t>
+          <t>17/08/2026 15:13</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>18/08/2026 22:58</t>
+          <t>19/08/2026 00:37</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4719,37 +4719,37 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0094754-39.2025.8.16.0000</t>
+          <t>0127459-90.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Peculato</t>
+          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins | Prisão Preventiva</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>17/08/2026 15:53</t>
+          <t>13/08/2026 20:53</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>17/08/2026 15:53</t>
+          <t>13/08/2026 20:53</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>18/08/2026 15:11</t>
+          <t>19/08/2026 02:20</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4766,7 +4766,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0109747-58.2023.8.16.0000</t>
+          <t>0131135-80.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4776,27 +4776,27 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Franquia</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>14/08/2026 18:33</t>
+          <t>14/08/2026 14:03</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>14/08/2026 18:33</t>
+          <t>14/08/2026 14:03</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>19/08/2026 02:20</t>
+          <t>18/08/2026 07:30</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4813,37 +4813,37 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0122142-48.2024.8.16.0000</t>
+          <t>0131195-19.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Desapropriação | Imissão na Posse</t>
+          <t>Associação para a Produção e Tráfico e Condutas Afins | Prisão Preventiva</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>12/08/2026 13:13</t>
+          <t>13/08/2026 21:53</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>12/08/2026 13:13</t>
+          <t>13/08/2026 21:53</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>18/08/2026 23:47</t>
+          <t>18/08/2026 12:05</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4860,37 +4860,37 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0124840-27.2024.8.16.0000</t>
+          <t>0152011-22.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação</t>
+          <t>Decorrente de Violência Doméstica | Injúria | Dano | Ameaça</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>02/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>14/08/2026 07:29</t>
+          <t>13/08/2026 21:03</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>14/08/2026 07:29</t>
+          <t>13/08/2026 21:03</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>18/08/2026 20:48</t>
+          <t>18/08/2026 11:17</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4907,7 +4907,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0126623-54.2024.8.16.0000</t>
+          <t>4002176-24.2025.8.16.4321</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4917,27 +4917,27 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Progressão de Regime</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>17/08/2026 15:13</t>
+          <t>18/08/2026 16:03</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>17/08/2026 15:13</t>
+          <t>18/08/2026 16:03</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>19/08/2026 00:37</t>
+          <t>19/08/2026 02:18</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4946,194 +4946,6 @@
         </is>
       </c>
       <c r="I96" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>0127459-90.2025.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins | Prisão Preventiva</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>14/01/2026</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>13/08/2026 20:53</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>13/08/2026 20:53</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>19/08/2026 02:20</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>0131195-19.2025.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Associação para a Produção e Tráfico e Condutas Afins | Prisão Preventiva</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>27/02/2026</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>13/08/2026 21:53</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>13/08/2026 21:53</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>18/08/2026 12:05</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>0152011-22.2025.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Decorrente de Violência Doméstica | Injúria | Dano | Ameaça</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>24/03/2026</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>13/08/2026 21:03</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>13/08/2026 21:03</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>18/08/2026 11:17</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>4002176-24.2025.8.16.4321</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Progressão de Regime</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>16/12/2025</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>18/08/2026 16:03</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>18/08/2026 16:03</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>19/08/2026 02:18</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>

--- a/docs/resultados.xlsx
+++ b/docs/resultados.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I96"/>
+  <dimension ref="A1:I101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
@@ -489,7 +489,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0000022-19.1988.8.16.0047</t>
+          <t>0021603-50.2020.8.16.0021</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -499,27 +499,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bancários</t>
+          <t>Locação de Imóvel</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>19/08/2024</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>17/08/2026 13:03</t>
+          <t>17/08/2026 14:53</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>17/08/2026 13:03</t>
+          <t>17/08/2026 14:53</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>19/08/2026 00:42</t>
+          <t>20/08/2026 22:45</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -536,7 +536,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0000174-98.2020.8.16.0062</t>
+          <t>0088421-71.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -551,22 +551,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>17/08/2026 18:03</t>
+          <t>13/08/2026 18:23</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17/08/2026 18:03</t>
+          <t>13/08/2026 18:23</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>18/08/2026 23:33</t>
+          <t>20/08/2026 22:45</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -583,7 +583,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0000272-47.2009.8.16.0037</t>
+          <t>0001893-39.2022.8.16.0097</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -593,27 +593,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Homicídio Qualificado</t>
+          <t>Crimes de Trânsito</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>13/08/2026 20:43</t>
+          <t>18/08/2026 16:13</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>13/08/2026 20:43</t>
+          <t>18/08/2026 16:13</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>18/08/2026 11:31</t>
+          <t>19/08/2026 03:41</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,37 +630,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0000470-27.2018.8.16.0051</t>
+          <t>0038454-62.2022.8.16.0000</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Usucapião Extraordinária</t>
+          <t>Direitos / Deveres do Condômino</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/10/2023</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>14/08/2026 14:24</t>
+          <t>14/08/2026 13:03</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>14/08/2026 14:24</t>
+          <t>14/08/2026 13:03</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>18/08/2026 22:23</t>
+          <t>19/08/2026 04:12</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -677,7 +677,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0000579-95.2025.8.16.0083</t>
+          <t>0028518-34.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -687,27 +687,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Furto Qualificado</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>19/08/2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>14/08/2026 15:13</t>
+          <t>13/08/2026 16:43</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>14/08/2026 15:13</t>
+          <t>13/08/2026 16:43</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>18/08/2026 10:42</t>
+          <t>19/08/2026 03:21</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -724,7 +724,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0000625-04.2023.8.16.0100</t>
+          <t>0037335-61.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Usucapião Ordinária</t>
+          <t>Limitação de Juros</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -744,17 +744,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>14/08/2026 20:33</t>
+          <t>12/08/2026 15:03</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>14/08/2026 20:33</t>
+          <t>12/08/2026 15:03</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>18/08/2026 10:44</t>
+          <t>19/08/2026 03:21</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -771,37 +771,37 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0000627-67.2022.8.16.0048</t>
+          <t>0002976-93.2025.8.16.0159</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Dano Qualificado contra a Administração Pública</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>02/09/2024</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>17/08/2026 13:53</t>
+          <t>13/08/2026 20:53</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>17/08/2026 13:53</t>
+          <t>13/08/2026 20:53</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>18/08/2026 05:35</t>
+          <t>19/08/2026 03:21</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -818,7 +818,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0000855-53.2024.8.16.0151</t>
+          <t>0001236-59.2021.8.16.0024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -828,27 +828,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Roubo Majorado</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>17/08/2026 15:53</t>
+          <t>18/08/2026 10:52</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>17/08/2026 15:53</t>
+          <t>18/08/2026 10:52</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>18/08/2026 07:13</t>
+          <t>19/08/2026 02:47</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -865,12 +865,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0001042-23.2024.8.16.0196</t>
+          <t>0050711-80.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -880,22 +880,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>14/08/2026 13:43</t>
+          <t>13/08/2026 17:13</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>14/08/2026 13:43</t>
+          <t>13/08/2026 17:13</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>19/08/2026 00:37</t>
+          <t>19/08/2026 02:47</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -912,37 +912,37 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0001125-91.2024.8.16.0114</t>
+          <t>0001373-33.2019.8.16.0017</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Receptação | Adulteração de Sinal Identificador de Veículo Automotor</t>
+          <t>Crimes de Trânsito</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>19/09/2025</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>13/08/2026 20:43</t>
+          <t>13/08/2026 20:53</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>13/08/2026 20:43</t>
+          <t>13/08/2026 20:53</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>19/08/2026 02:36</t>
+          <t>19/08/2026 02:47</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0001236-59.2021.8.16.0024</t>
+          <t>0026752-14.2021.8.16.0014</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -969,27 +969,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Pagamento</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>21/08/2024</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>18/08/2026 10:52</t>
+          <t>14/08/2026 15:43</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>18/08/2026 10:52</t>
+          <t>14/08/2026 15:43</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>19/08/2026 02:47</t>
+          <t>19/08/2026 02:48</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1006,7 +1006,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0001373-33.2019.8.16.0017</t>
+          <t>0016776-75.2024.8.16.0014</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1016,27 +1016,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Crimes de Trânsito</t>
+          <t>Plano de Saúde</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>13/08/2026 20:53</t>
+          <t>12/08/2026 14:03</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>13/08/2026 20:53</t>
+          <t>12/08/2026 14:03</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>19/08/2026 02:47</t>
+          <t>19/08/2026 02:48</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1053,7 +1053,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0001556-88.2013.8.16.0154</t>
+          <t>0009710-10.2025.8.16.0014</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1063,27 +1063,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Anulação de Débito Fiscal | Prescrição</t>
+          <t>Duplicata</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>14/08/2026 17:43</t>
+          <t>13/08/2026 18:33</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>14/08/2026 17:43</t>
+          <t>13/08/2026 18:33</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>18/08/2026 12:52</t>
+          <t>19/08/2026 02:48</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1100,37 +1100,37 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0001593-15.2020.8.16.0108</t>
+          <t>0019003-57.2023.8.16.0019</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Erro Médico | Erro Médico</t>
+          <t>Tráfico de Drogas e Condutas Afins | Desclassificação</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>02/10/2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>13/08/2026 16:43</t>
+          <t>17/08/2026 18:53</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>13/08/2026 16:43</t>
+          <t>17/08/2026 18:53</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>19/08/2026 00:37</t>
+          <t>19/08/2026 03:12</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1147,7 +1147,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0001652-58.2024.8.16.0109</t>
+          <t>0016302-44.2023.8.16.0013</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1157,27 +1157,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Crimes de Trânsito</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>12/08/2026 13:23</t>
+          <t>17/08/2026 18:33</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>12/08/2026 13:23</t>
+          <t>17/08/2026 18:33</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>18/08/2026 11:48</t>
+          <t>19/08/2026 02:36</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1194,37 +1194,37 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0001713-48.2023.8.16.0045</t>
+          <t>0001125-91.2024.8.16.0114</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Crimes Previstos no Estatuto da criança e do adolescente</t>
+          <t>Tráfico de Drogas e Condutas Afins | Receptação | Adulteração de Sinal Identificador de Veículo Automotor</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/09/2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>13/08/2026 21:13</t>
+          <t>13/08/2026 20:43</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>13/08/2026 21:13</t>
+          <t>13/08/2026 20:43</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>18/08/2026 07:46</t>
+          <t>19/08/2026 02:36</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1241,37 +1241,37 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0001849-73.2024.8.16.0089</t>
+          <t>0049454-20.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>Prisão Preventiva | Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>24/04/2025</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>14/08/2026 20:53</t>
+          <t>13/08/2026 17:33</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>14/08/2026 20:53</t>
+          <t>13/08/2026 17:33</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>18/08/2026 20:48</t>
+          <t>19/08/2026 02:36</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1288,37 +1288,37 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0001893-39.2022.8.16.0097</t>
+          <t>0032218-94.2023.8.16.0021</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Crimes de Trânsito</t>
+          <t>Crimes do Sistema Nacional de Armas | Receptação</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>18/08/2026 16:13</t>
+          <t>13/08/2026 16:33</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>18/08/2026 16:13</t>
+          <t>13/08/2026 16:33</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>19/08/2026 03:41</t>
+          <t>19/08/2026 02:14</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1335,7 +1335,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0002768-46.2025.8.16.0083</t>
+          <t>4002176-24.2025.8.16.4321</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1345,27 +1345,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Progressão de Regime</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>12/08/2026 14:43</t>
+          <t>18/08/2026 16:03</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>12/08/2026 14:43</t>
+          <t>18/08/2026 16:03</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>18/08/2026 04:24</t>
+          <t>19/08/2026 02:18</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1382,7 +1382,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0002961-64.2022.8.16.0019</t>
+          <t>0109747-58.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1392,27 +1392,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Crimes do Sistema Nacional de Armas</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>29/09/2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>12/08/2026 13:43</t>
+          <t>14/08/2026 18:33</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>12/08/2026 13:43</t>
+          <t>14/08/2026 18:33</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>18/08/2026 11:32</t>
+          <t>19/08/2026 02:20</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1429,7 +1429,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0002974-73.2012.8.16.0129</t>
+          <t>0010998-38.2022.8.16.0033</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1439,27 +1439,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Honorários Advocatícios | Pagamento do Débito | Cumprimento Provisório de Sentença</t>
+          <t>Tratamento médico-hospitalar</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>04/12/2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>14/08/2026 16:13</t>
+          <t>14/08/2026 20:03</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>14/08/2026 16:13</t>
+          <t>14/08/2026 20:03</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>18/08/2026 23:34</t>
+          <t>19/08/2026 02:20</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1476,22 +1476,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0002976-93.2025.8.16.0159</t>
+          <t>0127459-90.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dano Qualificado contra a Administração Pública</t>
+          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins | Prisão Preventiva</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>19/08/2026 03:21</t>
+          <t>19/08/2026 02:20</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1523,37 +1523,37 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0003154-89.2025.8.16.0014</t>
+          <t>0015822-25.2021.8.16.0017</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Comissão</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/12/2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>13/08/2026 21:53</t>
+          <t>14/08/2026 14:43</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>13/08/2026 21:53</t>
+          <t>14/08/2026 14:43</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>18/08/2026 21:05</t>
+          <t>19/08/2026 02:20</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1570,37 +1570,37 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0003523-75.2025.8.16.0146</t>
+          <t>0028981-20.2017.8.16.0035</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Roubo Majorado</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>17/08/2026 20:03</t>
+          <t>13/08/2026 21:53</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>17/08/2026 20:03</t>
+          <t>13/08/2026 21:53</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>18/08/2026 04:49</t>
+          <t>19/08/2026 00:16</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1617,7 +1617,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0004067-08.2022.8.16.0069</t>
+          <t>0012287-20.2023.8.16.0017</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1627,27 +1627,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação | Prescrição e Decadência</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>30/01/2025</t>
+          <t>18/11/2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>14/08/2026 15:03</t>
+          <t>14/08/2026 20:53</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>14/08/2026 15:03</t>
+          <t>14/08/2026 20:53</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>18/08/2026 12:27</t>
+          <t>19/08/2026 00:25</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1664,7 +1664,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0004410-05.2022.8.16.0004</t>
+          <t>0001593-15.2020.8.16.0108</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1674,27 +1674,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Equilíbrio Financeiro</t>
+          <t>Erro Médico | Erro Médico</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>17/08/2026 14:43</t>
+          <t>13/08/2026 16:43</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>17/08/2026 14:43</t>
+          <t>13/08/2026 16:43</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>18/08/2026 12:55</t>
+          <t>19/08/2026 00:37</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1711,37 +1711,37 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0004744-04.2024.8.16.0090</t>
+          <t>0126623-54.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Aplicação da Pena</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>13/08/2026 15:43</t>
+          <t>17/08/2026 15:13</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>13/08/2026 15:43</t>
+          <t>17/08/2026 15:13</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>18/08/2026 11:44</t>
+          <t>19/08/2026 00:37</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1758,37 +1758,37 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0004820-79.2022.8.16.0031</t>
+          <t>0001042-23.2024.8.16.0196</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Posse</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>17/08/2026 15:03</t>
+          <t>14/08/2026 13:43</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>17/08/2026 15:03</t>
+          <t>14/08/2026 13:43</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>18/08/2026 11:03</t>
+          <t>19/08/2026 00:37</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1805,37 +1805,37 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0004855-37.2019.8.16.0001</t>
+          <t>0060424-79.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>30/01/2024</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>14/08/2026 14:33</t>
+          <t>12/08/2026 09:26</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>14/08/2026 14:33</t>
+          <t>12/08/2026 09:26</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>18/08/2026 07:28</t>
+          <t>19/08/2026 00:37</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1852,7 +1852,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0004943-61.2022.8.16.0004</t>
+          <t>0000022-19.1988.8.16.0047</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1862,27 +1862,27 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ISS/ Imposto sobre Serviços</t>
+          <t>Bancários</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>19/08/2024</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>17/08/2026 15:25</t>
+          <t>17/08/2026 13:03</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>17/08/2026 15:25</t>
+          <t>17/08/2026 13:03</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>18/08/2026 05:23</t>
+          <t>19/08/2026 00:42</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1899,7 +1899,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0005206-31.2024.8.16.0196</t>
+          <t>0000470-27.2018.8.16.0051</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1909,27 +1909,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Usucapião Extraordinária</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>13/08/2026 13:23</t>
+          <t>14/08/2026 14:24</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>13/08/2026 13:23</t>
+          <t>14/08/2026 14:24</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>18/08/2026 04:01</t>
+          <t>18/08/2026 22:23</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1946,37 +1946,37 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0005407-05.2019.8.16.0194</t>
+          <t>0093139-77.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Locação de Imóvel</t>
+          <t>Seqüestro e cárcere privado | Crimes de Tortura | Lesão Cometida em Razão da Condição de Mulher | Ameaça</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>14/08/2026 13:33</t>
+          <t>17/08/2026 17:23</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>14/08/2026 13:33</t>
+          <t>17/08/2026 17:23</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>18/08/2026 13:44</t>
+          <t>18/08/2026 22:58</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0005523-98.2017.8.16.0026</t>
+          <t>0000174-98.2020.8.16.0062</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2003,27 +2003,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Multas e demais Sanções | Violação dos Princípios Administrativos | Termo de Ajustamento de Conduta - TAC | Ônus da Prova | Obrigação de Fazer / Não Fazer | Desvio de Função</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>17/10/2025</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>14/08/2026 13:23</t>
+          <t>17/08/2026 18:03</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>14/08/2026 13:23</t>
+          <t>17/08/2026 18:03</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>18/08/2026 04:35</t>
+          <t>18/08/2026 23:33</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2040,7 +2040,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0005818-14.2020.8.16.0194</t>
+          <t>0002974-73.2012.8.16.0129</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2050,27 +2050,27 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Abatimento proporcional do preço</t>
+          <t>Indenização por Dano Material | Honorários Advocatícios | Pagamento do Débito | Cumprimento Provisório de Sentença</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>14/08/2026 19:33</t>
+          <t>14/08/2026 16:13</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>14/08/2026 19:33</t>
+          <t>14/08/2026 16:13</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>18/08/2026 08:14</t>
+          <t>18/08/2026 23:34</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2087,7 +2087,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0005981-44.2023.8.16.0014</t>
+          <t>0025658-39.2023.8.16.0021</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2097,27 +2097,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Compra e Venda</t>
+          <t>Crimes do Sistema Nacional de Armas</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>17/08/2026 14:43</t>
+          <t>14/08/2026 14:33</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>17/08/2026 14:43</t>
+          <t>14/08/2026 14:33</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>18/08/2026 04:01</t>
+          <t>18/08/2026 23:34</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2134,7 +2134,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0007189-69.2024.8.16.0130</t>
+          <t>0122142-48.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2144,27 +2144,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Desapropriação | Imissão na Posse</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>14/08/2026 16:23</t>
+          <t>12/08/2026 13:13</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>14/08/2026 16:23</t>
+          <t>12/08/2026 13:13</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>18/08/2026 04:01</t>
+          <t>18/08/2026 23:47</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2181,37 +2181,37 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0007559-88.2023.8.16.0031</t>
+          <t>0003154-89.2025.8.16.0014</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Práticas Abusivas</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>14/08/2026 19:43</t>
+          <t>13/08/2026 21:53</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>14/08/2026 19:43</t>
+          <t>13/08/2026 21:53</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>18/08/2026 08:00</t>
+          <t>18/08/2026 21:05</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2228,7 +2228,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0008081-09.2023.8.16.0034</t>
+          <t>0035638-22.2019.8.16.0030</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2238,27 +2238,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Receptação Qualificada</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>13/11/2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>14/08/2026 16:53</t>
+          <t>13/08/2026 16:43</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>14/08/2026 16:53</t>
+          <t>13/08/2026 16:43</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>18/08/2026 05:36</t>
+          <t>18/08/2026 21:37</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2275,37 +2275,37 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0009080-35.2020.8.16.0173</t>
+          <t>0011811-63.2021.8.16.0045</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Crimes Previstos no Estatuto do Idoso</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>15/10/2025</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>14/08/2026 18:23</t>
+          <t>13/08/2026 17:13</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>14/08/2026 18:23</t>
+          <t>13/08/2026 17:13</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>18/08/2026 08:14</t>
+          <t>18/08/2026 21:37</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2322,7 +2322,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0009238-08.2024.8.16.0058</t>
+          <t>0012196-10.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2332,27 +2332,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Abuso de Poder | Defeito, nulidade ou anulação | Tutela de Evidência | Violação dos Princípios Administrativos | Cumprimento Provisório de Sentença | Legitimidade Ativa e Passiva</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>13/08/2026 21:03</t>
+          <t>14/08/2026 16:33</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>13/08/2026 21:03</t>
+          <t>14/08/2026 16:33</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>18/08/2026 12:05</t>
+          <t>18/08/2026 21:37</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2369,7 +2369,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0009710-10.2025.8.16.0014</t>
+          <t>0001849-73.2024.8.16.0089</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2379,27 +2379,27 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Duplicata</t>
+          <t>Dívida Ativa (Execução Fiscal)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>24/04/2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>13/08/2026 18:33</t>
+          <t>14/08/2026 20:53</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>13/08/2026 18:33</t>
+          <t>14/08/2026 20:53</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>19/08/2026 02:48</t>
+          <t>18/08/2026 20:48</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2416,7 +2416,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0010998-38.2022.8.16.0033</t>
+          <t>0023966-78.2018.8.16.0021</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2426,27 +2426,27 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tratamento médico-hospitalar</t>
+          <t>Inclusão Indevida em Cadastro de Inadimplentes</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>04/12/2025</t>
+          <t>25/08/2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>14/08/2026 20:03</t>
+          <t>14/08/2026 16:43</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>14/08/2026 20:03</t>
+          <t>14/08/2026 16:43</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>19/08/2026 02:20</t>
+          <t>18/08/2026 20:48</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2463,7 +2463,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0011811-63.2021.8.16.0045</t>
+          <t>0124840-27.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2473,27 +2473,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Crimes Previstos no Estatuto do Idoso</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>02/03/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>13/08/2026 17:13</t>
+          <t>14/08/2026 07:29</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>13/08/2026 17:13</t>
+          <t>14/08/2026 07:29</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>18/08/2026 21:37</t>
+          <t>18/08/2026 20:48</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2510,7 +2510,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0012196-10.2025.8.16.0000</t>
+          <t>0030427-19.2020.8.16.0014</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2520,27 +2520,27 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Abuso de Poder | Defeito, nulidade ou anulação | Tutela de Evidência | Violação dos Princípios Administrativos | Cumprimento Provisório de Sentença | Legitimidade Ativa e Passiva</t>
+          <t>Duplicata | Cédula de Produto Rural</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>11/08/2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>14/08/2026 16:33</t>
+          <t>14/08/2026 19:43</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>14/08/2026 16:33</t>
+          <t>14/08/2026 19:43</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>18/08/2026 21:37</t>
+          <t>18/08/2026 18:18</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2557,7 +2557,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0012287-20.2023.8.16.0017</t>
+          <t>0029973-10.2022.8.16.0001</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2567,27 +2567,27 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Previdência privada</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>18/11/2025</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>14/08/2026 20:53</t>
+          <t>17/08/2026 15:13</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>14/08/2026 20:53</t>
+          <t>17/08/2026 15:13</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>19/08/2026 00:25</t>
+          <t>18/08/2026 19:09</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2604,37 +2604,37 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0015241-62.2025.8.16.0019</t>
+          <t>0012180-37.2017.8.16.0194</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Indenização por Dano Moral | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>24/09/2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>13/08/2026 18:33</t>
+          <t>17/08/2026 13:03</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>13/08/2026 18:33</t>
+          <t>17/08/2026 13:03</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>18/08/2026 06:25</t>
+          <t>18/08/2026 19:20</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2651,7 +2651,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0015297-55.2025.8.16.0000</t>
+          <t>0002525-63.2015.8.16.0080</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2661,12 +2661,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Prestação de Serviços | Honorários Advocatícios</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>08/07/2025</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>18/08/2026 07:57</t>
+          <t>18/08/2026 17:14</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2698,7 +2698,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0015822-25.2021.8.16.0017</t>
+          <t>0002719-60.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2708,27 +2708,27 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Comissão</t>
+          <t>Acidente de Trânsito</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>17/12/2025</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>14/08/2026 14:43</t>
+          <t>14/08/2026 19:53</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>14/08/2026 14:43</t>
+          <t>14/08/2026 19:53</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>19/08/2026 02:20</t>
+          <t>18/08/2026 16:14</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2745,37 +2745,37 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0016302-44.2023.8.16.0013</t>
+          <t>0042997-32.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Crimes de Trânsito</t>
+          <t>Roubo Majorado</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>17/08/2026 18:33</t>
+          <t>13/08/2026 13:58</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>17/08/2026 18:33</t>
+          <t>13/08/2026 13:58</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>19/08/2026 02:36</t>
+          <t>18/08/2026 16:14</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2792,7 +2792,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0016776-75.2024.8.16.0014</t>
+          <t>0041319-84.2024.8.16.0001</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2802,27 +2802,27 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Plano de Saúde</t>
+          <t>Ingresso e Exclusão dos Sócios na Sociedade</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>26/05/2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>12/08/2026 14:03</t>
+          <t>17/08/2026 13:13</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>12/08/2026 14:03</t>
+          <t>17/08/2026 13:13</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>19/08/2026 02:48</t>
+          <t>18/08/2026 16:27</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2839,37 +2839,37 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0018929-14.2006.8.16.0014</t>
+          <t>0001965-03.2025.8.16.0006</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Homicídio Qualificado</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>23/05/2025</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>17/08/2026 13:53</t>
+          <t>14/08/2026 14:33</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>17/08/2026 13:53</t>
+          <t>14/08/2026 14:33</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>18/08/2026 07:57</t>
+          <t>18/08/2026 16:27</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2886,37 +2886,37 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0019003-57.2023.8.16.0019</t>
+          <t>0088933-88.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Desclassificação</t>
+          <t>Multas e demais Sanções</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>02/10/2025</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>17/08/2026 18:53</t>
+          <t>14/08/2026 20:33</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>17/08/2026 18:53</t>
+          <t>14/08/2026 20:33</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>19/08/2026 03:12</t>
+          <t>18/08/2026 16:27</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2933,37 +2933,37 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0021603-50.2020.8.16.0021</t>
+          <t>0003260-92.2022.8.16.0196</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Locação de Imóvel</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>27/11/2024</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>17/08/2026 14:53</t>
+          <t>17/08/2026 17:43</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>17/08/2026 14:53</t>
+          <t>17/08/2026 17:43</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20/08/2026 22:45</t>
+          <t>18/08/2026 16:29</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2980,7 +2980,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0023731-33.2025.8.16.0000</t>
+          <t>0010296-65.2020.8.16.0194</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2990,27 +2990,27 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Liminar | Adequação da Ação / Procedimento</t>
+          <t>Práticas Abusivas | Rescisão do contrato e devolução do dinheiro | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>17/08/2026 14:53</t>
+          <t>17/08/2026 14:23</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>17/08/2026 14:53</t>
+          <t>17/08/2026 14:23</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>18/08/2026 13:02</t>
+          <t>18/08/2026 16:41</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3027,7 +3027,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0023966-78.2018.8.16.0021</t>
+          <t>0000033-52.2025.8.16.0079</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3037,27 +3037,27 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Inclusão Indevida em Cadastro de Inadimplentes</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>25/08/2025</t>
+          <t>10/12/2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>14/08/2026 16:43</t>
+          <t>17/08/2026 13:13</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>14/08/2026 16:43</t>
+          <t>17/08/2026 13:13</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>18/08/2026 20:48</t>
+          <t>18/08/2026 16:46</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3074,7 +3074,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0025658-39.2023.8.16.0021</t>
+          <t>0005192-20.2021.8.16.0045</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3084,27 +3084,27 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Crimes do Sistema Nacional de Armas</t>
+          <t>Nomeação</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>06/08/2025</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>14/08/2026 14:33</t>
+          <t>14/08/2026 15:33</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>14/08/2026 14:33</t>
+          <t>14/08/2026 15:33</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>18/08/2026 23:34</t>
+          <t>18/08/2026 16:48</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3121,37 +3121,37 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0026752-14.2021.8.16.0014</t>
+          <t>0007668-63.2023.8.16.0044</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Pagamento</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>21/08/2024</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>14/08/2026 15:43</t>
+          <t>13/08/2026 17:13</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>14/08/2026 15:43</t>
+          <t>13/08/2026 17:13</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>19/08/2026 02:48</t>
+          <t>18/08/2026 17:06</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3168,37 +3168,37 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0027175-86.2016.8.16.0001</t>
+          <t>0002360-70.2019.8.16.0146</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Previdência privada</t>
+          <t>Arrendamento Rural | Perdas e Danos</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>23/02/2026</t>
+          <t>22/05/2024</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>12/08/2026 11:39</t>
+          <t>14/08/2026 21:03</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>12/08/2026 11:39</t>
+          <t>14/08/2026 21:03</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>18/08/2026 06:23</t>
+          <t>18/08/2026 15:28</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3215,37 +3215,37 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0028518-34.2023.8.16.0014</t>
+          <t>0065469-61.2022.8.16.0014</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>19/08/2025</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>13/08/2026 16:43</t>
+          <t>12/08/2026 13:53</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>13/08/2026 16:43</t>
+          <t>12/08/2026 13:53</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>19/08/2026 03:21</t>
+          <t>18/08/2026 15:43</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3262,7 +3262,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0028981-20.2017.8.16.0035</t>
+          <t>0011077-65.2022.8.16.0017</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3272,27 +3272,27 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Roubo Majorado</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/01/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>13/08/2026 21:53</t>
+          <t>13/08/2026 14:33</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>13/08/2026 21:53</t>
+          <t>13/08/2026 14:33</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>19/08/2026 00:16</t>
+          <t>18/08/2026 14:43</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3309,7 +3309,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0029973-10.2022.8.16.0001</t>
+          <t>0006707-23.2024.8.16.0098</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3319,27 +3319,27 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Previdência privada</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>17/08/2026 15:13</t>
+          <t>13/08/2026 17:13</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>17/08/2026 15:13</t>
+          <t>13/08/2026 17:13</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>18/08/2026 19:09</t>
+          <t>18/08/2026 14:57</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3356,7 +3356,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0030427-19.2020.8.16.0014</t>
+          <t>0094754-39.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3366,27 +3366,27 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Duplicata | Cédula de Produto Rural</t>
+          <t>Peculato</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>11/08/2025</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>14/08/2026 19:43</t>
+          <t>17/08/2026 15:53</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>14/08/2026 19:43</t>
+          <t>17/08/2026 15:53</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>18/08/2026 18:18</t>
+          <t>18/08/2026 15:11</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3403,37 +3403,37 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0032218-94.2023.8.16.0021</t>
+          <t>0046238-58.2024.8.16.0182</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Pedido de Uniformização de Interpretação de Lei Criminal</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Crimes do Sistema Nacional de Armas | Receptação</t>
+          <t>Residência Médica | Programas de Bolsas e Financiamento Estudantil com Recursos Públicos</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>03/04/2025</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>13/08/2026 16:33</t>
+          <t>18/08/2026 01:57</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>13/08/2026 16:33</t>
+          <t>18/08/2026 01:57</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>19/08/2026 02:14</t>
+          <t>18/08/2026 14:27</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3450,7 +3450,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0032747-79.2023.8.16.0000</t>
+          <t>0003825-94.2025.8.16.0117</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3460,27 +3460,27 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bens Públicos</t>
+          <t>Corrupção passiva</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>14/10/2025</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>13/08/2026 18:03</t>
+          <t>13/08/2026 20:33</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>13/08/2026 18:03</t>
+          <t>13/08/2026 20:33</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>18/08/2026 11:43</t>
+          <t>18/08/2026 14:32</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3497,7 +3497,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0033095-34.2023.8.16.0021</t>
+          <t>0007773-25.2020.8.16.0083</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3507,27 +3507,27 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Furto</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>13/08/2026 20:23</t>
+          <t>13/08/2026 19:13</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>13/08/2026 20:23</t>
+          <t>13/08/2026 19:13</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>18/08/2026 04:03</t>
+          <t>18/08/2026 14:32</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3544,37 +3544,37 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0035638-22.2019.8.16.0030</t>
+          <t>0000163-85.2024.8.16.0173</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Receptação Qualificada</t>
+          <t>Crimes de Trânsito</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>13/11/2025</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>13/08/2026 16:43</t>
+          <t>14/08/2026 17:13</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>13/08/2026 16:43</t>
+          <t>14/08/2026 17:13</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>18/08/2026 21:37</t>
+          <t>18/08/2026 13:38</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3591,7 +3591,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0036039-38.2024.8.16.0000</t>
+          <t>0007716-78.2022.8.16.0069</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3601,27 +3601,27 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Servidão Administrativa</t>
+          <t>Alienação Fiduciária</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>13/01/2025</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>12/08/2026 14:23</t>
+          <t>14/08/2026 20:03</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>12/08/2026 14:23</t>
+          <t>14/08/2026 20:03</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>18/08/2026 11:03</t>
+          <t>18/08/2026 13:42</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3638,7 +3638,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0037335-61.2025.8.16.0000</t>
+          <t>0005407-05.2019.8.16.0194</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Limitação de Juros</t>
+          <t>Locação de Imóvel</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3658,17 +3658,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>12/08/2026 15:03</t>
+          <t>14/08/2026 13:33</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>12/08/2026 15:03</t>
+          <t>14/08/2026 13:33</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>19/08/2026 03:21</t>
+          <t>18/08/2026 13:44</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3685,37 +3685,37 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0038454-62.2022.8.16.0000</t>
+          <t>0018604-92.2023.8.16.0030</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Direitos / Deveres do Condômino</t>
+          <t>Dever de Informação</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>03/10/2023</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>14/08/2026 13:03</t>
+          <t>12/08/2026 13:13</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>14/08/2026 13:03</t>
+          <t>12/08/2026 13:13</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>19/08/2026 04:12</t>
+          <t>18/08/2026 13:44</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3732,7 +3732,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0039374-82.2012.8.16.0001</t>
+          <t>0001165-69.2023.8.16.0159</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3742,27 +3742,27 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Auxílio-Doença Acidentário</t>
+          <t>Fornecimento</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>05/06/2025</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>14/08/2026 15:03</t>
+          <t>14/08/2026 19:43</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>14/08/2026 15:03</t>
+          <t>14/08/2026 19:43</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>18/08/2026 12:55</t>
+          <t>18/08/2026 13:44</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3779,7 +3779,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0040465-59.2025.8.16.0000</t>
+          <t>0024261-64.2025.8.16.0185</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3789,27 +3789,27 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Dívida Ativa (Execução Fiscal)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>13/08/2026 21:33</t>
+          <t>14/08/2026 19:23</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>13/08/2026 21:33</t>
+          <t>14/08/2026 19:23</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>18/08/2026 07:46</t>
+          <t>18/08/2026 13:56</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3826,37 +3826,37 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0042134-16.2026.8.16.0000</t>
+          <t>0010323-40.2023.8.16.0001</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Furto Qualificado</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>13/08/2026 19:53</t>
+          <t>12/08/2026 14:53</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>13/08/2026 19:53</t>
+          <t>12/08/2026 14:53</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>18/08/2026 04:24</t>
+          <t>18/08/2026 14:24</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3873,7 +3873,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0046203-28.2025.8.16.0000</t>
+          <t>0012621-37.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3883,27 +3883,27 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Despesas Condominiais</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>12/08/2026 14:23</t>
+          <t>14/08/2026 14:33</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>12/08/2026 14:23</t>
+          <t>14/08/2026 14:33</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>18/08/2026 07:46</t>
+          <t>18/08/2026 14:27</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3920,37 +3920,37 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0049454-20.2026.8.16.0000</t>
+          <t>0000706-08.2025.8.16.0156</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Prisão Preventiva | Tráfico de Drogas e Condutas Afins</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>13/08/2026 17:33</t>
+          <t>13/08/2026 14:03</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>13/08/2026 17:33</t>
+          <t>13/08/2026 14:03</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>19/08/2026 02:36</t>
+          <t>18/08/2026 13:26</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3967,37 +3967,37 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0050711-80.2026.8.16.0000</t>
+          <t>0008905-80.2017.8.16.0000</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Pagamento Atrasado / Correção Monetária</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>12/03/2025</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>13/08/2026 17:13</t>
+          <t>13/08/2026 15:43</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>13/08/2026 17:13</t>
+          <t>13/08/2026 15:43</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>19/08/2026 02:47</t>
+          <t>18/08/2026 13:38</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -4014,7 +4014,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0058234-17.2024.8.16.0000</t>
+          <t>0068649-22.2021.8.16.0014</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4024,27 +4024,27 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Ato Lesivo ao Patrimônio Artístico, Estético, Histórico ou Turístico</t>
+          <t>Inventário e Partilha | Bem de Família Legal</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>14/10/2025</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>14/08/2026 16:23</t>
+          <t>17/08/2026 13:33</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>14/08/2026 16:23</t>
+          <t>17/08/2026 13:33</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>18/08/2026 09:19</t>
+          <t>18/08/2026 13:38</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4061,37 +4061,37 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0060424-79.2026.8.16.0000</t>
+          <t>0001556-88.2013.8.16.0154</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Anulação de Débito Fiscal | Prescrição</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>12/08/2026 09:26</t>
+          <t>14/08/2026 17:43</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>12/08/2026 09:26</t>
+          <t>14/08/2026 17:43</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>19/08/2026 00:37</t>
+          <t>18/08/2026 12:52</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -4108,37 +4108,37 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0064158-64.2024.8.16.0014</t>
+          <t>0039374-82.2012.8.16.0001</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Auxílio-Doença Acidentário</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/06/2025</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>13/08/2026 14:33</t>
+          <t>14/08/2026 15:03</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>13/08/2026 14:33</t>
+          <t>14/08/2026 15:03</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>18/08/2026 11:03</t>
+          <t>18/08/2026 12:55</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4155,7 +4155,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0064838-91.2024.8.16.0000</t>
+          <t>0004410-05.2022.8.16.0004</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4165,27 +4165,27 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Servidores Inativos | Requisição de Pequeno Valor - RPV</t>
+          <t>Equilíbrio Financeiro</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>23/02/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>17/08/2026 14:03</t>
+          <t>17/08/2026 14:43</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>17/08/2026 14:03</t>
+          <t>17/08/2026 14:43</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>18/08/2026 13:13</t>
+          <t>18/08/2026 12:55</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4202,37 +4202,37 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0065092-93.2026.8.16.0000</t>
+          <t>0023731-33.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Homicídio Qualificado | Crime Tentado</t>
+          <t>Indenização por Dano Moral | Liminar | Adequação da Ação / Procedimento</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>17/08/2026 18:43</t>
+          <t>17/08/2026 14:53</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>17/08/2026 18:43</t>
+          <t>17/08/2026 14:53</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>18/08/2026 10:25</t>
+          <t>18/08/2026 13:02</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4249,37 +4249,37 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0066120-96.2026.8.16.0000</t>
+          <t>0064838-91.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Servidores Inativos | Requisição de Pequeno Valor - RPV</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>23/02/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>17/08/2026 17:13</t>
+          <t>17/08/2026 14:03</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>17/08/2026 17:13</t>
+          <t>17/08/2026 14:03</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>18/08/2026 11:44</t>
+          <t>18/08/2026 13:13</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4296,7 +4296,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0068216-55.2024.8.16.0000</t>
+          <t>0000521-43.2023.8.16.0122</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4306,27 +4306,27 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Cobrança | Obrigação de Fazer / Não Fazer</t>
+          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>02/02/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>14/08/2026 20:33</t>
+          <t>14/08/2026 21:43</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>14/08/2026 20:33</t>
+          <t>14/08/2026 21:43</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>18/08/2026 09:16</t>
+          <t>18/08/2026 13:13</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4343,7 +4343,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0070705-31.2025.8.16.0000</t>
+          <t>0004067-08.2022.8.16.0069</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4353,27 +4353,27 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Condomínio</t>
+          <t>Defeito, nulidade ou anulação | Prescrição e Decadência</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>30/01/2025</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>14/08/2026 18:03</t>
+          <t>14/08/2026 15:03</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>14/08/2026 18:03</t>
+          <t>14/08/2026 15:03</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>18/08/2026 10:26</t>
+          <t>18/08/2026 12:27</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4390,37 +4390,37 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0088421-71.2025.8.16.0000</t>
+          <t>0131195-19.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Associação para a Produção e Tráfico e Condutas Afins | Prisão Preventiva</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>13/08/2026 18:23</t>
+          <t>13/08/2026 21:53</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>13/08/2026 18:23</t>
+          <t>13/08/2026 21:53</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20/08/2026 22:45</t>
+          <t>18/08/2026 12:05</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4437,37 +4437,37 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0093139-77.2026.8.16.0000</t>
+          <t>0009238-08.2024.8.16.0058</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Seqüestro e cárcere privado | Crimes de Tortura | Lesão Cometida em Razão da Condição de Mulher | Ameaça</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>17/08/2026 17:23</t>
+          <t>13/08/2026 21:03</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>17/08/2026 17:23</t>
+          <t>13/08/2026 21:03</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>18/08/2026 22:58</t>
+          <t>18/08/2026 12:05</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4484,37 +4484,37 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0109747-58.2023.8.16.0000</t>
+          <t>0152011-22.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Decorrente de Violência Doméstica | Injúria | Dano | Ameaça</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>14/08/2026 18:33</t>
+          <t>13/08/2026 21:03</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>14/08/2026 18:33</t>
+          <t>13/08/2026 21:03</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>19/08/2026 02:20</t>
+          <t>18/08/2026 11:17</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4531,37 +4531,37 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0109806-12.2024.8.16.0000</t>
+          <t>0000272-47.2009.8.16.0037</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Invalidez Permanente</t>
+          <t>Homicídio Qualificado</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>13/08/2026 21:53</t>
+          <t>13/08/2026 20:43</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>13/08/2026 21:53</t>
+          <t>13/08/2026 20:43</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>18/08/2026 09:05</t>
+          <t>18/08/2026 11:31</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4578,7 +4578,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0122142-48.2024.8.16.0000</t>
+          <t>0002961-64.2022.8.16.0019</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4588,27 +4588,27 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Desapropriação | Imissão na Posse</t>
+          <t>Crimes do Sistema Nacional de Armas</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>12/08/2026 13:13</t>
+          <t>12/08/2026 13:43</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>12/08/2026 13:13</t>
+          <t>12/08/2026 13:43</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>18/08/2026 23:47</t>
+          <t>18/08/2026 11:32</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4625,7 +4625,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0124840-27.2024.8.16.0000</t>
+          <t>0032747-79.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4635,27 +4635,27 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação</t>
+          <t>Bens Públicos</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>02/03/2026</t>
+          <t>14/10/2025</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>14/08/2026 07:29</t>
+          <t>13/08/2026 18:03</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>14/08/2026 07:29</t>
+          <t>13/08/2026 18:03</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>18/08/2026 20:48</t>
+          <t>18/08/2026 11:43</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4672,37 +4672,37 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0126623-54.2024.8.16.0000</t>
+          <t>0004744-04.2024.8.16.0090</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Tráfico de Drogas e Condutas Afins | Aplicação da Pena</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>17/08/2026 15:13</t>
+          <t>13/08/2026 15:43</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>17/08/2026 15:13</t>
+          <t>13/08/2026 15:43</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>19/08/2026 00:37</t>
+          <t>18/08/2026 11:44</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4719,7 +4719,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0127459-90.2025.8.16.0000</t>
+          <t>0066120-96.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4729,27 +4729,27 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins | Prisão Preventiva</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>13/08/2026 20:53</t>
+          <t>17/08/2026 17:13</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>13/08/2026 20:53</t>
+          <t>17/08/2026 17:13</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>19/08/2026 02:20</t>
+          <t>18/08/2026 11:44</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4766,7 +4766,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0131135-80.2024.8.16.0000</t>
+          <t>0001652-58.2024.8.16.0109</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4776,27 +4776,27 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Franquia</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>14/08/2026 14:03</t>
+          <t>12/08/2026 13:23</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>14/08/2026 14:03</t>
+          <t>12/08/2026 13:23</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>18/08/2026 07:30</t>
+          <t>18/08/2026 11:48</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4813,7 +4813,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0131195-19.2025.8.16.0000</t>
+          <t>0065092-93.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4823,27 +4823,27 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Associação para a Produção e Tráfico e Condutas Afins | Prisão Preventiva</t>
+          <t>Homicídio Qualificado | Crime Tentado</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>13/08/2026 21:53</t>
+          <t>17/08/2026 18:43</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>13/08/2026 21:53</t>
+          <t>17/08/2026 18:43</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>18/08/2026 12:05</t>
+          <t>18/08/2026 10:25</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4860,37 +4860,37 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0152011-22.2025.8.16.0000</t>
+          <t>0070705-31.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Decorrente de Violência Doméstica | Injúria | Dano | Ameaça</t>
+          <t>Condomínio</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>13/08/2026 21:03</t>
+          <t>14/08/2026 18:03</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>13/08/2026 21:03</t>
+          <t>14/08/2026 18:03</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>18/08/2026 11:17</t>
+          <t>18/08/2026 10:26</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4907,37 +4907,37 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>4002176-24.2025.8.16.4321</t>
+          <t>0000579-95.2025.8.16.0083</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Progressão de Regime</t>
+          <t>Furto Qualificado</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>18/08/2026 16:03</t>
+          <t>14/08/2026 15:13</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>18/08/2026 16:03</t>
+          <t>14/08/2026 15:13</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>19/08/2026 02:18</t>
+          <t>18/08/2026 10:42</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4946,6 +4946,241 @@
         </is>
       </c>
       <c r="I96" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>0000625-04.2023.8.16.0100</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Usucapião Ordinária</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>14/08/2026 20:33</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>14/08/2026 20:33</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>18/08/2026 10:44</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>0064158-64.2024.8.16.0014</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>13/08/2026 14:33</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>13/08/2026 14:33</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>18/08/2026 11:03</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>0036039-38.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Servidão Administrativa</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>12/08/2026 14:23</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>12/08/2026 14:23</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>18/08/2026 11:03</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>0004820-79.2022.8.16.0031</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Posse</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>17/08/2026 15:03</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>17/08/2026 15:03</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>18/08/2026 11:03</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>0025803-15.2020.8.16.0017</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Tratamento médico-hospitalar</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>14/08/2026 18:43</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>14/08/2026 18:43</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>18/08/2026 03:33</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>

--- a/docs/resultados.xlsx
+++ b/docs/resultados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I101"/>
+  <dimension ref="A1:I100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -489,7 +489,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0021603-50.2020.8.16.0021</t>
+          <t>0000022-19.1988.8.16.0047</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -499,27 +499,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Locação de Imóvel</t>
+          <t>Bancários</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>19/08/2024</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>17/08/2026 14:53</t>
+          <t>17/08/2026 13:03</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>17/08/2026 14:53</t>
+          <t>17/08/2026 13:03</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>20/08/2026 22:45</t>
+          <t>19/08/2026 00:42</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -536,7 +536,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0088421-71.2025.8.16.0000</t>
+          <t>0000033-52.2025.8.16.0079</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -546,27 +546,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>10/12/2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>13/08/2026 18:23</t>
+          <t>17/08/2026 13:13</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>13/08/2026 18:23</t>
+          <t>17/08/2026 13:13</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>20/08/2026 22:45</t>
+          <t>18/08/2026 16:46</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -583,12 +583,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0001893-39.2022.8.16.0097</t>
+          <t>0000163-85.2024.8.16.0173</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -598,22 +598,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>18/08/2026 16:13</t>
+          <t>14/08/2026 17:13</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>18/08/2026 16:13</t>
+          <t>14/08/2026 17:13</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>19/08/2026 03:41</t>
+          <t>18/08/2026 13:38</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,37 +630,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0038454-62.2022.8.16.0000</t>
+          <t>0000174-98.2020.8.16.0062</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Direitos / Deveres do Condômino</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>03/10/2023</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>14/08/2026 13:03</t>
+          <t>17/08/2026 18:03</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>14/08/2026 13:03</t>
+          <t>17/08/2026 18:03</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>19/08/2026 04:12</t>
+          <t>18/08/2026 23:33</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -677,37 +677,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0028518-34.2023.8.16.0014</t>
+          <t>0000272-47.2009.8.16.0037</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Homicídio Qualificado</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>19/08/2025</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>13/08/2026 16:43</t>
+          <t>13/08/2026 20:43</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>13/08/2026 16:43</t>
+          <t>13/08/2026 20:43</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>19/08/2026 03:21</t>
+          <t>18/08/2026 11:31</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -724,7 +724,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0037335-61.2025.8.16.0000</t>
+          <t>0000470-27.2018.8.16.0051</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -734,27 +734,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Limitação de Juros</t>
+          <t>Usucapião Extraordinária</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12/08/2026 15:03</t>
+          <t>14/08/2026 14:24</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>12/08/2026 15:03</t>
+          <t>14/08/2026 14:24</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>19/08/2026 03:21</t>
+          <t>18/08/2026 22:23</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -771,7 +771,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0002976-93.2025.8.16.0159</t>
+          <t>0000521-43.2023.8.16.0122</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -781,27 +781,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dano Qualificado contra a Administração Pública</t>
+          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>13/08/2026 20:53</t>
+          <t>14/08/2026 21:43</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>13/08/2026 20:53</t>
+          <t>14/08/2026 21:43</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>19/08/2026 03:21</t>
+          <t>18/08/2026 13:13</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -818,37 +818,37 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0001236-59.2021.8.16.0024</t>
+          <t>0000579-95.2025.8.16.0083</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Furto Qualificado</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>18/08/2026 10:52</t>
+          <t>14/08/2026 15:13</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>18/08/2026 10:52</t>
+          <t>14/08/2026 15:13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>19/08/2026 02:47</t>
+          <t>18/08/2026 10:42</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -865,37 +865,37 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0050711-80.2026.8.16.0000</t>
+          <t>0000625-04.2023.8.16.0100</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Usucapião Ordinária</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>13/08/2026 17:13</t>
+          <t>14/08/2026 20:33</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>13/08/2026 17:13</t>
+          <t>14/08/2026 20:33</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>19/08/2026 02:47</t>
+          <t>18/08/2026 10:44</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -912,37 +912,37 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0001373-33.2019.8.16.0017</t>
+          <t>0000706-08.2025.8.16.0156</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Crimes de Trânsito</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>13/08/2026 20:53</t>
+          <t>13/08/2026 14:03</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>13/08/2026 20:53</t>
+          <t>13/08/2026 14:03</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>19/08/2026 02:47</t>
+          <t>18/08/2026 13:26</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -959,37 +959,37 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0026752-14.2021.8.16.0014</t>
+          <t>0001042-23.2024.8.16.0196</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pagamento</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>21/08/2024</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>14/08/2026 15:43</t>
+          <t>14/08/2026 13:43</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>14/08/2026 15:43</t>
+          <t>14/08/2026 13:43</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>19/08/2026 02:48</t>
+          <t>19/08/2026 00:37</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1006,37 +1006,37 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0016776-75.2024.8.16.0014</t>
+          <t>0001125-91.2024.8.16.0114</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Plano de Saúde</t>
+          <t>Tráfico de Drogas e Condutas Afins | Receptação | Adulteração de Sinal Identificador de Veículo Automotor</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/09/2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>12/08/2026 14:03</t>
+          <t>13/08/2026 20:43</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>12/08/2026 14:03</t>
+          <t>13/08/2026 20:43</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>19/08/2026 02:48</t>
+          <t>19/08/2026 02:36</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1053,7 +1053,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0009710-10.2025.8.16.0014</t>
+          <t>0001165-69.2023.8.16.0159</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1063,27 +1063,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Duplicata</t>
+          <t>Fornecimento</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>13/08/2026 18:33</t>
+          <t>14/08/2026 19:43</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>13/08/2026 18:33</t>
+          <t>14/08/2026 19:43</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>19/08/2026 02:48</t>
+          <t>18/08/2026 13:44</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1100,37 +1100,37 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0019003-57.2023.8.16.0019</t>
+          <t>0001236-59.2021.8.16.0024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Desclassificação</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>02/10/2025</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>17/08/2026 18:53</t>
+          <t>18/08/2026 10:52</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>17/08/2026 18:53</t>
+          <t>18/08/2026 10:52</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>19/08/2026 03:12</t>
+          <t>19/08/2026 02:47</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1147,7 +1147,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0016302-44.2023.8.16.0013</t>
+          <t>0001373-33.2019.8.16.0017</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1162,22 +1162,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>17/08/2026 18:33</t>
+          <t>13/08/2026 20:53</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>17/08/2026 18:33</t>
+          <t>13/08/2026 20:53</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>19/08/2026 02:36</t>
+          <t>19/08/2026 02:47</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1194,37 +1194,37 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0001125-91.2024.8.16.0114</t>
+          <t>0001556-88.2013.8.16.0154</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Receptação | Adulteração de Sinal Identificador de Veículo Automotor</t>
+          <t>Anulação de Débito Fiscal | Prescrição</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>19/09/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>13/08/2026 20:43</t>
+          <t>14/08/2026 17:43</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>13/08/2026 20:43</t>
+          <t>14/08/2026 17:43</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>19/08/2026 02:36</t>
+          <t>18/08/2026 12:52</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1241,37 +1241,37 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0049454-20.2026.8.16.0000</t>
+          <t>0001593-15.2020.8.16.0108</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Prisão Preventiva | Tráfico de Drogas e Condutas Afins</t>
+          <t>Erro Médico | Erro Médico</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>13/08/2026 17:33</t>
+          <t>13/08/2026 16:43</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>13/08/2026 17:33</t>
+          <t>13/08/2026 16:43</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>19/08/2026 02:36</t>
+          <t>19/08/2026 00:37</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1288,37 +1288,37 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0032218-94.2023.8.16.0021</t>
+          <t>0001652-58.2024.8.16.0109</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Crimes do Sistema Nacional de Armas | Receptação</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>13/08/2026 16:33</t>
+          <t>12/08/2026 13:23</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>13/08/2026 16:33</t>
+          <t>12/08/2026 13:23</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>19/08/2026 02:14</t>
+          <t>18/08/2026 11:48</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1335,7 +1335,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4002176-24.2025.8.16.4321</t>
+          <t>0001849-73.2024.8.16.0089</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1345,27 +1345,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Progressão de Regime</t>
+          <t>Dívida Ativa (Execução Fiscal)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>24/04/2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>18/08/2026 16:03</t>
+          <t>14/08/2026 20:53</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>18/08/2026 16:03</t>
+          <t>14/08/2026 20:53</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>19/08/2026 02:18</t>
+          <t>18/08/2026 20:48</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1382,7 +1382,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0109747-58.2023.8.16.0000</t>
+          <t>0001893-39.2022.8.16.0097</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1392,27 +1392,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Crimes de Trânsito</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>14/08/2026 18:33</t>
+          <t>18/08/2026 16:13</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>14/08/2026 18:33</t>
+          <t>18/08/2026 16:13</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>19/08/2026 02:20</t>
+          <t>19/08/2026 03:41</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1429,7 +1429,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0010998-38.2022.8.16.0033</t>
+          <t>0001965-03.2025.8.16.0006</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1439,27 +1439,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tratamento médico-hospitalar</t>
+          <t>Homicídio Qualificado</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>04/12/2025</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>14/08/2026 20:03</t>
+          <t>14/08/2026 14:33</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>14/08/2026 20:03</t>
+          <t>14/08/2026 14:33</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>19/08/2026 02:20</t>
+          <t>18/08/2026 16:27</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1476,37 +1476,37 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0127459-90.2025.8.16.0000</t>
+          <t>0002360-70.2019.8.16.0146</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins | Prisão Preventiva</t>
+          <t>Arrendamento Rural | Perdas e Danos</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>22/05/2024</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>13/08/2026 20:53</t>
+          <t>14/08/2026 21:03</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>13/08/2026 20:53</t>
+          <t>14/08/2026 21:03</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>19/08/2026 02:20</t>
+          <t>18/08/2026 15:28</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1523,7 +1523,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0015822-25.2021.8.16.0017</t>
+          <t>0002525-63.2015.8.16.0080</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1533,27 +1533,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Comissão</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>17/12/2025</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>14/08/2026 14:43</t>
+          <t>14/08/2026 18:33</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>14/08/2026 14:43</t>
+          <t>14/08/2026 18:33</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>19/08/2026 02:20</t>
+          <t>18/08/2026 17:14</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1570,7 +1570,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0028981-20.2017.8.16.0035</t>
+          <t>0002719-60.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1580,27 +1580,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Roubo Majorado</t>
+          <t>Acidente de Trânsito</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>13/08/2026 21:53</t>
+          <t>14/08/2026 19:53</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>13/08/2026 21:53</t>
+          <t>14/08/2026 19:53</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>19/08/2026 00:16</t>
+          <t>18/08/2026 16:14</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1617,7 +1617,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0012287-20.2023.8.16.0017</t>
+          <t>0002961-64.2022.8.16.0019</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1627,27 +1627,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Crimes do Sistema Nacional de Armas</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>18/11/2025</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>14/08/2026 20:53</t>
+          <t>12/08/2026 13:43</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>14/08/2026 20:53</t>
+          <t>12/08/2026 13:43</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>19/08/2026 00:25</t>
+          <t>18/08/2026 11:32</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1664,7 +1664,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0001593-15.2020.8.16.0108</t>
+          <t>0002974-73.2012.8.16.0129</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1674,27 +1674,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Erro Médico | Erro Médico</t>
+          <t>Indenização por Dano Material | Honorários Advocatícios | Pagamento do Débito | Cumprimento Provisório de Sentença</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>13/08/2026 16:43</t>
+          <t>14/08/2026 16:13</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>13/08/2026 16:43</t>
+          <t>14/08/2026 16:13</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>19/08/2026 00:37</t>
+          <t>18/08/2026 23:34</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0126623-54.2024.8.16.0000</t>
+          <t>0002976-93.2025.8.16.0159</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1721,27 +1721,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Dano Qualificado contra a Administração Pública</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>17/08/2026 15:13</t>
+          <t>13/08/2026 20:53</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>17/08/2026 15:13</t>
+          <t>13/08/2026 20:53</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>19/08/2026 00:37</t>
+          <t>19/08/2026 03:21</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1758,7 +1758,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0001042-23.2024.8.16.0196</t>
+          <t>0003154-89.2025.8.16.0014</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1773,22 +1773,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>14/08/2026 13:43</t>
+          <t>13/08/2026 21:53</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>14/08/2026 13:43</t>
+          <t>13/08/2026 21:53</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>19/08/2026 00:37</t>
+          <t>18/08/2026 21:05</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1805,12 +1805,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0060424-79.2026.8.16.0000</t>
+          <t>0003260-92.2022.8.16.0196</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1820,22 +1820,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>27/11/2024</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>12/08/2026 09:26</t>
+          <t>17/08/2026 17:43</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>12/08/2026 09:26</t>
+          <t>17/08/2026 17:43</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>19/08/2026 00:37</t>
+          <t>18/08/2026 16:29</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1852,7 +1852,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0000022-19.1988.8.16.0047</t>
+          <t>0003825-94.2025.8.16.0117</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1862,27 +1862,27 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bancários</t>
+          <t>Corrupção passiva</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>19/08/2024</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>17/08/2026 13:03</t>
+          <t>13/08/2026 20:33</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>17/08/2026 13:03</t>
+          <t>13/08/2026 20:33</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>19/08/2026 00:42</t>
+          <t>18/08/2026 14:32</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1899,7 +1899,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0000470-27.2018.8.16.0051</t>
+          <t>0004067-08.2022.8.16.0069</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1909,27 +1909,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Usucapião Extraordinária</t>
+          <t>Defeito, nulidade ou anulação | Prescrição e Decadência</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>30/01/2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>14/08/2026 14:24</t>
+          <t>14/08/2026 15:03</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>14/08/2026 14:24</t>
+          <t>14/08/2026 15:03</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>18/08/2026 22:23</t>
+          <t>18/08/2026 12:27</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1946,37 +1946,37 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0093139-77.2026.8.16.0000</t>
+          <t>0004410-05.2022.8.16.0004</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Seqüestro e cárcere privado | Crimes de Tortura | Lesão Cometida em Razão da Condição de Mulher | Ameaça</t>
+          <t>Equilíbrio Financeiro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>17/08/2026 17:23</t>
+          <t>17/08/2026 14:43</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>17/08/2026 17:23</t>
+          <t>17/08/2026 14:43</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>18/08/2026 22:58</t>
+          <t>18/08/2026 12:55</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1993,37 +1993,37 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0000174-98.2020.8.16.0062</t>
+          <t>0004744-04.2024.8.16.0090</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Tráfico de Drogas e Condutas Afins | Aplicação da Pena</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>17/08/2026 18:03</t>
+          <t>13/08/2026 15:43</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>17/08/2026 18:03</t>
+          <t>13/08/2026 15:43</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>18/08/2026 23:33</t>
+          <t>18/08/2026 11:44</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2040,7 +2040,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0002974-73.2012.8.16.0129</t>
+          <t>0004820-79.2022.8.16.0031</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2050,27 +2050,27 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Honorários Advocatícios | Pagamento do Débito | Cumprimento Provisório de Sentença</t>
+          <t>Posse</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>14/08/2026 16:13</t>
+          <t>17/08/2026 15:03</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>14/08/2026 16:13</t>
+          <t>17/08/2026 15:03</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>18/08/2026 23:34</t>
+          <t>18/08/2026 11:03</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2087,7 +2087,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0025658-39.2023.8.16.0021</t>
+          <t>0005192-20.2021.8.16.0045</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2097,27 +2097,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Crimes do Sistema Nacional de Armas</t>
+          <t>Nomeação</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>06/08/2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>14/08/2026 14:33</t>
+          <t>14/08/2026 15:33</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>14/08/2026 14:33</t>
+          <t>14/08/2026 15:33</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>18/08/2026 23:34</t>
+          <t>18/08/2026 16:48</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2134,7 +2134,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0122142-48.2024.8.16.0000</t>
+          <t>0005407-05.2019.8.16.0194</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2144,27 +2144,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Desapropriação | Imissão na Posse</t>
+          <t>Locação de Imóvel</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>12/08/2026 13:13</t>
+          <t>14/08/2026 13:33</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>12/08/2026 13:13</t>
+          <t>14/08/2026 13:33</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>18/08/2026 23:47</t>
+          <t>18/08/2026 13:44</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2181,12 +2181,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0003154-89.2025.8.16.0014</t>
+          <t>0006707-23.2024.8.16.0098</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2196,22 +2196,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>13/08/2026 21:53</t>
+          <t>13/08/2026 17:13</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>13/08/2026 21:53</t>
+          <t>13/08/2026 17:13</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>18/08/2026 21:05</t>
+          <t>18/08/2026 14:57</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2228,37 +2228,37 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0035638-22.2019.8.16.0030</t>
+          <t>0007668-63.2023.8.16.0044</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Receptação Qualificada</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>13/11/2025</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>13/08/2026 16:43</t>
+          <t>13/08/2026 17:13</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>13/08/2026 16:43</t>
+          <t>13/08/2026 17:13</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>18/08/2026 21:37</t>
+          <t>18/08/2026 17:06</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2275,7 +2275,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0011811-63.2021.8.16.0045</t>
+          <t>0007716-78.2022.8.16.0069</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2285,27 +2285,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Crimes Previstos no Estatuto do Idoso</t>
+          <t>Alienação Fiduciária</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>13/01/2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>13/08/2026 17:13</t>
+          <t>14/08/2026 20:03</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>13/08/2026 17:13</t>
+          <t>14/08/2026 20:03</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>18/08/2026 21:37</t>
+          <t>18/08/2026 13:42</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2322,7 +2322,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0012196-10.2025.8.16.0000</t>
+          <t>0007773-25.2020.8.16.0083</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2332,27 +2332,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Abuso de Poder | Defeito, nulidade ou anulação | Tutela de Evidência | Violação dos Princípios Administrativos | Cumprimento Provisório de Sentença | Legitimidade Ativa e Passiva</t>
+          <t>Furto</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>14/08/2026 16:33</t>
+          <t>13/08/2026 19:13</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>14/08/2026 16:33</t>
+          <t>13/08/2026 19:13</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>18/08/2026 21:37</t>
+          <t>18/08/2026 14:32</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2369,37 +2369,37 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0001849-73.2024.8.16.0089</t>
+          <t>0008905-80.2017.8.16.0000</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>Pagamento Atrasado / Correção Monetária</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>24/04/2025</t>
+          <t>12/03/2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>14/08/2026 20:53</t>
+          <t>13/08/2026 15:43</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>14/08/2026 20:53</t>
+          <t>13/08/2026 15:43</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>18/08/2026 20:48</t>
+          <t>18/08/2026 13:38</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2416,7 +2416,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0023966-78.2018.8.16.0021</t>
+          <t>0009238-08.2024.8.16.0058</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2426,27 +2426,27 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Inclusão Indevida em Cadastro de Inadimplentes</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>25/08/2025</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>14/08/2026 16:43</t>
+          <t>13/08/2026 21:03</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>14/08/2026 16:43</t>
+          <t>13/08/2026 21:03</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>18/08/2026 20:48</t>
+          <t>18/08/2026 12:05</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2463,7 +2463,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0124840-27.2024.8.16.0000</t>
+          <t>0009710-10.2025.8.16.0014</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2473,27 +2473,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação</t>
+          <t>Duplicata</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>02/03/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>14/08/2026 07:29</t>
+          <t>13/08/2026 18:33</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>14/08/2026 07:29</t>
+          <t>13/08/2026 18:33</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>18/08/2026 20:48</t>
+          <t>19/08/2026 02:48</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2510,7 +2510,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0030427-19.2020.8.16.0014</t>
+          <t>0010296-65.2020.8.16.0194</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2520,27 +2520,27 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Duplicata | Cédula de Produto Rural</t>
+          <t>Práticas Abusivas | Rescisão do contrato e devolução do dinheiro | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>11/08/2025</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>14/08/2026 19:43</t>
+          <t>17/08/2026 14:23</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>14/08/2026 19:43</t>
+          <t>17/08/2026 14:23</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>18/08/2026 18:18</t>
+          <t>18/08/2026 16:41</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2557,7 +2557,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0029973-10.2022.8.16.0001</t>
+          <t>0010323-40.2023.8.16.0001</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2567,27 +2567,27 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Previdência privada</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>17/08/2026 15:13</t>
+          <t>12/08/2026 14:53</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>17/08/2026 15:13</t>
+          <t>12/08/2026 14:53</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>18/08/2026 19:09</t>
+          <t>18/08/2026 14:24</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2604,7 +2604,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0012180-37.2017.8.16.0194</t>
+          <t>0010998-38.2022.8.16.0033</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2614,27 +2614,27 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Indenização por Dano Material</t>
+          <t>Tratamento médico-hospitalar</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>24/09/2025</t>
+          <t>04/12/2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>17/08/2026 13:03</t>
+          <t>14/08/2026 20:03</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>17/08/2026 13:03</t>
+          <t>14/08/2026 20:03</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>18/08/2026 19:20</t>
+          <t>19/08/2026 02:20</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2651,7 +2651,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0002525-63.2015.8.16.0080</t>
+          <t>0011077-65.2022.8.16.0017</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2661,27 +2661,27 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>15/01/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>14/08/2026 18:33</t>
+          <t>13/08/2026 14:33</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>14/08/2026 18:33</t>
+          <t>13/08/2026 14:33</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>18/08/2026 17:14</t>
+          <t>18/08/2026 14:43</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2698,7 +2698,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0002719-60.2025.8.16.0000</t>
+          <t>0011811-63.2021.8.16.0045</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2708,27 +2708,27 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Acidente de Trânsito</t>
+          <t>Crimes Previstos no Estatuto do Idoso</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>14/08/2026 19:53</t>
+          <t>13/08/2026 17:13</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>14/08/2026 19:53</t>
+          <t>13/08/2026 17:13</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>18/08/2026 16:14</t>
+          <t>18/08/2026 21:37</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2745,37 +2745,37 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0042997-32.2023.8.16.0014</t>
+          <t>0012180-37.2017.8.16.0194</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Roubo Majorado</t>
+          <t>Indenização por Dano Moral | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>24/09/2025</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>13/08/2026 13:58</t>
+          <t>17/08/2026 13:03</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>13/08/2026 13:58</t>
+          <t>17/08/2026 13:03</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>18/08/2026 16:14</t>
+          <t>18/08/2026 19:20</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2792,7 +2792,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0041319-84.2024.8.16.0001</t>
+          <t>0012196-10.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2802,27 +2802,27 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ingresso e Exclusão dos Sócios na Sociedade</t>
+          <t>Abuso de Poder | Defeito, nulidade ou anulação | Tutela de Evidência | Violação dos Princípios Administrativos | Cumprimento Provisório de Sentença | Legitimidade Ativa e Passiva</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>26/05/2025</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>17/08/2026 13:13</t>
+          <t>14/08/2026 16:33</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>17/08/2026 13:13</t>
+          <t>14/08/2026 16:33</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>18/08/2026 16:27</t>
+          <t>18/08/2026 21:37</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2839,7 +2839,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0001965-03.2025.8.16.0006</t>
+          <t>0012287-20.2023.8.16.0017</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2849,27 +2849,27 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Homicídio Qualificado</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>18/11/2025</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>14/08/2026 14:33</t>
+          <t>14/08/2026 20:53</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>14/08/2026 14:33</t>
+          <t>14/08/2026 20:53</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>18/08/2026 16:27</t>
+          <t>19/08/2026 00:25</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2886,7 +2886,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0088933-88.2024.8.16.0000</t>
+          <t>0012621-37.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2896,27 +2896,27 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Multas e demais Sanções</t>
+          <t>Despesas Condominiais</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>14/08/2026 20:33</t>
+          <t>14/08/2026 14:33</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>14/08/2026 20:33</t>
+          <t>14/08/2026 14:33</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>18/08/2026 16:27</t>
+          <t>18/08/2026 14:27</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2933,37 +2933,37 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0003260-92.2022.8.16.0196</t>
+          <t>0015822-25.2021.8.16.0017</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Comissão</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>27/11/2024</t>
+          <t>17/12/2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>17/08/2026 17:43</t>
+          <t>14/08/2026 14:43</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>17/08/2026 17:43</t>
+          <t>14/08/2026 14:43</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>18/08/2026 16:29</t>
+          <t>19/08/2026 02:20</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2980,7 +2980,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0010296-65.2020.8.16.0194</t>
+          <t>0016302-44.2023.8.16.0013</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2990,27 +2990,27 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Práticas Abusivas | Rescisão do contrato e devolução do dinheiro | Indenização por Dano Moral</t>
+          <t>Crimes de Trânsito</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>17/08/2026 14:23</t>
+          <t>17/08/2026 18:33</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>17/08/2026 14:23</t>
+          <t>17/08/2026 18:33</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>18/08/2026 16:41</t>
+          <t>19/08/2026 02:36</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3027,7 +3027,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0000033-52.2025.8.16.0079</t>
+          <t>0016776-75.2024.8.16.0014</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3037,27 +3037,27 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação</t>
+          <t>Plano de Saúde</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>10/12/2025</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>17/08/2026 13:13</t>
+          <t>12/08/2026 14:03</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>17/08/2026 13:13</t>
+          <t>12/08/2026 14:03</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>18/08/2026 16:46</t>
+          <t>19/08/2026 02:48</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3074,7 +3074,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0005192-20.2021.8.16.0045</t>
+          <t>0018604-92.2023.8.16.0030</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3084,27 +3084,27 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Nomeação</t>
+          <t>Dever de Informação</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>06/08/2025</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>14/08/2026 15:33</t>
+          <t>12/08/2026 13:13</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>14/08/2026 15:33</t>
+          <t>12/08/2026 13:13</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>18/08/2026 16:48</t>
+          <t>18/08/2026 13:44</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3121,7 +3121,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0007668-63.2023.8.16.0044</t>
+          <t>0019003-57.2023.8.16.0019</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3131,27 +3131,27 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Tráfico de Drogas e Condutas Afins | Desclassificação</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>02/10/2025</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>13/08/2026 17:13</t>
+          <t>17/08/2026 18:53</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>13/08/2026 17:13</t>
+          <t>17/08/2026 18:53</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>18/08/2026 17:06</t>
+          <t>19/08/2026 03:12</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3168,7 +3168,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0002360-70.2019.8.16.0146</t>
+          <t>0021603-50.2020.8.16.0021</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3178,27 +3178,27 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Arrendamento Rural | Perdas e Danos</t>
+          <t>Locação de Imóvel</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>22/05/2024</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>14/08/2026 21:03</t>
+          <t>17/08/2026 14:53</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>14/08/2026 21:03</t>
+          <t>17/08/2026 14:53</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>18/08/2026 15:28</t>
+          <t>20/08/2026 22:45</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3215,7 +3215,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0065469-61.2022.8.16.0014</t>
+          <t>0023731-33.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3225,27 +3225,27 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação</t>
+          <t>Indenização por Dano Moral | Liminar | Adequação da Ação / Procedimento</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>12/08/2026 13:53</t>
+          <t>17/08/2026 14:53</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>12/08/2026 13:53</t>
+          <t>17/08/2026 14:53</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>18/08/2026 15:43</t>
+          <t>18/08/2026 13:02</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3262,7 +3262,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0011077-65.2022.8.16.0017</t>
+          <t>0023966-78.2018.8.16.0021</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3272,27 +3272,27 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Inclusão Indevida em Cadastro de Inadimplentes</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>15/01/2026</t>
+          <t>25/08/2025</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>13/08/2026 14:33</t>
+          <t>14/08/2026 16:43</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>13/08/2026 14:33</t>
+          <t>14/08/2026 16:43</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>18/08/2026 14:43</t>
+          <t>18/08/2026 20:48</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3309,7 +3309,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0006707-23.2024.8.16.0098</t>
+          <t>0024261-64.2025.8.16.0185</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3319,27 +3319,27 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Dívida Ativa (Execução Fiscal)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>13/08/2026 17:13</t>
+          <t>14/08/2026 19:23</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>13/08/2026 17:13</t>
+          <t>14/08/2026 19:23</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>18/08/2026 14:57</t>
+          <t>18/08/2026 13:56</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3356,7 +3356,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0094754-39.2025.8.16.0000</t>
+          <t>0025658-39.2023.8.16.0021</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3366,27 +3366,27 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Peculato</t>
+          <t>Crimes do Sistema Nacional de Armas</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>17/08/2026 15:53</t>
+          <t>14/08/2026 14:33</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>17/08/2026 15:53</t>
+          <t>14/08/2026 14:33</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>18/08/2026 15:11</t>
+          <t>18/08/2026 23:34</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3403,37 +3403,37 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0046238-58.2024.8.16.0182</t>
+          <t>0026752-14.2021.8.16.0014</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Pedido de Uniformização de Interpretação de Lei Criminal</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Residência Médica | Programas de Bolsas e Financiamento Estudantil com Recursos Públicos</t>
+          <t>Pagamento</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>03/04/2025</t>
+          <t>21/08/2024</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>18/08/2026 01:57</t>
+          <t>14/08/2026 15:43</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>18/08/2026 01:57</t>
+          <t>14/08/2026 15:43</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>18/08/2026 14:27</t>
+          <t>19/08/2026 02:48</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3450,37 +3450,37 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0003825-94.2025.8.16.0117</t>
+          <t>0028518-34.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Corrupção passiva</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>19/08/2025</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>13/08/2026 20:33</t>
+          <t>13/08/2026 16:43</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>13/08/2026 20:33</t>
+          <t>13/08/2026 16:43</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>18/08/2026 14:32</t>
+          <t>19/08/2026 03:21</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3497,7 +3497,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0007773-25.2020.8.16.0083</t>
+          <t>0028981-20.2017.8.16.0035</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3507,27 +3507,27 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Furto</t>
+          <t>Roubo Majorado</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>13/08/2026 19:13</t>
+          <t>13/08/2026 21:53</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>13/08/2026 19:13</t>
+          <t>13/08/2026 21:53</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>18/08/2026 14:32</t>
+          <t>19/08/2026 00:16</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3544,37 +3544,37 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0000163-85.2024.8.16.0173</t>
+          <t>0030192-26.2018.8.16.0013</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Embargos de Divergência em Recurso Especial</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Crimes de Trânsito</t>
+          <t>Roubo Majorado</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>13/10/2022</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>14/08/2026 17:13</t>
+          <t>17/08/2026 13:23</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>14/08/2026 17:13</t>
+          <t>17/08/2026 13:23</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>18/08/2026 13:38</t>
+          <t>18/08/2026 03:55</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3591,37 +3591,37 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0007716-78.2022.8.16.0069</t>
+          <t>0032218-94.2023.8.16.0021</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Alienação Fiduciária</t>
+          <t>Crimes do Sistema Nacional de Armas | Receptação</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>13/01/2025</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>14/08/2026 20:03</t>
+          <t>13/08/2026 16:33</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>14/08/2026 20:03</t>
+          <t>13/08/2026 16:33</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>18/08/2026 13:42</t>
+          <t>19/08/2026 02:14</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3638,7 +3638,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0005407-05.2019.8.16.0194</t>
+          <t>0032747-79.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3648,27 +3648,27 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Locação de Imóvel</t>
+          <t>Bens Públicos</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>14/10/2025</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>14/08/2026 13:33</t>
+          <t>13/08/2026 18:03</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>14/08/2026 13:33</t>
+          <t>13/08/2026 18:03</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>18/08/2026 13:44</t>
+          <t>18/08/2026 11:43</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3685,7 +3685,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0018604-92.2023.8.16.0030</t>
+          <t>0035638-22.2019.8.16.0030</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3695,27 +3695,27 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Dever de Informação</t>
+          <t>Receptação Qualificada</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>13/11/2025</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>12/08/2026 13:13</t>
+          <t>13/08/2026 16:43</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>12/08/2026 13:13</t>
+          <t>13/08/2026 16:43</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>18/08/2026 13:44</t>
+          <t>18/08/2026 21:37</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3732,7 +3732,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0001165-69.2023.8.16.0159</t>
+          <t>0036039-38.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3742,27 +3742,27 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Fornecimento</t>
+          <t>Servidão Administrativa</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>14/08/2026 19:43</t>
+          <t>12/08/2026 14:23</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>14/08/2026 19:43</t>
+          <t>12/08/2026 14:23</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>18/08/2026 13:44</t>
+          <t>18/08/2026 11:03</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3779,7 +3779,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0024261-64.2025.8.16.0185</t>
+          <t>0037335-61.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3789,27 +3789,27 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>Limitação de Juros</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>14/08/2026 19:23</t>
+          <t>12/08/2026 15:03</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>14/08/2026 19:23</t>
+          <t>12/08/2026 15:03</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>18/08/2026 13:56</t>
+          <t>19/08/2026 03:21</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3826,37 +3826,37 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0010323-40.2023.8.16.0001</t>
+          <t>0038454-62.2022.8.16.0000</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Direitos / Deveres do Condômino</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>03/10/2023</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>12/08/2026 14:53</t>
+          <t>14/08/2026 13:03</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>12/08/2026 14:53</t>
+          <t>14/08/2026 13:03</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>18/08/2026 14:24</t>
+          <t>19/08/2026 04:12</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3873,7 +3873,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0012621-37.2025.8.16.0000</t>
+          <t>0039374-82.2012.8.16.0001</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3883,27 +3883,27 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Despesas Condominiais</t>
+          <t>Auxílio-Doença Acidentário</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>05/06/2025</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>14/08/2026 14:33</t>
+          <t>14/08/2026 15:03</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>14/08/2026 14:33</t>
+          <t>14/08/2026 15:03</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>18/08/2026 14:27</t>
+          <t>18/08/2026 12:55</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3920,37 +3920,37 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0000706-08.2025.8.16.0156</t>
+          <t>0041319-84.2024.8.16.0001</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Ingresso e Exclusão dos Sócios na Sociedade</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>26/05/2025</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>13/08/2026 14:03</t>
+          <t>17/08/2026 13:13</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>13/08/2026 14:03</t>
+          <t>17/08/2026 13:13</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>18/08/2026 13:26</t>
+          <t>18/08/2026 16:27</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3967,7 +3967,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0008905-80.2017.8.16.0000</t>
+          <t>0042997-32.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3977,27 +3977,27 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Pagamento Atrasado / Correção Monetária</t>
+          <t>Roubo Majorado</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>12/03/2025</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>13/08/2026 15:43</t>
+          <t>13/08/2026 13:58</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>13/08/2026 15:43</t>
+          <t>13/08/2026 13:58</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>18/08/2026 13:38</t>
+          <t>18/08/2026 16:14</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -4014,37 +4014,37 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0068649-22.2021.8.16.0014</t>
+          <t>0046238-58.2024.8.16.0182</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Pedido de Uniformização de Interpretação de Lei Criminal</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Inventário e Partilha | Bem de Família Legal</t>
+          <t>Residência Médica | Programas de Bolsas e Financiamento Estudantil com Recursos Públicos</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>14/10/2025</t>
+          <t>03/04/2025</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>17/08/2026 13:33</t>
+          <t>18/08/2026 01:57</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>17/08/2026 13:33</t>
+          <t>18/08/2026 01:57</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>18/08/2026 13:38</t>
+          <t>18/08/2026 14:27</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4061,37 +4061,37 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0001556-88.2013.8.16.0154</t>
+          <t>0049454-20.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Anulação de Débito Fiscal | Prescrição</t>
+          <t>Prisão Preventiva | Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>14/08/2026 17:43</t>
+          <t>13/08/2026 17:33</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>14/08/2026 17:43</t>
+          <t>13/08/2026 17:33</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>18/08/2026 12:52</t>
+          <t>19/08/2026 02:36</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -4108,37 +4108,37 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0039374-82.2012.8.16.0001</t>
+          <t>0050711-80.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Auxílio-Doença Acidentário</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>05/06/2025</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>14/08/2026 15:03</t>
+          <t>13/08/2026 17:13</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>14/08/2026 15:03</t>
+          <t>13/08/2026 17:13</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>18/08/2026 12:55</t>
+          <t>19/08/2026 02:47</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4155,37 +4155,37 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0004410-05.2022.8.16.0004</t>
+          <t>0059258-46.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Equilíbrio Financeiro</t>
+          <t>Descontos Indevidos</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>17/08/2026 14:43</t>
+          <t>13/08/2026 19:33</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>17/08/2026 14:43</t>
+          <t>13/08/2026 19:33</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>18/08/2026 12:55</t>
+          <t>18/08/2026 03:55</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4202,37 +4202,37 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0023731-33.2025.8.16.0000</t>
+          <t>0060424-79.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Liminar | Adequação da Ação / Procedimento</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>17/08/2026 14:53</t>
+          <t>12/08/2026 09:26</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>17/08/2026 14:53</t>
+          <t>12/08/2026 09:26</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>18/08/2026 13:02</t>
+          <t>19/08/2026 00:37</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4249,37 +4249,37 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0064838-91.2024.8.16.0000</t>
+          <t>0064158-64.2024.8.16.0014</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Servidores Inativos | Requisição de Pequeno Valor - RPV</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>23/02/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>17/08/2026 14:03</t>
+          <t>13/08/2026 14:33</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>17/08/2026 14:03</t>
+          <t>13/08/2026 14:33</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>18/08/2026 13:13</t>
+          <t>18/08/2026 11:03</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4296,7 +4296,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0000521-43.2023.8.16.0122</t>
+          <t>0064838-91.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4306,22 +4306,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins</t>
+          <t>Servidores Inativos | Requisição de Pequeno Valor - RPV</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>23/02/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>14/08/2026 21:43</t>
+          <t>17/08/2026 14:03</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>14/08/2026 21:43</t>
+          <t>17/08/2026 14:03</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4343,37 +4343,37 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0004067-08.2022.8.16.0069</t>
+          <t>0065092-93.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação | Prescrição e Decadência</t>
+          <t>Homicídio Qualificado | Crime Tentado</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>30/01/2025</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>14/08/2026 15:03</t>
+          <t>17/08/2026 18:43</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>14/08/2026 15:03</t>
+          <t>17/08/2026 18:43</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>18/08/2026 12:27</t>
+          <t>18/08/2026 10:25</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4390,37 +4390,37 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0131195-19.2025.8.16.0000</t>
+          <t>0065469-61.2022.8.16.0014</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Associação para a Produção e Tráfico e Condutas Afins | Prisão Preventiva</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>13/08/2026 21:53</t>
+          <t>12/08/2026 13:53</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>13/08/2026 21:53</t>
+          <t>12/08/2026 13:53</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>18/08/2026 12:05</t>
+          <t>18/08/2026 15:43</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4437,12 +4437,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0009238-08.2024.8.16.0058</t>
+          <t>0066120-96.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4452,22 +4452,22 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>13/08/2026 21:03</t>
+          <t>17/08/2026 17:13</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>13/08/2026 21:03</t>
+          <t>17/08/2026 17:13</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>18/08/2026 12:05</t>
+          <t>18/08/2026 11:44</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4484,37 +4484,37 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0152011-22.2025.8.16.0000</t>
+          <t>0068649-22.2021.8.16.0014</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Decorrente de Violência Doméstica | Injúria | Dano | Ameaça</t>
+          <t>Inventário e Partilha | Bem de Família Legal</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>14/10/2025</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>13/08/2026 21:03</t>
+          <t>17/08/2026 13:33</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>13/08/2026 21:03</t>
+          <t>17/08/2026 13:33</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>18/08/2026 11:17</t>
+          <t>18/08/2026 13:38</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4531,7 +4531,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0000272-47.2009.8.16.0037</t>
+          <t>0070705-31.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4541,27 +4541,27 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Homicídio Qualificado</t>
+          <t>Condomínio</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>13/08/2026 20:43</t>
+          <t>14/08/2026 18:03</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>13/08/2026 20:43</t>
+          <t>14/08/2026 18:03</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>18/08/2026 11:31</t>
+          <t>18/08/2026 10:26</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4578,7 +4578,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0002961-64.2022.8.16.0019</t>
+          <t>0088421-71.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4588,27 +4588,27 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Crimes do Sistema Nacional de Armas</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>12/08/2026 13:43</t>
+          <t>13/08/2026 18:23</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>12/08/2026 13:43</t>
+          <t>13/08/2026 18:23</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>18/08/2026 11:32</t>
+          <t>20/08/2026 22:45</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4625,7 +4625,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0032747-79.2023.8.16.0000</t>
+          <t>0088933-88.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4635,27 +4635,27 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Bens Públicos</t>
+          <t>Multas e demais Sanções</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>14/10/2025</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>13/08/2026 18:03</t>
+          <t>14/08/2026 20:33</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>13/08/2026 18:03</t>
+          <t>14/08/2026 20:33</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>18/08/2026 11:43</t>
+          <t>18/08/2026 16:27</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4672,37 +4672,37 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0004744-04.2024.8.16.0090</t>
+          <t>0093139-77.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Aplicação da Pena</t>
+          <t>Seqüestro e cárcere privado | Crimes de Tortura | Lesão Cometida em Razão da Condição de Mulher | Ameaça</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>13/08/2026 15:43</t>
+          <t>17/08/2026 17:23</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>13/08/2026 15:43</t>
+          <t>17/08/2026 17:23</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>18/08/2026 11:44</t>
+          <t>18/08/2026 22:58</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4719,37 +4719,37 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0066120-96.2026.8.16.0000</t>
+          <t>0094754-39.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Peculato</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>17/08/2026 17:13</t>
+          <t>17/08/2026 15:53</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>17/08/2026 17:13</t>
+          <t>17/08/2026 15:53</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>18/08/2026 11:44</t>
+          <t>18/08/2026 15:11</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4766,7 +4766,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0001652-58.2024.8.16.0109</t>
+          <t>0109747-58.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4776,27 +4776,27 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>29/09/2025</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>12/08/2026 13:23</t>
+          <t>14/08/2026 18:33</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>12/08/2026 13:23</t>
+          <t>14/08/2026 18:33</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>18/08/2026 11:48</t>
+          <t>19/08/2026 02:20</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4813,37 +4813,37 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0065092-93.2026.8.16.0000</t>
+          <t>0122142-48.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Homicídio Qualificado | Crime Tentado</t>
+          <t>Desapropriação | Imissão na Posse</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>17/08/2026 18:43</t>
+          <t>12/08/2026 13:13</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>17/08/2026 18:43</t>
+          <t>12/08/2026 13:13</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>18/08/2026 10:25</t>
+          <t>18/08/2026 23:47</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4860,7 +4860,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0070705-31.2025.8.16.0000</t>
+          <t>0124840-27.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4870,27 +4870,27 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Condomínio</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>02/03/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>14/08/2026 18:03</t>
+          <t>14/08/2026 07:29</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>14/08/2026 18:03</t>
+          <t>14/08/2026 07:29</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>18/08/2026 10:26</t>
+          <t>18/08/2026 20:48</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4907,37 +4907,37 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0000579-95.2025.8.16.0083</t>
+          <t>0126623-54.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Furto Qualificado</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>14/08/2026 15:13</t>
+          <t>17/08/2026 15:13</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>14/08/2026 15:13</t>
+          <t>17/08/2026 15:13</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>18/08/2026 10:42</t>
+          <t>19/08/2026 00:37</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4954,37 +4954,37 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0000625-04.2023.8.16.0100</t>
+          <t>0127459-90.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Usucapião Ordinária</t>
+          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins | Prisão Preventiva</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>14/08/2026 20:33</t>
+          <t>13/08/2026 20:53</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>14/08/2026 20:33</t>
+          <t>13/08/2026 20:53</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>18/08/2026 10:44</t>
+          <t>19/08/2026 02:20</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -5001,37 +5001,37 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0064158-64.2024.8.16.0014</t>
+          <t>0131195-19.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Associação para a Produção e Tráfico e Condutas Afins | Prisão Preventiva</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>13/08/2026 14:33</t>
+          <t>13/08/2026 21:53</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>13/08/2026 14:33</t>
+          <t>13/08/2026 21:53</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>18/08/2026 11:03</t>
+          <t>18/08/2026 12:05</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -5048,37 +5048,37 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0036039-38.2024.8.16.0000</t>
+          <t>0152011-22.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Servidão Administrativa</t>
+          <t>Decorrente de Violência Doméstica | Injúria | Dano | Ameaça</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>12/08/2026 14:23</t>
+          <t>13/08/2026 21:03</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>12/08/2026 14:23</t>
+          <t>13/08/2026 21:03</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>18/08/2026 11:03</t>
+          <t>18/08/2026 11:17</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -5095,7 +5095,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0004820-79.2022.8.16.0031</t>
+          <t>4002176-24.2025.8.16.4321</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -5105,27 +5105,27 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Posse</t>
+          <t>Progressão de Regime</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>17/08/2026 15:03</t>
+          <t>18/08/2026 16:03</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>17/08/2026 15:03</t>
+          <t>18/08/2026 16:03</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>18/08/2026 11:03</t>
+          <t>19/08/2026 02:18</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -5134,53 +5134,6 @@
         </is>
       </c>
       <c r="I100" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>0025803-15.2020.8.16.0017</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Tratamento médico-hospitalar</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>14/08/2026 18:43</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>14/08/2026 18:43</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>18/08/2026 03:33</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>

--- a/docs/resultados.xlsx
+++ b/docs/resultados.xlsx
@@ -583,37 +583,37 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0000163-85.2024.8.16.0173</t>
+          <t>0000174-98.2020.8.16.0062</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Crimes de Trânsito</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>14/08/2026 17:13</t>
+          <t>17/08/2026 18:03</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>14/08/2026 17:13</t>
+          <t>17/08/2026 18:03</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>18/08/2026 13:38</t>
+          <t>18/08/2026 23:33</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,7 +630,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0000174-98.2020.8.16.0062</t>
+          <t>0000576-36.2025.8.16.0053</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -640,27 +640,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Promessa de Compra e Venda | Rescisão / Resolução</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>10/04/2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17/08/2026 18:03</t>
+          <t>17/08/2026 13:23</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>17/08/2026 18:03</t>
+          <t>17/08/2026 13:23</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>18/08/2026 23:33</t>
+          <t>18/08/2026 08:14</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -677,37 +677,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0000272-47.2009.8.16.0037</t>
+          <t>0000627-67.2022.8.16.0048</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Homicídio Qualificado</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>02/09/2024</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>13/08/2026 20:43</t>
+          <t>17/08/2026 13:53</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>13/08/2026 20:43</t>
+          <t>17/08/2026 13:53</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>18/08/2026 11:31</t>
+          <t>18/08/2026 05:35</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -724,7 +724,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0000470-27.2018.8.16.0051</t>
+          <t>0000804-49.2022.8.16.0139</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -734,27 +734,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Usucapião Extraordinária</t>
+          <t>Violência Psicológica contra a Mulher | Regime inicial | Prova Ilícita | Cerceamento de Defesa</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>14/08/2026 14:24</t>
+          <t>17/08/2026 15:33</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>14/08/2026 14:24</t>
+          <t>17/08/2026 15:33</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>18/08/2026 22:23</t>
+          <t>18/08/2026 03:48</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -771,7 +771,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0000521-43.2023.8.16.0122</t>
+          <t>0000855-53.2024.8.16.0151</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -781,27 +781,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins</t>
+          <t>Roubo Majorado</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>14/08/2026 21:43</t>
+          <t>17/08/2026 15:53</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>14/08/2026 21:43</t>
+          <t>17/08/2026 15:53</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>18/08/2026 13:13</t>
+          <t>18/08/2026 07:13</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -818,37 +818,37 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0000579-95.2025.8.16.0083</t>
+          <t>0000890-52.2009.8.16.0114</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Furto Qualificado</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>06/10/2023</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>14/08/2026 15:13</t>
+          <t>17/08/2026 14:43</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>14/08/2026 15:13</t>
+          <t>17/08/2026 14:43</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>18/08/2026 10:42</t>
+          <t>18/08/2026 08:14</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -865,37 +865,37 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0000625-04.2023.8.16.0100</t>
+          <t>0000929-14.2020.8.16.0001</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Usucapião Ordinária</t>
+          <t>Espécies de Contratos</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>10/12/2024</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>14/08/2026 20:33</t>
+          <t>17/08/2026 13:33</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>14/08/2026 20:33</t>
+          <t>17/08/2026 13:33</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>18/08/2026 10:44</t>
+          <t>18/08/2026 05:23</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -912,37 +912,37 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0000706-08.2025.8.16.0156</t>
+          <t>0000982-42.2013.8.16.0097</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Embargos de Divergência em Recurso Especial</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Produto Impróprio</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>19/06/2024</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>13/08/2026 14:03</t>
+          <t>17/08/2026 15:03</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>13/08/2026 14:03</t>
+          <t>17/08/2026 15:03</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>18/08/2026 13:26</t>
+          <t>18/08/2026 21:59</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0001042-23.2024.8.16.0196</t>
+          <t>0001217-92.2018.8.16.0142</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -969,27 +969,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Receptação Qualificada</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>14/08/2026 13:43</t>
+          <t>17/08/2026 18:53</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>14/08/2026 13:43</t>
+          <t>17/08/2026 18:53</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>19/08/2026 00:37</t>
+          <t>19/08/2026 02:19</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1006,37 +1006,37 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0001125-91.2024.8.16.0114</t>
+          <t>0001236-59.2021.8.16.0024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Receptação | Adulteração de Sinal Identificador de Veículo Automotor</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>19/09/2025</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>13/08/2026 20:43</t>
+          <t>18/08/2026 10:52</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>13/08/2026 20:43</t>
+          <t>18/08/2026 10:52</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>19/08/2026 02:36</t>
+          <t>19/08/2026 02:47</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1053,7 +1053,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0001165-69.2023.8.16.0159</t>
+          <t>0001611-17.2023.8.16.0048</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1063,27 +1063,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Fornecimento</t>
+          <t>Pagamento com Sub-rogação | Inexequibilidade do Título / Inexigibilidade da Obrigação</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>15/05/2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>14/08/2026 19:43</t>
+          <t>17/08/2026 13:23</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>14/08/2026 19:43</t>
+          <t>17/08/2026 13:23</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>18/08/2026 13:44</t>
+          <t>18/08/2026 11:31</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0001236-59.2021.8.16.0024</t>
+          <t>0001644-85.2024.8.16.0140</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1110,27 +1110,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Alienação Fiduciária</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>23/02/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>18/08/2026 10:52</t>
+          <t>17/08/2026 14:43</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>18/08/2026 10:52</t>
+          <t>17/08/2026 14:43</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>19/08/2026 02:47</t>
+          <t>18/08/2026 03:39</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1147,7 +1147,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0001373-33.2019.8.16.0017</t>
+          <t>0001893-39.2022.8.16.0097</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1162,22 +1162,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>13/08/2026 20:53</t>
+          <t>18/08/2026 16:13</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>13/08/2026 20:53</t>
+          <t>18/08/2026 16:13</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>19/08/2026 02:47</t>
+          <t>19/08/2026 03:41</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1194,37 +1194,37 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0001556-88.2013.8.16.0154</t>
+          <t>0002077-91.2021.8.16.0044</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Anulação de Débito Fiscal | Prescrição</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>13/12/2024</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>14/08/2026 17:43</t>
+          <t>17/08/2026 13:53</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>14/08/2026 17:43</t>
+          <t>17/08/2026 13:53</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>18/08/2026 12:52</t>
+          <t>18/08/2026 23:35</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1241,7 +1241,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0001593-15.2020.8.16.0108</t>
+          <t>0002099-57.2023.8.16.0149</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1251,27 +1251,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Erro Médico | Erro Médico</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>13/08/2026 16:43</t>
+          <t>17/08/2026 14:23</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>13/08/2026 16:43</t>
+          <t>17/08/2026 14:23</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>19/08/2026 00:37</t>
+          <t>18/08/2026 15:54</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1288,37 +1288,37 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0001652-58.2024.8.16.0109</t>
+          <t>0002143-33.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Homicídio Qualificado | Crime Tentado</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>12/08/2026 13:23</t>
+          <t>17/08/2026 16:33</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>12/08/2026 13:23</t>
+          <t>17/08/2026 16:33</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>18/08/2026 11:48</t>
+          <t>18/08/2026 04:35</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1335,7 +1335,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0001849-73.2024.8.16.0089</t>
+          <t>0002386-96.2009.8.16.0153</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1345,27 +1345,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>24/04/2025</t>
+          <t>27/01/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>14/08/2026 20:53</t>
+          <t>17/08/2026 13:33</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>14/08/2026 20:53</t>
+          <t>17/08/2026 13:33</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>18/08/2026 20:48</t>
+          <t>19/08/2026 02:47</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1382,7 +1382,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0001893-39.2022.8.16.0097</t>
+          <t>0002396-07.2022.8.16.0147</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1392,27 +1392,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Crimes de Trânsito</t>
+          <t>Oferta e Publicidade | Jogos / Sorteios / Promoções comerciais</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>18/08/2026 16:13</t>
+          <t>17/08/2026 16:53</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>18/08/2026 16:13</t>
+          <t>17/08/2026 16:53</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>19/08/2026 03:41</t>
+          <t>18/08/2026 20:48</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1429,37 +1429,37 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0001965-03.2025.8.16.0006</t>
+          <t>0002499-91.2019.8.16.0123</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Homicídio Qualificado</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>05/03/2024</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>14/08/2026 14:33</t>
+          <t>18/08/2026 13:43</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>14/08/2026 14:33</t>
+          <t>18/08/2026 13:43</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>18/08/2026 16:27</t>
+          <t>18/08/2026 17:07</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1476,7 +1476,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0002360-70.2019.8.16.0146</t>
+          <t>0002904-98.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1486,27 +1486,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Arrendamento Rural | Perdas e Danos</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>22/05/2024</t>
+          <t>06/03/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>14/08/2026 21:03</t>
+          <t>17/08/2026 15:13</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>14/08/2026 21:03</t>
+          <t>17/08/2026 15:13</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>18/08/2026 15:28</t>
+          <t>18/08/2026 11:32</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1523,7 +1523,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0002525-63.2015.8.16.0080</t>
+          <t>0002959-48.2022.8.16.0196</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1533,27 +1533,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Perigo para a vida ou saúde de outrem</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>14/08/2026 18:33</t>
+          <t>17/08/2026 17:43</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>14/08/2026 18:33</t>
+          <t>17/08/2026 17:43</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>18/08/2026 17:14</t>
+          <t>18/08/2026 11:44</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1570,37 +1570,37 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0002719-60.2025.8.16.0000</t>
+          <t>0002965-47.2022.8.16.0134</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Acidente de Trânsito</t>
+          <t>Pesca Ilegal</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>14/08/2026 19:53</t>
+          <t>17/08/2026 16:03</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>14/08/2026 19:53</t>
+          <t>17/08/2026 16:03</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>18/08/2026 16:14</t>
+          <t>18/08/2026 03:35</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1617,37 +1617,37 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0002961-64.2022.8.16.0019</t>
+          <t>0003260-92.2022.8.16.0196</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Crimes do Sistema Nacional de Armas</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>27/11/2024</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>12/08/2026 13:43</t>
+          <t>17/08/2026 17:43</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>12/08/2026 13:43</t>
+          <t>17/08/2026 17:43</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>18/08/2026 11:32</t>
+          <t>18/08/2026 16:29</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1664,7 +1664,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0002974-73.2012.8.16.0129</t>
+          <t>0003308-26.2020.8.16.0033</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1674,27 +1674,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Honorários Advocatícios | Pagamento do Débito | Cumprimento Provisório de Sentença</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>14/08/2026 16:13</t>
+          <t>17/08/2026 14:33</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>14/08/2026 16:13</t>
+          <t>17/08/2026 14:33</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>18/08/2026 23:34</t>
+          <t>18/08/2026 12:42</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0002976-93.2025.8.16.0159</t>
+          <t>0003385-13.2017.8.16.0139</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1721,27 +1721,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dano Qualificado contra a Administração Pública</t>
+          <t>Homicídio Qualificado</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>13/08/2026 20:53</t>
+          <t>17/08/2026 16:13</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>13/08/2026 20:53</t>
+          <t>17/08/2026 16:13</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>19/08/2026 03:21</t>
+          <t>18/08/2026 03:27</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1758,7 +1758,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0003154-89.2025.8.16.0014</t>
+          <t>0003523-75.2025.8.16.0146</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1773,22 +1773,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>13/08/2026 21:53</t>
+          <t>17/08/2026 20:03</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>13/08/2026 21:53</t>
+          <t>17/08/2026 20:03</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>18/08/2026 21:05</t>
+          <t>18/08/2026 04:49</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1805,37 +1805,37 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0003260-92.2022.8.16.0196</t>
+          <t>0003634-04.2025.8.16.0035</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Homicídio Qualificado</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>27/11/2024</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>17/08/2026 17:43</t>
+          <t>18/08/2026 16:43</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>17/08/2026 17:43</t>
+          <t>18/08/2026 16:43</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>18/08/2026 16:29</t>
+          <t>19/08/2026 04:08</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1852,37 +1852,37 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0003825-94.2025.8.16.0117</t>
+          <t>0003762-42.2019.8.16.0194</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Corrupção passiva</t>
+          <t>Obrigação de Fazer / Não Fazer</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>05/05/2022</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>13/08/2026 20:33</t>
+          <t>17/08/2026 14:13</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>13/08/2026 20:33</t>
+          <t>17/08/2026 14:13</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>18/08/2026 14:32</t>
+          <t>19/08/2026 02:36</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1899,7 +1899,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0004067-08.2022.8.16.0069</t>
+          <t>0003845-76.2024.8.16.0196</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1909,27 +1909,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação | Prescrição e Decadência</t>
+          <t>Roubo Majorado</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>30/01/2025</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>14/08/2026 15:03</t>
+          <t>17/08/2026 16:13</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>14/08/2026 15:03</t>
+          <t>17/08/2026 16:13</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>18/08/2026 12:27</t>
+          <t>18/08/2026 12:17</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1946,7 +1946,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0004410-05.2022.8.16.0004</t>
+          <t>0004167-78.2024.8.16.0105</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1956,27 +1956,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Equilíbrio Financeiro</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>17/08/2026 14:43</t>
+          <t>17/08/2026 15:43</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>17/08/2026 14:43</t>
+          <t>17/08/2026 15:43</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>18/08/2026 12:55</t>
+          <t>18/08/2026 07:30</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1993,37 +1993,37 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0004744-04.2024.8.16.0090</t>
+          <t>0004410-05.2022.8.16.0004</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Aplicação da Pena</t>
+          <t>Equilíbrio Financeiro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>13/08/2026 15:43</t>
+          <t>17/08/2026 14:43</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>13/08/2026 15:43</t>
+          <t>17/08/2026 14:43</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>18/08/2026 11:44</t>
+          <t>18/08/2026 12:55</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2040,37 +2040,37 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0004820-79.2022.8.16.0031</t>
+          <t>0004506-74.2024.8.16.0028</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Posse</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>17/08/2026 15:03</t>
+          <t>17/08/2026 17:53</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>17/08/2026 15:03</t>
+          <t>17/08/2026 17:53</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>18/08/2026 11:03</t>
+          <t>18/08/2026 03:27</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2087,37 +2087,37 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0005192-20.2021.8.16.0045</t>
+          <t>0004672-24.2019.8.16.0112</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Nomeação</t>
+          <t>Tráfico de Drogas e Condutas Afins | Crimes do Sistema Nacional de Armas</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>06/08/2025</t>
+          <t>22/02/2024</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>14/08/2026 15:33</t>
+          <t>17/08/2026 13:13</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>14/08/2026 15:33</t>
+          <t>17/08/2026 13:13</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>18/08/2026 16:48</t>
+          <t>18/08/2026 15:40</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2134,7 +2134,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0005407-05.2019.8.16.0194</t>
+          <t>0004820-79.2022.8.16.0031</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2144,27 +2144,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Locação de Imóvel</t>
+          <t>Posse</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>14/08/2026 13:33</t>
+          <t>17/08/2026 15:03</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>14/08/2026 13:33</t>
+          <t>17/08/2026 15:03</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>18/08/2026 13:44</t>
+          <t>18/08/2026 11:03</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2181,12 +2181,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0006707-23.2024.8.16.0098</t>
+          <t>0004851-22.2024.8.16.0034</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2196,22 +2196,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>03/02/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>13/08/2026 17:13</t>
+          <t>17/08/2026 18:33</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>13/08/2026 17:13</t>
+          <t>17/08/2026 18:33</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>18/08/2026 14:57</t>
+          <t>18/08/2026 14:27</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2228,37 +2228,37 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0007668-63.2023.8.16.0044</t>
+          <t>0004943-61.2022.8.16.0004</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>ISS/ Imposto sobre Serviços</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>13/08/2026 17:13</t>
+          <t>17/08/2026 15:25</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>13/08/2026 17:13</t>
+          <t>17/08/2026 15:25</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>18/08/2026 17:06</t>
+          <t>18/08/2026 05:23</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2275,7 +2275,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0007716-78.2022.8.16.0069</t>
+          <t>0005198-43.2019.8.16.0030</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2285,27 +2285,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Alienação Fiduciária</t>
+          <t>Mútuo</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>13/01/2025</t>
+          <t>22/10/2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>14/08/2026 20:03</t>
+          <t>17/08/2026 14:53</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>14/08/2026 20:03</t>
+          <t>17/08/2026 14:53</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>18/08/2026 13:42</t>
+          <t>18/08/2026 03:55</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2322,7 +2322,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0007773-25.2020.8.16.0083</t>
+          <t>0005981-44.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2332,27 +2332,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Furto</t>
+          <t>Compra e Venda</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>13/08/2026 19:13</t>
+          <t>17/08/2026 14:43</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>13/08/2026 19:13</t>
+          <t>17/08/2026 14:43</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>18/08/2026 14:32</t>
+          <t>18/08/2026 04:01</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2369,37 +2369,37 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0008905-80.2017.8.16.0000</t>
+          <t>0006265-81.2024.8.16.0090</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Pagamento Atrasado / Correção Monetária</t>
+          <t>Estelionato contra Idoso</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>12/03/2025</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>13/08/2026 15:43</t>
+          <t>17/08/2026 15:53</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>13/08/2026 15:43</t>
+          <t>17/08/2026 15:53</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>18/08/2026 13:38</t>
+          <t>19/08/2026 01:56</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2416,7 +2416,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0009238-08.2024.8.16.0058</t>
+          <t>0007237-51.2023.8.16.0069</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2426,27 +2426,27 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Roubo Majorado</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>13/08/2026 21:03</t>
+          <t>17/08/2026 16:13</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>13/08/2026 21:03</t>
+          <t>17/08/2026 16:13</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>18/08/2026 12:05</t>
+          <t>18/08/2026 04:35</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2463,7 +2463,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0009710-10.2025.8.16.0014</t>
+          <t>0008942-75.2022.8.16.0148</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2473,27 +2473,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Duplicata</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>13/08/2026 18:33</t>
+          <t>17/08/2026 14:33</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>13/08/2026 18:33</t>
+          <t>17/08/2026 14:33</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>19/08/2026 02:48</t>
+          <t>18/08/2026 06:41</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2557,7 +2557,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0010323-40.2023.8.16.0001</t>
+          <t>0010800-42.2018.8.16.0194</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2567,27 +2567,27 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>12/08/2026 14:53</t>
+          <t>18/08/2026 15:23</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>12/08/2026 14:53</t>
+          <t>18/08/2026 15:23</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>18/08/2026 14:24</t>
+          <t>18/08/2026 23:35</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2604,37 +2604,37 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0010998-38.2022.8.16.0033</t>
+          <t>0011816-50.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tratamento médico-hospitalar</t>
+          <t>Associação Criminosa | Adulteração de Sinal Identificador de Veículo Automotor | Desobediência | Prisão Preventiva</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>04/12/2025</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>14/08/2026 20:03</t>
+          <t>17/08/2026 13:23</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>14/08/2026 20:03</t>
+          <t>17/08/2026 13:23</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>19/08/2026 02:20</t>
+          <t>18/08/2026 03:43</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2651,7 +2651,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0011077-65.2022.8.16.0017</t>
+          <t>0012180-37.2017.8.16.0194</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2661,27 +2661,27 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Indenização por Dano Moral | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>15/01/2026</t>
+          <t>24/09/2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>13/08/2026 14:33</t>
+          <t>17/08/2026 13:03</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>13/08/2026 14:33</t>
+          <t>17/08/2026 13:03</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>18/08/2026 14:43</t>
+          <t>18/08/2026 19:20</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2698,37 +2698,37 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0011811-63.2021.8.16.0045</t>
+          <t>0014325-63.2017.8.16.0001</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Crimes Previstos no Estatuto do Idoso</t>
+          <t>Rescisão / Resolução | Perdas e Danos</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>03/07/2024</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>13/08/2026 17:13</t>
+          <t>18/08/2026 14:13</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>13/08/2026 17:13</t>
+          <t>18/08/2026 14:13</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>18/08/2026 21:37</t>
+          <t>18/08/2026 23:47</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2745,37 +2745,37 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0012180-37.2017.8.16.0194</t>
+          <t>0014915-64.2009.8.16.0019</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Indenização por Dano Material</t>
+          <t>Espécies de Títulos de Crédito | Cédula Hipotecária</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>24/09/2025</t>
+          <t>27/11/2020</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>17/08/2026 13:03</t>
+          <t>18/08/2026 14:23</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>17/08/2026 13:03</t>
+          <t>18/08/2026 14:23</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>18/08/2026 19:20</t>
+          <t>18/08/2026 20:21</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2792,7 +2792,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0012196-10.2025.8.16.0000</t>
+          <t>0016302-44.2023.8.16.0013</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2802,27 +2802,27 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Abuso de Poder | Defeito, nulidade ou anulação | Tutela de Evidência | Violação dos Princípios Administrativos | Cumprimento Provisório de Sentença | Legitimidade Ativa e Passiva</t>
+          <t>Crimes de Trânsito</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>14/08/2026 16:33</t>
+          <t>17/08/2026 18:33</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>14/08/2026 16:33</t>
+          <t>17/08/2026 18:33</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>18/08/2026 21:37</t>
+          <t>19/08/2026 02:36</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2839,7 +2839,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0012287-20.2023.8.16.0017</t>
+          <t>0018353-50.2022.8.16.0017</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2849,27 +2849,27 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>18/11/2025</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>14/08/2026 20:53</t>
+          <t>17/08/2026 15:23</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>14/08/2026 20:53</t>
+          <t>17/08/2026 15:23</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>19/08/2026 00:25</t>
+          <t>18/08/2026 23:35</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2886,37 +2886,37 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0012621-37.2025.8.16.0000</t>
+          <t>0018805-89.2024.8.16.0017</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Despesas Condominiais</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>14/08/2026 14:33</t>
+          <t>17/08/2026 20:33</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>14/08/2026 14:33</t>
+          <t>17/08/2026 20:33</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>18/08/2026 14:27</t>
+          <t>19/08/2026 03:30</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2933,37 +2933,37 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0015822-25.2021.8.16.0017</t>
+          <t>0018929-14.2006.8.16.0014</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Comissão</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>17/12/2025</t>
+          <t>23/05/2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>14/08/2026 14:43</t>
+          <t>17/08/2026 13:53</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>14/08/2026 14:43</t>
+          <t>17/08/2026 13:53</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>19/08/2026 02:20</t>
+          <t>18/08/2026 07:57</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2980,7 +2980,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0016302-44.2023.8.16.0013</t>
+          <t>0018976-80.2019.8.16.0030</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2990,27 +2990,27 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Crimes de Trânsito</t>
+          <t>Práticas Abusivas</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>17/08/2026 18:33</t>
+          <t>17/08/2026 15:03</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>17/08/2026 18:33</t>
+          <t>17/08/2026 15:03</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>19/08/2026 02:36</t>
+          <t>18/08/2026 22:21</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3027,37 +3027,37 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0016776-75.2024.8.16.0014</t>
+          <t>0019003-57.2023.8.16.0019</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Plano de Saúde</t>
+          <t>Tráfico de Drogas e Condutas Afins | Desclassificação</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>02/10/2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>12/08/2026 14:03</t>
+          <t>17/08/2026 18:53</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>12/08/2026 14:03</t>
+          <t>17/08/2026 18:53</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>19/08/2026 02:48</t>
+          <t>19/08/2026 03:12</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3074,7 +3074,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0018604-92.2023.8.16.0030</t>
+          <t>0019271-25.2006.8.16.0014</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3084,27 +3084,27 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Dever de Informação</t>
+          <t>Tratamento médico-hospitalar | Obrigação de Fazer / Não Fazer | Fornecimento de insumos</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>30/12/1899</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>12/08/2026 13:13</t>
+          <t>18/08/2026 14:23</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>12/08/2026 13:13</t>
+          <t>18/08/2026 14:23</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>18/08/2026 13:44</t>
+          <t>18/08/2026 23:35</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3121,37 +3121,37 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0019003-57.2023.8.16.0019</t>
+          <t>0020939-43.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Desclassificação</t>
+          <t>Cobrança | Negativa de Prestação Jurisdicional | Cerceamento de Defesa</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>02/10/2025</t>
+          <t>12/08/2025</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>17/08/2026 18:53</t>
+          <t>17/08/2026 14:13</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>17/08/2026 18:53</t>
+          <t>17/08/2026 14:13</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>19/08/2026 03:12</t>
+          <t>18/08/2026 03:37</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3262,37 +3262,37 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0023966-78.2018.8.16.0021</t>
+          <t>0026052-12.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Inclusão Indevida em Cadastro de Inadimplentes</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>25/08/2025</t>
+          <t>05/08/2024</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>14/08/2026 16:43</t>
+          <t>17/08/2026 14:13</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>14/08/2026 16:43</t>
+          <t>17/08/2026 14:13</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>18/08/2026 20:48</t>
+          <t>18/08/2026 13:26</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3309,7 +3309,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0024261-64.2025.8.16.0185</t>
+          <t>0029973-10.2022.8.16.0001</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3319,27 +3319,27 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>Previdência privada</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>14/08/2026 19:23</t>
+          <t>17/08/2026 15:13</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>14/08/2026 19:23</t>
+          <t>17/08/2026 15:13</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>18/08/2026 13:56</t>
+          <t>18/08/2026 19:09</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3356,7 +3356,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0025658-39.2023.8.16.0021</t>
+          <t>0030073-94.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3366,27 +3366,27 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Crimes do Sistema Nacional de Armas</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/02/2025</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>14/08/2026 14:33</t>
+          <t>17/08/2026 16:43</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>14/08/2026 14:33</t>
+          <t>17/08/2026 16:43</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>18/08/2026 23:34</t>
+          <t>18/08/2026 12:27</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3403,37 +3403,37 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0026752-14.2021.8.16.0014</t>
+          <t>0030192-26.2018.8.16.0013</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Embargos de Divergência em Recurso Especial</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Pagamento</t>
+          <t>Roubo Majorado</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>21/08/2024</t>
+          <t>13/10/2022</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>14/08/2026 15:43</t>
+          <t>17/08/2026 13:23</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>14/08/2026 15:43</t>
+          <t>17/08/2026 13:23</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>19/08/2026 02:48</t>
+          <t>18/08/2026 03:55</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3450,37 +3450,37 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0028518-34.2023.8.16.0014</t>
+          <t>0035479-62.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Práticas Abusivas</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>19/08/2025</t>
+          <t>19/03/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>13/08/2026 16:43</t>
+          <t>17/08/2026 14:23</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>13/08/2026 16:43</t>
+          <t>17/08/2026 14:23</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>19/08/2026 03:21</t>
+          <t>18/08/2026 08:47</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3497,7 +3497,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0028981-20.2017.8.16.0035</t>
+          <t>0038200-18.2024.8.16.0001</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3507,27 +3507,27 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Roubo Majorado</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>13/08/2026 21:53</t>
+          <t>17/08/2026 15:23</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>13/08/2026 21:53</t>
+          <t>17/08/2026 15:23</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>19/08/2026 00:16</t>
+          <t>18/08/2026 15:54</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3544,37 +3544,37 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0030192-26.2018.8.16.0013</t>
+          <t>0039901-46.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Embargos de Divergência em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Roubo Majorado</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>13/10/2022</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>17/08/2026 13:23</t>
+          <t>17/08/2026 16:33</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>17/08/2026 13:23</t>
+          <t>17/08/2026 16:33</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>18/08/2026 03:55</t>
+          <t>18/08/2026 12:42</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3591,37 +3591,37 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0032218-94.2023.8.16.0021</t>
+          <t>0040013-83.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Crimes do Sistema Nacional de Armas | Receptação</t>
+          <t>Locação de Móvel</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>13/08/2026 16:33</t>
+          <t>18/08/2026 14:13</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>13/08/2026 16:33</t>
+          <t>18/08/2026 14:13</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>19/08/2026 02:14</t>
+          <t>19/08/2026 03:30</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3638,7 +3638,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0032747-79.2023.8.16.0000</t>
+          <t>0041319-84.2024.8.16.0001</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3648,27 +3648,27 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bens Públicos</t>
+          <t>Ingresso e Exclusão dos Sócios na Sociedade</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>14/10/2025</t>
+          <t>26/05/2025</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>13/08/2026 18:03</t>
+          <t>17/08/2026 13:13</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>13/08/2026 18:03</t>
+          <t>17/08/2026 13:13</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>18/08/2026 11:43</t>
+          <t>18/08/2026 16:27</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3685,7 +3685,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0035638-22.2019.8.16.0030</t>
+          <t>0043199-72.2024.8.16.0014</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3695,27 +3695,27 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Receptação Qualificada</t>
+          <t>Furto Qualificado</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>13/11/2025</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>13/08/2026 16:43</t>
+          <t>17/08/2026 18:33</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>13/08/2026 16:43</t>
+          <t>17/08/2026 18:33</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>18/08/2026 21:37</t>
+          <t>19/08/2026 02:59</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3732,37 +3732,37 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0036039-38.2024.8.16.0000</t>
+          <t>0044188-91.2022.8.16.0000</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Servidão Administrativa</t>
+          <t>Cédula Hipotecária</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>14/02/2024</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>12/08/2026 14:23</t>
+          <t>17/08/2026 13:33</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>12/08/2026 14:23</t>
+          <t>17/08/2026 13:33</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>18/08/2026 11:03</t>
+          <t>18/08/2026 11:22</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3779,37 +3779,37 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0037335-61.2025.8.16.0000</t>
+          <t>0046238-58.2024.8.16.0182</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Pedido de Uniformização de Interpretação de Lei Criminal</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Limitação de Juros</t>
+          <t>Residência Médica | Programas de Bolsas e Financiamento Estudantil com Recursos Públicos</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>03/04/2025</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>12/08/2026 15:03</t>
+          <t>18/08/2026 01:57</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>12/08/2026 15:03</t>
+          <t>18/08/2026 01:57</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>19/08/2026 03:21</t>
+          <t>18/08/2026 14:27</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3826,37 +3826,37 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0038454-62.2022.8.16.0000</t>
+          <t>0051721-96.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Direitos / Deveres do Condômino</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>03/10/2023</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>14/08/2026 13:03</t>
+          <t>18/08/2026 14:13</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>14/08/2026 13:03</t>
+          <t>18/08/2026 14:13</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>19/08/2026 04:12</t>
+          <t>19/08/2026 02:59</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3873,37 +3873,37 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0039374-82.2012.8.16.0001</t>
+          <t>0052981-77.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Auxílio-Doença Acidentário</t>
+          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>05/06/2025</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>14/08/2026 15:03</t>
+          <t>17/08/2026 17:34</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>14/08/2026 15:03</t>
+          <t>17/08/2026 17:34</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>18/08/2026 12:55</t>
+          <t>18/08/2026 03:36</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3920,7 +3920,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0041319-84.2024.8.16.0001</t>
+          <t>0057175-91.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3930,12 +3930,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Ingresso e Exclusão dos Sócios na Sociedade</t>
+          <t>Vícios de Construção | Assistência Judiciária Gratuita</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>26/05/2025</t>
+          <t>27/01/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>18/08/2026 16:27</t>
+          <t>18/08/2026 17:27</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3967,37 +3967,37 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0042997-32.2023.8.16.0014</t>
+          <t>0061924-46.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Roubo Majorado</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>13/08/2026 13:58</t>
+          <t>17/08/2026 18:23</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>13/08/2026 13:58</t>
+          <t>17/08/2026 18:23</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>18/08/2026 16:14</t>
+          <t>19/08/2026 03:12</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -4014,37 +4014,37 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0046238-58.2024.8.16.0182</t>
+          <t>0062940-43.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Pedido de Uniformização de Interpretação de Lei Criminal</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Residência Médica | Programas de Bolsas e Financiamento Estudantil com Recursos Públicos</t>
+          <t>Dissolução</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>03/04/2025</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>18/08/2026 01:57</t>
+          <t>17/08/2026 14:23</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>18/08/2026 01:57</t>
+          <t>17/08/2026 14:23</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>18/08/2026 14:27</t>
+          <t>18/08/2026 15:33</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4061,37 +4061,37 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0049454-20.2026.8.16.0000</t>
+          <t>0064838-91.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Prisão Preventiva | Tráfico de Drogas e Condutas Afins</t>
+          <t>Servidores Inativos | Requisição de Pequeno Valor - RPV</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>23/02/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>13/08/2026 17:33</t>
+          <t>17/08/2026 14:03</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>13/08/2026 17:33</t>
+          <t>17/08/2026 14:03</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>19/08/2026 02:36</t>
+          <t>18/08/2026 13:13</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -4108,7 +4108,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0050711-80.2026.8.16.0000</t>
+          <t>0065092-93.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4118,27 +4118,27 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Homicídio Qualificado | Crime Tentado</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>13/08/2026 17:13</t>
+          <t>17/08/2026 18:43</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>13/08/2026 17:13</t>
+          <t>17/08/2026 18:43</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>19/08/2026 02:47</t>
+          <t>18/08/2026 10:25</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4155,37 +4155,37 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0059258-46.2025.8.16.0000</t>
+          <t>0065776-52.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Descontos Indevidos</t>
+          <t>Ameaça | Prisão Preventiva | Violação de domicílio</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>29/09/2025</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>13/08/2026 19:33</t>
+          <t>18/08/2026 16:13</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>13/08/2026 19:33</t>
+          <t>18/08/2026 16:13</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>18/08/2026 03:55</t>
+          <t>19/08/2026 02:52</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4202,7 +4202,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0060424-79.2026.8.16.0000</t>
+          <t>0066120-96.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4217,22 +4217,22 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>12/08/2026 09:26</t>
+          <t>17/08/2026 17:13</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>12/08/2026 09:26</t>
+          <t>17/08/2026 17:13</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>19/08/2026 00:37</t>
+          <t>18/08/2026 11:44</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4249,37 +4249,37 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0064158-64.2024.8.16.0014</t>
+          <t>0068649-22.2021.8.16.0014</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Inventário e Partilha | Bem de Família Legal</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>14/10/2025</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>13/08/2026 14:33</t>
+          <t>17/08/2026 13:33</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>13/08/2026 14:33</t>
+          <t>17/08/2026 13:33</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>18/08/2026 11:03</t>
+          <t>18/08/2026 13:38</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4296,7 +4296,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0064838-91.2024.8.16.0000</t>
+          <t>0073315-32.2022.8.16.0014</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4306,27 +4306,27 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Servidores Inativos | Requisição de Pequeno Valor - RPV</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>23/02/2026</t>
+          <t>13/01/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>17/08/2026 14:03</t>
+          <t>17/08/2026 13:53</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>17/08/2026 14:03</t>
+          <t>17/08/2026 13:53</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>18/08/2026 13:13</t>
+          <t>18/08/2026 12:05</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4343,37 +4343,37 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0065092-93.2026.8.16.0000</t>
+          <t>0074360-45.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Homicídio Qualificado | Crime Tentado</t>
+          <t>Dívida Ativa (Execução Fiscal) | Citação</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>17/08/2026 18:43</t>
+          <t>17/08/2026 14:43</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>17/08/2026 18:43</t>
+          <t>17/08/2026 14:43</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>18/08/2026 10:25</t>
+          <t>18/08/2026 18:32</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4390,7 +4390,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0065469-61.2022.8.16.0014</t>
+          <t>0077298-13.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4400,27 +4400,27 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação</t>
+          <t>Dano ao Erário</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>20/10/2025</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>12/08/2026 13:53</t>
+          <t>17/08/2026 16:53</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>12/08/2026 13:53</t>
+          <t>17/08/2026 16:53</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>18/08/2026 15:43</t>
+          <t>18/08/2026 03:50</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4437,7 +4437,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0066120-96.2026.8.16.0000</t>
+          <t>0083631-10.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4447,27 +4447,27 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Tráfico de Drogas e Condutas Afins | Resistência</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>17/08/2026 17:13</t>
+          <t>17/08/2026 16:13</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>17/08/2026 17:13</t>
+          <t>17/08/2026 16:13</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>18/08/2026 11:44</t>
+          <t>18/08/2026 04:53</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4484,7 +4484,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0068649-22.2021.8.16.0014</t>
+          <t>0084281-28.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4494,27 +4494,27 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Inventário e Partilha | Bem de Família Legal</t>
+          <t>Liquidação</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>14/10/2025</t>
+          <t>13/02/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>17/08/2026 13:33</t>
+          <t>17/08/2026 14:43</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>17/08/2026 13:33</t>
+          <t>17/08/2026 14:43</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>18/08/2026 13:38</t>
+          <t>19/08/2026 04:07</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4531,37 +4531,37 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0070705-31.2025.8.16.0000</t>
+          <t>0089924-98.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Embargos de Divergência em Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Condomínio</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>24/04/2025</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>14/08/2026 18:03</t>
+          <t>17/08/2026 14:03</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>14/08/2026 18:03</t>
+          <t>17/08/2026 14:03</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>18/08/2026 10:26</t>
+          <t>18/08/2026 17:06</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4578,7 +4578,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0088421-71.2025.8.16.0000</t>
+          <t>0091213-32.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4588,27 +4588,27 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Recuperação judicial e Falência</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>13/08/2026 18:23</t>
+          <t>17/08/2026 14:33</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>13/08/2026 18:23</t>
+          <t>17/08/2026 14:33</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20/08/2026 22:45</t>
+          <t>18/08/2026 10:29</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4625,37 +4625,37 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0088933-88.2024.8.16.0000</t>
+          <t>0093139-77.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Multas e demais Sanções</t>
+          <t>Seqüestro e cárcere privado | Crimes de Tortura | Lesão Cometida em Razão da Condição de Mulher | Ameaça</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>14/08/2026 20:33</t>
+          <t>17/08/2026 17:23</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>14/08/2026 20:33</t>
+          <t>17/08/2026 17:23</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>18/08/2026 16:27</t>
+          <t>18/08/2026 22:58</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4672,37 +4672,37 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0093139-77.2026.8.16.0000</t>
+          <t>0094754-39.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Seqüestro e cárcere privado | Crimes de Tortura | Lesão Cometida em Razão da Condição de Mulher | Ameaça</t>
+          <t>Peculato</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>17/08/2026 17:23</t>
+          <t>17/08/2026 15:53</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>17/08/2026 17:23</t>
+          <t>17/08/2026 15:53</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>18/08/2026 22:58</t>
+          <t>18/08/2026 15:11</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4719,7 +4719,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0094754-39.2025.8.16.0000</t>
+          <t>0099048-08.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4729,27 +4729,27 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Peculato</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>04/10/2024</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>17/08/2026 15:53</t>
+          <t>18/08/2026 13:13</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>17/08/2026 15:53</t>
+          <t>18/08/2026 13:13</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>18/08/2026 15:11</t>
+          <t>19/08/2026 00:46</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4766,7 +4766,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0109747-58.2023.8.16.0000</t>
+          <t>0106494-28.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4776,27 +4776,27 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>08/12/2025</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>14/08/2026 18:33</t>
+          <t>17/08/2026 13:33</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>14/08/2026 18:33</t>
+          <t>17/08/2026 13:33</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>19/08/2026 02:20</t>
+          <t>18/08/2026 12:05</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4813,37 +4813,37 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0122142-48.2024.8.16.0000</t>
+          <t>0108328-32.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Desapropriação | Imissão na Posse</t>
+          <t>Latrocínio</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>12/08/2026 13:13</t>
+          <t>17/08/2026 17:53</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>12/08/2026 13:13</t>
+          <t>17/08/2026 17:53</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>18/08/2026 23:47</t>
+          <t>18/08/2026 09:15</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4860,7 +4860,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0124840-27.2024.8.16.0000</t>
+          <t>0111584-17.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4870,27 +4870,27 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação</t>
+          <t>Seguro | Honorários Advocatícios | Provas</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>02/03/2026</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>14/08/2026 07:29</t>
+          <t>17/08/2026 13:23</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>14/08/2026 07:29</t>
+          <t>17/08/2026 13:23</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>18/08/2026 20:48</t>
+          <t>18/08/2026 09:30</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4954,37 +4954,37 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0127459-90.2025.8.16.0000</t>
+          <t>0130983-32.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins | Prisão Preventiva</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>13/08/2026 20:53</t>
+          <t>17/08/2026 14:23</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>13/08/2026 20:53</t>
+          <t>17/08/2026 14:23</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>19/08/2026 02:20</t>
+          <t>18/08/2026 03:39</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -5001,37 +5001,37 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0131195-19.2025.8.16.0000</t>
+          <t>0142492-23.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Associação para a Produção e Tráfico e Condutas Afins | Prisão Preventiva</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>13/08/2026 21:53</t>
+          <t>17/08/2026 18:03</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>13/08/2026 21:53</t>
+          <t>17/08/2026 18:03</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>18/08/2026 12:05</t>
+          <t>18/08/2026 04:02</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -5048,37 +5048,37 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0152011-22.2025.8.16.0000</t>
+          <t>4002176-24.2025.8.16.4321</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Decorrente de Violência Doméstica | Injúria | Dano | Ameaça</t>
+          <t>Progressão de Regime</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>13/08/2026 21:03</t>
+          <t>18/08/2026 16:03</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>13/08/2026 21:03</t>
+          <t>18/08/2026 16:03</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>18/08/2026 11:17</t>
+          <t>19/08/2026 02:18</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -5095,7 +5095,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>4002176-24.2025.8.16.4321</t>
+          <t>4006248-54.2025.8.16.4321</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -5105,27 +5105,27 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Progressão de Regime</t>
+          <t>Progressão de Regime | Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>18/08/2026 16:03</t>
+          <t>17/08/2026 16:33</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>18/08/2026 16:03</t>
+          <t>17/08/2026 16:33</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>19/08/2026 02:18</t>
+          <t>18/08/2026 03:35</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">

--- a/docs/resultados.xlsx
+++ b/docs/resultados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I100"/>
+  <dimension ref="A1:I101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -489,37 +489,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0000022-19.1988.8.16.0047</t>
+          <t>0002529-36.2021.8.16.0098</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bancários</t>
+          <t>Dever de Informação | Irregularidade no atendimento</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>19/08/2024</t>
+          <t>02/08/2024</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>17/08/2026 13:03</t>
+          <t>31/08/2026 11:38</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>17/08/2026 13:03</t>
+          <t>31/08/2026 11:38</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>19/08/2026 00:42</t>
+          <t>10/09/2026 21:14</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -536,7 +536,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0000033-52.2025.8.16.0079</t>
+          <t>0008017-50.2023.8.16.0017</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -546,27 +546,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação</t>
+          <t>Locação de Imóvel | Embargos de Terceiro</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>10/12/2025</t>
+          <t>29/01/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>17/08/2026 13:13</t>
+          <t>25/08/2026 17:43</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17/08/2026 13:13</t>
+          <t>25/08/2026 17:43</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>18/08/2026 16:46</t>
+          <t>10/09/2026 21:14</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -583,12 +583,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0000174-98.2020.8.16.0062</t>
+          <t>0022909-70.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -598,22 +598,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/09/2024</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>17/08/2026 18:03</t>
+          <t>27/08/2026 15:59</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>17/08/2026 18:03</t>
+          <t>27/08/2026 15:59</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>18/08/2026 23:33</t>
+          <t>10/09/2026 21:14</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,7 +630,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0000576-36.2025.8.16.0053</t>
+          <t>0109932-62.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -640,27 +640,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Promessa de Compra e Venda | Rescisão / Resolução</t>
+          <t>Prescrição e Decadência</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>10/04/2025</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17/08/2026 13:23</t>
+          <t>24/08/2026 16:53</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>17/08/2026 13:23</t>
+          <t>24/08/2026 16:53</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>18/08/2026 08:14</t>
+          <t>10/09/2026 21:16</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -677,37 +677,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0000627-67.2022.8.16.0048</t>
+          <t>0005311-55.2024.8.16.0148</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Práticas Abusivas</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>02/09/2024</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>17/08/2026 13:53</t>
+          <t>28/08/2026 15:13</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>17/08/2026 13:53</t>
+          <t>28/08/2026 15:13</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>18/08/2026 05:35</t>
+          <t>10/09/2026 21:16</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -724,7 +724,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0000804-49.2022.8.16.0139</t>
+          <t>0000245-29.2022.8.16.0160</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -734,27 +734,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Violência Psicológica contra a Mulher | Regime inicial | Prova Ilícita | Cerceamento de Defesa</t>
+          <t>Contratos Bancários | Perdas e Danos | Cerceamento de Defesa | Provas | Obrigação de Entregar</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>17/08/2026 15:33</t>
+          <t>10/09/2026 15:23</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>17/08/2026 15:33</t>
+          <t>10/09/2026 15:23</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>18/08/2026 03:48</t>
+          <t>10/09/2026 21:24</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -771,37 +771,37 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0000855-53.2024.8.16.0151</t>
+          <t>0000627-67.2022.8.16.0048</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Roubo Majorado</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>02/09/2024</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>17/08/2026 15:53</t>
+          <t>17/08/2026 13:53</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>17/08/2026 15:53</t>
+          <t>17/08/2026 13:53</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>18/08/2026 07:13</t>
+          <t>10/09/2026 21:29</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -818,7 +818,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0000890-52.2009.8.16.0114</t>
+          <t>0081354-89.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -828,27 +828,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Indenização por Dano Moral | Penhora / Depósito/ Avaliação | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>06/10/2023</t>
+          <t>26/09/2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>17/08/2026 14:43</t>
+          <t>31/08/2026 16:43</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>17/08/2026 14:43</t>
+          <t>31/08/2026 16:43</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>18/08/2026 08:14</t>
+          <t>10/09/2026 21:29</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -865,37 +865,37 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0000929-14.2020.8.16.0001</t>
+          <t>0065092-93.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Espécies de Contratos</t>
+          <t>Homicídio Qualificado | Crime Tentado</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>10/12/2024</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>17/08/2026 13:33</t>
+          <t>17/08/2026 18:43</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>17/08/2026 13:33</t>
+          <t>17/08/2026 18:43</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>18/08/2026 05:23</t>
+          <t>18/08/2026 10:25</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -912,22 +912,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0000982-42.2013.8.16.0097</t>
+          <t>0004820-79.2022.8.16.0031</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Embargos de Divergência em Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Produto Impróprio</t>
+          <t>Posse</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>19/06/2024</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>18/08/2026 21:59</t>
+          <t>18/08/2026 11:03</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -959,37 +959,37 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0001217-92.2018.8.16.0142</t>
+          <t>0066120-96.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Receptação Qualificada</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>17/08/2026 18:53</t>
+          <t>17/08/2026 17:13</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>17/08/2026 18:53</t>
+          <t>17/08/2026 17:13</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>19/08/2026 02:19</t>
+          <t>18/08/2026 11:44</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1006,7 +1006,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0001236-59.2021.8.16.0024</t>
+          <t>0004410-05.2022.8.16.0004</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1016,27 +1016,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Equilíbrio Financeiro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>18/08/2026 10:52</t>
+          <t>17/08/2026 14:43</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>18/08/2026 10:52</t>
+          <t>17/08/2026 14:43</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>19/08/2026 02:47</t>
+          <t>18/08/2026 12:55</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1053,7 +1053,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0001611-17.2023.8.16.0048</t>
+          <t>0023731-33.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1063,27 +1063,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Pagamento com Sub-rogação | Inexequibilidade do Título / Inexigibilidade da Obrigação</t>
+          <t>Indenização por Dano Moral | Liminar | Adequação da Ação / Procedimento</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>15/05/2025</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>17/08/2026 13:23</t>
+          <t>17/08/2026 14:53</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>17/08/2026 13:23</t>
+          <t>17/08/2026 14:53</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>18/08/2026 11:31</t>
+          <t>18/08/2026 13:02</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0001644-85.2024.8.16.0140</t>
+          <t>0064838-91.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Alienação Fiduciária</t>
+          <t>Servidores Inativos | Requisição de Pequeno Valor - RPV</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1120,17 +1120,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>17/08/2026 14:43</t>
+          <t>17/08/2026 14:03</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>17/08/2026 14:43</t>
+          <t>17/08/2026 14:03</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>18/08/2026 03:39</t>
+          <t>18/08/2026 13:13</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1147,7 +1147,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0001893-39.2022.8.16.0097</t>
+          <t>0068649-22.2021.8.16.0014</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1157,27 +1157,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Crimes de Trânsito</t>
+          <t>Inventário e Partilha | Bem de Família Legal</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>14/10/2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>18/08/2026 16:13</t>
+          <t>17/08/2026 13:33</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>18/08/2026 16:13</t>
+          <t>17/08/2026 13:33</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>19/08/2026 03:41</t>
+          <t>18/08/2026 13:38</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1194,37 +1194,37 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0002077-91.2021.8.16.0044</t>
+          <t>0046238-58.2024.8.16.0182</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Pedido de Uniformização de Interpretação de Lei Criminal</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Residência Médica | Programas de Bolsas e Financiamento Estudantil com Recursos Públicos</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>13/12/2024</t>
+          <t>03/04/2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>17/08/2026 13:53</t>
+          <t>18/08/2026 01:57</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>17/08/2026 13:53</t>
+          <t>18/08/2026 01:57</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>18/08/2026 23:35</t>
+          <t>18/08/2026 14:27</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1241,7 +1241,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0002099-57.2023.8.16.0149</t>
+          <t>0094754-39.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1251,27 +1251,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Peculato</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>17/08/2026 14:23</t>
+          <t>17/08/2026 15:53</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>17/08/2026 14:23</t>
+          <t>17/08/2026 15:53</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>18/08/2026 15:54</t>
+          <t>18/08/2026 15:11</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1288,37 +1288,37 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0002143-33.2026.8.16.0000</t>
+          <t>0041319-84.2024.8.16.0001</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Homicídio Qualificado | Crime Tentado</t>
+          <t>Ingresso e Exclusão dos Sócios na Sociedade</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>26/05/2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>17/08/2026 16:33</t>
+          <t>17/08/2026 13:13</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>17/08/2026 16:33</t>
+          <t>17/08/2026 13:13</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>18/08/2026 04:35</t>
+          <t>18/08/2026 16:27</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1335,37 +1335,37 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0002386-96.2009.8.16.0153</t>
+          <t>0003260-92.2022.8.16.0196</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>27/01/2026</t>
+          <t>27/11/2024</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>17/08/2026 13:33</t>
+          <t>17/08/2026 17:43</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>17/08/2026 13:33</t>
+          <t>17/08/2026 17:43</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>19/08/2026 02:47</t>
+          <t>18/08/2026 16:29</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1382,7 +1382,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0002396-07.2022.8.16.0147</t>
+          <t>0010296-65.2020.8.16.0194</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1392,27 +1392,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Oferta e Publicidade | Jogos / Sorteios / Promoções comerciais</t>
+          <t>Práticas Abusivas | Rescisão do contrato e devolução do dinheiro | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>17/08/2026 16:53</t>
+          <t>17/08/2026 14:23</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>17/08/2026 16:53</t>
+          <t>17/08/2026 14:23</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>18/08/2026 20:48</t>
+          <t>18/08/2026 16:41</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1429,37 +1429,37 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0002499-91.2019.8.16.0123</t>
+          <t>0000033-52.2025.8.16.0079</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>05/03/2024</t>
+          <t>10/12/2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>18/08/2026 13:43</t>
+          <t>17/08/2026 13:13</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>18/08/2026 13:43</t>
+          <t>17/08/2026 13:13</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>18/08/2026 17:07</t>
+          <t>18/08/2026 16:46</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1476,7 +1476,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0002904-98.2025.8.16.0000</t>
+          <t>0029973-10.2022.8.16.0001</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Previdência privada</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>18/08/2026 11:32</t>
+          <t>18/08/2026 19:09</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1523,7 +1523,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0002959-48.2022.8.16.0196</t>
+          <t>0012180-37.2017.8.16.0194</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1533,27 +1533,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Perigo para a vida ou saúde de outrem</t>
+          <t>Indenização por Dano Moral | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>24/09/2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>17/08/2026 17:43</t>
+          <t>17/08/2026 13:03</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>17/08/2026 17:43</t>
+          <t>17/08/2026 13:03</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>18/08/2026 11:44</t>
+          <t>18/08/2026 19:20</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1570,37 +1570,37 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0002965-47.2022.8.16.0134</t>
+          <t>0093139-77.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Pesca Ilegal</t>
+          <t>Seqüestro e cárcere privado | Crimes de Tortura | Lesão Cometida em Razão da Condição de Mulher | Ameaça</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>17/08/2026 16:03</t>
+          <t>17/08/2026 17:23</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>17/08/2026 16:03</t>
+          <t>17/08/2026 17:23</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>18/08/2026 03:35</t>
+          <t>18/08/2026 22:58</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1617,12 +1617,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0003260-92.2022.8.16.0196</t>
+          <t>0000174-98.2020.8.16.0062</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1632,22 +1632,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>27/11/2024</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>17/08/2026 17:43</t>
+          <t>17/08/2026 18:03</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>17/08/2026 17:43</t>
+          <t>17/08/2026 18:03</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>18/08/2026 16:29</t>
+          <t>18/08/2026 23:33</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1664,7 +1664,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0003308-26.2020.8.16.0033</t>
+          <t>0126623-54.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1674,27 +1674,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>17/08/2026 14:33</t>
+          <t>17/08/2026 15:13</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>17/08/2026 14:33</t>
+          <t>17/08/2026 15:13</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>18/08/2026 12:42</t>
+          <t>19/08/2026 00:37</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0003385-13.2017.8.16.0139</t>
+          <t>0000022-19.1988.8.16.0047</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1721,27 +1721,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Homicídio Qualificado</t>
+          <t>Bancários</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>19/08/2024</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>17/08/2026 16:13</t>
+          <t>17/08/2026 13:03</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>17/08/2026 16:13</t>
+          <t>17/08/2026 13:03</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>18/08/2026 03:27</t>
+          <t>19/08/2026 00:42</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1758,37 +1758,37 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0003523-75.2025.8.16.0146</t>
+          <t>4002176-24.2025.8.16.4321</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Progressão de Regime</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>17/08/2026 20:03</t>
+          <t>18/08/2026 16:03</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>17/08/2026 20:03</t>
+          <t>18/08/2026 16:03</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>18/08/2026 04:49</t>
+          <t>19/08/2026 02:18</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1805,7 +1805,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0003634-04.2025.8.16.0035</t>
+          <t>0016302-44.2023.8.16.0013</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1815,27 +1815,27 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Homicídio Qualificado</t>
+          <t>Crimes de Trânsito</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>18/08/2026 16:43</t>
+          <t>17/08/2026 18:33</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>18/08/2026 16:43</t>
+          <t>17/08/2026 18:33</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>19/08/2026 04:08</t>
+          <t>19/08/2026 02:36</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1852,37 +1852,37 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0003762-42.2019.8.16.0194</t>
+          <t>0001236-59.2021.8.16.0024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Obrigação de Fazer / Não Fazer</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>05/05/2022</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>17/08/2026 14:13</t>
+          <t>18/08/2026 10:52</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>17/08/2026 14:13</t>
+          <t>18/08/2026 10:52</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>19/08/2026 02:36</t>
+          <t>19/08/2026 02:47</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1899,37 +1899,37 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0003845-76.2024.8.16.0196</t>
+          <t>0019003-57.2023.8.16.0019</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Roubo Majorado</t>
+          <t>Tráfico de Drogas e Condutas Afins | Desclassificação</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>02/10/2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>17/08/2026 16:13</t>
+          <t>17/08/2026 18:53</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>17/08/2026 16:13</t>
+          <t>17/08/2026 18:53</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>18/08/2026 12:17</t>
+          <t>19/08/2026 03:12</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1946,7 +1946,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0004167-78.2024.8.16.0105</t>
+          <t>0001893-39.2022.8.16.0097</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1956,27 +1956,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Crimes de Trânsito</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>17/08/2026 15:43</t>
+          <t>18/08/2026 16:13</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>17/08/2026 15:43</t>
+          <t>18/08/2026 16:13</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>18/08/2026 07:30</t>
+          <t>19/08/2026 03:41</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0004410-05.2022.8.16.0004</t>
+          <t>0021603-50.2020.8.16.0021</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2003,27 +2003,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Equilíbrio Financeiro</t>
+          <t>Locação de Imóvel</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>17/08/2026 14:43</t>
+          <t>17/08/2026 14:53</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>17/08/2026 14:43</t>
+          <t>17/08/2026 14:53</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>18/08/2026 12:55</t>
+          <t>20/08/2026 22:45</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2040,37 +2040,37 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0004506-74.2024.8.16.0028</t>
+          <t>0008652-53.2021.8.16.0000</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Administração judicial</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>01/10/2025</t>
+          <t>20/07/2022</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>17/08/2026 17:53</t>
+          <t>04/09/2026 13:13</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>17/08/2026 17:53</t>
+          <t>04/09/2026 13:13</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>18/08/2026 03:27</t>
+          <t>07/09/2026 14:45</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2087,37 +2087,37 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0004672-24.2019.8.16.0112</t>
+          <t>0017529-91.2012.8.16.0001</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Crimes do Sistema Nacional de Armas</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>22/02/2024</t>
+          <t>27/01/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>17/08/2026 13:13</t>
+          <t>27/08/2026 21:23</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>17/08/2026 13:13</t>
+          <t>27/08/2026 21:23</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>18/08/2026 15:40</t>
+          <t>07/09/2026 14:45</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2134,7 +2134,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0004820-79.2022.8.16.0031</t>
+          <t>0002951-67.2023.8.16.0089</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2144,27 +2144,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Posse</t>
+          <t>Anulação e Correção de Provas / Questões</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>17/08/2026 15:03</t>
+          <t>27/08/2026 21:33</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>17/08/2026 15:03</t>
+          <t>27/08/2026 21:33</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>18/08/2026 11:03</t>
+          <t>07/09/2026 14:45</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2181,37 +2181,37 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0004851-22.2024.8.16.0034</t>
+          <t>0083650-50.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Promessa de Compra e Venda | Esbulho / Turbação / Ameaça | Requerimento de Reintegração de Posse</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>03/02/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>17/08/2026 18:33</t>
+          <t>27/08/2026 19:53</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>17/08/2026 18:33</t>
+          <t>27/08/2026 19:53</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>18/08/2026 14:27</t>
+          <t>07/09/2026 14:46</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2228,7 +2228,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0004943-61.2022.8.16.0004</t>
+          <t>0007090-04.2023.8.16.0173</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2238,27 +2238,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ISS/ Imposto sobre Serviços</t>
+          <t>Compra e Venda</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>24/04/2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>17/08/2026 15:25</t>
+          <t>28/08/2026 12:56</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>17/08/2026 15:25</t>
+          <t>28/08/2026 12:56</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>18/08/2026 05:23</t>
+          <t>10/09/2026 20:44</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2275,7 +2275,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0005198-43.2019.8.16.0030</t>
+          <t>0003825-19.2024.8.16.0024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2285,27 +2285,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Mútuo</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>22/10/2025</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>17/08/2026 14:53</t>
+          <t>26/08/2026 08:33</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>17/08/2026 14:53</t>
+          <t>26/08/2026 08:33</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>18/08/2026 03:55</t>
+          <t>10/09/2026 20:46</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2322,7 +2322,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0005981-44.2023.8.16.0014</t>
+          <t>0035495-50.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2332,27 +2332,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Compra e Venda</t>
+          <t>Evicção ou Vicio Redibitório | Indenização por Dano Moral | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>17/08/2026 14:43</t>
+          <t>27/08/2026 21:33</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>17/08/2026 14:43</t>
+          <t>27/08/2026 21:33</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>18/08/2026 04:01</t>
+          <t>10/09/2026 20:46</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2369,37 +2369,37 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0006265-81.2024.8.16.0090</t>
+          <t>4002116-51.2025.8.16.4321</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Estelionato contra Idoso</t>
+          <t>Remição</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>17/08/2026 15:53</t>
+          <t>25/08/2026 17:03</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>17/08/2026 15:53</t>
+          <t>25/08/2026 17:03</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>19/08/2026 01:56</t>
+          <t>10/09/2026 20:46</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2416,37 +2416,37 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0007237-51.2023.8.16.0069</t>
+          <t>0028035-41.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Roubo Majorado</t>
+          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>17/08/2026 16:13</t>
+          <t>02/09/2026 08:35</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>17/08/2026 16:13</t>
+          <t>02/09/2026 08:35</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>18/08/2026 04:35</t>
+          <t>10/09/2026 20:46</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2463,37 +2463,37 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0008942-75.2022.8.16.0148</t>
+          <t>0052981-77.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>17/08/2026 14:33</t>
+          <t>17/08/2026 17:34</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>17/08/2026 14:33</t>
+          <t>17/08/2026 17:34</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>18/08/2026 06:41</t>
+          <t>18/08/2026 03:36</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2510,7 +2510,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0010296-65.2020.8.16.0194</t>
+          <t>0130983-32.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Práticas Abusivas | Rescisão do contrato e devolução do dinheiro | Indenização por Dano Moral</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>18/08/2026 16:41</t>
+          <t>18/08/2026 03:39</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2557,37 +2557,37 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0010800-42.2018.8.16.0194</t>
+          <t>0030192-26.2018.8.16.0013</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Embargos de Divergência em Recurso Especial</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação</t>
+          <t>Roubo Majorado</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>13/10/2022</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>18/08/2026 15:23</t>
+          <t>17/08/2026 13:23</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>18/08/2026 15:23</t>
+          <t>17/08/2026 13:23</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>18/08/2026 23:35</t>
+          <t>18/08/2026 03:55</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2604,37 +2604,37 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0011816-50.2026.8.16.0000</t>
+          <t>0005981-44.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Associação Criminosa | Adulteração de Sinal Identificador de Veículo Automotor | Desobediência | Prisão Preventiva</t>
+          <t>Compra e Venda</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>17/08/2026 13:23</t>
+          <t>17/08/2026 14:43</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>17/08/2026 13:23</t>
+          <t>17/08/2026 14:43</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>18/08/2026 03:43</t>
+          <t>18/08/2026 04:01</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2651,37 +2651,37 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0012180-37.2017.8.16.0194</t>
+          <t>0003523-75.2025.8.16.0146</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Indenização por Dano Material</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>24/09/2025</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>17/08/2026 13:03</t>
+          <t>17/08/2026 20:03</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>17/08/2026 13:03</t>
+          <t>17/08/2026 20:03</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>18/08/2026 19:20</t>
+          <t>18/08/2026 04:49</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2698,37 +2698,37 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0014325-63.2017.8.16.0001</t>
+          <t>0004943-61.2022.8.16.0004</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Rescisão / Resolução | Perdas e Danos</t>
+          <t>ISS/ Imposto sobre Serviços</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>03/07/2024</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>18/08/2026 14:13</t>
+          <t>17/08/2026 15:25</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>18/08/2026 14:13</t>
+          <t>17/08/2026 15:25</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>18/08/2026 23:47</t>
+          <t>18/08/2026 05:23</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2745,37 +2745,37 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0014915-64.2009.8.16.0019</t>
+          <t>0000855-53.2024.8.16.0151</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Espécies de Títulos de Crédito | Cédula Hipotecária</t>
+          <t>Roubo Majorado</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>27/11/2020</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>18/08/2026 14:23</t>
+          <t>17/08/2026 15:53</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>18/08/2026 14:23</t>
+          <t>17/08/2026 15:53</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>18/08/2026 20:21</t>
+          <t>18/08/2026 07:13</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2792,37 +2792,37 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0016302-44.2023.8.16.0013</t>
+          <t>0018929-14.2006.8.16.0014</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Crimes de Trânsito</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>23/05/2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>17/08/2026 18:33</t>
+          <t>17/08/2026 13:53</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>17/08/2026 18:33</t>
+          <t>17/08/2026 13:53</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>19/08/2026 02:36</t>
+          <t>18/08/2026 07:57</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2839,37 +2839,37 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0018353-50.2022.8.16.0017</t>
+          <t>0037878-35.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Comodato</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>11/12/2024</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>17/08/2026 15:23</t>
+          <t>02/09/2026 14:53</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>17/08/2026 15:23</t>
+          <t>02/09/2026 14:53</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>18/08/2026 23:35</t>
+          <t>10/09/2026 20:57</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2886,37 +2886,37 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0018805-89.2024.8.16.0017</t>
+          <t>0031845-47.2009.8.16.0185</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Dívida Ativa (Execução Fiscal)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>17/08/2026 20:33</t>
+          <t>26/08/2026 14:13</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>17/08/2026 20:33</t>
+          <t>26/08/2026 14:13</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>19/08/2026 03:30</t>
+          <t>10/09/2026 20:59</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2933,37 +2933,37 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0018929-14.2006.8.16.0014</t>
+          <t>0010345-55.2021.8.16.0038</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>23/05/2025</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>17/08/2026 13:53</t>
+          <t>27/08/2026 20:13</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>17/08/2026 13:53</t>
+          <t>27/08/2026 20:13</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>18/08/2026 07:57</t>
+          <t>10/09/2026 20:59</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2980,37 +2980,37 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0018976-80.2019.8.16.0030</t>
+          <t>0005250-69.2024.8.16.0028</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Práticas Abusivas</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>09/12/2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>17/08/2026 15:03</t>
+          <t>18/08/2026 16:33</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>17/08/2026 15:03</t>
+          <t>18/08/2026 16:33</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>18/08/2026 22:21</t>
+          <t>10/09/2026 21:16</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3027,37 +3027,37 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0019003-57.2023.8.16.0019</t>
+          <t>0000804-49.2022.8.16.0139</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Desclassificação</t>
+          <t>Violência Psicológica contra a Mulher | Regime inicial | Prova Ilícita | Cerceamento de Defesa</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>02/10/2025</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>17/08/2026 18:53</t>
+          <t>17/08/2026 15:33</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>17/08/2026 18:53</t>
+          <t>17/08/2026 15:33</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>19/08/2026 03:12</t>
+          <t>10/09/2026 21:16</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3074,7 +3074,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0019271-25.2006.8.16.0014</t>
+          <t>0035488-24.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3084,27 +3084,27 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tratamento médico-hospitalar | Obrigação de Fazer / Não Fazer | Fornecimento de insumos</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>30/12/1899</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>18/08/2026 14:23</t>
+          <t>27/08/2026 13:53</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>18/08/2026 14:23</t>
+          <t>27/08/2026 13:53</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>18/08/2026 23:35</t>
+          <t>10/09/2026 21:16</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3121,7 +3121,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0020939-43.2024.8.16.0000</t>
+          <t>0061410-04.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3131,27 +3131,27 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Cobrança | Negativa de Prestação Jurisdicional | Cerceamento de Defesa</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>12/08/2025</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>17/08/2026 14:13</t>
+          <t>28/08/2026 16:43</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>17/08/2026 14:13</t>
+          <t>28/08/2026 16:43</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>18/08/2026 03:37</t>
+          <t>10/09/2026 21:16</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3168,7 +3168,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0021603-50.2020.8.16.0021</t>
+          <t>0047704-17.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3178,27 +3178,27 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Locação de Imóvel</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>17/08/2026 14:53</t>
+          <t>26/08/2026 15:23</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>17/08/2026 14:53</t>
+          <t>26/08/2026 15:23</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20/08/2026 22:45</t>
+          <t>10/09/2026 21:29</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3215,7 +3215,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0023731-33.2025.8.16.0000</t>
+          <t>0001107-89.2023.8.16.0119</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3225,27 +3225,27 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Liminar | Adequação da Ação / Procedimento</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>17/08/2026 14:53</t>
+          <t>27/08/2026 19:43</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>17/08/2026 14:53</t>
+          <t>27/08/2026 19:43</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>18/08/2026 13:02</t>
+          <t>07/09/2026 14:45</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3262,37 +3262,37 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0026052-12.2023.8.16.0000</t>
+          <t>0115570-76.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Práticas Abusivas</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>05/08/2024</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>17/08/2026 14:13</t>
+          <t>27/08/2026 20:33</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>17/08/2026 14:13</t>
+          <t>27/08/2026 20:33</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>18/08/2026 13:26</t>
+          <t>07/09/2026 14:45</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3309,7 +3309,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0029973-10.2022.8.16.0001</t>
+          <t>0101965-97.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3319,27 +3319,27 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Previdência privada</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>29/10/2024</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>17/08/2026 15:13</t>
+          <t>27/08/2026 21:43</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>17/08/2026 15:13</t>
+          <t>27/08/2026 21:43</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>18/08/2026 19:09</t>
+          <t>07/09/2026 14:45</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3356,12 +3356,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0030073-94.2024.8.16.0000</t>
+          <t>0091159-95.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3371,22 +3371,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>26/02/2025</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>17/08/2026 16:43</t>
+          <t>01/09/2026 13:03</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>17/08/2026 16:43</t>
+          <t>01/09/2026 13:03</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>18/08/2026 12:27</t>
+          <t>07/09/2026 14:45</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3403,37 +3403,37 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0030192-26.2018.8.16.0013</t>
+          <t>0062461-50.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Embargos de Divergência em Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Roubo Majorado</t>
+          <t>Concurso de Credores</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>13/10/2022</t>
+          <t>20/01/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>17/08/2026 13:23</t>
+          <t>27/08/2026 19:43</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>17/08/2026 13:23</t>
+          <t>27/08/2026 19:43</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>18/08/2026 03:55</t>
+          <t>07/09/2026 14:45</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3450,37 +3450,37 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0035479-62.2025.8.16.0000</t>
+          <t>0025685-85.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Práticas Abusivas</t>
+          <t>Contratos Bancários | Cessão de Crédito | Suspensão da Execução | Penhora / Depósito/ Avaliação</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>19/06/2024</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>17/08/2026 14:23</t>
+          <t>21/08/2026 14:43</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>17/08/2026 14:23</t>
+          <t>21/08/2026 14:43</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>18/08/2026 08:47</t>
+          <t>10/09/2026 20:44</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3497,7 +3497,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0038200-18.2024.8.16.0001</t>
+          <t>0000163-44.2023.8.16.0004</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3507,27 +3507,27 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>ICMS/ Imposto sobre Circulação de Mercadorias</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>24/10/2025</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>17/08/2026 15:23</t>
+          <t>25/08/2026 16:23</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>17/08/2026 15:23</t>
+          <t>25/08/2026 16:23</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>18/08/2026 15:54</t>
+          <t>10/09/2026 20:44</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3544,37 +3544,37 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0039901-46.2026.8.16.0000</t>
+          <t>0008854-86.2019.8.16.0004</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>ICMS/ Imposto sobre Circulação de Mercadorias</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>17/08/2026 16:33</t>
+          <t>19/08/2026 14:33</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>17/08/2026 16:33</t>
+          <t>19/08/2026 14:33</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>18/08/2026 12:42</t>
+          <t>10/09/2026 20:46</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3591,37 +3591,37 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0040013-83.2024.8.16.0000</t>
+          <t>0001878-68.2022.8.16.0130</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Locação de Móvel</t>
+          <t>Seguro | Seguro</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>18/08/2026 14:13</t>
+          <t>28/08/2026 21:43</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>18/08/2026 14:13</t>
+          <t>28/08/2026 21:43</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>19/08/2026 03:30</t>
+          <t>10/09/2026 20:46</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3638,7 +3638,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0041319-84.2024.8.16.0001</t>
+          <t>0051721-96.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3648,27 +3648,27 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ingresso e Exclusão dos Sócios na Sociedade</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>26/05/2025</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>17/08/2026 13:13</t>
+          <t>18/08/2026 14:13</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>17/08/2026 13:13</t>
+          <t>18/08/2026 14:13</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>18/08/2026 16:27</t>
+          <t>19/08/2026 02:59</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3685,7 +3685,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0043199-72.2024.8.16.0014</t>
+          <t>0061924-46.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3695,27 +3695,27 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Furto Qualificado</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>17/08/2026 18:33</t>
+          <t>17/08/2026 18:23</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>17/08/2026 18:33</t>
+          <t>17/08/2026 18:23</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>19/08/2026 02:59</t>
+          <t>19/08/2026 03:12</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3732,37 +3732,37 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0044188-91.2022.8.16.0000</t>
+          <t>0040013-83.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Cédula Hipotecária</t>
+          <t>Locação de Móvel</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>14/02/2024</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>17/08/2026 13:33</t>
+          <t>18/08/2026 14:13</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>17/08/2026 13:33</t>
+          <t>18/08/2026 14:13</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>18/08/2026 11:22</t>
+          <t>19/08/2026 03:30</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3779,37 +3779,37 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0046238-58.2024.8.16.0182</t>
+          <t>0065776-52.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Pedido de Uniformização de Interpretação de Lei Criminal</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Residência Médica | Programas de Bolsas e Financiamento Estudantil com Recursos Públicos</t>
+          <t>Ameaça | Prisão Preventiva | Violação de domicílio</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>03/04/2025</t>
+          <t>29/09/2025</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>18/08/2026 01:57</t>
+          <t>18/08/2026 16:13</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>18/08/2026 01:57</t>
+          <t>18/08/2026 16:13</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>18/08/2026 14:27</t>
+          <t>19/08/2026 02:52</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3826,7 +3826,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0051721-96.2025.8.16.0000</t>
+          <t>0002386-96.2009.8.16.0153</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3836,27 +3836,27 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>27/01/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>18/08/2026 14:13</t>
+          <t>17/08/2026 13:33</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>18/08/2026 14:13</t>
+          <t>17/08/2026 13:33</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>19/08/2026 02:59</t>
+          <t>19/08/2026 02:47</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3873,37 +3873,37 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0052981-77.2026.8.16.0000</t>
+          <t>0003762-42.2019.8.16.0194</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins</t>
+          <t>Obrigação de Fazer / Não Fazer</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>05/05/2022</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>17/08/2026 17:34</t>
+          <t>17/08/2026 14:13</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>17/08/2026 17:34</t>
+          <t>17/08/2026 14:13</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>18/08/2026 03:36</t>
+          <t>19/08/2026 02:36</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3920,7 +3920,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0057175-91.2024.8.16.0000</t>
+          <t>0006265-81.2024.8.16.0090</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3930,27 +3930,27 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Vícios de Construção | Assistência Judiciária Gratuita</t>
+          <t>Estelionato contra Idoso</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>27/01/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>17/08/2026 13:13</t>
+          <t>17/08/2026 15:53</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>17/08/2026 13:13</t>
+          <t>17/08/2026 15:53</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>18/08/2026 17:27</t>
+          <t>19/08/2026 01:56</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3967,7 +3967,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0061924-46.2023.8.16.0014</t>
+          <t>0019271-25.2006.8.16.0014</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3977,27 +3977,27 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Tratamento médico-hospitalar | Obrigação de Fazer / Não Fazer | Fornecimento de insumos</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/12/1899</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>17/08/2026 18:23</t>
+          <t>18/08/2026 14:23</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>17/08/2026 18:23</t>
+          <t>18/08/2026 14:23</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>19/08/2026 03:12</t>
+          <t>18/08/2026 23:35</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -4014,37 +4014,37 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0062940-43.2024.8.16.0000</t>
+          <t>0014325-63.2017.8.16.0001</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Dissolução</t>
+          <t>Rescisão / Resolução | Perdas e Danos</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>03/07/2024</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>17/08/2026 14:23</t>
+          <t>18/08/2026 14:13</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>17/08/2026 14:23</t>
+          <t>18/08/2026 14:13</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>18/08/2026 15:33</t>
+          <t>18/08/2026 23:47</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4061,37 +4061,37 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0064838-91.2024.8.16.0000</t>
+          <t>0000982-42.2013.8.16.0097</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Embargos de Divergência em Recurso Especial</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Servidores Inativos | Requisição de Pequeno Valor - RPV</t>
+          <t>Produto Impróprio</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>23/02/2026</t>
+          <t>19/06/2024</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>17/08/2026 14:03</t>
+          <t>17/08/2026 15:03</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>17/08/2026 14:03</t>
+          <t>17/08/2026 15:03</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>18/08/2026 13:13</t>
+          <t>18/08/2026 21:59</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -4108,37 +4108,37 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0065092-93.2026.8.16.0000</t>
+          <t>0002396-07.2022.8.16.0147</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Homicídio Qualificado | Crime Tentado</t>
+          <t>Oferta e Publicidade | Jogos / Sorteios / Promoções comerciais</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>17/08/2026 18:43</t>
+          <t>17/08/2026 16:53</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>17/08/2026 18:43</t>
+          <t>17/08/2026 16:53</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>18/08/2026 10:25</t>
+          <t>18/08/2026 20:48</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4155,37 +4155,37 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0065776-52.2025.8.16.0000</t>
+          <t>0089924-98.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Embargos de Divergência em Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Ameaça | Prisão Preventiva | Violação de domicílio</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>24/04/2025</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>18/08/2026 16:13</t>
+          <t>17/08/2026 14:03</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>18/08/2026 16:13</t>
+          <t>17/08/2026 14:03</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>19/08/2026 02:52</t>
+          <t>18/08/2026 17:06</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4202,37 +4202,37 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0066120-96.2026.8.16.0000</t>
+          <t>0002499-91.2019.8.16.0123</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>05/03/2024</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>17/08/2026 17:13</t>
+          <t>18/08/2026 13:43</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>17/08/2026 17:13</t>
+          <t>18/08/2026 13:43</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>18/08/2026 11:44</t>
+          <t>18/08/2026 17:07</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4249,7 +4249,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0068649-22.2021.8.16.0014</t>
+          <t>0020939-43.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4259,27 +4259,27 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Inventário e Partilha | Bem de Família Legal</t>
+          <t>Cobrança | Negativa de Prestação Jurisdicional | Cerceamento de Defesa</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>14/10/2025</t>
+          <t>12/08/2025</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>17/08/2026 13:33</t>
+          <t>17/08/2026 14:13</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>17/08/2026 13:33</t>
+          <t>17/08/2026 14:13</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>18/08/2026 13:38</t>
+          <t>18/08/2026 03:37</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4296,7 +4296,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0073315-32.2022.8.16.0014</t>
+          <t>0001644-85.2024.8.16.0140</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4306,27 +4306,27 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Alienação Fiduciária</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>13/01/2026</t>
+          <t>23/02/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>17/08/2026 13:53</t>
+          <t>17/08/2026 14:43</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>17/08/2026 13:53</t>
+          <t>17/08/2026 14:43</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>18/08/2026 12:05</t>
+          <t>18/08/2026 03:39</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4343,37 +4343,37 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0074360-45.2024.8.16.0000</t>
+          <t>0011816-50.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal) | Citação</t>
+          <t>Associação Criminosa | Adulteração de Sinal Identificador de Veículo Automotor | Desobediência | Prisão Preventiva</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>17/08/2026 14:43</t>
+          <t>17/08/2026 13:23</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>17/08/2026 14:43</t>
+          <t>17/08/2026 13:23</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>18/08/2026 18:32</t>
+          <t>18/08/2026 03:43</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4390,7 +4390,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0077298-13.2024.8.16.0000</t>
+          <t>0008942-75.2022.8.16.0148</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4400,27 +4400,27 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Dano ao Erário</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>20/10/2025</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>17/08/2026 16:53</t>
+          <t>17/08/2026 14:33</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>17/08/2026 16:53</t>
+          <t>17/08/2026 14:33</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>18/08/2026 03:50</t>
+          <t>18/08/2026 06:41</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4437,37 +4437,37 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0083631-10.2026.8.16.0000</t>
+          <t>0000576-36.2025.8.16.0053</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Resistência</t>
+          <t>Promessa de Compra e Venda | Rescisão / Resolução</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>10/04/2025</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>17/08/2026 16:13</t>
+          <t>17/08/2026 13:23</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>17/08/2026 16:13</t>
+          <t>17/08/2026 13:23</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>18/08/2026 04:53</t>
+          <t>18/08/2026 08:14</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4484,7 +4484,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0084281-28.2024.8.16.0000</t>
+          <t>0000890-52.2009.8.16.0114</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Liquidação</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>13/02/2026</t>
+          <t>06/10/2023</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>19/08/2026 04:07</t>
+          <t>18/08/2026 08:14</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4531,37 +4531,37 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0089924-98.2023.8.16.0000</t>
+          <t>0035479-62.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Embargos de Divergência em Agravo em Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Práticas Abusivas</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>24/04/2025</t>
+          <t>19/03/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>17/08/2026 14:03</t>
+          <t>17/08/2026 14:23</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>17/08/2026 14:03</t>
+          <t>17/08/2026 14:23</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>18/08/2026 17:06</t>
+          <t>18/08/2026 08:47</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4625,37 +4625,37 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0093139-77.2026.8.16.0000</t>
+          <t>0044188-91.2022.8.16.0000</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Seqüestro e cárcere privado | Crimes de Tortura | Lesão Cometida em Razão da Condição de Mulher | Ameaça</t>
+          <t>Cédula Hipotecária</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>14/02/2024</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>17/08/2026 17:23</t>
+          <t>17/08/2026 13:33</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>17/08/2026 17:23</t>
+          <t>17/08/2026 13:33</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>18/08/2026 22:58</t>
+          <t>18/08/2026 11:22</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4672,7 +4672,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0094754-39.2025.8.16.0000</t>
+          <t>0001611-17.2023.8.16.0048</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4682,27 +4682,27 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Peculato</t>
+          <t>Pagamento com Sub-rogação | Inexequibilidade do Título / Inexigibilidade da Obrigação</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>15/05/2025</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>17/08/2026 15:53</t>
+          <t>17/08/2026 13:23</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>17/08/2026 15:53</t>
+          <t>17/08/2026 13:23</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>18/08/2026 15:11</t>
+          <t>18/08/2026 11:31</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4719,7 +4719,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0099048-08.2023.8.16.0000</t>
+          <t>0002959-48.2022.8.16.0196</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4729,27 +4729,27 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Perigo para a vida ou saúde de outrem</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>04/10/2024</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>18/08/2026 13:13</t>
+          <t>17/08/2026 17:43</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>18/08/2026 13:13</t>
+          <t>17/08/2026 17:43</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>19/08/2026 00:46</t>
+          <t>18/08/2026 11:44</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4813,37 +4813,37 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0108328-32.2025.8.16.0000</t>
+          <t>0003845-76.2024.8.16.0196</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Latrocínio</t>
+          <t>Roubo Majorado</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>17/08/2026 17:53</t>
+          <t>17/08/2026 16:13</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>17/08/2026 17:53</t>
+          <t>17/08/2026 16:13</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>18/08/2026 09:15</t>
+          <t>18/08/2026 12:17</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4860,7 +4860,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0111584-17.2024.8.16.0000</t>
+          <t>0003308-26.2020.8.16.0033</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4870,27 +4870,27 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Seguro | Honorários Advocatícios | Provas</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>17/08/2026 13:23</t>
+          <t>17/08/2026 14:33</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>17/08/2026 13:23</t>
+          <t>17/08/2026 14:33</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>18/08/2026 09:30</t>
+          <t>18/08/2026 12:42</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4907,37 +4907,37 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0126623-54.2024.8.16.0000</t>
+          <t>0026052-12.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>05/08/2024</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>17/08/2026 15:13</t>
+          <t>17/08/2026 14:13</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>17/08/2026 15:13</t>
+          <t>17/08/2026 14:13</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>19/08/2026 00:37</t>
+          <t>18/08/2026 13:26</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4954,37 +4954,37 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0130983-32.2024.8.16.0000</t>
+          <t>0004851-22.2024.8.16.0034</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>03/02/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>17/08/2026 14:23</t>
+          <t>17/08/2026 18:33</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>17/08/2026 14:23</t>
+          <t>17/08/2026 18:33</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>18/08/2026 03:39</t>
+          <t>18/08/2026 14:27</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -5001,37 +5001,37 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0142492-23.2025.8.16.0000</t>
+          <t>0062940-43.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Dissolução</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>17/08/2026 18:03</t>
+          <t>17/08/2026 14:23</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>17/08/2026 18:03</t>
+          <t>17/08/2026 14:23</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>18/08/2026 04:02</t>
+          <t>18/08/2026 15:33</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -5048,37 +5048,37 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>4002176-24.2025.8.16.4321</t>
+          <t>0004672-24.2019.8.16.0112</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Progressão de Regime</t>
+          <t>Tráfico de Drogas e Condutas Afins | Crimes do Sistema Nacional de Armas</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>22/02/2024</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>18/08/2026 16:03</t>
+          <t>17/08/2026 13:13</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>18/08/2026 16:03</t>
+          <t>17/08/2026 13:13</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>19/08/2026 02:18</t>
+          <t>18/08/2026 15:40</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -5095,7 +5095,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>4006248-54.2025.8.16.4321</t>
+          <t>0002099-57.2023.8.16.0149</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -5105,27 +5105,27 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Progressão de Regime | Tráfico de Drogas e Condutas Afins</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>17/08/2026 16:33</t>
+          <t>17/08/2026 14:23</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>17/08/2026 16:33</t>
+          <t>17/08/2026 14:23</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>18/08/2026 03:35</t>
+          <t>18/08/2026 15:54</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -5134,6 +5134,53 @@
         </is>
       </c>
       <c r="I100" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>0018344-29.2024.8.16.0014</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Material</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>14/10/2025</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>25/08/2026 18:53</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>25/08/2026 18:53</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>10/09/2026 21:14</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>

--- a/docs/resultados.xlsx
+++ b/docs/resultados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I101"/>
+  <dimension ref="A1:I95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -489,37 +489,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0002529-36.2021.8.16.0098</t>
+          <t>0000022-19.1988.8.16.0047</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dever de Informação | Irregularidade no atendimento</t>
+          <t>Bancários</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>02/08/2024</t>
+          <t>19/08/2024</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>31/08/2026 11:38</t>
+          <t>17/08/2026 13:03</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>31/08/2026 11:38</t>
+          <t>17/08/2026 13:03</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>10/09/2026 21:14</t>
+          <t>19/08/2026 00:42</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -536,7 +536,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0008017-50.2023.8.16.0017</t>
+          <t>0000163-44.2023.8.16.0004</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -546,27 +546,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Locação de Imóvel | Embargos de Terceiro</t>
+          <t>ICMS/ Imposto sobre Circulação de Mercadorias</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
+          <t>24/10/2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>25/08/2026 17:43</t>
+          <t>25/08/2026 16:23</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>25/08/2026 17:43</t>
+          <t>25/08/2026 16:23</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10/09/2026 21:14</t>
+          <t>10/09/2026 20:44</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -583,12 +583,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0022909-70.2023.8.16.0014</t>
+          <t>0000174-98.2020.8.16.0062</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -598,22 +598,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>27/09/2024</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>27/08/2026 15:59</t>
+          <t>17/08/2026 18:03</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>27/08/2026 15:59</t>
+          <t>17/08/2026 18:03</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>10/09/2026 21:14</t>
+          <t>18/08/2026 23:33</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,7 +630,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0109932-62.2024.8.16.0000</t>
+          <t>0000245-29.2022.8.16.0160</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -640,27 +640,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Prescrição e Decadência</t>
+          <t>Contratos Bancários | Perdas e Danos | Cerceamento de Defesa | Provas | Obrigação de Entregar</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>24/08/2026 16:53</t>
+          <t>10/09/2026 15:23</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>24/08/2026 16:53</t>
+          <t>10/09/2026 15:23</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>10/09/2026 21:16</t>
+          <t>10/09/2026 21:24</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -677,7 +677,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0005311-55.2024.8.16.0148</t>
+          <t>0000576-36.2025.8.16.0053</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -687,27 +687,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Práticas Abusivas</t>
+          <t>Promessa de Compra e Venda | Rescisão / Resolução</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>10/04/2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>28/08/2026 15:13</t>
+          <t>17/08/2026 13:23</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>28/08/2026 15:13</t>
+          <t>17/08/2026 13:23</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>10/09/2026 21:16</t>
+          <t>18/08/2026 08:14</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -724,37 +724,37 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0000245-29.2022.8.16.0160</t>
+          <t>0000627-67.2022.8.16.0048</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Contratos Bancários | Perdas e Danos | Cerceamento de Defesa | Provas | Obrigação de Entregar</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/09/2024</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>10/09/2026 15:23</t>
+          <t>17/08/2026 13:53</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>10/09/2026 15:23</t>
+          <t>17/08/2026 13:53</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>10/09/2026 21:24</t>
+          <t>10/09/2026 21:29</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -771,37 +771,37 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0000627-67.2022.8.16.0048</t>
+          <t>0000804-49.2022.8.16.0139</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Violência Psicológica contra a Mulher | Regime inicial | Prova Ilícita | Cerceamento de Defesa</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>02/09/2024</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>17/08/2026 13:53</t>
+          <t>17/08/2026 15:33</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>17/08/2026 13:53</t>
+          <t>17/08/2026 15:33</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>10/09/2026 21:29</t>
+          <t>10/09/2026 21:16</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -818,7 +818,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0081354-89.2024.8.16.0000</t>
+          <t>0000855-53.2024.8.16.0151</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -828,27 +828,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Penhora / Depósito/ Avaliação | Indenização por Dano Material</t>
+          <t>Roubo Majorado</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>26/09/2025</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>31/08/2026 16:43</t>
+          <t>17/08/2026 15:53</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>31/08/2026 16:43</t>
+          <t>17/08/2026 15:53</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>10/09/2026 21:29</t>
+          <t>18/08/2026 07:13</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -865,37 +865,37 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0065092-93.2026.8.16.0000</t>
+          <t>0000890-52.2009.8.16.0114</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Homicídio Qualificado | Crime Tentado</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>06/10/2023</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>17/08/2026 18:43</t>
+          <t>17/08/2026 14:43</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>17/08/2026 18:43</t>
+          <t>17/08/2026 14:43</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>18/08/2026 10:25</t>
+          <t>18/08/2026 08:14</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -912,22 +912,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0004820-79.2022.8.16.0031</t>
+          <t>0000982-42.2013.8.16.0097</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Embargos de Divergência em Recurso Especial</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Posse</t>
+          <t>Produto Impróprio</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>19/06/2024</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>18/08/2026 11:03</t>
+          <t>18/08/2026 21:59</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -959,37 +959,37 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0066120-96.2026.8.16.0000</t>
+          <t>0001107-89.2023.8.16.0119</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>17/08/2026 17:13</t>
+          <t>27/08/2026 19:43</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>17/08/2026 17:13</t>
+          <t>27/08/2026 19:43</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>18/08/2026 11:44</t>
+          <t>07/09/2026 14:45</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1006,7 +1006,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0004410-05.2022.8.16.0004</t>
+          <t>0001236-59.2021.8.16.0024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1016,27 +1016,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Equilíbrio Financeiro</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>17/08/2026 14:43</t>
+          <t>18/08/2026 10:52</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>17/08/2026 14:43</t>
+          <t>18/08/2026 10:52</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>18/08/2026 12:55</t>
+          <t>19/08/2026 02:47</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1053,7 +1053,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0023731-33.2025.8.16.0000</t>
+          <t>0001611-17.2023.8.16.0048</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1063,27 +1063,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Liminar | Adequação da Ação / Procedimento</t>
+          <t>Pagamento com Sub-rogação | Inexequibilidade do Título / Inexigibilidade da Obrigação</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>15/05/2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>17/08/2026 14:53</t>
+          <t>17/08/2026 13:23</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>17/08/2026 14:53</t>
+          <t>17/08/2026 13:23</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>18/08/2026 13:02</t>
+          <t>18/08/2026 11:31</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0064838-91.2024.8.16.0000</t>
+          <t>0001644-85.2024.8.16.0140</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Servidores Inativos | Requisição de Pequeno Valor - RPV</t>
+          <t>Alienação Fiduciária</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1120,17 +1120,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>17/08/2026 14:03</t>
+          <t>17/08/2026 14:43</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>17/08/2026 14:03</t>
+          <t>17/08/2026 14:43</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>18/08/2026 13:13</t>
+          <t>18/08/2026 03:39</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1147,37 +1147,37 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0068649-22.2021.8.16.0014</t>
+          <t>0001878-68.2022.8.16.0130</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Inventário e Partilha | Bem de Família Legal</t>
+          <t>Seguro | Seguro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>14/10/2025</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>17/08/2026 13:33</t>
+          <t>28/08/2026 21:43</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>17/08/2026 13:33</t>
+          <t>28/08/2026 21:43</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>18/08/2026 13:38</t>
+          <t>10/09/2026 20:46</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1194,37 +1194,37 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0046238-58.2024.8.16.0182</t>
+          <t>0001893-39.2022.8.16.0097</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pedido de Uniformização de Interpretação de Lei Criminal</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Residência Médica | Programas de Bolsas e Financiamento Estudantil com Recursos Públicos</t>
+          <t>Crimes de Trânsito</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>03/04/2025</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>18/08/2026 01:57</t>
+          <t>18/08/2026 16:13</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>18/08/2026 01:57</t>
+          <t>18/08/2026 16:13</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>18/08/2026 14:27</t>
+          <t>19/08/2026 03:41</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1241,7 +1241,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0094754-39.2025.8.16.0000</t>
+          <t>0002099-57.2023.8.16.0149</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1251,27 +1251,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Peculato</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>17/08/2026 15:53</t>
+          <t>17/08/2026 14:23</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>17/08/2026 15:53</t>
+          <t>17/08/2026 14:23</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>18/08/2026 15:11</t>
+          <t>18/08/2026 15:54</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1288,7 +1288,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0041319-84.2024.8.16.0001</t>
+          <t>0002386-96.2009.8.16.0153</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1298,27 +1298,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ingresso e Exclusão dos Sócios na Sociedade</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>26/05/2025</t>
+          <t>27/01/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>17/08/2026 13:13</t>
+          <t>17/08/2026 13:33</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>17/08/2026 13:13</t>
+          <t>17/08/2026 13:33</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>18/08/2026 16:27</t>
+          <t>19/08/2026 02:47</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1335,37 +1335,37 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0003260-92.2022.8.16.0196</t>
+          <t>0002396-07.2022.8.16.0147</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Oferta e Publicidade | Jogos / Sorteios / Promoções comerciais</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>27/11/2024</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>17/08/2026 17:43</t>
+          <t>17/08/2026 16:53</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>17/08/2026 17:43</t>
+          <t>17/08/2026 16:53</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>18/08/2026 16:29</t>
+          <t>18/08/2026 20:48</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1382,37 +1382,37 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0010296-65.2020.8.16.0194</t>
+          <t>0002499-91.2019.8.16.0123</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Práticas Abusivas | Rescisão do contrato e devolução do dinheiro | Indenização por Dano Moral</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>05/03/2024</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>17/08/2026 14:23</t>
+          <t>18/08/2026 13:43</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>17/08/2026 14:23</t>
+          <t>18/08/2026 13:43</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>18/08/2026 16:41</t>
+          <t>18/08/2026 17:07</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1429,37 +1429,37 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0000033-52.2025.8.16.0079</t>
+          <t>0002529-36.2021.8.16.0098</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação</t>
+          <t>Dever de Informação | Irregularidade no atendimento</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>10/12/2025</t>
+          <t>02/08/2024</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>17/08/2026 13:13</t>
+          <t>31/08/2026 11:38</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>17/08/2026 13:13</t>
+          <t>31/08/2026 11:38</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>18/08/2026 16:46</t>
+          <t>10/09/2026 21:14</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1476,7 +1476,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0029973-10.2022.8.16.0001</t>
+          <t>0002951-67.2023.8.16.0089</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1486,27 +1486,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Previdência privada</t>
+          <t>Anulação e Correção de Provas / Questões</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>17/08/2026 15:13</t>
+          <t>27/08/2026 21:33</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>17/08/2026 15:13</t>
+          <t>27/08/2026 21:33</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>18/08/2026 19:09</t>
+          <t>07/09/2026 14:45</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1523,7 +1523,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0012180-37.2017.8.16.0194</t>
+          <t>0002959-48.2022.8.16.0196</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1533,27 +1533,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Indenização por Dano Material</t>
+          <t>Perigo para a vida ou saúde de outrem</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>24/09/2025</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>17/08/2026 13:03</t>
+          <t>17/08/2026 17:43</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>17/08/2026 13:03</t>
+          <t>17/08/2026 17:43</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>18/08/2026 19:20</t>
+          <t>18/08/2026 11:44</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1570,37 +1570,37 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0093139-77.2026.8.16.0000</t>
+          <t>0003308-26.2020.8.16.0033</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Seqüestro e cárcere privado | Crimes de Tortura | Lesão Cometida em Razão da Condição de Mulher | Ameaça</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>17/08/2026 17:23</t>
+          <t>17/08/2026 14:33</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>17/08/2026 17:23</t>
+          <t>17/08/2026 14:33</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>18/08/2026 22:58</t>
+          <t>18/08/2026 12:42</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1617,12 +1617,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0000174-98.2020.8.16.0062</t>
+          <t>0003523-75.2025.8.16.0146</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1632,22 +1632,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>17/08/2026 18:03</t>
+          <t>17/08/2026 20:03</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>17/08/2026 18:03</t>
+          <t>17/08/2026 20:03</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>18/08/2026 23:33</t>
+          <t>18/08/2026 04:49</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1664,37 +1664,37 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0126623-54.2024.8.16.0000</t>
+          <t>0003762-42.2019.8.16.0194</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Obrigação de Fazer / Não Fazer</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>05/05/2022</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>17/08/2026 15:13</t>
+          <t>17/08/2026 14:13</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>17/08/2026 15:13</t>
+          <t>17/08/2026 14:13</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>19/08/2026 00:37</t>
+          <t>19/08/2026 02:36</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0000022-19.1988.8.16.0047</t>
+          <t>0003825-19.2024.8.16.0024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1721,27 +1721,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bancários</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>19/08/2024</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>17/08/2026 13:03</t>
+          <t>26/08/2026 08:33</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>17/08/2026 13:03</t>
+          <t>26/08/2026 08:33</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>19/08/2026 00:42</t>
+          <t>10/09/2026 20:46</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1758,7 +1758,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>4002176-24.2025.8.16.4321</t>
+          <t>0003845-76.2024.8.16.0196</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1768,27 +1768,27 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Progressão de Regime</t>
+          <t>Roubo Majorado</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>18/08/2026 16:03</t>
+          <t>17/08/2026 16:13</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>18/08/2026 16:03</t>
+          <t>17/08/2026 16:13</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>19/08/2026 02:18</t>
+          <t>18/08/2026 12:17</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1805,7 +1805,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0016302-44.2023.8.16.0013</t>
+          <t>0004410-05.2022.8.16.0004</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1815,27 +1815,27 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Crimes de Trânsito</t>
+          <t>Equilíbrio Financeiro</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>17/08/2026 18:33</t>
+          <t>17/08/2026 14:43</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>17/08/2026 18:33</t>
+          <t>17/08/2026 14:43</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>19/08/2026 02:36</t>
+          <t>18/08/2026 12:55</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1852,37 +1852,37 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0001236-59.2021.8.16.0024</t>
+          <t>0004672-24.2019.8.16.0112</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Tráfico de Drogas e Condutas Afins | Crimes do Sistema Nacional de Armas</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>22/02/2024</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>18/08/2026 10:52</t>
+          <t>17/08/2026 13:13</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>18/08/2026 10:52</t>
+          <t>17/08/2026 13:13</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>19/08/2026 02:47</t>
+          <t>18/08/2026 15:40</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1899,37 +1899,37 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0019003-57.2023.8.16.0019</t>
+          <t>0004820-79.2022.8.16.0031</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Desclassificação</t>
+          <t>Posse</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>02/10/2025</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>17/08/2026 18:53</t>
+          <t>17/08/2026 15:03</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>17/08/2026 18:53</t>
+          <t>17/08/2026 15:03</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>19/08/2026 03:12</t>
+          <t>18/08/2026 11:03</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1946,37 +1946,37 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0001893-39.2022.8.16.0097</t>
+          <t>0004851-22.2024.8.16.0034</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Crimes de Trânsito</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>03/02/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>18/08/2026 16:13</t>
+          <t>17/08/2026 18:33</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>18/08/2026 16:13</t>
+          <t>17/08/2026 18:33</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>19/08/2026 03:41</t>
+          <t>18/08/2026 14:27</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0021603-50.2020.8.16.0021</t>
+          <t>0004943-61.2022.8.16.0004</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2003,27 +2003,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Locação de Imóvel</t>
+          <t>ISS/ Imposto sobre Serviços</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>17/08/2026 14:53</t>
+          <t>17/08/2026 15:25</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>17/08/2026 14:53</t>
+          <t>17/08/2026 15:25</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20/08/2026 22:45</t>
+          <t>18/08/2026 05:23</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2040,37 +2040,37 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0008652-53.2021.8.16.0000</t>
+          <t>0005250-69.2024.8.16.0028</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Administração judicial</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>20/07/2022</t>
+          <t>09/12/2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>04/09/2026 13:13</t>
+          <t>18/08/2026 16:33</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>04/09/2026 13:13</t>
+          <t>18/08/2026 16:33</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>07/09/2026 14:45</t>
+          <t>10/09/2026 21:16</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2087,7 +2087,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0017529-91.2012.8.16.0001</t>
+          <t>0005311-55.2024.8.16.0148</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2097,27 +2097,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Práticas Abusivas</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>27/01/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>27/08/2026 21:23</t>
+          <t>28/08/2026 15:13</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>27/08/2026 21:23</t>
+          <t>28/08/2026 15:13</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>07/09/2026 14:45</t>
+          <t>10/09/2026 21:16</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2134,7 +2134,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0002951-67.2023.8.16.0089</t>
+          <t>0005981-44.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2144,27 +2144,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Anulação e Correção de Provas / Questões</t>
+          <t>Compra e Venda</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>27/08/2026 21:33</t>
+          <t>17/08/2026 14:43</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>27/08/2026 21:33</t>
+          <t>17/08/2026 14:43</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>07/09/2026 14:45</t>
+          <t>18/08/2026 04:01</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2181,7 +2181,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0083650-50.2025.8.16.0000</t>
+          <t>0006265-81.2024.8.16.0090</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2191,27 +2191,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Promessa de Compra e Venda | Esbulho / Turbação / Ameaça | Requerimento de Reintegração de Posse</t>
+          <t>Estelionato contra Idoso</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>27/08/2026 19:53</t>
+          <t>17/08/2026 15:53</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>27/08/2026 19:53</t>
+          <t>17/08/2026 15:53</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>07/09/2026 14:46</t>
+          <t>19/08/2026 01:56</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2275,7 +2275,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0003825-19.2024.8.16.0024</t>
+          <t>0008017-50.2023.8.16.0017</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2285,27 +2285,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Locação de Imóvel | Embargos de Terceiro</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>29/01/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>26/08/2026 08:33</t>
+          <t>25/08/2026 17:43</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>26/08/2026 08:33</t>
+          <t>25/08/2026 17:43</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>10/09/2026 20:46</t>
+          <t>10/09/2026 21:14</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2322,7 +2322,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0035495-50.2024.8.16.0000</t>
+          <t>0008652-53.2021.8.16.0000</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2332,27 +2332,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Evicção ou Vicio Redibitório | Indenização por Dano Moral | Indenização por Dano Material</t>
+          <t>Administração judicial</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>20/07/2022</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>27/08/2026 21:33</t>
+          <t>04/09/2026 13:13</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>27/08/2026 21:33</t>
+          <t>04/09/2026 13:13</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>10/09/2026 20:46</t>
+          <t>07/09/2026 14:45</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2369,32 +2369,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4002116-51.2025.8.16.4321</t>
+          <t>0008854-86.2019.8.16.0004</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remição</t>
+          <t>ICMS/ Imposto sobre Circulação de Mercadorias</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>25/08/2026 17:03</t>
+          <t>19/08/2026 14:33</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>25/08/2026 17:03</t>
+          <t>19/08/2026 14:33</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2416,17 +2416,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0028035-41.2026.8.16.0000</t>
+          <t>0008942-75.2022.8.16.0148</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2436,17 +2436,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>02/09/2026 08:35</t>
+          <t>17/08/2026 14:33</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>02/09/2026 08:35</t>
+          <t>17/08/2026 14:33</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>10/09/2026 20:46</t>
+          <t>18/08/2026 06:41</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2463,37 +2463,37 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0052981-77.2026.8.16.0000</t>
+          <t>0010345-55.2021.8.16.0038</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins</t>
+          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>17/08/2026 17:34</t>
+          <t>27/08/2026 20:13</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>17/08/2026 17:34</t>
+          <t>27/08/2026 20:13</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>18/08/2026 03:36</t>
+          <t>10/09/2026 20:59</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2510,37 +2510,37 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0130983-32.2024.8.16.0000</t>
+          <t>0011816-50.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Associação Criminosa | Adulteração de Sinal Identificador de Veículo Automotor | Desobediência | Prisão Preventiva</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>17/08/2026 14:23</t>
+          <t>17/08/2026 13:23</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>17/08/2026 14:23</t>
+          <t>17/08/2026 13:23</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>18/08/2026 03:39</t>
+          <t>18/08/2026 03:43</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2557,37 +2557,37 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0030192-26.2018.8.16.0013</t>
+          <t>0012180-37.2017.8.16.0194</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Embargos de Divergência em Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Roubo Majorado</t>
+          <t>Indenização por Dano Moral | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>13/10/2022</t>
+          <t>24/09/2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>17/08/2026 13:23</t>
+          <t>17/08/2026 13:03</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>17/08/2026 13:23</t>
+          <t>17/08/2026 13:03</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>18/08/2026 03:55</t>
+          <t>18/08/2026 19:20</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2604,37 +2604,37 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0005981-44.2023.8.16.0014</t>
+          <t>0014325-63.2017.8.16.0001</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Compra e Venda</t>
+          <t>Rescisão / Resolução | Perdas e Danos</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>03/07/2024</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>17/08/2026 14:43</t>
+          <t>18/08/2026 14:13</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>17/08/2026 14:43</t>
+          <t>18/08/2026 14:13</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>18/08/2026 04:01</t>
+          <t>18/08/2026 23:47</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2651,37 +2651,37 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0003523-75.2025.8.16.0146</t>
+          <t>0016302-44.2023.8.16.0013</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Crimes de Trânsito</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>17/08/2026 20:03</t>
+          <t>17/08/2026 18:33</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>17/08/2026 20:03</t>
+          <t>17/08/2026 18:33</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>18/08/2026 04:49</t>
+          <t>19/08/2026 02:36</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2698,7 +2698,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0004943-61.2022.8.16.0004</t>
+          <t>0017529-91.2012.8.16.0001</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2708,27 +2708,27 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ISS/ Imposto sobre Serviços</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>27/01/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>17/08/2026 15:25</t>
+          <t>27/08/2026 21:23</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>17/08/2026 15:25</t>
+          <t>27/08/2026 21:23</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>18/08/2026 05:23</t>
+          <t>07/09/2026 14:45</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2745,37 +2745,37 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0000855-53.2024.8.16.0151</t>
+          <t>0018929-14.2006.8.16.0014</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Roubo Majorado</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>23/05/2025</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>17/08/2026 15:53</t>
+          <t>17/08/2026 13:53</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>17/08/2026 15:53</t>
+          <t>17/08/2026 13:53</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>18/08/2026 07:13</t>
+          <t>18/08/2026 07:57</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2792,7 +2792,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0018929-14.2006.8.16.0014</t>
+          <t>0019003-57.2023.8.16.0019</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2802,27 +2802,27 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Tráfico de Drogas e Condutas Afins | Desclassificação</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>23/05/2025</t>
+          <t>02/10/2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>17/08/2026 13:53</t>
+          <t>17/08/2026 18:53</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>17/08/2026 13:53</t>
+          <t>17/08/2026 18:53</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>18/08/2026 07:57</t>
+          <t>19/08/2026 03:12</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2839,37 +2839,37 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0037878-35.2023.8.16.0000</t>
+          <t>0019271-25.2006.8.16.0014</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Comodato</t>
+          <t>Tratamento médico-hospitalar | Obrigação de Fazer / Não Fazer | Fornecimento de insumos</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>11/12/2024</t>
+          <t>30/12/1899</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>02/09/2026 14:53</t>
+          <t>18/08/2026 14:23</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>02/09/2026 14:53</t>
+          <t>18/08/2026 14:23</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>10/09/2026 20:57</t>
+          <t>18/08/2026 23:35</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2886,7 +2886,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0031845-47.2009.8.16.0185</t>
+          <t>0020939-43.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2896,27 +2896,27 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>Cobrança | Negativa de Prestação Jurisdicional | Cerceamento de Defesa</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/08/2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>26/08/2026 14:13</t>
+          <t>17/08/2026 14:13</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>26/08/2026 14:13</t>
+          <t>17/08/2026 14:13</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>10/09/2026 20:59</t>
+          <t>18/08/2026 03:37</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2933,7 +2933,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0010345-55.2021.8.16.0038</t>
+          <t>0021603-50.2020.8.16.0021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2943,27 +2943,27 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
+          <t>Locação de Imóvel</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>27/08/2026 20:13</t>
+          <t>17/08/2026 14:53</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>27/08/2026 20:13</t>
+          <t>17/08/2026 14:53</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>10/09/2026 20:59</t>
+          <t>20/08/2026 22:45</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2980,7 +2980,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0005250-69.2024.8.16.0028</t>
+          <t>0022909-70.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2995,22 +2995,22 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>09/12/2025</t>
+          <t>27/09/2024</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>18/08/2026 16:33</t>
+          <t>27/08/2026 15:59</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>18/08/2026 16:33</t>
+          <t>27/08/2026 15:59</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>10/09/2026 21:16</t>
+          <t>10/09/2026 21:14</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3027,7 +3027,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0000804-49.2022.8.16.0139</t>
+          <t>0023731-33.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3037,27 +3037,27 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Violência Psicológica contra a Mulher | Regime inicial | Prova Ilícita | Cerceamento de Defesa</t>
+          <t>Indenização por Dano Moral | Liminar | Adequação da Ação / Procedimento</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>17/08/2026 15:33</t>
+          <t>17/08/2026 14:53</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>17/08/2026 15:33</t>
+          <t>17/08/2026 14:53</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>10/09/2026 21:16</t>
+          <t>18/08/2026 13:02</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3074,37 +3074,37 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0035488-24.2025.8.16.0000</t>
+          <t>0025685-85.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Contratos Bancários | Cessão de Crédito | Suspensão da Execução | Penhora / Depósito/ Avaliação</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>19/06/2024</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>27/08/2026 13:53</t>
+          <t>21/08/2026 14:43</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>27/08/2026 13:53</t>
+          <t>21/08/2026 14:43</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>10/09/2026 21:16</t>
+          <t>10/09/2026 20:44</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3121,37 +3121,37 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0061410-04.2024.8.16.0000</t>
+          <t>0026052-12.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/08/2024</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>28/08/2026 16:43</t>
+          <t>17/08/2026 14:13</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>28/08/2026 16:43</t>
+          <t>17/08/2026 14:13</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>10/09/2026 21:16</t>
+          <t>18/08/2026 13:26</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3168,37 +3168,37 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0047704-17.2025.8.16.0000</t>
+          <t>0028035-41.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>26/08/2026 15:23</t>
+          <t>02/09/2026 08:35</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>26/08/2026 15:23</t>
+          <t>02/09/2026 08:35</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>10/09/2026 21:29</t>
+          <t>10/09/2026 20:46</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3215,37 +3215,37 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0001107-89.2023.8.16.0119</t>
+          <t>0030192-26.2018.8.16.0013</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Embargos de Divergência em Recurso Especial</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Roubo Majorado</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>13/10/2022</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>27/08/2026 19:43</t>
+          <t>17/08/2026 13:23</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>27/08/2026 19:43</t>
+          <t>17/08/2026 13:23</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>07/09/2026 14:45</t>
+          <t>18/08/2026 03:55</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3262,7 +3262,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0115570-76.2024.8.16.0000</t>
+          <t>0031845-47.2009.8.16.0185</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3272,27 +3272,27 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Práticas Abusivas</t>
+          <t>Dívida Ativa (Execução Fiscal)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>27/08/2026 20:33</t>
+          <t>26/08/2026 14:13</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>27/08/2026 20:33</t>
+          <t>26/08/2026 14:13</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>07/09/2026 14:45</t>
+          <t>10/09/2026 20:59</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3309,7 +3309,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0101965-97.2023.8.16.0000</t>
+          <t>0035479-62.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3319,27 +3319,27 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Práticas Abusivas</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>29/10/2024</t>
+          <t>19/03/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>27/08/2026 21:43</t>
+          <t>17/08/2026 14:23</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>27/08/2026 21:43</t>
+          <t>17/08/2026 14:23</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>07/09/2026 14:45</t>
+          <t>18/08/2026 08:47</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3356,37 +3356,37 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0091159-95.2026.8.16.0000</t>
+          <t>0035488-24.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>01/09/2026 13:03</t>
+          <t>27/08/2026 13:53</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>01/09/2026 13:03</t>
+          <t>27/08/2026 13:53</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>07/09/2026 14:45</t>
+          <t>10/09/2026 21:16</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3403,7 +3403,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0062461-50.2024.8.16.0000</t>
+          <t>0035495-50.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3413,27 +3413,27 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Concurso de Credores</t>
+          <t>Evicção ou Vicio Redibitório | Indenização por Dano Moral | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>20/01/2026</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>27/08/2026 19:43</t>
+          <t>27/08/2026 21:33</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>27/08/2026 19:43</t>
+          <t>27/08/2026 21:33</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>07/09/2026 14:45</t>
+          <t>10/09/2026 20:46</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3450,7 +3450,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0025685-85.2023.8.16.0000</t>
+          <t>0037878-35.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3460,27 +3460,27 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Contratos Bancários | Cessão de Crédito | Suspensão da Execução | Penhora / Depósito/ Avaliação</t>
+          <t>Comodato</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>19/06/2024</t>
+          <t>11/12/2024</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>21/08/2026 14:43</t>
+          <t>02/09/2026 14:53</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>21/08/2026 14:43</t>
+          <t>02/09/2026 14:53</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>10/09/2026 20:44</t>
+          <t>10/09/2026 20:57</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3497,7 +3497,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0000163-44.2023.8.16.0004</t>
+          <t>0040013-83.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3507,27 +3507,27 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ICMS/ Imposto sobre Circulação de Mercadorias</t>
+          <t>Locação de Móvel</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>24/10/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>25/08/2026 16:23</t>
+          <t>18/08/2026 14:13</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>25/08/2026 16:23</t>
+          <t>18/08/2026 14:13</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>10/09/2026 20:44</t>
+          <t>19/08/2026 03:30</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3544,7 +3544,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0008854-86.2019.8.16.0004</t>
+          <t>0041319-84.2024.8.16.0001</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3554,27 +3554,27 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ICMS/ Imposto sobre Circulação de Mercadorias</t>
+          <t>Ingresso e Exclusão dos Sócios na Sociedade</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>26/05/2025</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>19/08/2026 14:33</t>
+          <t>17/08/2026 13:13</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>19/08/2026 14:33</t>
+          <t>17/08/2026 13:13</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>10/09/2026 20:46</t>
+          <t>18/08/2026 16:27</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3591,7 +3591,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0001878-68.2022.8.16.0130</t>
+          <t>0044188-91.2022.8.16.0000</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3601,27 +3601,27 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Seguro | Seguro</t>
+          <t>Cédula Hipotecária</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>14/02/2024</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>28/08/2026 21:43</t>
+          <t>17/08/2026 13:33</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>28/08/2026 21:43</t>
+          <t>17/08/2026 13:33</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>10/09/2026 20:46</t>
+          <t>18/08/2026 11:22</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3638,37 +3638,37 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0051721-96.2025.8.16.0000</t>
+          <t>0046238-58.2024.8.16.0182</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Pedido de Uniformização de Interpretação de Lei Criminal</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Residência Médica | Programas de Bolsas e Financiamento Estudantil com Recursos Públicos</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>03/04/2025</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>18/08/2026 14:13</t>
+          <t>18/08/2026 01:57</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>18/08/2026 14:13</t>
+          <t>18/08/2026 01:57</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>19/08/2026 02:59</t>
+          <t>18/08/2026 14:27</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3685,7 +3685,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0061924-46.2023.8.16.0014</t>
+          <t>0047704-17.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3695,27 +3695,27 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>17/08/2026 18:23</t>
+          <t>26/08/2026 15:23</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>17/08/2026 18:23</t>
+          <t>26/08/2026 15:23</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>19/08/2026 03:12</t>
+          <t>10/09/2026 21:29</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3732,7 +3732,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0040013-83.2024.8.16.0000</t>
+          <t>0051721-96.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Locação de Móvel</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>19/08/2026 03:30</t>
+          <t>19/08/2026 02:59</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3779,37 +3779,37 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0065776-52.2025.8.16.0000</t>
+          <t>0061410-04.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Ameaça | Prisão Preventiva | Violação de domicílio</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>18/08/2026 16:13</t>
+          <t>28/08/2026 16:43</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>18/08/2026 16:13</t>
+          <t>28/08/2026 16:43</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>19/08/2026 02:52</t>
+          <t>10/09/2026 21:16</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3826,7 +3826,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0002386-96.2009.8.16.0153</t>
+          <t>0061924-46.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3836,27 +3836,27 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>27/01/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>17/08/2026 13:33</t>
+          <t>17/08/2026 18:23</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>17/08/2026 13:33</t>
+          <t>17/08/2026 18:23</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>19/08/2026 02:47</t>
+          <t>19/08/2026 03:12</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3873,37 +3873,37 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0003762-42.2019.8.16.0194</t>
+          <t>0062461-50.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Obrigação de Fazer / Não Fazer</t>
+          <t>Concurso de Credores</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>05/05/2022</t>
+          <t>20/01/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>17/08/2026 14:13</t>
+          <t>27/08/2026 19:43</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>17/08/2026 14:13</t>
+          <t>27/08/2026 19:43</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>19/08/2026 02:36</t>
+          <t>07/09/2026 14:45</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3920,7 +3920,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0006265-81.2024.8.16.0090</t>
+          <t>0062940-43.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3930,27 +3930,27 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Estelionato contra Idoso</t>
+          <t>Dissolução</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>17/08/2026 15:53</t>
+          <t>17/08/2026 14:23</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>17/08/2026 15:53</t>
+          <t>17/08/2026 14:23</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>19/08/2026 01:56</t>
+          <t>18/08/2026 15:33</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3967,7 +3967,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0019271-25.2006.8.16.0014</t>
+          <t>0064838-91.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3977,27 +3977,27 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Tratamento médico-hospitalar | Obrigação de Fazer / Não Fazer | Fornecimento de insumos</t>
+          <t>Servidores Inativos | Requisição de Pequeno Valor - RPV</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>30/12/1899</t>
+          <t>23/02/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>18/08/2026 14:23</t>
+          <t>17/08/2026 14:03</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>18/08/2026 14:23</t>
+          <t>17/08/2026 14:03</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>18/08/2026 23:35</t>
+          <t>18/08/2026 13:13</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -4014,37 +4014,37 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0014325-63.2017.8.16.0001</t>
+          <t>0065092-93.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Rescisão / Resolução | Perdas e Danos</t>
+          <t>Homicídio Qualificado | Crime Tentado</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>03/07/2024</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>18/08/2026 14:13</t>
+          <t>17/08/2026 18:43</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>18/08/2026 14:13</t>
+          <t>17/08/2026 18:43</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>18/08/2026 23:47</t>
+          <t>18/08/2026 10:25</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4061,37 +4061,37 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0000982-42.2013.8.16.0097</t>
+          <t>0065776-52.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Embargos de Divergência em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Produto Impróprio</t>
+          <t>Ameaça | Prisão Preventiva | Violação de domicílio</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>19/06/2024</t>
+          <t>29/09/2025</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>17/08/2026 15:03</t>
+          <t>18/08/2026 16:13</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>17/08/2026 15:03</t>
+          <t>18/08/2026 16:13</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>18/08/2026 21:59</t>
+          <t>19/08/2026 02:52</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -4108,37 +4108,37 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0002396-07.2022.8.16.0147</t>
+          <t>0066120-96.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Oferta e Publicidade | Jogos / Sorteios / Promoções comerciais</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>17/08/2026 16:53</t>
+          <t>17/08/2026 17:13</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>17/08/2026 16:53</t>
+          <t>17/08/2026 17:13</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>18/08/2026 20:48</t>
+          <t>18/08/2026 11:44</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4155,37 +4155,37 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0089924-98.2023.8.16.0000</t>
+          <t>0068649-22.2021.8.16.0014</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Embargos de Divergência em Agravo em Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Inventário e Partilha | Bem de Família Legal</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>24/04/2025</t>
+          <t>14/10/2025</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>17/08/2026 14:03</t>
+          <t>17/08/2026 13:33</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>17/08/2026 14:03</t>
+          <t>17/08/2026 13:33</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>18/08/2026 17:06</t>
+          <t>18/08/2026 13:38</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4202,37 +4202,37 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0002499-91.2019.8.16.0123</t>
+          <t>0081354-89.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Indenização por Dano Moral | Penhora / Depósito/ Avaliação | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>05/03/2024</t>
+          <t>26/09/2025</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>18/08/2026 13:43</t>
+          <t>31/08/2026 16:43</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>18/08/2026 13:43</t>
+          <t>31/08/2026 16:43</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>18/08/2026 17:07</t>
+          <t>10/09/2026 21:29</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4249,7 +4249,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0020939-43.2024.8.16.0000</t>
+          <t>0083650-50.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4259,27 +4259,27 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Cobrança | Negativa de Prestação Jurisdicional | Cerceamento de Defesa</t>
+          <t>Promessa de Compra e Venda | Esbulho / Turbação / Ameaça | Requerimento de Reintegração de Posse</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>12/08/2025</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>17/08/2026 14:13</t>
+          <t>27/08/2026 19:53</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>17/08/2026 14:13</t>
+          <t>27/08/2026 19:53</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>18/08/2026 03:37</t>
+          <t>07/09/2026 14:46</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4296,37 +4296,37 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0001644-85.2024.8.16.0140</t>
+          <t>0089924-98.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Embargos de Divergência em Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Alienação Fiduciária</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>23/02/2026</t>
+          <t>24/04/2025</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>17/08/2026 14:43</t>
+          <t>17/08/2026 14:03</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>17/08/2026 14:43</t>
+          <t>17/08/2026 14:03</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>18/08/2026 03:39</t>
+          <t>18/08/2026 17:06</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4343,7 +4343,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0011816-50.2026.8.16.0000</t>
+          <t>0091159-95.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4353,27 +4353,27 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Associação Criminosa | Adulteração de Sinal Identificador de Veículo Automotor | Desobediência | Prisão Preventiva</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>17/08/2026 13:23</t>
+          <t>01/09/2026 13:03</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>17/08/2026 13:23</t>
+          <t>01/09/2026 13:03</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>18/08/2026 03:43</t>
+          <t>07/09/2026 14:45</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4390,7 +4390,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0008942-75.2022.8.16.0148</t>
+          <t>0091213-32.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Recuperação judicial e Falência</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>18/08/2026 06:41</t>
+          <t>18/08/2026 10:29</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4437,37 +4437,37 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0000576-36.2025.8.16.0053</t>
+          <t>0093139-77.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Promessa de Compra e Venda | Rescisão / Resolução</t>
+          <t>Seqüestro e cárcere privado | Crimes de Tortura | Lesão Cometida em Razão da Condição de Mulher | Ameaça</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>10/04/2025</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>17/08/2026 13:23</t>
+          <t>17/08/2026 17:23</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>17/08/2026 13:23</t>
+          <t>17/08/2026 17:23</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>18/08/2026 08:14</t>
+          <t>18/08/2026 22:58</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4484,7 +4484,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0000890-52.2009.8.16.0114</t>
+          <t>0094754-39.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4494,27 +4494,27 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Peculato</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>06/10/2023</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>17/08/2026 14:43</t>
+          <t>17/08/2026 15:53</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>17/08/2026 14:43</t>
+          <t>17/08/2026 15:53</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>18/08/2026 08:14</t>
+          <t>18/08/2026 15:11</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4531,7 +4531,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0035479-62.2025.8.16.0000</t>
+          <t>0101965-97.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4541,27 +4541,27 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Práticas Abusivas</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>29/10/2024</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>17/08/2026 14:23</t>
+          <t>27/08/2026 21:43</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>17/08/2026 14:23</t>
+          <t>27/08/2026 21:43</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>18/08/2026 08:47</t>
+          <t>07/09/2026 14:45</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4578,7 +4578,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0091213-32.2024.8.16.0000</t>
+          <t>0106494-28.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4588,27 +4588,27 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Recuperação judicial e Falência</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>08/12/2025</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>17/08/2026 14:33</t>
+          <t>17/08/2026 13:33</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>17/08/2026 14:33</t>
+          <t>17/08/2026 13:33</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>18/08/2026 10:29</t>
+          <t>18/08/2026 12:05</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4625,37 +4625,37 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0044188-91.2022.8.16.0000</t>
+          <t>0109932-62.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Cédula Hipotecária</t>
+          <t>Prescrição e Decadência</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>14/02/2024</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>17/08/2026 13:33</t>
+          <t>24/08/2026 16:53</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>17/08/2026 13:33</t>
+          <t>24/08/2026 16:53</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>18/08/2026 11:22</t>
+          <t>10/09/2026 21:16</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4672,7 +4672,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0001611-17.2023.8.16.0048</t>
+          <t>0115570-76.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4682,27 +4682,27 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Pagamento com Sub-rogação | Inexequibilidade do Título / Inexigibilidade da Obrigação</t>
+          <t>Práticas Abusivas</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>15/05/2025</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>17/08/2026 13:23</t>
+          <t>27/08/2026 20:33</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>17/08/2026 13:23</t>
+          <t>27/08/2026 20:33</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>18/08/2026 11:31</t>
+          <t>07/09/2026 14:45</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4719,7 +4719,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0002959-48.2022.8.16.0196</t>
+          <t>0126623-54.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4729,27 +4729,27 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Perigo para a vida ou saúde de outrem</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>17/08/2026 17:43</t>
+          <t>17/08/2026 15:13</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>17/08/2026 17:43</t>
+          <t>17/08/2026 15:13</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>18/08/2026 11:44</t>
+          <t>19/08/2026 00:37</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4766,7 +4766,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0106494-28.2024.8.16.0000</t>
+          <t>0130983-32.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4776,27 +4776,27 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>08/12/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>17/08/2026 13:33</t>
+          <t>17/08/2026 14:23</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>17/08/2026 13:33</t>
+          <t>17/08/2026 14:23</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>18/08/2026 12:05</t>
+          <t>18/08/2026 03:39</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4813,37 +4813,37 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0003845-76.2024.8.16.0196</t>
+          <t>4002116-51.2025.8.16.4321</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Roubo Majorado</t>
+          <t>Remição</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>17/08/2026 16:13</t>
+          <t>25/08/2026 17:03</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>17/08/2026 16:13</t>
+          <t>25/08/2026 17:03</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>18/08/2026 12:17</t>
+          <t>10/09/2026 20:46</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4860,7 +4860,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0003308-26.2020.8.16.0033</t>
+          <t>4002176-24.2025.8.16.4321</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4870,27 +4870,27 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Progressão de Regime</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>17/08/2026 14:33</t>
+          <t>18/08/2026 16:03</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>17/08/2026 14:33</t>
+          <t>18/08/2026 16:03</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>18/08/2026 12:42</t>
+          <t>19/08/2026 02:18</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4899,288 +4899,6 @@
         </is>
       </c>
       <c r="I95" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>0026052-12.2023.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Indenização por Dano Moral</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>05/08/2024</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>17/08/2026 14:13</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>17/08/2026 14:13</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>18/08/2026 13:26</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>0004851-22.2024.8.16.0034</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>03/02/2026</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>17/08/2026 18:33</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>17/08/2026 18:33</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>18/08/2026 14:27</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>0062940-43.2024.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Dissolução</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>12/03/2026</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>17/08/2026 14:23</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>17/08/2026 14:23</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>18/08/2026 15:33</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>0004672-24.2019.8.16.0112</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Tráfico de Drogas e Condutas Afins | Crimes do Sistema Nacional de Armas</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>22/02/2024</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>17/08/2026 13:13</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>17/08/2026 13:13</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>18/08/2026 15:40</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>0002099-57.2023.8.16.0149</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Indenização por Dano Material</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>21/01/2026</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>17/08/2026 14:23</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>17/08/2026 14:23</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>18/08/2026 15:54</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>0018344-29.2024.8.16.0014</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Indenização por Dano Material</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>14/10/2025</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>25/08/2026 18:53</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>25/08/2026 18:53</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>10/09/2026 21:14</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>

--- a/docs/resultados.xlsx
+++ b/docs/resultados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I95"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -489,7 +489,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0000022-19.1988.8.16.0047</t>
+          <t>0000163-44.2023.8.16.0004</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -499,27 +499,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bancários</t>
+          <t>ICMS/ Imposto sobre Circulação de Mercadorias</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>19/08/2024</t>
+          <t>24/10/2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>17/08/2026 13:03</t>
+          <t>25/08/2026 16:23</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>17/08/2026 13:03</t>
+          <t>25/08/2026 16:23</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>19/08/2026 00:42</t>
+          <t>10/09/2026 20:44</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -536,7 +536,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0000163-44.2023.8.16.0004</t>
+          <t>0000245-29.2022.8.16.0160</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -546,27 +546,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ICMS/ Imposto sobre Circulação de Mercadorias</t>
+          <t>Contratos Bancários | Perdas e Danos | Cerceamento de Defesa | Provas | Obrigação de Entregar</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>24/10/2025</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>25/08/2026 16:23</t>
+          <t>10/09/2026 15:23</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>25/08/2026 16:23</t>
+          <t>10/09/2026 15:23</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10/09/2026 20:44</t>
+          <t>10/09/2026 21:24</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -583,7 +583,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0000174-98.2020.8.16.0062</t>
+          <t>0001107-89.2023.8.16.0119</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -593,27 +593,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>17/08/2026 18:03</t>
+          <t>27/08/2026 19:43</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>17/08/2026 18:03</t>
+          <t>27/08/2026 19:43</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>18/08/2026 23:33</t>
+          <t>07/09/2026 14:45</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,7 +630,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0000245-29.2022.8.16.0160</t>
+          <t>0001236-59.2021.8.16.0024</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -640,27 +640,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Contratos Bancários | Perdas e Danos | Cerceamento de Defesa | Provas | Obrigação de Entregar</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>10/09/2026 15:23</t>
+          <t>18/08/2026 10:52</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>10/09/2026 15:23</t>
+          <t>18/08/2026 10:52</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>10/09/2026 21:24</t>
+          <t>19/08/2026 02:47</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -677,37 +677,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0000576-36.2025.8.16.0053</t>
+          <t>0001878-68.2022.8.16.0130</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Promessa de Compra e Venda | Rescisão / Resolução</t>
+          <t>Seguro | Seguro</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>10/04/2025</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>17/08/2026 13:23</t>
+          <t>28/08/2026 21:43</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>17/08/2026 13:23</t>
+          <t>28/08/2026 21:43</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>18/08/2026 08:14</t>
+          <t>10/09/2026 20:46</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -724,37 +724,37 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0000627-67.2022.8.16.0048</t>
+          <t>0001893-39.2022.8.16.0097</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Crimes de Trânsito</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>02/09/2024</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>17/08/2026 13:53</t>
+          <t>18/08/2026 16:13</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>17/08/2026 13:53</t>
+          <t>18/08/2026 16:13</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>10/09/2026 21:29</t>
+          <t>19/08/2026 03:41</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -771,37 +771,37 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0000804-49.2022.8.16.0139</t>
+          <t>0002499-91.2019.8.16.0123</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Violência Psicológica contra a Mulher | Regime inicial | Prova Ilícita | Cerceamento de Defesa</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/03/2024</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>17/08/2026 15:33</t>
+          <t>18/08/2026 13:43</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>17/08/2026 15:33</t>
+          <t>18/08/2026 13:43</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>10/09/2026 21:16</t>
+          <t>18/08/2026 17:07</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -818,37 +818,37 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0000855-53.2024.8.16.0151</t>
+          <t>0002529-36.2021.8.16.0098</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Roubo Majorado</t>
+          <t>Dever de Informação | Irregularidade no atendimento</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>02/08/2024</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>17/08/2026 15:53</t>
+          <t>31/08/2026 11:38</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>17/08/2026 15:53</t>
+          <t>31/08/2026 11:38</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>18/08/2026 07:13</t>
+          <t>10/09/2026 21:14</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -865,7 +865,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0000890-52.2009.8.16.0114</t>
+          <t>0002951-67.2023.8.16.0089</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -875,27 +875,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Anulação e Correção de Provas / Questões</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>06/10/2023</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>17/08/2026 14:43</t>
+          <t>27/08/2026 21:33</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>17/08/2026 14:43</t>
+          <t>27/08/2026 21:33</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>18/08/2026 08:14</t>
+          <t>07/09/2026 14:45</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -912,37 +912,37 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0000982-42.2013.8.16.0097</t>
+          <t>0003634-04.2025.8.16.0035</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Embargos de Divergência em Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Produto Impróprio</t>
+          <t>Homicídio Qualificado</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>19/06/2024</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>17/08/2026 15:03</t>
+          <t>18/08/2026 16:43</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>17/08/2026 15:03</t>
+          <t>18/08/2026 16:43</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>18/08/2026 21:59</t>
+          <t>19/08/2026 04:08</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0001107-89.2023.8.16.0119</t>
+          <t>0003825-19.2024.8.16.0024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -969,27 +969,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>27/08/2026 19:43</t>
+          <t>26/08/2026 08:33</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>27/08/2026 19:43</t>
+          <t>26/08/2026 08:33</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>07/09/2026 14:45</t>
+          <t>10/09/2026 20:46</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1006,7 +1006,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0001236-59.2021.8.16.0024</t>
+          <t>0004591-16.2002.8.16.0001</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1016,27 +1016,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Compra e Venda</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>18/08/2026 10:52</t>
+          <t>04/09/2026 15:23</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>18/08/2026 10:52</t>
+          <t>04/09/2026 15:23</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>19/08/2026 02:47</t>
+          <t>07/09/2026 14:45</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1053,37 +1053,37 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0001611-17.2023.8.16.0048</t>
+          <t>0005115-18.2021.8.16.0075</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Pagamento com Sub-rogação | Inexequibilidade do Título / Inexigibilidade da Obrigação</t>
+          <t>Alienação Fiduciária</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>15/05/2025</t>
+          <t>11/09/2024</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>17/08/2026 13:23</t>
+          <t>28/08/2026 20:53</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>17/08/2026 13:23</t>
+          <t>28/08/2026 20:53</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>18/08/2026 11:31</t>
+          <t>10/09/2026 20:44</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1100,37 +1100,37 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0001644-85.2024.8.16.0140</t>
+          <t>0005250-69.2024.8.16.0028</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Alienação Fiduciária</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>23/02/2026</t>
+          <t>09/12/2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>17/08/2026 14:43</t>
+          <t>18/08/2026 16:33</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>17/08/2026 14:43</t>
+          <t>18/08/2026 16:33</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>18/08/2026 03:39</t>
+          <t>10/09/2026 21:16</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1147,37 +1147,37 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0001878-68.2022.8.16.0130</t>
+          <t>0005311-55.2024.8.16.0148</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Seguro | Seguro</t>
+          <t>Práticas Abusivas</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>28/08/2026 21:43</t>
+          <t>28/08/2026 15:13</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>28/08/2026 21:43</t>
+          <t>28/08/2026 15:13</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>10/09/2026 20:46</t>
+          <t>10/09/2026 21:16</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1194,7 +1194,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0001893-39.2022.8.16.0097</t>
+          <t>0007090-04.2023.8.16.0173</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1204,27 +1204,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Crimes de Trânsito</t>
+          <t>Compra e Venda</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>24/04/2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>18/08/2026 16:13</t>
+          <t>28/08/2026 12:56</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>18/08/2026 16:13</t>
+          <t>28/08/2026 12:56</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>19/08/2026 03:41</t>
+          <t>10/09/2026 20:44</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1241,7 +1241,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0002099-57.2023.8.16.0149</t>
+          <t>0008017-50.2023.8.16.0017</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1251,27 +1251,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Locação de Imóvel | Embargos de Terceiro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>29/01/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>17/08/2026 14:23</t>
+          <t>25/08/2026 17:43</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>17/08/2026 14:23</t>
+          <t>25/08/2026 17:43</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>18/08/2026 15:54</t>
+          <t>10/09/2026 21:14</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1288,7 +1288,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0002386-96.2009.8.16.0153</t>
+          <t>0008652-53.2021.8.16.0000</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1298,27 +1298,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Administração judicial</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>27/01/2026</t>
+          <t>20/07/2022</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>17/08/2026 13:33</t>
+          <t>04/09/2026 13:13</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>17/08/2026 13:33</t>
+          <t>04/09/2026 13:13</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>19/08/2026 02:47</t>
+          <t>07/09/2026 14:45</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1335,7 +1335,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0002396-07.2022.8.16.0147</t>
+          <t>0008854-86.2019.8.16.0004</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1345,27 +1345,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Oferta e Publicidade | Jogos / Sorteios / Promoções comerciais</t>
+          <t>ICMS/ Imposto sobre Circulação de Mercadorias</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>17/08/2026 16:53</t>
+          <t>19/08/2026 14:33</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>17/08/2026 16:53</t>
+          <t>19/08/2026 14:33</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>18/08/2026 20:48</t>
+          <t>10/09/2026 20:46</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1382,37 +1382,37 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0002499-91.2019.8.16.0123</t>
+          <t>0008932-19.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Administração judicial</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>05/03/2024</t>
+          <t>27/03/2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>18/08/2026 13:43</t>
+          <t>31/08/2026 19:43</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>18/08/2026 13:43</t>
+          <t>31/08/2026 19:43</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>18/08/2026 17:07</t>
+          <t>10/09/2026 20:44</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1429,37 +1429,37 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0002529-36.2021.8.16.0098</t>
+          <t>0009875-56.2015.8.16.0160</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dever de Informação | Irregularidade no atendimento</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>02/08/2024</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>31/08/2026 11:38</t>
+          <t>27/08/2026 15:53</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>31/08/2026 11:38</t>
+          <t>27/08/2026 15:53</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>10/09/2026 21:14</t>
+          <t>10/09/2026 21:16</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1476,7 +1476,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0002951-67.2023.8.16.0089</t>
+          <t>0010345-55.2021.8.16.0038</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1486,27 +1486,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Anulação e Correção de Provas / Questões</t>
+          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>27/08/2026 21:33</t>
+          <t>27/08/2026 20:13</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>27/08/2026 21:33</t>
+          <t>27/08/2026 20:13</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>07/09/2026 14:45</t>
+          <t>10/09/2026 20:59</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1523,7 +1523,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0002959-48.2022.8.16.0196</t>
+          <t>0010800-42.2018.8.16.0194</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1533,27 +1533,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Perigo para a vida ou saúde de outrem</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>17/08/2026 17:43</t>
+          <t>18/08/2026 15:23</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>17/08/2026 17:43</t>
+          <t>18/08/2026 15:23</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>18/08/2026 11:44</t>
+          <t>18/08/2026 23:35</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1570,7 +1570,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0003308-26.2020.8.16.0033</t>
+          <t>0011761-36.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1580,27 +1580,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Taxa de Licenciamento de Estabelecimento | Penhora no Rosto dos Autos</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>17/08/2026 14:33</t>
+          <t>02/09/2026 14:43</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>17/08/2026 14:33</t>
+          <t>02/09/2026 14:43</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>18/08/2026 12:42</t>
+          <t>10/09/2026 21:29</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1617,7 +1617,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0003523-75.2025.8.16.0146</t>
+          <t>0013567-29.2013.8.16.0000</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1627,27 +1627,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Sistema Financeiro da Habitação</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>17/08/2026 20:03</t>
+          <t>31/08/2026 19:23</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>17/08/2026 20:03</t>
+          <t>31/08/2026 19:23</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>18/08/2026 04:49</t>
+          <t>10/09/2026 20:59</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1664,37 +1664,37 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0003762-42.2019.8.16.0194</t>
+          <t>0014002-49.2013.8.16.0017</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Embargos de Divergência em Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Obrigação de Fazer / Não Fazer</t>
+          <t>Vícios de Construção</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>05/05/2022</t>
+          <t>24/05/2024</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>17/08/2026 14:13</t>
+          <t>27/08/2026 19:03</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>17/08/2026 14:13</t>
+          <t>27/08/2026 19:03</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>19/08/2026 02:36</t>
+          <t>10/09/2026 20:44</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1711,37 +1711,37 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0003825-19.2024.8.16.0024</t>
+          <t>0014325-63.2017.8.16.0001</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Rescisão / Resolução | Perdas e Danos</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/07/2024</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>26/08/2026 08:33</t>
+          <t>18/08/2026 14:13</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>26/08/2026 08:33</t>
+          <t>18/08/2026 14:13</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>10/09/2026 20:46</t>
+          <t>18/08/2026 23:47</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1758,37 +1758,37 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0003845-76.2024.8.16.0196</t>
+          <t>0014915-64.2009.8.16.0019</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Roubo Majorado</t>
+          <t>Espécies de Títulos de Crédito | Cédula Hipotecária</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>27/11/2020</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>17/08/2026 16:13</t>
+          <t>18/08/2026 14:23</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>17/08/2026 16:13</t>
+          <t>18/08/2026 14:23</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>18/08/2026 12:17</t>
+          <t>18/08/2026 20:21</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1805,7 +1805,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0004410-05.2022.8.16.0004</t>
+          <t>0017529-91.2012.8.16.0001</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1815,27 +1815,27 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Equilíbrio Financeiro</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>27/01/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>17/08/2026 14:43</t>
+          <t>27/08/2026 21:23</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>17/08/2026 14:43</t>
+          <t>27/08/2026 21:23</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>18/08/2026 12:55</t>
+          <t>07/09/2026 14:45</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1852,37 +1852,37 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0004672-24.2019.8.16.0112</t>
+          <t>0018344-29.2024.8.16.0014</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Crimes do Sistema Nacional de Armas</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>22/02/2024</t>
+          <t>14/10/2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>17/08/2026 13:13</t>
+          <t>25/08/2026 18:53</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>17/08/2026 13:13</t>
+          <t>25/08/2026 18:53</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>18/08/2026 15:40</t>
+          <t>10/09/2026 21:14</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1899,7 +1899,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0004820-79.2022.8.16.0031</t>
+          <t>0019271-25.2006.8.16.0014</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1909,27 +1909,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Posse</t>
+          <t>Tratamento médico-hospitalar | Obrigação de Fazer / Não Fazer | Fornecimento de insumos</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>30/12/1899</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>17/08/2026 15:03</t>
+          <t>18/08/2026 14:23</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>17/08/2026 15:03</t>
+          <t>18/08/2026 14:23</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>18/08/2026 11:03</t>
+          <t>18/08/2026 23:35</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1946,7 +1946,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0004851-22.2024.8.16.0034</t>
+          <t>0022909-70.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1961,22 +1961,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>03/02/2026</t>
+          <t>27/09/2024</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>17/08/2026 18:33</t>
+          <t>27/08/2026 15:59</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>17/08/2026 18:33</t>
+          <t>27/08/2026 15:59</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>18/08/2026 14:27</t>
+          <t>10/09/2026 21:14</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1993,37 +1993,37 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0004943-61.2022.8.16.0004</t>
+          <t>0025685-85.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ISS/ Imposto sobre Serviços</t>
+          <t>Contratos Bancários | Cessão de Crédito | Suspensão da Execução | Penhora / Depósito/ Avaliação</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>19/06/2024</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>17/08/2026 15:25</t>
+          <t>21/08/2026 14:43</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>17/08/2026 15:25</t>
+          <t>21/08/2026 14:43</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>18/08/2026 05:23</t>
+          <t>10/09/2026 20:44</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2040,37 +2040,37 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0005250-69.2024.8.16.0028</t>
+          <t>0028035-41.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>09/12/2025</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>18/08/2026 16:33</t>
+          <t>02/09/2026 08:35</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>18/08/2026 16:33</t>
+          <t>02/09/2026 08:35</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>10/09/2026 21:16</t>
+          <t>10/09/2026 20:46</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2087,7 +2087,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0005311-55.2024.8.16.0148</t>
+          <t>0031845-47.2009.8.16.0185</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2097,27 +2097,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Práticas Abusivas</t>
+          <t>Dívida Ativa (Execução Fiscal)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>28/08/2026 15:13</t>
+          <t>26/08/2026 14:13</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>28/08/2026 15:13</t>
+          <t>26/08/2026 14:13</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>10/09/2026 21:16</t>
+          <t>10/09/2026 20:59</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2134,7 +2134,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0005981-44.2023.8.16.0014</t>
+          <t>0035488-24.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2144,27 +2144,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Compra e Venda</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>17/08/2026 14:43</t>
+          <t>27/08/2026 13:53</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>17/08/2026 14:43</t>
+          <t>27/08/2026 13:53</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>18/08/2026 04:01</t>
+          <t>10/09/2026 21:16</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2181,7 +2181,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0006265-81.2024.8.16.0090</t>
+          <t>0035495-50.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2191,27 +2191,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Estelionato contra Idoso</t>
+          <t>Evicção ou Vicio Redibitório | Indenização por Dano Moral | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>17/08/2026 15:53</t>
+          <t>27/08/2026 21:33</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>17/08/2026 15:53</t>
+          <t>27/08/2026 21:33</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>19/08/2026 01:56</t>
+          <t>10/09/2026 20:46</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2228,37 +2228,37 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0007090-04.2023.8.16.0173</t>
+          <t>0037878-35.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Compra e Venda</t>
+          <t>Comodato</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>24/04/2025</t>
+          <t>11/12/2024</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>28/08/2026 12:56</t>
+          <t>02/09/2026 14:53</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>28/08/2026 12:56</t>
+          <t>02/09/2026 14:53</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>10/09/2026 20:44</t>
+          <t>10/09/2026 20:57</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2275,7 +2275,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0008017-50.2023.8.16.0017</t>
+          <t>0040013-83.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2285,27 +2285,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Locação de Imóvel | Embargos de Terceiro</t>
+          <t>Locação de Móvel</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>25/08/2026 17:43</t>
+          <t>18/08/2026 14:13</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>25/08/2026 17:43</t>
+          <t>18/08/2026 14:13</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>10/09/2026 21:14</t>
+          <t>19/08/2026 03:30</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2322,37 +2322,37 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0008652-53.2021.8.16.0000</t>
+          <t>0046238-58.2024.8.16.0182</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Pedido de Uniformização de Interpretação de Lei Criminal</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Administração judicial</t>
+          <t>Residência Médica | Programas de Bolsas e Financiamento Estudantil com Recursos Públicos</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>20/07/2022</t>
+          <t>03/04/2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>04/09/2026 13:13</t>
+          <t>18/08/2026 01:57</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>04/09/2026 13:13</t>
+          <t>18/08/2026 01:57</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>07/09/2026 14:45</t>
+          <t>18/08/2026 14:27</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2369,7 +2369,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0008854-86.2019.8.16.0004</t>
+          <t>0046534-44.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2379,27 +2379,27 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ICMS/ Imposto sobre Circulação de Mercadorias</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>26/11/2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>19/08/2026 14:33</t>
+          <t>27/08/2026 16:00</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>19/08/2026 14:33</t>
+          <t>27/08/2026 16:00</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>10/09/2026 20:46</t>
+          <t>07/09/2026 14:45</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2416,7 +2416,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0008942-75.2022.8.16.0148</t>
+          <t>0047704-17.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2426,27 +2426,27 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>17/08/2026 14:33</t>
+          <t>26/08/2026 15:23</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>17/08/2026 14:33</t>
+          <t>26/08/2026 15:23</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>18/08/2026 06:41</t>
+          <t>10/09/2026 21:29</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2463,7 +2463,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0010345-55.2021.8.16.0038</t>
+          <t>0051721-96.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2473,27 +2473,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>27/08/2026 20:13</t>
+          <t>18/08/2026 14:13</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>27/08/2026 20:13</t>
+          <t>18/08/2026 14:13</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>10/09/2026 20:59</t>
+          <t>19/08/2026 02:59</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2510,17 +2510,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0011816-50.2026.8.16.0000</t>
+          <t>0061410-04.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Associação Criminosa | Adulteração de Sinal Identificador de Veículo Automotor | Desobediência | Prisão Preventiva</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2530,17 +2530,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>17/08/2026 13:23</t>
+          <t>28/08/2026 16:43</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>17/08/2026 13:23</t>
+          <t>28/08/2026 16:43</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>18/08/2026 03:43</t>
+          <t>10/09/2026 21:16</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2557,7 +2557,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0012180-37.2017.8.16.0194</t>
+          <t>0062461-50.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2567,27 +2567,27 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Indenização por Dano Material</t>
+          <t>Concurso de Credores</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>24/09/2025</t>
+          <t>20/01/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>17/08/2026 13:03</t>
+          <t>27/08/2026 19:43</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>17/08/2026 13:03</t>
+          <t>27/08/2026 19:43</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>18/08/2026 19:20</t>
+          <t>07/09/2026 14:45</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2604,37 +2604,37 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0014325-63.2017.8.16.0001</t>
+          <t>0065776-52.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Rescisão / Resolução | Perdas e Danos</t>
+          <t>Ameaça | Prisão Preventiva | Violação de domicílio</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>03/07/2024</t>
+          <t>29/09/2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>18/08/2026 14:13</t>
+          <t>18/08/2026 16:13</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>18/08/2026 14:13</t>
+          <t>18/08/2026 16:13</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>18/08/2026 23:47</t>
+          <t>19/08/2026 02:52</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2651,7 +2651,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0016302-44.2023.8.16.0013</t>
+          <t>0081354-89.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2661,27 +2661,27 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Crimes de Trânsito</t>
+          <t>Indenização por Dano Moral | Penhora / Depósito/ Avaliação | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>26/09/2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>17/08/2026 18:33</t>
+          <t>31/08/2026 16:43</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>17/08/2026 18:33</t>
+          <t>31/08/2026 16:43</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>19/08/2026 02:36</t>
+          <t>10/09/2026 21:29</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2698,7 +2698,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0017529-91.2012.8.16.0001</t>
+          <t>0083650-50.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2708,27 +2708,27 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Promessa de Compra e Venda | Esbulho / Turbação / Ameaça | Requerimento de Reintegração de Posse</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>27/01/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>27/08/2026 21:23</t>
+          <t>27/08/2026 19:53</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>27/08/2026 21:23</t>
+          <t>27/08/2026 19:53</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>07/09/2026 14:45</t>
+          <t>07/09/2026 14:46</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2745,37 +2745,37 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0018929-14.2006.8.16.0014</t>
+          <t>0091159-95.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>23/05/2025</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>17/08/2026 13:53</t>
+          <t>01/09/2026 13:03</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>17/08/2026 13:53</t>
+          <t>01/09/2026 13:03</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>18/08/2026 07:57</t>
+          <t>07/09/2026 14:45</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2792,37 +2792,37 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0019003-57.2023.8.16.0019</t>
+          <t>0099048-08.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Desclassificação</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>02/10/2025</t>
+          <t>04/10/2024</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>17/08/2026 18:53</t>
+          <t>18/08/2026 13:13</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>17/08/2026 18:53</t>
+          <t>18/08/2026 13:13</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>19/08/2026 03:12</t>
+          <t>19/08/2026 00:46</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2839,7 +2839,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0019271-25.2006.8.16.0014</t>
+          <t>0100027-96.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2849,27 +2849,27 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tratamento médico-hospitalar | Obrigação de Fazer / Não Fazer | Fornecimento de insumos</t>
+          <t>Dívida Ativa (Execução Fiscal)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>30/12/1899</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>18/08/2026 14:23</t>
+          <t>04/09/2026 14:03</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>18/08/2026 14:23</t>
+          <t>04/09/2026 14:03</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>18/08/2026 23:35</t>
+          <t>07/09/2026 14:45</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2886,7 +2886,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0020939-43.2024.8.16.0000</t>
+          <t>0101965-97.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2896,27 +2896,27 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Cobrança | Negativa de Prestação Jurisdicional | Cerceamento de Defesa</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>12/08/2025</t>
+          <t>29/10/2024</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>17/08/2026 14:13</t>
+          <t>27/08/2026 21:43</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>17/08/2026 14:13</t>
+          <t>27/08/2026 21:43</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>18/08/2026 03:37</t>
+          <t>07/09/2026 14:45</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2933,7 +2933,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0021603-50.2020.8.16.0021</t>
+          <t>0107197-56.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2943,27 +2943,27 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Locação de Imóvel</t>
+          <t>Despejo por Inadimplemento</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>17/08/2026 14:53</t>
+          <t>27/08/2026 21:33</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>17/08/2026 14:53</t>
+          <t>27/08/2026 21:33</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20/08/2026 22:45</t>
+          <t>07/09/2026 14:45</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2980,37 +2980,37 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0022909-70.2023.8.16.0014</t>
+          <t>0109932-62.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Prescrição e Decadência</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>27/09/2024</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>27/08/2026 15:59</t>
+          <t>24/08/2026 16:53</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>27/08/2026 15:59</t>
+          <t>24/08/2026 16:53</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>10/09/2026 21:14</t>
+          <t>10/09/2026 21:16</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3027,7 +3027,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0023731-33.2025.8.16.0000</t>
+          <t>0115570-76.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3037,27 +3037,27 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Liminar | Adequação da Ação / Procedimento</t>
+          <t>Práticas Abusivas</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>17/08/2026 14:53</t>
+          <t>27/08/2026 20:33</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>17/08/2026 14:53</t>
+          <t>27/08/2026 20:33</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>18/08/2026 13:02</t>
+          <t>07/09/2026 14:45</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3074,37 +3074,37 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0025685-85.2023.8.16.0000</t>
+          <t>0133047-15.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Contratos Bancários | Cessão de Crédito | Suspensão da Execução | Penhora / Depósito/ Avaliação</t>
+          <t>Comissão</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>19/06/2024</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>21/08/2026 14:43</t>
+          <t>01/09/2026 16:23</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>21/08/2026 14:43</t>
+          <t>01/09/2026 16:23</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>10/09/2026 20:44</t>
+          <t>10/09/2026 21:14</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3121,7 +3121,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0026052-12.2023.8.16.0000</t>
+          <t>4002116-51.2025.8.16.4321</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3131,27 +3131,27 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Remição</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>05/08/2024</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>17/08/2026 14:13</t>
+          <t>25/08/2026 17:03</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>17/08/2026 14:13</t>
+          <t>25/08/2026 17:03</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>18/08/2026 13:26</t>
+          <t>10/09/2026 20:46</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3168,37 +3168,37 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0028035-41.2026.8.16.0000</t>
+          <t>4002176-24.2025.8.16.4321</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins</t>
+          <t>Progressão de Regime</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>02/09/2026 08:35</t>
+          <t>18/08/2026 16:03</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>02/09/2026 08:35</t>
+          <t>18/08/2026 16:03</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>10/09/2026 20:46</t>
+          <t>19/08/2026 02:18</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3207,1698 +3207,6 @@
         </is>
       </c>
       <c r="I59" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>0030192-26.2018.8.16.0013</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Embargos de Divergência em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Roubo Majorado</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>13/10/2022</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>17/08/2026 13:23</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>17/08/2026 13:23</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>18/08/2026 03:55</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>0031845-47.2009.8.16.0185</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>26/08/2026 14:13</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>26/08/2026 14:13</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>10/09/2026 20:59</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>0035479-62.2025.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Práticas Abusivas</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>19/03/2026</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>17/08/2026 14:23</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>17/08/2026 14:23</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>18/08/2026 08:47</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>0035488-24.2025.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Cédula de Crédito Bancário</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>27/08/2026 13:53</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>27/08/2026 13:53</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>10/09/2026 21:16</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>0035495-50.2024.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Evicção ou Vicio Redibitório | Indenização por Dano Moral | Indenização por Dano Material</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>09/03/2026</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>27/08/2026 21:33</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>27/08/2026 21:33</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>10/09/2026 20:46</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>0037878-35.2023.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Comodato</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>11/12/2024</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>02/09/2026 14:53</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>02/09/2026 14:53</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>10/09/2026 20:57</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>0040013-83.2024.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Locação de Móvel</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>12/12/2025</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>18/08/2026 14:13</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>18/08/2026 14:13</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>19/08/2026 03:30</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>0041319-84.2024.8.16.0001</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ingresso e Exclusão dos Sócios na Sociedade</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>26/05/2025</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>17/08/2026 13:13</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>17/08/2026 13:13</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>18/08/2026 16:27</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>0044188-91.2022.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Cédula Hipotecária</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>14/02/2024</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>17/08/2026 13:33</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>17/08/2026 13:33</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>18/08/2026 11:22</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>0046238-58.2024.8.16.0182</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Pedido de Uniformização de Interpretação de Lei Criminal</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Residência Médica | Programas de Bolsas e Financiamento Estudantil com Recursos Públicos</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>03/04/2025</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>18/08/2026 01:57</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>18/08/2026 01:57</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>18/08/2026 14:27</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>0047704-17.2025.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Indenização por Dano Material</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>26/08/2026 15:23</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>26/08/2026 15:23</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>10/09/2026 21:29</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>0051721-96.2025.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Prestação de Serviços</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>12/03/2026</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>18/08/2026 14:13</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>18/08/2026 14:13</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>19/08/2026 02:59</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>0061410-04.2024.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Contratos Bancários</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>28/08/2026 16:43</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>28/08/2026 16:43</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>10/09/2026 21:16</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>0061924-46.2023.8.16.0014</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>17/08/2026 18:23</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>17/08/2026 18:23</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>19/08/2026 03:12</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>0062461-50.2024.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Concurso de Credores</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>20/01/2026</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>27/08/2026 19:43</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>27/08/2026 19:43</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>07/09/2026 14:45</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>0062940-43.2024.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Dissolução</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>12/03/2026</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>17/08/2026 14:23</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>17/08/2026 14:23</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>18/08/2026 15:33</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>0064838-91.2024.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Servidores Inativos | Requisição de Pequeno Valor - RPV</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>23/02/2026</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>17/08/2026 14:03</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>17/08/2026 14:03</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>18/08/2026 13:13</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>0065092-93.2026.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Homicídio Qualificado | Crime Tentado</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>17/08/2026 18:43</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>17/08/2026 18:43</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>18/08/2026 10:25</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>0065776-52.2025.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Ameaça | Prisão Preventiva | Violação de domicílio</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>29/09/2025</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>18/08/2026 16:13</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>18/08/2026 16:13</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>19/08/2026 02:52</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>0066120-96.2026.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>25/06/2026</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>17/08/2026 17:13</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>17/08/2026 17:13</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>18/08/2026 11:44</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>0068649-22.2021.8.16.0014</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Inventário e Partilha | Bem de Família Legal</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>14/10/2025</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>17/08/2026 13:33</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>17/08/2026 13:33</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>18/08/2026 13:38</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>0081354-89.2024.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Indenização por Dano Moral | Penhora / Depósito/ Avaliação | Indenização por Dano Material</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>26/09/2025</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>31/08/2026 16:43</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>31/08/2026 16:43</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>10/09/2026 21:29</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>0083650-50.2025.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Promessa de Compra e Venda | Esbulho / Turbação / Ameaça | Requerimento de Reintegração de Posse</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>27/08/2026 19:53</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>27/08/2026 19:53</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>07/09/2026 14:46</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>0089924-98.2023.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Embargos de Divergência em Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Contratos Bancários</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>24/04/2025</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>17/08/2026 14:03</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>17/08/2026 14:03</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>18/08/2026 17:06</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>0091159-95.2026.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>20/08/2026</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>01/09/2026 13:03</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>01/09/2026 13:03</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>07/09/2026 14:45</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>0091213-32.2024.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Recuperação judicial e Falência</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>04/03/2026</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>17/08/2026 14:33</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>17/08/2026 14:33</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>18/08/2026 10:29</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>0093139-77.2026.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Seqüestro e cárcere privado | Crimes de Tortura | Lesão Cometida em Razão da Condição de Mulher | Ameaça</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>24/07/2026</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>17/08/2026 17:23</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>17/08/2026 17:23</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>18/08/2026 22:58</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>0094754-39.2025.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Peculato</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>07/07/2026</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>17/08/2026 15:53</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>17/08/2026 15:53</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>18/08/2026 15:11</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>0101965-97.2023.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Contratos Bancários</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>29/10/2024</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>27/08/2026 21:43</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>27/08/2026 21:43</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>07/09/2026 14:45</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>0106494-28.2024.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Prestação de Serviços</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>08/12/2025</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>17/08/2026 13:33</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>17/08/2026 13:33</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>18/08/2026 12:05</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>0109932-62.2024.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Prescrição e Decadência</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>24/08/2026 16:53</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>24/08/2026 16:53</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>10/09/2026 21:16</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>0115570-76.2024.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Práticas Abusivas</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>27/08/2026 20:33</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>27/08/2026 20:33</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>07/09/2026 14:45</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>0126623-54.2024.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Cédula de Crédito Bancário</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>10/02/2026</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>17/08/2026 15:13</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>17/08/2026 15:13</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>19/08/2026 00:37</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>0130983-32.2024.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Contratos Bancários</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>12/12/2025</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>17/08/2026 14:23</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>17/08/2026 14:23</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>18/08/2026 03:39</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>4002116-51.2025.8.16.4321</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Remição</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>25/08/2026 17:03</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>25/08/2026 17:03</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>10/09/2026 20:46</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>4002176-24.2025.8.16.4321</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Progressão de Regime</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>16/12/2025</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>18/08/2026 16:03</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>18/08/2026 16:03</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>19/08/2026 02:18</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>

--- a/docs/resultados.xlsx
+++ b/docs/resultados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -630,37 +630,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0001236-59.2021.8.16.0024</t>
+          <t>0001878-68.2022.8.16.0130</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Seguro | Seguro</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>18/08/2026 10:52</t>
+          <t>28/08/2026 21:43</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>18/08/2026 10:52</t>
+          <t>28/08/2026 21:43</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>19/08/2026 02:47</t>
+          <t>10/09/2026 20:46</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -677,7 +677,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0001878-68.2022.8.16.0130</t>
+          <t>0002529-36.2021.8.16.0098</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -687,27 +687,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Seguro | Seguro</t>
+          <t>Dever de Informação | Irregularidade no atendimento</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>02/08/2024</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>28/08/2026 21:43</t>
+          <t>31/08/2026 11:38</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>28/08/2026 21:43</t>
+          <t>31/08/2026 11:38</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>10/09/2026 20:46</t>
+          <t>10/09/2026 21:14</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -724,7 +724,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0001893-39.2022.8.16.0097</t>
+          <t>0002951-67.2023.8.16.0089</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -734,27 +734,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Crimes de Trânsito</t>
+          <t>Anulação e Correção de Provas / Questões</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>18/08/2026 16:13</t>
+          <t>27/08/2026 21:33</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>18/08/2026 16:13</t>
+          <t>27/08/2026 21:33</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>19/08/2026 03:41</t>
+          <t>07/09/2026 14:45</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -771,37 +771,37 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0002499-91.2019.8.16.0123</t>
+          <t>0003825-19.2024.8.16.0024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>05/03/2024</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>18/08/2026 13:43</t>
+          <t>26/08/2026 08:33</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>18/08/2026 13:43</t>
+          <t>26/08/2026 08:33</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>18/08/2026 17:07</t>
+          <t>10/09/2026 20:46</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -818,37 +818,37 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0002529-36.2021.8.16.0098</t>
+          <t>0004591-16.2002.8.16.0001</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dever de Informação | Irregularidade no atendimento</t>
+          <t>Compra e Venda</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>02/08/2024</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>31/08/2026 11:38</t>
+          <t>04/09/2026 15:23</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>31/08/2026 11:38</t>
+          <t>04/09/2026 15:23</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>10/09/2026 21:14</t>
+          <t>07/09/2026 14:45</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -865,37 +865,37 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0002951-67.2023.8.16.0089</t>
+          <t>0005115-18.2021.8.16.0075</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Anulação e Correção de Provas / Questões</t>
+          <t>Alienação Fiduciária</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>11/09/2024</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>27/08/2026 21:33</t>
+          <t>28/08/2026 20:53</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>27/08/2026 21:33</t>
+          <t>28/08/2026 20:53</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>07/09/2026 14:45</t>
+          <t>10/09/2026 20:44</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -912,7 +912,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0003634-04.2025.8.16.0035</t>
+          <t>0005311-55.2024.8.16.0148</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -922,27 +922,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Homicídio Qualificado</t>
+          <t>Práticas Abusivas</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>18/08/2026 16:43</t>
+          <t>28/08/2026 15:13</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>18/08/2026 16:43</t>
+          <t>28/08/2026 15:13</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>19/08/2026 04:08</t>
+          <t>10/09/2026 21:16</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0003825-19.2024.8.16.0024</t>
+          <t>0007090-04.2023.8.16.0173</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -969,27 +969,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Compra e Venda</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>24/04/2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>26/08/2026 08:33</t>
+          <t>28/08/2026 12:56</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>26/08/2026 08:33</t>
+          <t>28/08/2026 12:56</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>10/09/2026 20:46</t>
+          <t>10/09/2026 20:44</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1006,7 +1006,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0004591-16.2002.8.16.0001</t>
+          <t>0008017-50.2023.8.16.0017</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1016,27 +1016,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Compra e Venda</t>
+          <t>Locação de Imóvel | Embargos de Terceiro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>29/01/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>04/09/2026 15:23</t>
+          <t>25/08/2026 17:43</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>04/09/2026 15:23</t>
+          <t>25/08/2026 17:43</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>07/09/2026 14:45</t>
+          <t>10/09/2026 21:14</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1053,37 +1053,37 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0005115-18.2021.8.16.0075</t>
+          <t>0008652-53.2021.8.16.0000</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Alienação Fiduciária</t>
+          <t>Administração judicial</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>11/09/2024</t>
+          <t>20/07/2022</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>28/08/2026 20:53</t>
+          <t>04/09/2026 13:13</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>28/08/2026 20:53</t>
+          <t>04/09/2026 13:13</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>10/09/2026 20:44</t>
+          <t>07/09/2026 14:45</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1100,37 +1100,37 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0005250-69.2024.8.16.0028</t>
+          <t>0008854-86.2019.8.16.0004</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>ICMS/ Imposto sobre Circulação de Mercadorias</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>09/12/2025</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>18/08/2026 16:33</t>
+          <t>19/08/2026 14:33</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>18/08/2026 16:33</t>
+          <t>19/08/2026 14:33</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>10/09/2026 21:16</t>
+          <t>10/09/2026 20:46</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1147,7 +1147,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0005311-55.2024.8.16.0148</t>
+          <t>0008932-19.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1157,27 +1157,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Práticas Abusivas</t>
+          <t>Administração judicial</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>27/03/2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>28/08/2026 15:13</t>
+          <t>31/08/2026 19:43</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>28/08/2026 15:13</t>
+          <t>31/08/2026 19:43</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>10/09/2026 21:16</t>
+          <t>10/09/2026 20:44</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1194,7 +1194,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0007090-04.2023.8.16.0173</t>
+          <t>0009875-56.2015.8.16.0160</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1204,27 +1204,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Compra e Venda</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>24/04/2025</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>28/08/2026 12:56</t>
+          <t>27/08/2026 15:53</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>28/08/2026 12:56</t>
+          <t>27/08/2026 15:53</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>10/09/2026 20:44</t>
+          <t>10/09/2026 21:16</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1241,7 +1241,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0008017-50.2023.8.16.0017</t>
+          <t>0010345-55.2021.8.16.0038</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1251,27 +1251,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Locação de Imóvel | Embargos de Terceiro</t>
+          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>25/08/2026 17:43</t>
+          <t>27/08/2026 20:13</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>25/08/2026 17:43</t>
+          <t>27/08/2026 20:13</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>10/09/2026 21:14</t>
+          <t>10/09/2026 20:59</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1288,7 +1288,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0008652-53.2021.8.16.0000</t>
+          <t>0011761-36.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1298,27 +1298,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Administração judicial</t>
+          <t>Taxa de Licenciamento de Estabelecimento | Penhora no Rosto dos Autos</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>20/07/2022</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>04/09/2026 13:13</t>
+          <t>02/09/2026 14:43</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>04/09/2026 13:13</t>
+          <t>02/09/2026 14:43</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>07/09/2026 14:45</t>
+          <t>10/09/2026 21:29</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1335,37 +1335,37 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0008854-86.2019.8.16.0004</t>
+          <t>0013567-29.2013.8.16.0000</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ICMS/ Imposto sobre Circulação de Mercadorias</t>
+          <t>Sistema Financeiro da Habitação</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>19/08/2026 14:33</t>
+          <t>31/08/2026 19:23</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>19/08/2026 14:33</t>
+          <t>31/08/2026 19:23</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>10/09/2026 20:46</t>
+          <t>10/09/2026 20:59</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1382,32 +1382,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0008932-19.2024.8.16.0000</t>
+          <t>0014002-49.2013.8.16.0017</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Embargos de Divergência em Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Administração judicial</t>
+          <t>Vícios de Construção</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>27/03/2025</t>
+          <t>24/05/2024</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>31/08/2026 19:43</t>
+          <t>27/08/2026 19:03</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>31/08/2026 19:43</t>
+          <t>27/08/2026 19:03</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1429,7 +1429,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0009875-56.2015.8.16.0160</t>
+          <t>0017529-91.2012.8.16.0001</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1439,27 +1439,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>27/01/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>27/08/2026 15:53</t>
+          <t>27/08/2026 21:23</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>27/08/2026 15:53</t>
+          <t>27/08/2026 21:23</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>10/09/2026 21:16</t>
+          <t>07/09/2026 14:45</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1476,7 +1476,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0010345-55.2021.8.16.0038</t>
+          <t>0018344-29.2024.8.16.0014</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1486,27 +1486,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>14/10/2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>27/08/2026 20:13</t>
+          <t>25/08/2026 18:53</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>27/08/2026 20:13</t>
+          <t>25/08/2026 18:53</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>10/09/2026 20:59</t>
+          <t>10/09/2026 21:14</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1523,37 +1523,37 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0010800-42.2018.8.16.0194</t>
+          <t>0022909-70.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>27/09/2024</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>18/08/2026 15:23</t>
+          <t>27/08/2026 15:59</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>18/08/2026 15:23</t>
+          <t>27/08/2026 15:59</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>18/08/2026 23:35</t>
+          <t>10/09/2026 21:14</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1570,37 +1570,37 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0011761-36.2025.8.16.0000</t>
+          <t>0025685-85.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Taxa de Licenciamento de Estabelecimento | Penhora no Rosto dos Autos</t>
+          <t>Contratos Bancários | Cessão de Crédito | Suspensão da Execução | Penhora / Depósito/ Avaliação</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>30/09/2025</t>
+          <t>19/06/2024</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>02/09/2026 14:43</t>
+          <t>21/08/2026 14:43</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>02/09/2026 14:43</t>
+          <t>21/08/2026 14:43</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>10/09/2026 21:29</t>
+          <t>10/09/2026 20:44</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1617,37 +1617,37 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0013567-29.2013.8.16.0000</t>
+          <t>0028035-41.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sistema Financeiro da Habitação</t>
+          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>31/08/2026 19:23</t>
+          <t>02/09/2026 08:35</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>31/08/2026 19:23</t>
+          <t>02/09/2026 08:35</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>10/09/2026 20:59</t>
+          <t>10/09/2026 20:46</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1664,37 +1664,37 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0014002-49.2013.8.16.0017</t>
+          <t>0031845-47.2009.8.16.0185</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Embargos de Divergência em Agravo em Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Vícios de Construção</t>
+          <t>Dívida Ativa (Execução Fiscal)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>24/05/2024</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>27/08/2026 19:03</t>
+          <t>26/08/2026 14:13</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>27/08/2026 19:03</t>
+          <t>26/08/2026 14:13</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>10/09/2026 20:44</t>
+          <t>10/09/2026 20:59</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1711,37 +1711,37 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0014325-63.2017.8.16.0001</t>
+          <t>0035488-24.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Rescisão / Resolução | Perdas e Danos</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>03/07/2024</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>18/08/2026 14:13</t>
+          <t>27/08/2026 13:53</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>18/08/2026 14:13</t>
+          <t>27/08/2026 13:53</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>18/08/2026 23:47</t>
+          <t>10/09/2026 21:16</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1758,37 +1758,37 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0014915-64.2009.8.16.0019</t>
+          <t>0035495-50.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Espécies de Títulos de Crédito | Cédula Hipotecária</t>
+          <t>Evicção ou Vicio Redibitório | Indenização por Dano Moral | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>27/11/2020</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>18/08/2026 14:23</t>
+          <t>27/08/2026 21:33</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>18/08/2026 14:23</t>
+          <t>27/08/2026 21:33</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>18/08/2026 20:21</t>
+          <t>10/09/2026 20:46</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1805,37 +1805,37 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0017529-91.2012.8.16.0001</t>
+          <t>0037878-35.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Comodato</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>27/01/2026</t>
+          <t>11/12/2024</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>27/08/2026 21:23</t>
+          <t>02/09/2026 14:53</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>27/08/2026 21:23</t>
+          <t>02/09/2026 14:53</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>07/09/2026 14:45</t>
+          <t>10/09/2026 20:57</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1852,7 +1852,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0018344-29.2024.8.16.0014</t>
+          <t>0046534-44.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1862,27 +1862,27 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>14/10/2025</t>
+          <t>26/11/2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>25/08/2026 18:53</t>
+          <t>27/08/2026 16:00</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>25/08/2026 18:53</t>
+          <t>27/08/2026 16:00</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>10/09/2026 21:14</t>
+          <t>07/09/2026 14:45</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1899,7 +1899,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0019271-25.2006.8.16.0014</t>
+          <t>0047704-17.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1909,27 +1909,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tratamento médico-hospitalar | Obrigação de Fazer / Não Fazer | Fornecimento de insumos</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>30/12/1899</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>18/08/2026 14:23</t>
+          <t>26/08/2026 15:23</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>18/08/2026 14:23</t>
+          <t>26/08/2026 15:23</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>18/08/2026 23:35</t>
+          <t>10/09/2026 21:29</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1946,37 +1946,37 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0022909-70.2023.8.16.0014</t>
+          <t>0061410-04.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>27/09/2024</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>27/08/2026 15:59</t>
+          <t>28/08/2026 16:43</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>27/08/2026 15:59</t>
+          <t>28/08/2026 16:43</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>10/09/2026 21:14</t>
+          <t>10/09/2026 21:16</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1993,37 +1993,37 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0025685-85.2023.8.16.0000</t>
+          <t>0062461-50.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Contratos Bancários | Cessão de Crédito | Suspensão da Execução | Penhora / Depósito/ Avaliação</t>
+          <t>Concurso de Credores</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>19/06/2024</t>
+          <t>20/01/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>21/08/2026 14:43</t>
+          <t>27/08/2026 19:43</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>21/08/2026 14:43</t>
+          <t>27/08/2026 19:43</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>10/09/2026 20:44</t>
+          <t>07/09/2026 14:45</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2040,37 +2040,37 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0028035-41.2026.8.16.0000</t>
+          <t>0081354-89.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins</t>
+          <t>Indenização por Dano Moral | Penhora / Depósito/ Avaliação | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/09/2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>02/09/2026 08:35</t>
+          <t>31/08/2026 16:43</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>02/09/2026 08:35</t>
+          <t>31/08/2026 16:43</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>10/09/2026 20:46</t>
+          <t>10/09/2026 21:29</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2087,7 +2087,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0031845-47.2009.8.16.0185</t>
+          <t>0083650-50.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2097,27 +2097,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>Promessa de Compra e Venda | Esbulho / Turbação / Ameaça | Requerimento de Reintegração de Posse</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>26/08/2026 14:13</t>
+          <t>27/08/2026 19:53</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>26/08/2026 14:13</t>
+          <t>27/08/2026 19:53</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>10/09/2026 20:59</t>
+          <t>07/09/2026 14:46</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2134,37 +2134,37 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0035488-24.2025.8.16.0000</t>
+          <t>0091159-95.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>27/08/2026 13:53</t>
+          <t>01/09/2026 13:03</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>27/08/2026 13:53</t>
+          <t>01/09/2026 13:03</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>10/09/2026 21:16</t>
+          <t>07/09/2026 14:45</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2181,7 +2181,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0035495-50.2024.8.16.0000</t>
+          <t>0100027-96.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2191,27 +2191,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Evicção ou Vicio Redibitório | Indenização por Dano Moral | Indenização por Dano Material</t>
+          <t>Dívida Ativa (Execução Fiscal)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>27/08/2026 21:33</t>
+          <t>04/09/2026 14:03</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>27/08/2026 21:33</t>
+          <t>04/09/2026 14:03</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>10/09/2026 20:46</t>
+          <t>07/09/2026 14:45</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2228,37 +2228,37 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0037878-35.2023.8.16.0000</t>
+          <t>0101965-97.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Comodato</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>11/12/2024</t>
+          <t>29/10/2024</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>02/09/2026 14:53</t>
+          <t>27/08/2026 21:43</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>02/09/2026 14:53</t>
+          <t>27/08/2026 21:43</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>10/09/2026 20:57</t>
+          <t>07/09/2026 14:45</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2275,7 +2275,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0040013-83.2024.8.16.0000</t>
+          <t>0107197-56.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2285,27 +2285,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Locação de Móvel</t>
+          <t>Despejo por Inadimplemento</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>18/08/2026 14:13</t>
+          <t>27/08/2026 21:33</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>18/08/2026 14:13</t>
+          <t>27/08/2026 21:33</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>19/08/2026 03:30</t>
+          <t>07/09/2026 14:45</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2322,37 +2322,37 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0046238-58.2024.8.16.0182</t>
+          <t>0109932-62.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Pedido de Uniformização de Interpretação de Lei Criminal</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Residência Médica | Programas de Bolsas e Financiamento Estudantil com Recursos Públicos</t>
+          <t>Prescrição e Decadência</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>03/04/2025</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>18/08/2026 01:57</t>
+          <t>24/08/2026 16:53</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>18/08/2026 01:57</t>
+          <t>24/08/2026 16:53</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>18/08/2026 14:27</t>
+          <t>10/09/2026 21:16</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2369,7 +2369,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0046534-44.2024.8.16.0000</t>
+          <t>0115570-76.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2379,22 +2379,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Práticas Abusivas</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>26/11/2025</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>27/08/2026 16:00</t>
+          <t>27/08/2026 20:33</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>27/08/2026 16:00</t>
+          <t>27/08/2026 20:33</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2416,7 +2416,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0047704-17.2025.8.16.0000</t>
+          <t>0133047-15.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2426,27 +2426,27 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Comissão</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>26/08/2026 15:23</t>
+          <t>01/09/2026 16:23</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>26/08/2026 15:23</t>
+          <t>01/09/2026 16:23</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>10/09/2026 21:29</t>
+          <t>10/09/2026 21:14</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2463,37 +2463,37 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0051721-96.2025.8.16.0000</t>
+          <t>4002116-51.2025.8.16.4321</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Remição</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>18/08/2026 14:13</t>
+          <t>25/08/2026 17:03</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>18/08/2026 14:13</t>
+          <t>25/08/2026 17:03</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>19/08/2026 02:59</t>
+          <t>10/09/2026 20:46</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2502,711 +2502,6 @@
         </is>
       </c>
       <c r="I44" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>0061410-04.2024.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Contratos Bancários</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>28/08/2026 16:43</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>28/08/2026 16:43</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>10/09/2026 21:16</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>0062461-50.2024.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Concurso de Credores</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>20/01/2026</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>27/08/2026 19:43</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>27/08/2026 19:43</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>07/09/2026 14:45</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>0065776-52.2025.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ameaça | Prisão Preventiva | Violação de domicílio</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>29/09/2025</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>18/08/2026 16:13</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>18/08/2026 16:13</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>19/08/2026 02:52</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>0081354-89.2024.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Indenização por Dano Moral | Penhora / Depósito/ Avaliação | Indenização por Dano Material</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>26/09/2025</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>31/08/2026 16:43</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>31/08/2026 16:43</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>10/09/2026 21:29</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>0083650-50.2025.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Promessa de Compra e Venda | Esbulho / Turbação / Ameaça | Requerimento de Reintegração de Posse</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>27/08/2026 19:53</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>27/08/2026 19:53</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>07/09/2026 14:46</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>0091159-95.2026.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>20/08/2026</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>01/09/2026 13:03</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>01/09/2026 13:03</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>07/09/2026 14:45</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>0099048-08.2023.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Prestação de Serviços</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>04/10/2024</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>18/08/2026 13:13</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>18/08/2026 13:13</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>19/08/2026 00:46</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>0100027-96.2025.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>02/07/2026</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>04/09/2026 14:03</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>04/09/2026 14:03</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>07/09/2026 14:45</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>0101965-97.2023.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Contratos Bancários</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>29/10/2024</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>27/08/2026 21:43</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>27/08/2026 21:43</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>07/09/2026 14:45</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>0107197-56.2024.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Despejo por Inadimplemento</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>27/08/2026 21:33</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>27/08/2026 21:33</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>07/09/2026 14:45</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>0109932-62.2024.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Prescrição e Decadência</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>24/08/2026 16:53</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>24/08/2026 16:53</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>10/09/2026 21:16</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>0115570-76.2024.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Práticas Abusivas</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>27/08/2026 20:33</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>27/08/2026 20:33</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>07/09/2026 14:45</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>0133047-15.2024.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Comissão</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>25/11/2025</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>01/09/2026 16:23</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>01/09/2026 16:23</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>10/09/2026 21:14</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>4002116-51.2025.8.16.4321</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Remição</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>25/08/2026 17:03</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>25/08/2026 17:03</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>10/09/2026 20:46</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>4002176-24.2025.8.16.4321</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Progressão de Regime</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>16/12/2025</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>18/08/2026 16:03</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>18/08/2026 16:03</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>19/08/2026 02:18</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>

--- a/docs/resultados.xlsx
+++ b/docs/resultados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -1100,7 +1100,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0008854-86.2019.8.16.0004</t>
+          <t>0008932-19.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1110,27 +1110,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ICMS/ Imposto sobre Circulação de Mercadorias</t>
+          <t>Administração judicial</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>27/03/2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>19/08/2026 14:33</t>
+          <t>31/08/2026 19:43</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>19/08/2026 14:33</t>
+          <t>31/08/2026 19:43</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>10/09/2026 20:46</t>
+          <t>10/09/2026 20:44</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1147,7 +1147,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0008932-19.2024.8.16.0000</t>
+          <t>0009875-56.2015.8.16.0160</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1157,27 +1157,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Administração judicial</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>27/03/2025</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>31/08/2026 19:43</t>
+          <t>27/08/2026 15:53</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>31/08/2026 19:43</t>
+          <t>27/08/2026 15:53</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>10/09/2026 20:44</t>
+          <t>10/09/2026 21:16</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1194,7 +1194,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0009875-56.2015.8.16.0160</t>
+          <t>0010345-55.2021.8.16.0038</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1204,27 +1204,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>27/08/2026 15:53</t>
+          <t>27/08/2026 20:13</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>27/08/2026 15:53</t>
+          <t>27/08/2026 20:13</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>10/09/2026 21:16</t>
+          <t>10/09/2026 20:59</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1241,7 +1241,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0010345-55.2021.8.16.0038</t>
+          <t>0011761-36.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1251,27 +1251,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
+          <t>Taxa de Licenciamento de Estabelecimento | Penhora no Rosto dos Autos</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>27/08/2026 20:13</t>
+          <t>02/09/2026 14:43</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>27/08/2026 20:13</t>
+          <t>02/09/2026 14:43</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>10/09/2026 20:59</t>
+          <t>10/09/2026 21:29</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1288,37 +1288,37 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0011761-36.2025.8.16.0000</t>
+          <t>0013567-29.2013.8.16.0000</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Taxa de Licenciamento de Estabelecimento | Penhora no Rosto dos Autos</t>
+          <t>Sistema Financeiro da Habitação</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>30/09/2025</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>02/09/2026 14:43</t>
+          <t>31/08/2026 19:23</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>02/09/2026 14:43</t>
+          <t>31/08/2026 19:23</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>10/09/2026 21:29</t>
+          <t>10/09/2026 20:59</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1335,37 +1335,37 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0013567-29.2013.8.16.0000</t>
+          <t>0014002-49.2013.8.16.0017</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Embargos de Divergência em Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sistema Financeiro da Habitação</t>
+          <t>Vícios de Construção</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>24/05/2024</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>31/08/2026 19:23</t>
+          <t>27/08/2026 19:03</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>31/08/2026 19:23</t>
+          <t>27/08/2026 19:03</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>10/09/2026 20:59</t>
+          <t>10/09/2026 20:44</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1382,37 +1382,37 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0014002-49.2013.8.16.0017</t>
+          <t>0017529-91.2012.8.16.0001</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Embargos de Divergência em Agravo em Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Vícios de Construção</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>24/05/2024</t>
+          <t>27/01/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>27/08/2026 19:03</t>
+          <t>27/08/2026 21:23</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>27/08/2026 19:03</t>
+          <t>27/08/2026 21:23</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>10/09/2026 20:44</t>
+          <t>07/09/2026 14:45</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1429,7 +1429,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0017529-91.2012.8.16.0001</t>
+          <t>0018344-29.2024.8.16.0014</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1439,27 +1439,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>27/01/2026</t>
+          <t>14/10/2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>27/08/2026 21:23</t>
+          <t>25/08/2026 18:53</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>27/08/2026 21:23</t>
+          <t>25/08/2026 18:53</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>07/09/2026 14:45</t>
+          <t>10/09/2026 21:14</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1476,32 +1476,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0018344-29.2024.8.16.0014</t>
+          <t>0022909-70.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>14/10/2025</t>
+          <t>27/09/2024</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>25/08/2026 18:53</t>
+          <t>27/08/2026 15:59</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>25/08/2026 18:53</t>
+          <t>27/08/2026 15:59</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1523,37 +1523,37 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0022909-70.2023.8.16.0014</t>
+          <t>0028035-41.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>27/09/2024</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>27/08/2026 15:59</t>
+          <t>02/09/2026 08:35</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>27/08/2026 15:59</t>
+          <t>02/09/2026 08:35</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>10/09/2026 21:14</t>
+          <t>10/09/2026 20:46</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1570,37 +1570,37 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0025685-85.2023.8.16.0000</t>
+          <t>0031845-47.2009.8.16.0185</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Contratos Bancários | Cessão de Crédito | Suspensão da Execução | Penhora / Depósito/ Avaliação</t>
+          <t>Dívida Ativa (Execução Fiscal)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>19/06/2024</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>21/08/2026 14:43</t>
+          <t>26/08/2026 14:13</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>21/08/2026 14:43</t>
+          <t>26/08/2026 14:13</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>10/09/2026 20:44</t>
+          <t>10/09/2026 20:59</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1617,37 +1617,37 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0028035-41.2026.8.16.0000</t>
+          <t>0035488-24.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>02/09/2026 08:35</t>
+          <t>27/08/2026 13:53</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>02/09/2026 08:35</t>
+          <t>27/08/2026 13:53</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>10/09/2026 20:46</t>
+          <t>10/09/2026 21:16</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1664,7 +1664,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0031845-47.2009.8.16.0185</t>
+          <t>0035495-50.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1674,27 +1674,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>Evicção ou Vicio Redibitório | Indenização por Dano Moral | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>26/08/2026 14:13</t>
+          <t>27/08/2026 21:33</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>26/08/2026 14:13</t>
+          <t>27/08/2026 21:33</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>10/09/2026 20:59</t>
+          <t>10/09/2026 20:46</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1711,37 +1711,37 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0035488-24.2025.8.16.0000</t>
+          <t>0037878-35.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Comodato</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>11/12/2024</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>27/08/2026 13:53</t>
+          <t>02/09/2026 14:53</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>27/08/2026 13:53</t>
+          <t>02/09/2026 14:53</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>10/09/2026 21:16</t>
+          <t>10/09/2026 20:57</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1758,7 +1758,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0035495-50.2024.8.16.0000</t>
+          <t>0046534-44.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1768,27 +1768,27 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Evicção ou Vicio Redibitório | Indenização por Dano Moral | Indenização por Dano Material</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>26/11/2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>27/08/2026 21:33</t>
+          <t>27/08/2026 16:00</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>27/08/2026 21:33</t>
+          <t>27/08/2026 16:00</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>10/09/2026 20:46</t>
+          <t>07/09/2026 14:45</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1805,37 +1805,37 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0037878-35.2023.8.16.0000</t>
+          <t>0047704-17.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Comodato</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>11/12/2024</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>02/09/2026 14:53</t>
+          <t>26/08/2026 15:23</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>02/09/2026 14:53</t>
+          <t>26/08/2026 15:23</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>10/09/2026 20:57</t>
+          <t>10/09/2026 21:29</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1852,7 +1852,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0046534-44.2024.8.16.0000</t>
+          <t>0061410-04.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1862,27 +1862,27 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>26/11/2025</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>27/08/2026 16:00</t>
+          <t>28/08/2026 16:43</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>27/08/2026 16:00</t>
+          <t>28/08/2026 16:43</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>07/09/2026 14:45</t>
+          <t>10/09/2026 21:16</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1899,7 +1899,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0047704-17.2025.8.16.0000</t>
+          <t>0062461-50.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1909,27 +1909,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Concurso de Credores</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>20/01/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>26/08/2026 15:23</t>
+          <t>27/08/2026 19:43</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>26/08/2026 15:23</t>
+          <t>27/08/2026 19:43</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>10/09/2026 21:29</t>
+          <t>07/09/2026 14:45</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1946,7 +1946,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0061410-04.2024.8.16.0000</t>
+          <t>0081354-89.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1956,27 +1956,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Indenização por Dano Moral | Penhora / Depósito/ Avaliação | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>26/09/2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>28/08/2026 16:43</t>
+          <t>31/08/2026 16:43</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>28/08/2026 16:43</t>
+          <t>31/08/2026 16:43</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>10/09/2026 21:16</t>
+          <t>10/09/2026 21:29</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0062461-50.2024.8.16.0000</t>
+          <t>0083650-50.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2003,27 +2003,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Concurso de Credores</t>
+          <t>Promessa de Compra e Venda | Esbulho / Turbação / Ameaça | Requerimento de Reintegração de Posse</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>20/01/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>27/08/2026 19:43</t>
+          <t>27/08/2026 19:53</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>27/08/2026 19:43</t>
+          <t>27/08/2026 19:53</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>07/09/2026 14:45</t>
+          <t>07/09/2026 14:46</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2040,37 +2040,37 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0081354-89.2024.8.16.0000</t>
+          <t>0091159-95.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Penhora / Depósito/ Avaliação | Indenização por Dano Material</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>26/09/2025</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>31/08/2026 16:43</t>
+          <t>01/09/2026 13:03</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>31/08/2026 16:43</t>
+          <t>01/09/2026 13:03</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>10/09/2026 21:29</t>
+          <t>07/09/2026 14:45</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2087,7 +2087,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0083650-50.2025.8.16.0000</t>
+          <t>0100027-96.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2097,27 +2097,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Promessa de Compra e Venda | Esbulho / Turbação / Ameaça | Requerimento de Reintegração de Posse</t>
+          <t>Dívida Ativa (Execução Fiscal)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>27/08/2026 19:53</t>
+          <t>04/09/2026 14:03</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>27/08/2026 19:53</t>
+          <t>04/09/2026 14:03</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>07/09/2026 14:46</t>
+          <t>07/09/2026 14:45</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2134,32 +2134,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0091159-95.2026.8.16.0000</t>
+          <t>0101965-97.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>29/10/2024</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>01/09/2026 13:03</t>
+          <t>27/08/2026 21:43</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>01/09/2026 13:03</t>
+          <t>27/08/2026 21:43</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2181,7 +2181,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0100027-96.2025.8.16.0000</t>
+          <t>0107197-56.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2191,22 +2191,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>Despejo por Inadimplemento</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>04/09/2026 14:03</t>
+          <t>27/08/2026 21:33</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>04/09/2026 14:03</t>
+          <t>27/08/2026 21:33</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2228,7 +2228,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0101965-97.2023.8.16.0000</t>
+          <t>0109932-62.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2238,27 +2238,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Prescrição e Decadência</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>29/10/2024</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>27/08/2026 21:43</t>
+          <t>24/08/2026 16:53</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>27/08/2026 21:43</t>
+          <t>24/08/2026 16:53</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>07/09/2026 14:45</t>
+          <t>10/09/2026 21:16</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2275,7 +2275,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0107197-56.2024.8.16.0000</t>
+          <t>0115570-76.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2285,22 +2285,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Despejo por Inadimplemento</t>
+          <t>Práticas Abusivas</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>27/08/2026 21:33</t>
+          <t>27/08/2026 20:33</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>27/08/2026 21:33</t>
+          <t>27/08/2026 20:33</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2322,7 +2322,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0109932-62.2024.8.16.0000</t>
+          <t>0133047-15.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2332,27 +2332,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Prescrição e Decadência</t>
+          <t>Comissão</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>24/08/2026 16:53</t>
+          <t>01/09/2026 16:23</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>24/08/2026 16:53</t>
+          <t>01/09/2026 16:23</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>10/09/2026 21:16</t>
+          <t>10/09/2026 21:14</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2369,37 +2369,37 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0115570-76.2024.8.16.0000</t>
+          <t>4002116-51.2025.8.16.4321</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Práticas Abusivas</t>
+          <t>Remição</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>27/08/2026 20:33</t>
+          <t>25/08/2026 17:03</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>27/08/2026 20:33</t>
+          <t>25/08/2026 17:03</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>07/09/2026 14:45</t>
+          <t>10/09/2026 20:46</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2408,100 +2408,6 @@
         </is>
       </c>
       <c r="I42" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>0133047-15.2024.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Comissão</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>25/11/2025</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>01/09/2026 16:23</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>01/09/2026 16:23</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>10/09/2026 21:14</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>4002116-51.2025.8.16.4321</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Remição</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>25/08/2026 17:03</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>25/08/2026 17:03</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>10/09/2026 20:46</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>

--- a/docs/resultados.xlsx
+++ b/docs/resultados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -489,7 +489,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0000163-44.2023.8.16.0004</t>
+          <t>0000129-84.2026.8.16.0159</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -499,27 +499,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ICMS/ Imposto sobre Circulação de Mercadorias</t>
+          <t>Acidente de Trânsito</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>24/10/2025</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>25/08/2026 16:23</t>
+          <t>24/08/2026 16:13</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>25/08/2026 16:23</t>
+          <t>24/08/2026 16:13</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>10/09/2026 20:44</t>
+          <t>21/09/2026 16:13</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -536,7 +536,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0000245-29.2022.8.16.0160</t>
+          <t>0000159-93.2006.8.16.0071</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -546,27 +546,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Contratos Bancários | Perdas e Danos | Cerceamento de Defesa | Provas | Obrigação de Entregar</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>12/11/2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>10/09/2026 15:23</t>
+          <t>24/08/2026 14:43</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>10/09/2026 15:23</t>
+          <t>24/08/2026 14:43</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10/09/2026 21:24</t>
+          <t>21/09/2026 14:35</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -583,7 +583,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0001107-89.2023.8.16.0119</t>
+          <t>0000233-50.2020.8.16.0171</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -593,27 +593,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Cédula de Crédito Rural</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>27/08/2026 19:43</t>
+          <t>27/08/2026 14:43</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>27/08/2026 19:43</t>
+          <t>27/08/2026 14:43</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>07/09/2026 14:45</t>
+          <t>21/09/2026 15:43</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,37 +630,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0001878-68.2022.8.16.0130</t>
+          <t>0000245-29.2022.8.16.0160</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Seguro | Seguro</t>
+          <t>Contratos Bancários | Perdas e Danos | Cerceamento de Defesa | Provas | Obrigação de Entregar</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>28/08/2026 21:43</t>
+          <t>10/09/2026 15:23</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>28/08/2026 21:43</t>
+          <t>10/09/2026 15:23</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>10/09/2026 20:46</t>
+          <t>10/09/2026 21:24</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -677,37 +677,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0002529-36.2021.8.16.0098</t>
+          <t>0000250-62.2023.8.16.0048</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dever de Informação | Irregularidade no atendimento</t>
+          <t>Cheque | Perdas e Danos</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>02/08/2024</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>31/08/2026 11:38</t>
+          <t>27/08/2026 18:13</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>31/08/2026 11:38</t>
+          <t>27/08/2026 18:13</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>10/09/2026 21:14</t>
+          <t>21/09/2026 15:27</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -724,7 +724,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0002951-67.2023.8.16.0089</t>
+          <t>0000390-38.2022.8.16.0111</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -734,27 +734,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Anulação e Correção de Provas / Questões</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>08/10/2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>27/08/2026 21:33</t>
+          <t>18/09/2026 14:33</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>27/08/2026 21:33</t>
+          <t>18/09/2026 14:33</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>07/09/2026 14:45</t>
+          <t>21/09/2026 15:16</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -771,7 +771,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0003825-19.2024.8.16.0024</t>
+          <t>0000464-75.2024.8.16.0094</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -781,27 +781,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Crimes do Sistema Nacional de Armas</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>26/08/2026 08:33</t>
+          <t>08/09/2026 19:33</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>26/08/2026 08:33</t>
+          <t>08/09/2026 19:33</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>10/09/2026 20:46</t>
+          <t>21/09/2026 15:12</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -818,7 +818,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0004591-16.2002.8.16.0001</t>
+          <t>0000607-45.2017.8.16.0115</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -828,27 +828,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Compra e Venda</t>
+          <t>Cheque</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>04/09/2026 15:23</t>
+          <t>28/08/2026 18:23</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>04/09/2026 15:23</t>
+          <t>28/08/2026 18:23</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>07/09/2026 14:45</t>
+          <t>21/09/2026 15:27</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -865,37 +865,37 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0005115-18.2021.8.16.0075</t>
+          <t>0000908-97.2024.8.16.0033</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Alienação Fiduciária</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>11/09/2024</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>28/08/2026 20:53</t>
+          <t>15/09/2026 17:03</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>28/08/2026 20:53</t>
+          <t>15/09/2026 17:03</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>10/09/2026 20:44</t>
+          <t>21/09/2026 15:32</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -912,7 +912,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0005311-55.2024.8.16.0148</t>
+          <t>0000940-42.2025.8.16.0074</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -922,27 +922,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Práticas Abusivas</t>
+          <t>Rescisão / Resolução</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>28/08/2026 15:13</t>
+          <t>02/09/2026 13:23</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>28/08/2026 15:13</t>
+          <t>02/09/2026 13:23</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>10/09/2026 21:16</t>
+          <t>21/09/2026 15:43</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0007090-04.2023.8.16.0173</t>
+          <t>0000952-20.2009.8.16.0138</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -969,27 +969,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Compra e Venda</t>
+          <t>Anulação</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>24/04/2025</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>28/08/2026 12:56</t>
+          <t>31/08/2026 20:33</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>28/08/2026 12:56</t>
+          <t>31/08/2026 20:33</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>10/09/2026 20:44</t>
+          <t>21/09/2026 15:11</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1006,7 +1006,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0008017-50.2023.8.16.0017</t>
+          <t>0001007-92.2020.8.16.0167</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1016,27 +1016,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Locação de Imóvel | Embargos de Terceiro</t>
+          <t>Indenização por Dano Material | Indenização por Dano Moral | Tutela de Urgência</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>25/08/2026 17:43</t>
+          <t>27/08/2026 19:43</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>25/08/2026 17:43</t>
+          <t>27/08/2026 19:43</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>10/09/2026 21:14</t>
+          <t>21/09/2026 16:30</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1053,7 +1053,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0008652-53.2021.8.16.0000</t>
+          <t>0001089-25.2019.8.16.0017</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1063,27 +1063,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Administração judicial</t>
+          <t>Indenização por Dano Moral | Irregularidade no atendimento | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>20/07/2022</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>04/09/2026 13:13</t>
+          <t>27/08/2026 17:43</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>04/09/2026 13:13</t>
+          <t>27/08/2026 17:43</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>07/09/2026 14:45</t>
+          <t>21/09/2026 15:12</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0008932-19.2024.8.16.0000</t>
+          <t>0001355-61.2021.8.16.0075</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1110,27 +1110,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Administração judicial</t>
+          <t>PIS/PASEP</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>27/03/2025</t>
+          <t>13/01/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>31/08/2026 19:43</t>
+          <t>17/09/2026 14:23</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>31/08/2026 19:43</t>
+          <t>17/09/2026 14:23</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>10/09/2026 20:44</t>
+          <t>21/09/2026 15:17</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1147,7 +1147,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0009875-56.2015.8.16.0160</t>
+          <t>0001534-86.2022.8.16.0001</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1157,27 +1157,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Alienação Fiduciária</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>27/08/2026 15:53</t>
+          <t>31/08/2026 19:13</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>27/08/2026 15:53</t>
+          <t>31/08/2026 19:13</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>10/09/2026 21:16</t>
+          <t>21/09/2026 16:53</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1194,37 +1194,37 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0010345-55.2021.8.16.0038</t>
+          <t>0001673-07.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Embargos de Divergência em Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
+          <t>Prestação de Serviços | Honorários Advocatícios</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/11/2023</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>27/08/2026 20:13</t>
+          <t>02/09/2026 16:32</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>27/08/2026 20:13</t>
+          <t>02/09/2026 17:38</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>10/09/2026 20:59</t>
+          <t>21/09/2026 16:38</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1241,7 +1241,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0011761-36.2025.8.16.0000</t>
+          <t>0001736-85.2022.8.16.0123</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1251,27 +1251,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Taxa de Licenciamento de Estabelecimento | Penhora no Rosto dos Autos</t>
+          <t>Pagamento em Consignação</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>30/09/2025</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>02/09/2026 14:43</t>
+          <t>01/09/2026 19:53</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>02/09/2026 14:43</t>
+          <t>01/09/2026 19:53</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>10/09/2026 21:29</t>
+          <t>21/09/2026 14:02</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1288,37 +1288,37 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0013567-29.2013.8.16.0000</t>
+          <t>0001878-08.2025.8.16.0116</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sistema Financeiro da Habitação</t>
+          <t>Irregularidade no atendimento | Indenização por Dano Moral | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>31/08/2026 19:23</t>
+          <t>28/08/2026 18:53</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>31/08/2026 19:23</t>
+          <t>28/08/2026 18:53</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>10/09/2026 20:59</t>
+          <t>21/09/2026 16:50</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1335,37 +1335,37 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0014002-49.2013.8.16.0017</t>
+          <t>0002299-04.2015.8.16.0001</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Embargos de Divergência em Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Vícios de Construção</t>
+          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>24/05/2024</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>27/08/2026 19:03</t>
+          <t>17/09/2026 15:33</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>27/08/2026 19:03</t>
+          <t>17/09/2026 15:33</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>10/09/2026 20:44</t>
+          <t>21/09/2026 15:31</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1382,37 +1382,37 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0017529-91.2012.8.16.0001</t>
+          <t>0002529-36.2021.8.16.0098</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Dever de Informação | Irregularidade no atendimento</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>27/01/2026</t>
+          <t>02/08/2024</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>27/08/2026 21:23</t>
+          <t>31/08/2026 11:38</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>27/08/2026 21:23</t>
+          <t>31/08/2026 11:38</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>07/09/2026 14:45</t>
+          <t>10/09/2026 21:14</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1429,7 +1429,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0018344-29.2024.8.16.0014</t>
+          <t>0002642-82.2021.8.16.0035</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1439,27 +1439,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Rescisão / Resolução</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>14/10/2025</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>25/08/2026 18:53</t>
+          <t>16/09/2026 14:23</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>25/08/2026 18:53</t>
+          <t>16/09/2026 14:23</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>10/09/2026 21:14</t>
+          <t>21/09/2026 15:33</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1476,7 +1476,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0022909-70.2023.8.16.0014</t>
+          <t>0002705-17.2024.8.16.0031</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1486,27 +1486,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Uso de documento falso | Falso testemunho ou falsa perícia</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>27/09/2024</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>27/08/2026 15:59</t>
+          <t>01/09/2026 14:03</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>27/08/2026 15:59</t>
+          <t>01/09/2026 14:03</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>10/09/2026 21:14</t>
+          <t>21/09/2026 16:39</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1523,37 +1523,37 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0028035-41.2026.8.16.0000</t>
+          <t>0002709-14.2014.8.16.0190</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins</t>
+          <t>Assembléia | Saneamento</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>02/09/2026 08:35</t>
+          <t>28/08/2026 13:23</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>02/09/2026 08:35</t>
+          <t>28/08/2026 13:23</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>10/09/2026 20:46</t>
+          <t>21/09/2026 16:39</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1570,7 +1570,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0031845-47.2009.8.16.0185</t>
+          <t>0002760-24.2022.8.16.0035</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1580,27 +1580,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>Rescisão / Resolução</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>26/08/2026 14:13</t>
+          <t>27/08/2026 14:43</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>26/08/2026 14:13</t>
+          <t>27/08/2026 14:43</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>10/09/2026 20:59</t>
+          <t>21/09/2026 14:05</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1617,7 +1617,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0035488-24.2025.8.16.0000</t>
+          <t>0002951-67.2023.8.16.0089</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1627,27 +1627,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Anulação e Correção de Provas / Questões</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>27/08/2026 13:53</t>
+          <t>27/08/2026 21:33</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>27/08/2026 13:53</t>
+          <t>27/08/2026 21:33</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>10/09/2026 21:16</t>
+          <t>07/09/2026 14:45</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1664,7 +1664,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0035495-50.2024.8.16.0000</t>
+          <t>0003013-71.2020.8.16.0038</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1674,27 +1674,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Evicção ou Vicio Redibitório | Indenização por Dano Moral | Indenização por Dano Material</t>
+          <t>Nota Promissória</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>30/01/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>27/08/2026 21:33</t>
+          <t>16/09/2026 13:53</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>27/08/2026 21:33</t>
+          <t>16/09/2026 13:53</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>10/09/2026 20:46</t>
+          <t>21/09/2026 15:29</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1711,37 +1711,37 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0037878-35.2023.8.16.0000</t>
+          <t>0003051-27.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Comodato</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>11/12/2024</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>02/09/2026 14:53</t>
+          <t>31/08/2026 21:33</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>02/09/2026 14:53</t>
+          <t>31/08/2026 21:33</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>10/09/2026 20:57</t>
+          <t>21/09/2026 14:02</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1758,7 +1758,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0046534-44.2024.8.16.0000</t>
+          <t>0003380-39.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1768,27 +1768,27 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Cobrança de Aluguéis - Sem despejo</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>26/11/2025</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>27/08/2026 16:00</t>
+          <t>26/08/2026 13:33</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>27/08/2026 16:00</t>
+          <t>26/08/2026 13:33</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>07/09/2026 14:45</t>
+          <t>21/09/2026 16:39</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1805,37 +1805,37 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0047704-17.2025.8.16.0000</t>
+          <t>0003726-27.2016.8.16.0025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>26/08/2026 15:23</t>
+          <t>27/08/2026 15:13</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>26/08/2026 15:23</t>
+          <t>27/08/2026 15:13</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>10/09/2026 21:29</t>
+          <t>21/09/2026 15:23</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1852,7 +1852,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0061410-04.2024.8.16.0000</t>
+          <t>0003825-19.2024.8.16.0024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1862,27 +1862,27 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>28/08/2026 16:43</t>
+          <t>26/08/2026 08:33</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>28/08/2026 16:43</t>
+          <t>26/08/2026 08:33</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>10/09/2026 21:16</t>
+          <t>10/09/2026 20:46</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1899,7 +1899,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0062461-50.2024.8.16.0000</t>
+          <t>0003932-67.2020.8.16.0165</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1909,27 +1909,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Concurso de Credores</t>
+          <t>Rescisão / Resolução</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>20/01/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>27/08/2026 19:43</t>
+          <t>28/08/2026 15:23</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>27/08/2026 19:43</t>
+          <t>28/08/2026 15:23</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>07/09/2026 14:45</t>
+          <t>21/09/2026 16:39</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1946,7 +1946,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0081354-89.2024.8.16.0000</t>
+          <t>0004303-83.2016.8.16.0193</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1956,27 +1956,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Penhora / Depósito/ Avaliação | Indenização por Dano Material</t>
+          <t>Acidente de Trânsito</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>26/09/2025</t>
+          <t>24/04/2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>31/08/2026 16:43</t>
+          <t>01/09/2026 15:13</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>31/08/2026 16:43</t>
+          <t>01/09/2026 15:13</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>10/09/2026 21:29</t>
+          <t>21/09/2026 14:35</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0083650-50.2025.8.16.0000</t>
+          <t>0005076-02.2023.8.16.0188</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2003,27 +2003,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Promessa de Compra e Venda | Esbulho / Turbação / Ameaça | Requerimento de Reintegração de Posse</t>
+          <t>Inventário e Partilha</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>27/08/2026 19:53</t>
+          <t>31/08/2026 19:23</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>27/08/2026 19:53</t>
+          <t>31/08/2026 19:23</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>07/09/2026 14:46</t>
+          <t>21/09/2026 15:12</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2040,37 +2040,37 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0091159-95.2026.8.16.0000</t>
+          <t>0005148-49.2018.8.16.0160</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Acidente de Trânsito</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>16/11/2023</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>01/09/2026 13:03</t>
+          <t>03/09/2026 13:53</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>01/09/2026 13:03</t>
+          <t>03/09/2026 13:53</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>07/09/2026 14:45</t>
+          <t>21/09/2026 16:38</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2087,7 +2087,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0100027-96.2025.8.16.0000</t>
+          <t>0005311-55.2024.8.16.0148</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2097,27 +2097,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>Práticas Abusivas</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>04/09/2026 14:03</t>
+          <t>28/08/2026 15:13</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>04/09/2026 14:03</t>
+          <t>28/08/2026 15:13</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>07/09/2026 14:45</t>
+          <t>10/09/2026 21:16</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2134,37 +2134,37 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0101965-97.2023.8.16.0000</t>
+          <t>0005472-92.2018.8.16.0013</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Crimes Militares | Peculato | Prevaricação | Supressão de documento | Regime inicial | Ausência de Fundamentação | Aplicação da Pena</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>29/10/2024</t>
+          <t>20/11/2023</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>27/08/2026 21:43</t>
+          <t>25/08/2026 16:13</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>27/08/2026 21:43</t>
+          <t>25/08/2026 16:13</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>07/09/2026 14:45</t>
+          <t>21/09/2026 16:38</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2181,7 +2181,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0107197-56.2024.8.16.0000</t>
+          <t>0005600-81.2022.8.16.0075</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2191,27 +2191,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Despejo por Inadimplemento</t>
+          <t>Crime de Descumprimento de Medida Protetiva  de Urgência</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>27/08/2026 21:33</t>
+          <t>27/08/2026 14:53</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>27/08/2026 21:33</t>
+          <t>27/08/2026 14:53</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>07/09/2026 14:45</t>
+          <t>21/09/2026 16:50</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2228,7 +2228,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0109932-62.2024.8.16.0000</t>
+          <t>0005795-46.2012.8.16.0001</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2238,27 +2238,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Prescrição e Decadência</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>24/08/2026 16:53</t>
+          <t>11/09/2026 13:43</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>24/08/2026 16:53</t>
+          <t>11/09/2026 13:43</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>10/09/2026 21:16</t>
+          <t>21/09/2026 16:44</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2275,7 +2275,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0115570-76.2024.8.16.0000</t>
+          <t>0006176-27.2024.8.16.0165</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2285,27 +2285,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Práticas Abusivas</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>27/08/2026 20:33</t>
+          <t>24/08/2026 19:53</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>27/08/2026 20:33</t>
+          <t>24/08/2026 19:53</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>07/09/2026 14:45</t>
+          <t>21/09/2026 16:30</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2322,7 +2322,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0133047-15.2024.8.16.0000</t>
+          <t>0006306-67.2024.8.16.0019</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2332,27 +2332,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Comissão</t>
+          <t>Rescisão / Resolução | Sustação de Protesto | Duplicata</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>01/09/2026 16:23</t>
+          <t>25/08/2026 19:43</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>01/09/2026 16:23</t>
+          <t>25/08/2026 19:43</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>10/09/2026 21:14</t>
+          <t>21/09/2026 16:30</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2369,45 +2369,2442 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>0006682-16.2023.8.16.0075</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>16/12/2025</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>24/08/2026 16:43</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>24/08/2026 16:43</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>21/09/2026 15:23</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>0006933-31.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Reintegração | Licenciamento / Exclusão | Processo Administrativo Disciplinar / Sindicância</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>08/08/2025</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>16/09/2026 17:13</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>16/09/2026 17:13</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>21/09/2026 16:25</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>0007090-04.2023.8.16.0173</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Compra e Venda</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>24/04/2025</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>28/08/2026 12:56</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>28/08/2026 12:56</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>10/09/2026 20:44</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>0007230-04.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Rescisão / Resolução</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>25/03/2026</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>28/08/2026 18:43</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>28/08/2026 18:43</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>21/09/2026 15:25</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>0008017-50.2023.8.16.0017</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Locação de Imóvel | Embargos de Terceiro</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>29/01/2026</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>25/08/2026 17:43</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>25/08/2026 17:43</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>10/09/2026 21:14</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>0008652-53.2021.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Administração judicial</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>20/07/2022</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>04/09/2026 13:13</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>04/09/2026 13:13</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>07/09/2026 14:45</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>0008666-72.2016.8.16.0045</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Material | Irregularidade no atendimento</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>28/08/2026 14:13</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>28/08/2026 14:13</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>21/09/2026 15:43</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>0009622-11.2008.8.16.0129</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Ambiental</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>31/08/2026 20:53</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>31/08/2026 20:53</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>21/09/2026 15:27</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>0009982-24.2015.8.16.0056</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Extorsão</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>25/07/2023</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>01/09/2026 16:13</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>01/09/2026 16:13</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>21/09/2026 16:30</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>0010574-95.2022.8.16.0194</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Seguro</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>28/08/2026 21:03</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>28/08/2026 21:03</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>21/09/2026 15:12</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>0011153-70.2022.8.16.0185</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Dívida Ativa (Execução Fiscal)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>30/01/2026</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>01/09/2026 19:43</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>01/09/2026 19:43</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>21/09/2026 16:38</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>0012472-19.2014.8.16.0035</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Defeito, nulidade ou anulação</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>11/09/2023</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>27/08/2026 18:43</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>27/08/2026 18:43</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>21/09/2026 16:30</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>0014179-15.2023.8.16.0194</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Rescisão do contrato e devolução do dinheiro | Indenização por Dano Moral | Indenização por Dano Material | Dever de Informação</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>27/08/2026 14:03</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>27/08/2026 14:03</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>21/09/2026 15:25</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>0014882-98.2023.8.16.0014</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>17/02/2025</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>01/09/2026 15:53</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>01/09/2026 15:53</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>21/09/2026 13:59</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>0017529-91.2012.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>27/01/2026</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>27/08/2026 21:23</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>27/08/2026 21:23</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>07/09/2026 14:45</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>0020522-83.2025.8.16.0185</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Dívida Ativa (Execução Fiscal)</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>11/09/2026 15:49</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>11/09/2026 15:49</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>21/09/2026 14:29</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>0021915-38.2020.8.16.0017</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Compra e Venda</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>27/08/2025</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>27/08/2026 14:13</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>27/08/2026 14:13</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>21/09/2026 13:46</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>0022429-13.2018.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Anônima | Adimplemento e Extinção</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>06/03/2020</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>11/09/2026 15:03</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>11/09/2026 15:03</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>21/09/2026 16:30</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>0022909-70.2023.8.16.0014</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>27/09/2024</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>27/08/2026 15:59</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>27/08/2026 15:59</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>10/09/2026 21:14</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>0028035-41.2026.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Recurso Ordinário em Habeas Corpus</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>02/09/2026 08:35</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>02/09/2026 08:35</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>10/09/2026 20:46</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>0028491-41.2020.8.16.0019</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Defeito, nulidade ou anulação</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>20/05/2025</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>09/09/2026 17:03</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>09/09/2026 17:03</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>21/09/2026 15:11</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>0028571-45.2009.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Inventário e Partilha</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>05/11/2025</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>25/08/2026 20:03</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>25/08/2026 20:03</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>21/09/2026 14:54</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>0030612-23.2021.8.16.0014</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Acidente de Trânsito | Acidente de Trânsito</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>27/08/2026 20:43</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>27/08/2026 20:43</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>21/09/2026 14:19</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>0032406-05.2013.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Expurgos Inflacionários / Planos Econômicos</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>26/03/2015</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>24/08/2026 17:03</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>24/08/2026 17:03</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>21/09/2026 15:11</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>0033485-96.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Cédula de Crédito Bancário</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>24/08/2026 16:03</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>24/08/2026 16:03</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>21/09/2026 16:40</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>0035495-50.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Evicção ou Vicio Redibitório | Indenização por Dano Moral | Indenização por Dano Material</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>27/08/2026 21:33</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>27/08/2026 21:33</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>10/09/2026 20:46</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>0037574-28.2022.8.16.0014</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Locação de Imóvel</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>31/08/2026 19:03</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>31/08/2026 19:03</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>21/09/2026 16:40</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>0039715-57.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Práticas Abusivas</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>28/08/2026 17:23</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>28/08/2026 17:23</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>21/09/2026 16:25</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>0040099-71.2008.8.16.0014</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Enriquecimento ilícito</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>18/02/2022</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>31/08/2026 13:23</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>31/08/2026 13:23</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>21/09/2026 15:38</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>0045281-50.2026.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Recurso Ordinário em Habeas Corpus</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Homicídio Qualificado | Prisão Preventiva</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>01/09/2026 15:43</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>01/09/2026 15:43</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>21/09/2026 16:30</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>0057679-63.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Contratos Bancários</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>04/09/2026 15:03</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>04/09/2026 15:03</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>21/09/2026 14:35</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>0058218-29.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Locação de Imóvel</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>01/09/2026 21:23</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>01/09/2026 21:23</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>21/09/2026 14:35</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>0058940-63.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Contratos Bancários</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>01/09/2026 17:23</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>01/09/2026 17:23</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>21/09/2026 16:39</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>0058967-46.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Cédula de Crédito Rural</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>28/08/2026 21:23</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>28/08/2026 21:23</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>21/09/2026 15:16</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>0060797-47.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Gratuidade | Assistência Judiciária Gratuita</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>25/08/2026 19:23</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>25/08/2026 19:23</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>21/09/2026 16:40</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>0068139-43.2020.8.16.0014</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Erro Médico | Erro Médico</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>25/08/2026 14:33</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>25/08/2026 14:33</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>21/09/2026 15:25</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>0068730-71.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Crimes da Lei de licitações | Falsidade ideológica</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>15/12/2025</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>31/08/2026 09:22</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>31/08/2026 09:22</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>21/09/2026 14:17</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>0076534-56.2026.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Recurso Ordinário em Habeas Corpus</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Crimes do Sistema Nacional de Armas | Desobediência</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>13/08/2026</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>31/08/2026 17:23</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>31/08/2026 17:23</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>21/09/2026 15:43</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>0078301-66.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Cédula de Crédito Rural | Tutela de Urgência | Cédula de Produto Rural</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>31/08/2026 15:23</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>31/08/2026 15:23</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>21/09/2026 15:25</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>0078867-15.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Alienação Fiduciária</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>28/08/2026 19:33</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>28/08/2026 19:33</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>21/09/2026 15:25</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>0080874-14.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Duplicata</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>12/09/2025</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>27/08/2026 21:23</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>27/08/2026 21:23</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>21/09/2026 15:23</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>0081354-89.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Moral | Penhora / Depósito/ Avaliação | Indenização por Dano Material</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>26/09/2025</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>31/08/2026 16:43</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>31/08/2026 16:43</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>10/09/2026 21:29</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>0082930-85.2018.8.16.0014</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Homicídio Qualificado</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>25/02/2026</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>02/09/2026 14:23</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>02/09/2026 14:23</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>21/09/2026 14:02</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>0083650-50.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Promessa de Compra e Venda | Esbulho / Turbação / Ameaça | Requerimento de Reintegração de Posse</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>27/08/2026 19:53</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>27/08/2026 19:53</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>07/09/2026 14:46</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>0091747-39.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Desconsideração da Personalidade Jurídica</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>31/08/2026 13:03</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>31/08/2026 13:03</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>21/09/2026 16:39</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>0097979-04.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Despejo para Uso Próprio</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>27/08/2026 18:23</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>27/08/2026 18:23</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>21/09/2026 14:57</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>0109932-62.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Prescrição e Decadência</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>24/08/2026 16:53</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>24/08/2026 16:53</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>10/09/2026 21:16</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>0113231-47.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>21/07/2025</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>09/09/2026 21:03</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>09/09/2026 21:03</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>21/09/2026 16:40</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>0119994-64.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>IPTU/ Imposto Predial e Territorial Urbano</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>16/09/2026 14:23</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>16/09/2026 14:23</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>21/09/2026 15:12</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>0126160-15.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>05/11/2025</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>08/09/2026 14:43</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>08/09/2026 14:43</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>21/09/2026 14:54</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>0148342-58.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Recurso Ordinário em Habeas Corpus</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins | Cerceamento de Defesa | Prova Ilícita | Excesso de prazo para instrução / julgamento | Prisão Preventiva</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>24/08/2026 19:03</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>24/08/2026 19:03</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>21/09/2026 16:13</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
           <t>4002116-51.2025.8.16.4321</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>Recurso Especial</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>Remição</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D93" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E93" t="inlineStr">
         <is>
           <t>25/08/2026 17:03</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F93" t="inlineStr">
         <is>
           <t>25/08/2026 17:03</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G93" t="inlineStr">
         <is>
           <t>10/09/2026 20:46</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>

--- a/docs/resultados.xlsx
+++ b/docs/resultados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I93"/>
+  <dimension ref="A1:I101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -489,7 +489,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0000129-84.2026.8.16.0159</t>
+          <t>0005600-81.2022.8.16.0075</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -499,27 +499,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Acidente de Trânsito</t>
+          <t>Crime de Descumprimento de Medida Protetiva  de Urgência</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>24/08/2026 16:13</t>
+          <t>27/08/2026 14:53</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>24/08/2026 16:13</t>
+          <t>27/08/2026 14:53</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>21/09/2026 16:13</t>
+          <t>21/09/2026 16:50</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -536,7 +536,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0000159-93.2006.8.16.0071</t>
+          <t>0001534-86.2022.8.16.0001</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -546,27 +546,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Alienação Fiduciária</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>24/08/2026 14:43</t>
+          <t>31/08/2026 19:13</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>24/08/2026 14:43</t>
+          <t>31/08/2026 19:13</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>21/09/2026 14:35</t>
+          <t>21/09/2026 16:53</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -583,37 +583,37 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0000233-50.2020.8.16.0171</t>
+          <t>0005148-49.2018.8.16.0160</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Rural</t>
+          <t>Acidente de Trânsito</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>16/11/2023</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>27/08/2026 14:43</t>
+          <t>03/09/2026 13:53</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>27/08/2026 14:43</t>
+          <t>03/09/2026 13:53</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>21/09/2026 15:43</t>
+          <t>21/09/2026 16:38</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,37 +630,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0000245-29.2022.8.16.0160</t>
+          <t>0001673-07.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Embargos de Divergência em Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Contratos Bancários | Perdas e Danos | Cerceamento de Defesa | Provas | Obrigação de Entregar</t>
+          <t>Prestação de Serviços | Honorários Advocatícios</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>17/11/2023</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>10/09/2026 15:23</t>
+          <t>02/09/2026 16:32</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>10/09/2026 15:23</t>
+          <t>02/09/2026 17:38</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>10/09/2026 21:24</t>
+          <t>21/09/2026 16:38</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -677,7 +677,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0000250-62.2023.8.16.0048</t>
+          <t>0091747-39.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -687,27 +687,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cheque | Perdas e Danos</t>
+          <t>Desconsideração da Personalidade Jurídica</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>27/08/2026 18:13</t>
+          <t>31/08/2026 13:03</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>27/08/2026 18:13</t>
+          <t>31/08/2026 13:03</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>21/09/2026 15:27</t>
+          <t>21/09/2026 16:39</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -724,7 +724,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0000390-38.2022.8.16.0111</t>
+          <t>0003932-67.2020.8.16.0165</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -734,27 +734,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Rescisão / Resolução</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>08/10/2025</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>18/09/2026 14:33</t>
+          <t>28/08/2026 15:23</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>18/09/2026 14:33</t>
+          <t>28/08/2026 15:23</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>21/09/2026 15:16</t>
+          <t>21/09/2026 16:39</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -771,7 +771,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0000464-75.2024.8.16.0094</t>
+          <t>0002709-14.2014.8.16.0190</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -781,27 +781,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Crimes do Sistema Nacional de Armas</t>
+          <t>Assembléia | Saneamento</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>08/09/2026 19:33</t>
+          <t>28/08/2026 13:23</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>08/09/2026 19:33</t>
+          <t>28/08/2026 13:23</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>21/09/2026 15:12</t>
+          <t>21/09/2026 16:39</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -818,37 +818,37 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0000607-45.2017.8.16.0115</t>
+          <t>0002705-17.2024.8.16.0031</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cheque</t>
+          <t>Uso de documento falso | Falso testemunho ou falsa perícia</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>28/08/2026 18:23</t>
+          <t>01/09/2026 14:03</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>28/08/2026 18:23</t>
+          <t>01/09/2026 14:03</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>21/09/2026 15:27</t>
+          <t>21/09/2026 16:39</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -865,7 +865,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0000908-97.2024.8.16.0033</t>
+          <t>0003380-39.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -875,27 +875,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Cobrança de Aluguéis - Sem despejo</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>15/09/2026 17:03</t>
+          <t>26/08/2026 13:33</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>15/09/2026 17:03</t>
+          <t>26/08/2026 13:33</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>21/09/2026 15:32</t>
+          <t>21/09/2026 16:39</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -912,7 +912,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0000940-42.2025.8.16.0074</t>
+          <t>0113231-47.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -922,27 +922,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Rescisão / Resolução</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>02/09/2026 13:23</t>
+          <t>09/09/2026 21:03</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>02/09/2026 13:23</t>
+          <t>09/09/2026 21:03</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>21/09/2026 15:43</t>
+          <t>21/09/2026 16:40</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0000952-20.2009.8.16.0138</t>
+          <t>0068139-43.2020.8.16.0014</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -969,27 +969,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Anulação</t>
+          <t>Erro Médico | Erro Médico</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>12/01/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>31/08/2026 20:33</t>
+          <t>25/08/2026 14:33</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>31/08/2026 20:33</t>
+          <t>25/08/2026 14:33</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>21/09/2026 15:11</t>
+          <t>21/09/2026 15:25</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1006,7 +1006,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0001007-92.2020.8.16.0167</t>
+          <t>0078301-66.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1016,27 +1016,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Indenização por Dano Moral | Tutela de Urgência</t>
+          <t>Cédula de Crédito Rural | Tutela de Urgência | Cédula de Produto Rural</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>27/08/2026 19:43</t>
+          <t>31/08/2026 15:23</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>27/08/2026 19:43</t>
+          <t>31/08/2026 15:23</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>21/09/2026 16:30</t>
+          <t>21/09/2026 15:25</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1053,7 +1053,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0001089-25.2019.8.16.0017</t>
+          <t>0007230-04.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1063,27 +1063,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Irregularidade no atendimento | Indenização por Dano Material</t>
+          <t>Rescisão / Resolução</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>27/08/2026 17:43</t>
+          <t>28/08/2026 18:43</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>27/08/2026 17:43</t>
+          <t>28/08/2026 18:43</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>21/09/2026 15:12</t>
+          <t>21/09/2026 15:25</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0001355-61.2021.8.16.0075</t>
+          <t>0078867-15.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1110,27 +1110,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PIS/PASEP</t>
+          <t>Alienação Fiduciária</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>13/01/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>17/09/2026 14:23</t>
+          <t>28/08/2026 19:33</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>17/09/2026 14:23</t>
+          <t>28/08/2026 19:33</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>21/09/2026 15:17</t>
+          <t>21/09/2026 15:25</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1147,7 +1147,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0001534-86.2022.8.16.0001</t>
+          <t>0000250-62.2023.8.16.0048</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1157,27 +1157,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Alienação Fiduciária</t>
+          <t>Cheque | Perdas e Danos</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>31/08/2026 19:13</t>
+          <t>27/08/2026 18:13</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>31/08/2026 19:13</t>
+          <t>27/08/2026 18:13</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>21/09/2026 16:53</t>
+          <t>21/09/2026 15:27</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1194,37 +1194,37 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0001673-07.2023.8.16.0000</t>
+          <t>0003013-71.2020.8.16.0038</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Embargos de Divergência em Agravo em Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Prestação de Serviços | Honorários Advocatícios</t>
+          <t>Nota Promissória</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>17/11/2023</t>
+          <t>30/01/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>02/09/2026 16:32</t>
+          <t>16/09/2026 13:53</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>02/09/2026 17:38</t>
+          <t>16/09/2026 13:53</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>21/09/2026 16:38</t>
+          <t>21/09/2026 15:29</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1241,37 +1241,37 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0001736-85.2022.8.16.0123</t>
+          <t>0002299-04.2015.8.16.0001</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pagamento em Consignação</t>
+          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>01/09/2026 19:53</t>
+          <t>17/09/2026 15:33</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>01/09/2026 19:53</t>
+          <t>17/09/2026 15:33</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>21/09/2026 14:02</t>
+          <t>21/09/2026 15:31</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1288,7 +1288,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0001878-08.2025.8.16.0116</t>
+          <t>0000908-97.2024.8.16.0033</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1298,27 +1298,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Irregularidade no atendimento | Indenização por Dano Moral | Indenização por Dano Material</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>28/08/2026 18:53</t>
+          <t>15/09/2026 17:03</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>28/08/2026 18:53</t>
+          <t>15/09/2026 17:03</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>21/09/2026 16:50</t>
+          <t>21/09/2026 15:32</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1335,37 +1335,37 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0002299-04.2015.8.16.0001</t>
+          <t>0002642-82.2021.8.16.0035</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
+          <t>Rescisão / Resolução</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>17/09/2026 15:33</t>
+          <t>16/09/2026 14:23</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>17/09/2026 15:33</t>
+          <t>16/09/2026 14:23</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>21/09/2026 15:31</t>
+          <t>21/09/2026 15:33</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1382,37 +1382,37 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0002529-36.2021.8.16.0098</t>
+          <t>0000233-50.2020.8.16.0171</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dever de Informação | Irregularidade no atendimento</t>
+          <t>Cédula de Crédito Rural</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>02/08/2024</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>31/08/2026 11:38</t>
+          <t>27/08/2026 14:43</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>31/08/2026 11:38</t>
+          <t>27/08/2026 14:43</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>10/09/2026 21:14</t>
+          <t>21/09/2026 15:43</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1429,7 +1429,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0002642-82.2021.8.16.0035</t>
+          <t>0000940-42.2025.8.16.0074</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1444,22 +1444,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>16/09/2026 14:23</t>
+          <t>02/09/2026 13:23</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>16/09/2026 14:23</t>
+          <t>02/09/2026 13:23</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>21/09/2026 15:33</t>
+          <t>21/09/2026 15:43</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1476,37 +1476,37 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0002705-17.2024.8.16.0031</t>
+          <t>0148342-58.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Uso de documento falso | Falso testemunho ou falsa perícia</t>
+          <t>Tráfico de Drogas e Condutas Afins | Cerceamento de Defesa | Prova Ilícita | Excesso de prazo para instrução / julgamento | Prisão Preventiva</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>02/03/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>01/09/2026 14:03</t>
+          <t>24/08/2026 19:03</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>01/09/2026 14:03</t>
+          <t>24/08/2026 19:03</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>21/09/2026 16:39</t>
+          <t>21/09/2026 16:13</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1523,7 +1523,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0002709-14.2014.8.16.0190</t>
+          <t>0000129-84.2026.8.16.0159</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1533,27 +1533,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Assembléia | Saneamento</t>
+          <t>Acidente de Trânsito</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>28/08/2026 13:23</t>
+          <t>24/08/2026 16:13</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>28/08/2026 13:23</t>
+          <t>24/08/2026 16:13</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>21/09/2026 16:39</t>
+          <t>21/09/2026 16:13</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1570,7 +1570,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0002760-24.2022.8.16.0035</t>
+          <t>0039715-57.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1580,27 +1580,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Rescisão / Resolução</t>
+          <t>Práticas Abusivas</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>27/08/2026 14:43</t>
+          <t>28/08/2026 17:23</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>27/08/2026 14:43</t>
+          <t>28/08/2026 17:23</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>21/09/2026 14:05</t>
+          <t>21/09/2026 16:25</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1617,7 +1617,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0002951-67.2023.8.16.0089</t>
+          <t>0006933-31.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1627,27 +1627,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Anulação e Correção de Provas / Questões</t>
+          <t>Reintegração | Licenciamento / Exclusão | Processo Administrativo Disciplinar / Sindicância</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>08/08/2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>27/08/2026 21:33</t>
+          <t>16/09/2026 17:13</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>27/08/2026 21:33</t>
+          <t>16/09/2026 17:13</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>07/09/2026 14:45</t>
+          <t>21/09/2026 16:25</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1664,7 +1664,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0003013-71.2020.8.16.0038</t>
+          <t>0009982-24.2015.8.16.0056</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1674,27 +1674,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Nota Promissória</t>
+          <t>Extorsão</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>30/01/2026</t>
+          <t>25/07/2023</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>16/09/2026 13:53</t>
+          <t>01/09/2026 16:13</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>16/09/2026 13:53</t>
+          <t>01/09/2026 16:13</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>21/09/2026 15:29</t>
+          <t>21/09/2026 16:30</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1711,37 +1711,37 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0003051-27.2025.8.16.0000</t>
+          <t>0012472-19.2014.8.16.0035</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>11/09/2023</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>31/08/2026 21:33</t>
+          <t>27/08/2026 18:43</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>31/08/2026 21:33</t>
+          <t>27/08/2026 18:43</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>21/09/2026 14:02</t>
+          <t>21/09/2026 16:30</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1758,37 +1758,37 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0003380-39.2025.8.16.0000</t>
+          <t>0045281-50.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cobrança de Aluguéis - Sem despejo</t>
+          <t>Homicídio Qualificado | Prisão Preventiva</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>26/08/2026 13:33</t>
+          <t>01/09/2026 15:43</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>26/08/2026 13:33</t>
+          <t>01/09/2026 15:43</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>21/09/2026 16:39</t>
+          <t>21/09/2026 16:30</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1805,37 +1805,37 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0003726-27.2016.8.16.0025</t>
+          <t>0006176-27.2024.8.16.0165</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>27/08/2026 15:13</t>
+          <t>24/08/2026 19:53</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>27/08/2026 15:13</t>
+          <t>24/08/2026 19:53</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>21/09/2026 15:23</t>
+          <t>21/09/2026 16:30</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1852,7 +1852,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0003825-19.2024.8.16.0024</t>
+          <t>0004303-83.2016.8.16.0193</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1862,27 +1862,27 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Acidente de Trânsito</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>24/04/2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>26/08/2026 08:33</t>
+          <t>01/09/2026 15:13</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>26/08/2026 08:33</t>
+          <t>01/09/2026 15:13</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>10/09/2026 20:46</t>
+          <t>21/09/2026 14:35</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1899,7 +1899,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0003932-67.2020.8.16.0165</t>
+          <t>0000159-93.2006.8.16.0071</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1909,27 +1909,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Rescisão / Resolução</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>12/11/2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>28/08/2026 15:23</t>
+          <t>24/08/2026 14:43</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>28/08/2026 15:23</t>
+          <t>24/08/2026 14:43</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>21/09/2026 16:39</t>
+          <t>21/09/2026 14:35</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1946,7 +1946,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0004303-83.2016.8.16.0193</t>
+          <t>0058218-29.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1956,22 +1956,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Acidente de Trânsito</t>
+          <t>Locação de Imóvel</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>24/04/2025</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>01/09/2026 15:13</t>
+          <t>01/09/2026 21:23</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>01/09/2026 15:13</t>
+          <t>01/09/2026 21:23</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0005076-02.2023.8.16.0188</t>
+          <t>0057679-63.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2003,27 +2003,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Inventário e Partilha</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>31/08/2026 19:23</t>
+          <t>04/09/2026 15:03</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>31/08/2026 19:23</t>
+          <t>04/09/2026 15:03</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>21/09/2026 15:12</t>
+          <t>21/09/2026 14:35</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2040,37 +2040,37 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0005148-49.2018.8.16.0160</t>
+          <t>0024923-52.2018.8.16.0030</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Acidente de Trânsito</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>16/11/2023</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>03/09/2026 13:53</t>
+          <t>27/08/2026 13:53</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>03/09/2026 13:53</t>
+          <t>27/08/2026 13:53</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>21/09/2026 16:38</t>
+          <t>21/09/2026 14:37</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2087,7 +2087,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0005311-55.2024.8.16.0148</t>
+          <t>0011629-34.2023.8.16.0069</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2097,27 +2097,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Práticas Abusivas</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>19/01/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>28/08/2026 15:13</t>
+          <t>25/08/2026 17:33</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>28/08/2026 15:13</t>
+          <t>25/08/2026 17:33</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>10/09/2026 21:16</t>
+          <t>21/09/2026 14:54</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2134,37 +2134,37 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0005472-92.2018.8.16.0013</t>
+          <t>0019992-74.2020.8.16.0017</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Crimes Militares | Peculato | Prevaricação | Supressão de documento | Regime inicial | Ausência de Fundamentação | Aplicação da Pena</t>
+          <t>PASEP</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>20/11/2023</t>
+          <t>23/01/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>25/08/2026 16:13</t>
+          <t>27/08/2026 14:43</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>25/08/2026 16:13</t>
+          <t>27/08/2026 14:43</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>21/09/2026 16:38</t>
+          <t>21/09/2026 14:54</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2181,7 +2181,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0005600-81.2022.8.16.0075</t>
+          <t>0006475-31.2022.8.16.0017</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2191,27 +2191,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Crime de Descumprimento de Medida Protetiva  de Urgência</t>
+          <t>Aquisição</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>27/08/2026 14:53</t>
+          <t>01/09/2026 16:13</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>27/08/2026 14:53</t>
+          <t>01/09/2026 16:13</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>21/09/2026 16:50</t>
+          <t>21/09/2026 14:57</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2228,7 +2228,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0005795-46.2012.8.16.0001</t>
+          <t>0005353-92.2025.8.16.0173</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2238,27 +2238,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Superendividamento</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>11/09/2026 13:43</t>
+          <t>27/08/2026 17:43</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>11/09/2026 13:43</t>
+          <t>27/08/2026 17:43</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>21/09/2026 16:44</t>
+          <t>21/09/2026 14:57</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2275,7 +2275,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0006176-27.2024.8.16.0165</t>
+          <t>0001761-66.2014.8.16.0095</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2285,27 +2285,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Esbulho / Turbação / Ameaça | Requerimento de Reintegração de Posse</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>24/08/2026 19:53</t>
+          <t>28/08/2026 13:53</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>24/08/2026 19:53</t>
+          <t>28/08/2026 13:53</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>21/09/2026 16:30</t>
+          <t>21/09/2026 14:57</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2322,7 +2322,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0006306-67.2024.8.16.0019</t>
+          <t>0089279-39.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2332,27 +2332,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Rescisão / Resolução | Sustação de Protesto | Duplicata</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>25/08/2026 19:43</t>
+          <t>27/08/2026 14:03</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>25/08/2026 19:43</t>
+          <t>27/08/2026 14:03</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>21/09/2026 16:30</t>
+          <t>21/09/2026 14:57</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2369,37 +2369,37 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0006682-16.2023.8.16.0075</t>
+          <t>0022498-42.2018.8.16.0001</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Embargos de Divergência em Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Juros de Mora - Legais / Contratuais</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>30/07/2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>24/08/2026 16:43</t>
+          <t>18/09/2026 13:53</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>24/08/2026 16:43</t>
+          <t>18/09/2026 13:53</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>21/09/2026 15:23</t>
+          <t>21/09/2026 15:02</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2416,37 +2416,37 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0006933-31.2024.8.16.0000</t>
+          <t>0032406-05.2013.8.16.0000</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Reintegração | Licenciamento / Exclusão | Processo Administrativo Disciplinar / Sindicância</t>
+          <t>Expurgos Inflacionários / Planos Econômicos</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>08/08/2025</t>
+          <t>26/03/2015</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>16/09/2026 17:13</t>
+          <t>24/08/2026 17:03</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>16/09/2026 17:13</t>
+          <t>24/08/2026 17:03</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>21/09/2026 16:25</t>
+          <t>21/09/2026 15:11</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2463,7 +2463,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0007090-04.2023.8.16.0173</t>
+          <t>0000952-20.2009.8.16.0138</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2473,27 +2473,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Compra e Venda</t>
+          <t>Anulação</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>24/04/2025</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>28/08/2026 12:56</t>
+          <t>31/08/2026 20:33</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>28/08/2026 12:56</t>
+          <t>31/08/2026 20:33</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>10/09/2026 20:44</t>
+          <t>21/09/2026 15:11</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2510,7 +2510,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0007230-04.2025.8.16.0000</t>
+          <t>0028491-41.2020.8.16.0019</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2520,27 +2520,27 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Rescisão / Resolução</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>20/05/2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>28/08/2026 18:43</t>
+          <t>09/09/2026 17:03</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>28/08/2026 18:43</t>
+          <t>09/09/2026 17:03</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>21/09/2026 15:25</t>
+          <t>21/09/2026 15:11</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2557,7 +2557,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0008017-50.2023.8.16.0017</t>
+          <t>0010574-95.2022.8.16.0194</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2567,27 +2567,27 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Locação de Imóvel | Embargos de Terceiro</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>25/08/2026 17:43</t>
+          <t>28/08/2026 21:03</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>25/08/2026 17:43</t>
+          <t>28/08/2026 21:03</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>10/09/2026 21:14</t>
+          <t>21/09/2026 15:12</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2604,7 +2604,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0008652-53.2021.8.16.0000</t>
+          <t>0000464-75.2024.8.16.0094</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2614,27 +2614,27 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Administração judicial</t>
+          <t>Crimes do Sistema Nacional de Armas</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>20/07/2022</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>04/09/2026 13:13</t>
+          <t>08/09/2026 19:33</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>04/09/2026 13:13</t>
+          <t>08/09/2026 19:33</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>07/09/2026 14:45</t>
+          <t>21/09/2026 15:12</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2651,7 +2651,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0008666-72.2016.8.16.0045</t>
+          <t>0001089-25.2019.8.16.0017</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2661,27 +2661,27 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Irregularidade no atendimento</t>
+          <t>Indenização por Dano Moral | Irregularidade no atendimento | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>28/08/2026 14:13</t>
+          <t>27/08/2026 17:43</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>28/08/2026 14:13</t>
+          <t>27/08/2026 17:43</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>21/09/2026 15:43</t>
+          <t>21/09/2026 15:12</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2698,7 +2698,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0009622-11.2008.8.16.0129</t>
+          <t>0119994-64.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2708,27 +2708,27 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Indenização por Dano Ambiental</t>
+          <t>IPTU/ Imposto Predial e Territorial Urbano</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>31/08/2026 20:53</t>
+          <t>16/09/2026 14:23</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>31/08/2026 20:53</t>
+          <t>16/09/2026 14:23</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>21/09/2026 15:27</t>
+          <t>21/09/2026 15:12</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2745,7 +2745,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0009982-24.2015.8.16.0056</t>
+          <t>0001355-61.2021.8.16.0075</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2755,27 +2755,27 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Extorsão</t>
+          <t>PIS/PASEP</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>25/07/2023</t>
+          <t>13/01/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>01/09/2026 16:13</t>
+          <t>17/09/2026 14:23</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>01/09/2026 16:13</t>
+          <t>17/09/2026 14:23</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>21/09/2026 16:30</t>
+          <t>21/09/2026 15:17</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2792,37 +2792,37 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0010574-95.2022.8.16.0194</t>
+          <t>0068730-71.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Crimes da Lei de licitações | Falsidade ideológica</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>15/12/2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>28/08/2026 21:03</t>
+          <t>31/08/2026 09:22</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>28/08/2026 21:03</t>
+          <t>31/08/2026 09:22</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>21/09/2026 15:12</t>
+          <t>21/09/2026 14:17</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2839,7 +2839,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0011153-70.2022.8.16.0185</t>
+          <t>0030612-23.2021.8.16.0014</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2849,27 +2849,27 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>Acidente de Trânsito | Acidente de Trânsito</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>30/01/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>01/09/2026 19:43</t>
+          <t>27/08/2026 20:43</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>01/09/2026 19:43</t>
+          <t>27/08/2026 20:43</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>21/09/2026 16:38</t>
+          <t>21/09/2026 14:19</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2886,37 +2886,37 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0012472-19.2014.8.16.0035</t>
+          <t>0020522-83.2025.8.16.0185</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação</t>
+          <t>Dívida Ativa (Execução Fiscal)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>11/09/2023</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>27/08/2026 18:43</t>
+          <t>11/09/2026 15:49</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>27/08/2026 18:43</t>
+          <t>11/09/2026 15:49</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>21/09/2026 16:30</t>
+          <t>21/09/2026 14:29</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2933,7 +2933,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0014179-15.2023.8.16.0194</t>
+          <t>0021915-38.2020.8.16.0017</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2943,27 +2943,27 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Rescisão do contrato e devolução do dinheiro | Indenização por Dano Moral | Indenização por Dano Material | Dever de Informação</t>
+          <t>Compra e Venda</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>27/08/2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>27/08/2026 14:03</t>
+          <t>27/08/2026 14:13</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>27/08/2026 14:03</t>
+          <t>27/08/2026 14:13</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>21/09/2026 15:25</t>
+          <t>21/09/2026 13:46</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3027,7 +3027,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0017529-91.2012.8.16.0001</t>
+          <t>0003051-27.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3037,27 +3037,27 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>27/01/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>27/08/2026 21:23</t>
+          <t>31/08/2026 21:33</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>27/08/2026 21:23</t>
+          <t>31/08/2026 21:33</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>07/09/2026 14:45</t>
+          <t>21/09/2026 14:02</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3074,7 +3074,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0020522-83.2025.8.16.0185</t>
+          <t>0001736-85.2022.8.16.0123</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3084,27 +3084,27 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>Pagamento em Consignação</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>11/09/2026 15:49</t>
+          <t>01/09/2026 19:53</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>11/09/2026 15:49</t>
+          <t>01/09/2026 19:53</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>21/09/2026 14:29</t>
+          <t>21/09/2026 14:02</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3121,7 +3121,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0021915-38.2020.8.16.0017</t>
+          <t>0082930-85.2018.8.16.0014</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3131,27 +3131,27 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Compra e Venda</t>
+          <t>Homicídio Qualificado</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>27/08/2025</t>
+          <t>25/02/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>27/08/2026 14:13</t>
+          <t>02/09/2026 14:23</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>27/08/2026 14:13</t>
+          <t>02/09/2026 14:23</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>21/09/2026 13:46</t>
+          <t>21/09/2026 14:02</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3168,37 +3168,37 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0022429-13.2018.8.16.0000</t>
+          <t>0002760-24.2022.8.16.0035</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Anônima | Adimplemento e Extinção</t>
+          <t>Rescisão / Resolução</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>06/03/2020</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>11/09/2026 15:03</t>
+          <t>27/08/2026 14:43</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>11/09/2026 15:03</t>
+          <t>27/08/2026 14:43</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>21/09/2026 16:30</t>
+          <t>21/09/2026 14:05</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3215,7 +3215,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0022909-70.2023.8.16.0014</t>
+          <t>0002529-36.2021.8.16.0098</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3225,22 +3225,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Dever de Informação | Irregularidade no atendimento</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>27/09/2024</t>
+          <t>02/08/2024</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>27/08/2026 15:59</t>
+          <t>31/08/2026 11:38</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>27/08/2026 15:59</t>
+          <t>31/08/2026 11:38</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3262,37 +3262,37 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0028035-41.2026.8.16.0000</t>
+          <t>0008017-50.2023.8.16.0017</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins</t>
+          <t>Locação de Imóvel | Embargos de Terceiro</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>29/01/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>02/09/2026 08:35</t>
+          <t>25/08/2026 17:43</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>02/09/2026 08:35</t>
+          <t>25/08/2026 17:43</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>10/09/2026 20:46</t>
+          <t>10/09/2026 21:14</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3309,37 +3309,37 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0028491-41.2020.8.16.0019</t>
+          <t>0022909-70.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>20/05/2025</t>
+          <t>27/09/2024</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>09/09/2026 17:03</t>
+          <t>27/08/2026 15:59</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>09/09/2026 17:03</t>
+          <t>27/08/2026 15:59</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>21/09/2026 15:11</t>
+          <t>10/09/2026 21:14</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3356,7 +3356,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0028571-45.2009.8.16.0001</t>
+          <t>0109932-62.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3366,27 +3366,27 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Inventário e Partilha</t>
+          <t>Prescrição e Decadência</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>05/11/2025</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>25/08/2026 20:03</t>
+          <t>24/08/2026 16:53</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>25/08/2026 20:03</t>
+          <t>24/08/2026 16:53</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>21/09/2026 14:54</t>
+          <t>10/09/2026 21:16</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3403,7 +3403,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0030612-23.2021.8.16.0014</t>
+          <t>0005311-55.2024.8.16.0148</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3413,27 +3413,27 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Acidente de Trânsito | Acidente de Trânsito</t>
+          <t>Práticas Abusivas</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>27/08/2026 20:43</t>
+          <t>28/08/2026 15:13</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>27/08/2026 20:43</t>
+          <t>28/08/2026 15:13</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>21/09/2026 14:19</t>
+          <t>10/09/2026 21:16</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3450,37 +3450,37 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0032406-05.2013.8.16.0000</t>
+          <t>0000245-29.2022.8.16.0160</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Expurgos Inflacionários / Planos Econômicos</t>
+          <t>Contratos Bancários | Perdas e Danos | Cerceamento de Defesa | Provas | Obrigação de Entregar</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>26/03/2015</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>24/08/2026 17:03</t>
+          <t>10/09/2026 15:23</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>24/08/2026 17:03</t>
+          <t>10/09/2026 15:23</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>21/09/2026 15:11</t>
+          <t>10/09/2026 21:24</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3497,7 +3497,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0033485-96.2025.8.16.0000</t>
+          <t>0081354-89.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3507,27 +3507,27 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Indenização por Dano Moral | Penhora / Depósito/ Avaliação | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>26/09/2025</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>24/08/2026 16:03</t>
+          <t>31/08/2026 16:43</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>24/08/2026 16:03</t>
+          <t>31/08/2026 16:43</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>21/09/2026 16:40</t>
+          <t>10/09/2026 21:29</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3544,7 +3544,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0035495-50.2024.8.16.0000</t>
+          <t>0008652-53.2021.8.16.0000</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3554,27 +3554,27 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Evicção ou Vicio Redibitório | Indenização por Dano Moral | Indenização por Dano Material</t>
+          <t>Administração judicial</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>20/07/2022</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>27/08/2026 21:33</t>
+          <t>04/09/2026 13:13</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>27/08/2026 21:33</t>
+          <t>04/09/2026 13:13</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>10/09/2026 20:46</t>
+          <t>07/09/2026 14:45</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3591,7 +3591,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0037574-28.2022.8.16.0014</t>
+          <t>0017529-91.2012.8.16.0001</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3601,27 +3601,27 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Locação de Imóvel</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>27/01/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>31/08/2026 19:03</t>
+          <t>27/08/2026 21:23</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>31/08/2026 19:03</t>
+          <t>27/08/2026 21:23</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>21/09/2026 16:40</t>
+          <t>07/09/2026 14:45</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3638,7 +3638,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0039715-57.2025.8.16.0000</t>
+          <t>0002951-67.2023.8.16.0089</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3648,27 +3648,27 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Práticas Abusivas</t>
+          <t>Anulação e Correção de Provas / Questões</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>28/08/2026 17:23</t>
+          <t>27/08/2026 21:33</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>28/08/2026 17:23</t>
+          <t>27/08/2026 21:33</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>21/09/2026 16:25</t>
+          <t>07/09/2026 14:45</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3685,37 +3685,37 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0040099-71.2008.8.16.0014</t>
+          <t>0083650-50.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Enriquecimento ilícito</t>
+          <t>Promessa de Compra e Venda | Esbulho / Turbação / Ameaça | Requerimento de Reintegração de Posse</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>18/02/2022</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>31/08/2026 13:23</t>
+          <t>27/08/2026 19:53</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>31/08/2026 13:23</t>
+          <t>27/08/2026 19:53</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>21/09/2026 15:38</t>
+          <t>07/09/2026 14:46</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3732,37 +3732,37 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0045281-50.2026.8.16.0000</t>
+          <t>0007090-04.2023.8.16.0173</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Homicídio Qualificado | Prisão Preventiva</t>
+          <t>Compra e Venda</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>24/04/2025</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>01/09/2026 15:43</t>
+          <t>28/08/2026 12:56</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>01/09/2026 15:43</t>
+          <t>28/08/2026 12:56</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>21/09/2026 16:30</t>
+          <t>10/09/2026 20:44</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3779,7 +3779,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0057679-63.2025.8.16.0000</t>
+          <t>0003825-19.2024.8.16.0024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3789,27 +3789,27 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>04/09/2026 15:03</t>
+          <t>26/08/2026 08:33</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>04/09/2026 15:03</t>
+          <t>26/08/2026 08:33</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>21/09/2026 14:35</t>
+          <t>10/09/2026 20:46</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3826,7 +3826,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0058218-29.2025.8.16.0000</t>
+          <t>0035495-50.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3836,27 +3836,27 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Locação de Imóvel</t>
+          <t>Evicção ou Vicio Redibitório | Indenização por Dano Moral | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>01/09/2026 21:23</t>
+          <t>27/08/2026 21:33</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>01/09/2026 21:23</t>
+          <t>27/08/2026 21:33</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>21/09/2026 14:35</t>
+          <t>10/09/2026 20:46</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3873,37 +3873,37 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0058940-63.2025.8.16.0000</t>
+          <t>4002116-51.2025.8.16.4321</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Remição</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>01/09/2026 17:23</t>
+          <t>25/08/2026 17:03</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>01/09/2026 17:23</t>
+          <t>25/08/2026 17:03</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>21/09/2026 16:39</t>
+          <t>10/09/2026 20:46</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3920,37 +3920,37 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0058967-46.2025.8.16.0000</t>
+          <t>0028035-41.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Rural</t>
+          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>28/08/2026 21:23</t>
+          <t>02/09/2026 08:35</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>28/08/2026 21:23</t>
+          <t>02/09/2026 08:35</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>21/09/2026 15:16</t>
+          <t>10/09/2026 20:46</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3967,7 +3967,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0060797-47.2025.8.16.0000</t>
+          <t>0037574-28.2022.8.16.0014</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3977,22 +3977,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Gratuidade | Assistência Judiciária Gratuita</t>
+          <t>Locação de Imóvel</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>25/08/2026 19:23</t>
+          <t>31/08/2026 19:03</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>25/08/2026 19:23</t>
+          <t>31/08/2026 19:03</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4014,7 +4014,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0068139-43.2020.8.16.0014</t>
+          <t>0060797-47.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4024,27 +4024,27 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Erro Médico | Erro Médico</t>
+          <t>Gratuidade | Assistência Judiciária Gratuita</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>12/01/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>25/08/2026 14:33</t>
+          <t>25/08/2026 19:23</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>25/08/2026 14:33</t>
+          <t>25/08/2026 19:23</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>21/09/2026 15:25</t>
+          <t>21/09/2026 16:40</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4061,37 +4061,37 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0068730-71.2025.8.16.0000</t>
+          <t>0033485-96.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Crimes da Lei de licitações | Falsidade ideológica</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>15/12/2025</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>31/08/2026 09:22</t>
+          <t>24/08/2026 16:03</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>31/08/2026 09:22</t>
+          <t>24/08/2026 16:03</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>21/09/2026 14:17</t>
+          <t>21/09/2026 16:40</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -4108,37 +4108,37 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0076534-56.2026.8.16.0000</t>
+          <t>0005795-46.2012.8.16.0001</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Crimes do Sistema Nacional de Armas | Desobediência</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>31/08/2026 17:23</t>
+          <t>11/09/2026 13:43</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>31/08/2026 17:23</t>
+          <t>11/09/2026 13:43</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>21/09/2026 15:43</t>
+          <t>21/09/2026 16:44</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4155,7 +4155,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0078301-66.2025.8.16.0000</t>
+          <t>0001878-08.2025.8.16.0116</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4165,27 +4165,27 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Rural | Tutela de Urgência | Cédula de Produto Rural</t>
+          <t>Irregularidade no atendimento | Indenização por Dano Moral | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>31/08/2026 15:23</t>
+          <t>28/08/2026 18:53</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>31/08/2026 15:23</t>
+          <t>28/08/2026 18:53</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>21/09/2026 15:25</t>
+          <t>21/09/2026 16:50</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4202,7 +4202,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0078867-15.2025.8.16.0000</t>
+          <t>0006306-67.2024.8.16.0019</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4212,27 +4212,27 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Alienação Fiduciária</t>
+          <t>Rescisão / Resolução | Sustação de Protesto | Duplicata</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>28/08/2026 19:33</t>
+          <t>25/08/2026 19:43</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>28/08/2026 19:33</t>
+          <t>25/08/2026 19:43</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>21/09/2026 15:25</t>
+          <t>21/09/2026 16:30</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4249,7 +4249,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0080874-14.2024.8.16.0000</t>
+          <t>0001007-92.2020.8.16.0167</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4259,27 +4259,27 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Duplicata</t>
+          <t>Indenização por Dano Material | Indenização por Dano Moral | Tutela de Urgência</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>12/09/2025</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>27/08/2026 21:23</t>
+          <t>27/08/2026 19:43</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>27/08/2026 21:23</t>
+          <t>27/08/2026 19:43</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>21/09/2026 15:23</t>
+          <t>21/09/2026 16:30</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4296,37 +4296,37 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0081354-89.2024.8.16.0000</t>
+          <t>0022429-13.2018.8.16.0000</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Penhora / Depósito/ Avaliação | Indenização por Dano Material</t>
+          <t>Anônima | Adimplemento e Extinção</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>26/09/2025</t>
+          <t>06/03/2020</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>31/08/2026 16:43</t>
+          <t>11/09/2026 15:03</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>31/08/2026 16:43</t>
+          <t>11/09/2026 15:03</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>10/09/2026 21:29</t>
+          <t>21/09/2026 16:30</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4343,37 +4343,37 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0082930-85.2018.8.16.0014</t>
+          <t>0005472-92.2018.8.16.0013</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Homicídio Qualificado</t>
+          <t>Crimes Militares | Peculato | Prevaricação | Supressão de documento | Regime inicial | Ausência de Fundamentação | Aplicação da Pena</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>25/02/2026</t>
+          <t>20/11/2023</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>02/09/2026 14:23</t>
+          <t>25/08/2026 16:13</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>02/09/2026 14:23</t>
+          <t>25/08/2026 16:13</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>21/09/2026 14:02</t>
+          <t>21/09/2026 16:38</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4390,7 +4390,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0083650-50.2025.8.16.0000</t>
+          <t>0011153-70.2022.8.16.0185</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4400,27 +4400,27 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Promessa de Compra e Venda | Esbulho / Turbação / Ameaça | Requerimento de Reintegração de Posse</t>
+          <t>Dívida Ativa (Execução Fiscal)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>30/01/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>27/08/2026 19:53</t>
+          <t>01/09/2026 19:43</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>27/08/2026 19:53</t>
+          <t>01/09/2026 19:43</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>07/09/2026 14:46</t>
+          <t>21/09/2026 16:38</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4437,7 +4437,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0091747-39.2025.8.16.0000</t>
+          <t>0058940-63.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4447,22 +4447,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Desconsideração da Personalidade Jurídica</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>31/08/2026 13:03</t>
+          <t>01/09/2026 17:23</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>31/08/2026 13:03</t>
+          <t>01/09/2026 17:23</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -4484,37 +4484,37 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0097979-04.2024.8.16.0000</t>
+          <t>0126160-15.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Despejo para Uso Próprio</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>27/08/2026 18:23</t>
+          <t>08/09/2026 14:43</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>27/08/2026 18:23</t>
+          <t>08/09/2026 14:43</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>21/09/2026 14:57</t>
+          <t>21/09/2026 14:54</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4531,7 +4531,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0109932-62.2024.8.16.0000</t>
+          <t>0028571-45.2009.8.16.0001</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4541,27 +4541,27 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Prescrição e Decadência</t>
+          <t>Inventário e Partilha</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>24/08/2026 16:53</t>
+          <t>25/08/2026 20:03</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>24/08/2026 16:53</t>
+          <t>25/08/2026 20:03</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>10/09/2026 21:16</t>
+          <t>21/09/2026 14:54</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4578,7 +4578,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0113231-47.2024.8.16.0000</t>
+          <t>0097979-04.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4588,27 +4588,27 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Despejo para Uso Próprio</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>09/09/2026 21:03</t>
+          <t>27/08/2026 18:23</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>09/09/2026 21:03</t>
+          <t>27/08/2026 18:23</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>21/09/2026 16:40</t>
+          <t>21/09/2026 14:57</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4625,7 +4625,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0119994-64.2024.8.16.0000</t>
+          <t>0005076-02.2023.8.16.0188</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4635,22 +4635,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>IPTU/ Imposto Predial e Territorial Urbano</t>
+          <t>Inventário e Partilha</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>16/09/2026 14:23</t>
+          <t>31/08/2026 19:23</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>16/09/2026 14:23</t>
+          <t>31/08/2026 19:23</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -4672,37 +4672,37 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0126160-15.2024.8.16.0000</t>
+          <t>0058967-46.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Cédula de Crédito Rural</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>05/11/2025</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>08/09/2026 14:43</t>
+          <t>28/08/2026 21:23</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>08/09/2026 14:43</t>
+          <t>28/08/2026 21:23</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>21/09/2026 14:54</t>
+          <t>21/09/2026 15:16</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4719,37 +4719,37 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0148342-58.2025.8.16.0000</t>
+          <t>0000390-38.2022.8.16.0111</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Cerceamento de Defesa | Prova Ilícita | Excesso de prazo para instrução / julgamento | Prisão Preventiva</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>02/03/2026</t>
+          <t>08/10/2025</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>24/08/2026 19:03</t>
+          <t>18/09/2026 14:33</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>24/08/2026 19:03</t>
+          <t>18/09/2026 14:33</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>21/09/2026 16:13</t>
+          <t>21/09/2026 15:16</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4766,7 +4766,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>4002116-51.2025.8.16.4321</t>
+          <t>0003726-27.2016.8.16.0025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4776,27 +4776,27 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Remição</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>25/08/2026 17:03</t>
+          <t>27/08/2026 15:13</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>25/08/2026 17:03</t>
+          <t>27/08/2026 15:13</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>10/09/2026 20:46</t>
+          <t>21/09/2026 15:23</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4805,6 +4805,382 @@
         </is>
       </c>
       <c r="I93" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>0080874-14.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Duplicata</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>12/09/2025</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>27/08/2026 21:23</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>27/08/2026 21:23</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>21/09/2026 15:23</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>0006682-16.2023.8.16.0075</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>16/12/2025</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>24/08/2026 16:43</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>24/08/2026 16:43</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>21/09/2026 15:23</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>0014179-15.2023.8.16.0194</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Rescisão do contrato e devolução do dinheiro | Indenização por Dano Moral | Indenização por Dano Material | Dever de Informação</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>27/08/2026 14:03</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>27/08/2026 14:03</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>21/09/2026 15:25</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>0009622-11.2008.8.16.0129</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Ambiental</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>31/08/2026 20:53</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>31/08/2026 20:53</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>21/09/2026 15:27</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>0000607-45.2017.8.16.0115</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>28/08/2026 18:23</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>28/08/2026 18:23</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>21/09/2026 15:27</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>0040099-71.2008.8.16.0014</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Enriquecimento ilícito</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>18/02/2022</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>31/08/2026 13:23</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>31/08/2026 13:23</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>21/09/2026 15:38</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>0076534-56.2026.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Recurso Ordinário em Habeas Corpus</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Crimes do Sistema Nacional de Armas | Desobediência</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>13/08/2026</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>31/08/2026 17:23</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>31/08/2026 17:23</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>21/09/2026 15:43</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>0008666-72.2016.8.16.0045</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Material | Irregularidade no atendimento</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>28/08/2026 14:13</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>28/08/2026 14:13</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>21/09/2026 15:43</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>

--- a/docs/resultados.xlsx
+++ b/docs/resultados.xlsx
@@ -425,12 +425,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
@@ -486,6 +486,4706 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>0005600-81.2022.8.16.0075</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Crime de Descumprimento de Medida Protetiva  de Urgência</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>27/08/2026 14:53</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>27/08/2026 14:53</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>21/09/2026 16:50</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>0001534-86.2022.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Alienação Fiduciária</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>11/03/2026</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>31/08/2026 19:13</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>31/08/2026 19:13</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>21/09/2026 16:53</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>0005148-49.2018.8.16.0160</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Acidente de Trânsito</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>16/11/2023</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>03/09/2026 13:53</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>03/09/2026 13:53</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>21/09/2026 16:38</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>0001673-07.2023.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Embargos de Divergência em Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços | Honorários Advocatícios</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>17/11/2023</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>02/09/2026 16:32</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>02/09/2026 17:38</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>21/09/2026 16:38</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>0091747-39.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Desconsideração da Personalidade Jurídica</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>31/08/2026 13:03</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>31/08/2026 13:03</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>21/09/2026 16:39</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>0003932-67.2020.8.16.0165</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Rescisão / Resolução</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>28/08/2026 15:23</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>28/08/2026 15:23</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>21/09/2026 16:39</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>0002709-14.2014.8.16.0190</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Assembléia | Saneamento</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>28/08/2026 13:23</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>28/08/2026 13:23</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>21/09/2026 16:39</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>0002705-17.2024.8.16.0031</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Uso de documento falso | Falso testemunho ou falsa perícia</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>01/09/2026 14:03</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>01/09/2026 14:03</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>21/09/2026 16:39</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>0003380-39.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Cobrança de Aluguéis - Sem despejo</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>26/08/2026 13:33</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>26/08/2026 13:33</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>21/09/2026 16:39</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>0113231-47.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>21/07/2025</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>09/09/2026 21:03</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>09/09/2026 21:03</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>21/09/2026 16:40</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>0078301-66.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Cédula de Crédito Rural | Tutela de Urgência | Cédula de Produto Rural</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>31/08/2026 15:23</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>31/08/2026 15:23</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>21/09/2026 15:25</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>0007230-04.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Rescisão / Resolução</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>25/03/2026</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>28/08/2026 18:43</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>28/08/2026 18:43</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>21/09/2026 15:25</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>0078867-15.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Alienação Fiduciária</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>28/08/2026 19:33</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>28/08/2026 19:33</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>21/09/2026 15:25</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>0000250-62.2023.8.16.0048</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Cheque | Perdas e Danos</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>27/08/2026 18:13</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>27/08/2026 18:13</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>21/09/2026 15:27</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>0003013-71.2020.8.16.0038</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Nota Promissória</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>30/01/2026</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>16/09/2026 13:53</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>16/09/2026 13:53</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>21/09/2026 15:29</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>0002299-04.2015.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>17/09/2026 15:33</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>17/09/2026 15:33</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>21/09/2026 15:31</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>0000908-97.2024.8.16.0033</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>15/09/2026 17:03</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>15/09/2026 17:03</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>21/09/2026 15:32</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>0002642-82.2021.8.16.0035</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Rescisão / Resolução</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>16/09/2026 14:23</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>16/09/2026 14:23</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>21/09/2026 15:33</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>0000233-50.2020.8.16.0171</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Cédula de Crédito Rural</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>27/08/2026 14:43</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>27/08/2026 14:43</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>21/09/2026 15:43</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>0000940-42.2025.8.16.0074</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Rescisão / Resolução</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>02/09/2026 13:23</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>02/09/2026 13:23</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>21/09/2026 15:43</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>0039715-57.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Práticas Abusivas</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>28/08/2026 17:23</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>28/08/2026 17:23</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>21/09/2026 16:25</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>0006933-31.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Reintegração | Licenciamento / Exclusão | Processo Administrativo Disciplinar / Sindicância</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>08/08/2025</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>16/09/2026 17:13</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>16/09/2026 17:13</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>21/09/2026 16:25</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>0009982-24.2015.8.16.0056</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Extorsão</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>25/07/2023</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>01/09/2026 16:13</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>01/09/2026 16:13</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>21/09/2026 16:30</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>0012472-19.2014.8.16.0035</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Defeito, nulidade ou anulação</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>11/09/2023</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>27/08/2026 18:43</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>27/08/2026 18:43</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>21/09/2026 16:30</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>0045281-50.2026.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Recurso Ordinário em Habeas Corpus</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Homicídio Qualificado | Prisão Preventiva</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>01/09/2026 15:43</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>01/09/2026 15:43</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>21/09/2026 16:30</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>0004303-83.2016.8.16.0193</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Acidente de Trânsito</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>24/04/2025</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>01/09/2026 15:13</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>01/09/2026 15:13</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>21/09/2026 14:35</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>0058218-29.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Locação de Imóvel</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>01/09/2026 21:23</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>01/09/2026 21:23</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>21/09/2026 14:35</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>0057679-63.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Contratos Bancários</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>04/09/2026 15:03</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>04/09/2026 15:03</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>21/09/2026 14:35</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>0024923-52.2018.8.16.0030</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Contratos Bancários</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>27/08/2026 13:53</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>27/08/2026 13:53</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>21/09/2026 14:37</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>0019992-74.2020.8.16.0017</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>PASEP</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>23/01/2026</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>27/08/2026 14:43</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>27/08/2026 14:43</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>21/09/2026 14:54</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>0006475-31.2022.8.16.0017</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Aquisição</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>01/09/2026 16:13</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>01/09/2026 16:13</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>21/09/2026 14:57</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>0005353-92.2025.8.16.0173</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Superendividamento</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>27/08/2026 17:43</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>27/08/2026 17:43</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>21/09/2026 14:57</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>0001761-66.2014.8.16.0095</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Esbulho / Turbação / Ameaça | Requerimento de Reintegração de Posse</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>28/08/2026 13:53</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>28/08/2026 13:53</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>21/09/2026 14:57</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>0089279-39.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>27/08/2026 14:03</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>27/08/2026 14:03</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>21/09/2026 14:57</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>0022498-42.2018.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Embargos de Divergência em Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Juros de Mora - Legais / Contratuais</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>30/07/2025</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>18/09/2026 13:53</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>18/09/2026 13:53</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>21/09/2026 15:02</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>0000952-20.2009.8.16.0138</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Anulação</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>28/01/2026</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>31/08/2026 20:33</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>31/08/2026 20:33</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>21/09/2026 15:11</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>0028491-41.2020.8.16.0019</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Defeito, nulidade ou anulação</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>20/05/2025</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>09/09/2026 17:03</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>09/09/2026 17:03</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>21/09/2026 15:11</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>0010574-95.2022.8.16.0194</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Seguro</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>28/08/2026 21:03</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>28/08/2026 21:03</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>21/09/2026 15:12</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>0000464-75.2024.8.16.0094</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Crimes do Sistema Nacional de Armas</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>08/09/2026 19:33</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>08/09/2026 19:33</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>21/09/2026 15:12</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>0001089-25.2019.8.16.0017</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Moral | Irregularidade no atendimento | Indenização por Dano Material</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>27/08/2026 17:43</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>27/08/2026 17:43</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>21/09/2026 15:12</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>0119994-64.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>IPTU/ Imposto Predial e Territorial Urbano</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>16/09/2026 14:23</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>16/09/2026 14:23</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>21/09/2026 15:12</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>0001355-61.2021.8.16.0075</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>PIS/PASEP</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>13/01/2026</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>17/09/2026 14:23</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>17/09/2026 14:23</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>21/09/2026 15:17</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>0068730-71.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Crimes da Lei de licitações | Falsidade ideológica</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>15/12/2025</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>31/08/2026 09:22</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>31/08/2026 09:22</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>21/09/2026 14:17</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>0030612-23.2021.8.16.0014</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Acidente de Trânsito | Acidente de Trânsito</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>27/08/2026 20:43</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>27/08/2026 20:43</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>21/09/2026 14:19</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>0020522-83.2025.8.16.0185</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Dívida Ativa (Execução Fiscal)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>11/09/2026 15:49</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>11/09/2026 15:49</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>21/09/2026 14:29</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>0021915-38.2020.8.16.0017</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Compra e Venda</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>27/08/2025</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>27/08/2026 14:13</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>27/08/2026 14:13</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>21/09/2026 13:46</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>0014882-98.2023.8.16.0014</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>17/02/2025</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>01/09/2026 15:53</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>01/09/2026 15:53</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>21/09/2026 13:59</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>0003051-27.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Contratos Bancários</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>31/08/2026 21:33</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>31/08/2026 21:33</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>21/09/2026 14:02</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>0001736-85.2022.8.16.0123</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Pagamento em Consignação</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>01/09/2026 19:53</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>01/09/2026 19:53</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>21/09/2026 14:02</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>0082930-85.2018.8.16.0014</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Homicídio Qualificado</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>25/02/2026</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>02/09/2026 14:23</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>02/09/2026 14:23</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>21/09/2026 14:02</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>0002760-24.2022.8.16.0035</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Rescisão / Resolução</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>27/08/2026 14:43</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>27/08/2026 14:43</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>21/09/2026 14:05</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>0002529-36.2021.8.16.0098</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Dever de Informação | Irregularidade no atendimento</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>02/08/2024</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>31/08/2026 11:38</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>31/08/2026 11:38</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>10/09/2026 21:14</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>0022909-70.2023.8.16.0014</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>27/09/2024</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>27/08/2026 15:59</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>27/08/2026 15:59</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>10/09/2026 21:14</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>0005311-55.2024.8.16.0148</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Práticas Abusivas</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>28/08/2026 15:13</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>28/08/2026 15:13</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>10/09/2026 21:16</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>0000245-29.2022.8.16.0160</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Contratos Bancários | Perdas e Danos | Cerceamento de Defesa | Provas | Obrigação de Entregar</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>10/09/2026 15:23</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>10/09/2026 15:23</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>10/09/2026 21:24</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>0081354-89.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Moral | Penhora / Depósito/ Avaliação | Indenização por Dano Material</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>26/09/2025</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>31/08/2026 16:43</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>31/08/2026 16:43</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>10/09/2026 21:29</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>0008652-53.2021.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Administração judicial</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>20/07/2022</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>04/09/2026 13:13</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>04/09/2026 13:13</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>07/09/2026 14:45</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>0017529-91.2012.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>27/01/2026</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>27/08/2026 21:23</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>27/08/2026 21:23</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>07/09/2026 14:45</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>0002951-67.2023.8.16.0089</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Anulação e Correção de Provas / Questões</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>27/08/2026 21:33</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>27/08/2026 21:33</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>07/09/2026 14:45</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>0083650-50.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Promessa de Compra e Venda | Esbulho / Turbação / Ameaça | Requerimento de Reintegração de Posse</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>27/08/2026 19:53</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>27/08/2026 19:53</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>07/09/2026 14:46</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>0007090-04.2023.8.16.0173</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Compra e Venda</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>24/04/2025</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>28/08/2026 12:56</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>28/08/2026 12:56</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>10/09/2026 20:44</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>0003825-19.2024.8.16.0024</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>26/08/2026 08:33</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>26/08/2026 08:33</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>10/09/2026 20:46</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>0035495-50.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Evicção ou Vicio Redibitório | Indenização por Dano Moral | Indenização por Dano Material</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>27/08/2026 21:33</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>27/08/2026 21:33</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>10/09/2026 20:46</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>0028035-41.2026.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Recurso Ordinário em Habeas Corpus</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>02/09/2026 08:35</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>02/09/2026 08:35</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>10/09/2026 20:46</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>0037574-28.2022.8.16.0014</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Locação de Imóvel</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>31/08/2026 19:03</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>31/08/2026 19:03</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>21/09/2026 16:40</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>0005795-46.2012.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Contratos Bancários</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>11/09/2026 13:43</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>11/09/2026 13:43</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>21/09/2026 16:44</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>0001878-08.2025.8.16.0116</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Irregularidade no atendimento | Indenização por Dano Moral | Indenização por Dano Material</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>28/08/2026 18:53</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>28/08/2026 18:53</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>21/09/2026 16:50</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>0009622-11.2008.8.16.0129</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Ambiental</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>31/08/2026 20:53</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>31/08/2026 20:53</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>21/09/2026 15:27</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>0000607-45.2017.8.16.0115</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>28/08/2026 18:23</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>28/08/2026 18:23</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>21/09/2026 15:27</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>0040099-71.2008.8.16.0014</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Enriquecimento ilícito</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>18/02/2022</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>31/08/2026 13:23</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>31/08/2026 13:23</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>21/09/2026 15:38</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>0076534-56.2026.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Recurso Ordinário em Habeas Corpus</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Crimes do Sistema Nacional de Armas | Desobediência</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>13/08/2026</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>31/08/2026 17:23</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>31/08/2026 17:23</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>21/09/2026 15:43</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>0008666-72.2016.8.16.0045</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Material | Irregularidade no atendimento</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>28/08/2026 14:13</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>28/08/2026 14:13</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>21/09/2026 15:43</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>0016803-88.2020.8.16.0017</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Interpretação / Revisão de Contrato | Limitação de Juros</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>21/03/2023</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>31/08/2026 21:43</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>31/08/2026 21:43</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>21/09/2026 16:13</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>0001656-36.2023.8.16.0043</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Direito de Vizinhança</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>31/08/2026 20:53</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>31/08/2026 20:53</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>21/09/2026 16:25</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>0094271-09.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Cédula de Crédito Bancário</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>31/08/2026 19:43</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>31/08/2026 19:43</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>21/09/2026 16:25</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>0001007-92.2020.8.16.0167</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Material | Indenização por Dano Moral | Tutela de Urgência</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>27/08/2026 19:43</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>27/08/2026 19:43</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>21/09/2026 16:30</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>0022429-13.2018.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Anônima | Adimplemento e Extinção</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>06/03/2020</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>11/09/2026 15:03</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>11/09/2026 15:03</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>21/09/2026 16:30</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>0011153-70.2022.8.16.0185</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Dívida Ativa (Execução Fiscal)</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>30/01/2026</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>01/09/2026 19:43</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>01/09/2026 19:43</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>21/09/2026 16:38</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>0058940-63.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Contratos Bancários</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>01/09/2026 17:23</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>01/09/2026 17:23</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>21/09/2026 16:39</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>0003726-27.2016.8.16.0025</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Moral</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>14/03/2025</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>27/08/2026 15:13</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>27/08/2026 15:13</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>21/09/2026 15:23</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>0080874-14.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Duplicata</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>12/09/2025</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>27/08/2026 21:23</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>27/08/2026 21:23</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>21/09/2026 15:23</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>0014179-15.2023.8.16.0194</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Rescisão do contrato e devolução do dinheiro | Indenização por Dano Moral | Indenização por Dano Material | Dever de Informação</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>27/08/2026 14:03</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>27/08/2026 14:03</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>21/09/2026 15:25</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>0015051-90.2024.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Pagamento com Sub-rogação</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>11/09/2026 15:33</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>11/09/2026 15:33</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>21/09/2026 14:41</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>0000369-26.2023.8.16.0047</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Contratos Bancários</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>17/09/2026 13:13</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>17/09/2026 13:13</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>21/09/2026 14:43</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>0126160-15.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>05/11/2025</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>08/09/2026 14:43</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>08/09/2026 14:43</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>21/09/2026 14:54</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>0097979-04.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Despejo para Uso Próprio</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>27/08/2026 18:23</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>27/08/2026 18:23</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>21/09/2026 14:57</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>0005076-02.2023.8.16.0188</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Inventário e Partilha</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>31/08/2026 19:23</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>31/08/2026 19:23</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>21/09/2026 15:12</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>0058967-46.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Cédula de Crédito Rural</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>28/08/2026 21:23</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>28/08/2026 21:23</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>21/09/2026 15:16</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>0000390-38.2022.8.16.0111</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Seguro</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>08/10/2025</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>18/09/2026 14:33</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>18/09/2026 14:33</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>21/09/2026 15:16</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>0057555-24.2014.8.16.0014</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Receptação</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>26/08/2026 13:13</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>26/08/2026 13:13</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>21/09/2026 13:48</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>0055564-27.2025.8.16.0014</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>01/09/2026 13:23</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>01/09/2026 13:23</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>21/09/2026 13:48</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>0005264-71.2023.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>28/07/2025</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>27/08/2026 19:03</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>27/08/2026 19:03</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>21/09/2026 13:59</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>0018231-22.2021.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Planos de saúde</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>08/01/2026</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>27/08/2026 15:53</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>27/08/2026 15:53</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>21/09/2026 14:02</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>0000779-72.2025.8.16.0190</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Pedido de Uniformização de Interpretação de Lei Criminal</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Adicional de Insalubridade</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>31/08/2026 16:53</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>31/08/2026 16:53</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>21/09/2026 14:02</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>0004606-37.2020.8.16.0103</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Adimplemento e Extinção | Espécies de Contratos</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>05/08/2024</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>08/09/2026 15:53</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>08/09/2026 15:53</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>21/09/2026 14:17</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>0005776-89.2016.8.16.0004</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Reajustes de Remuneração, Proventos ou Pensão</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>02/02/2024</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>26/08/2026 15:23</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>26/08/2026 15:23</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>21/09/2026 14:35</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>0000457-45.2021.8.16.0076</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Usucapião Extraordinária</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>27/08/2026 20:23</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>27/08/2026 20:23</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>21/09/2026 14:35</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>0037878-35.2023.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Comodato</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>11/12/2024</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>02/09/2026 14:53</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>02/09/2026 14:53</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>10/09/2026 20:57</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>0031845-47.2009.8.16.0185</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Dívida Ativa (Execução Fiscal)</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>26/08/2026 14:13</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>26/08/2026 14:13</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>10/09/2026 20:59</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>0010345-55.2021.8.16.0038</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>27/08/2026 20:13</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>27/08/2026 20:13</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>10/09/2026 20:59</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/resultados.xlsx
+++ b/docs/resultados.xlsx
@@ -425,12 +425,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
@@ -486,6 +486,3155 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>0000063-25.2024.8.16.0014</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Transporte de Coisas</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>25/02/2026</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>25/09/2026 18:23</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>25/09/2026 18:23</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>26/09/2026 03:30</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>0000223-64.2021.8.16.0108</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Dever de Informação</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>25/09/2026 13:43</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>25/09/2026 13:43</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>26/09/2026 05:50</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>0000486-51.2023.8.16.0165</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Revisão de Juros Remuneratórios, Capitalização/Anatocismo</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>16/09/2026 14:13</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>16/09/2026 14:13</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>26/09/2026 05:20</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>0000536-79.2024.8.16.0056</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Calúnia</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>13/02/2026</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>31/08/2026 08:55</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>31/08/2026 08:56</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>26/09/2026 05:20</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>0000558-26.2006.8.16.0103</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Sistema Financeiro da Habitação | Seguro</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>18/09/2026 13:13</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>18/09/2026 13:13</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>26/09/2026 05:40</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>0000823-87.2016.8.16.0164</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Inventário e Partilha</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>25/09/2026 16:03</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>25/09/2026 16:03</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>26/09/2026 05:20</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>0000963-09.2022.8.16.0004</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ato Normativo | Defeito, nulidade ou anulação</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>10/06/2025</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>17/09/2026 14:33</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>17/09/2026 14:33</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>26/09/2026 05:00</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>0001678-72.2023.8.16.0115</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Suspensão | Efeito Suspensivo / Impugnação / Embargos à Execução</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>25/09/2026 18:33</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>25/09/2026 18:33</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>26/09/2026 04:00</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>0002284-74.2025.8.16.0004</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Defeito, nulidade ou anulação | Indenização por Dano Moral | Indenização por Dano Material | Abuso de Poder</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>24/09/2026 13:03</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>24/09/2026 13:03</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>25/09/2026 05:28</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>0002802-91.2022.8.16.0126</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Títulos de Crédito | Embargos de Terceiro</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>16/09/2026 16:03</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>16/09/2026 16:03</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>26/09/2026 05:30</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>0002809-68.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>16/09/2026 13:23</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>16/09/2026 13:23</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>25/09/2026 09:15</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>0003013-71.2020.8.16.0038</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Nota Promissória</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>30/01/2026</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>16/09/2026 13:53</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>16/09/2026 13:53</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>25/09/2026 05:34</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>0003076-48.2023.8.16.0117</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Franquia</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>25/09/2026 14:23</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>25/09/2026 14:23</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>26/09/2026 04:00</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>0003195-32.2018.8.16.0069</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Erro Médico | Erro Médico</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>24/09/2026 14:43</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>24/09/2026 14:43</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>25/09/2026 05:48</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>0003663-88.2023.8.16.0014</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Rescisão do contrato e devolução do dinheiro | Indenização por Dano Material</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>25/09/2026 15:23</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>25/09/2026 15:23</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>26/09/2026 04:10</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>0004171-98.2022.8.16.0004</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Irredutibilidade de Vencimentos</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>15/12/2025</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>25/09/2026 18:23</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>25/09/2026 18:23</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>26/09/2026 03:40</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>0004317-38.2018.8.16.0083</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Erro Médico</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>20/01/2026</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>16/09/2026 13:53</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>16/09/2026 13:53</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>25/09/2026 09:15</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>0004944-02.2015.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Alienação Fiduciária</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>25/09/2026 13:23</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>25/09/2026 13:23</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>26/09/2026 05:40</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>0005298-13.2024.8.16.0033</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Superendividamento</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>16/09/2026 13:43</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>16/09/2026 13:43</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>25/09/2026 09:15</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>0005623-66.2016.8.16.0130</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Inventário e Partilha</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>24/09/2026 16:33</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>24/09/2026 16:33</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>25/09/2026 05:43</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>0005630-14.2023.8.16.0130</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Confissão/Composição de Dívida | Efeito Suspensivo / Impugnação / Embargos à Execução</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>28/01/2026</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>25/09/2026 17:13</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>25/09/2026 17:13</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>26/09/2026 04:00</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>0005784-65.2017.8.16.0090</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Erro Médico | Erro Médico</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>16/09/2026 14:33</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>16/09/2026 14:33</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>26/09/2026 05:40</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>0005801-34.2004.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Fiança</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>06/03/2026</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>25/09/2026 15:53</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>25/09/2026 15:53</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>26/09/2026 05:50</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>0008391-41.2022.8.16.0069</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Embargos de Divergência em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Alienação Fiduciária</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>18/07/2024</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>24/09/2026 13:33</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>24/09/2026 13:33</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>25/09/2026 05:28</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>0009896-40.2025.8.16.0044</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Associação para a Produção e Tráfico e Condutas Afins</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>15/09/2026 15:03</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>15/09/2026 15:03</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>25/09/2026 05:19</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>0009971-90.2012.8.16.0026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Rescisão / Resolução</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>25/08/2025</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>25/09/2026 18:33</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>25/09/2026 18:33</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>26/09/2026 03:30</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>0010154-54.2021.8.16.0185</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Dívida Ativa (Execução Fiscal)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>16/09/2026 14:03</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>16/09/2026 14:03</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>25/09/2026 05:20</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>0011222-02.2024.8.16.0131</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>23/09/2026 13:23</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>23/09/2026 13:23</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>26/09/2026 05:30</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>0011262-51.2024.8.16.0044</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Associação para a Produção e Tráfico e Condutas Afins | Promoção, constituição, financiamento ou integração de Organização Criminosa | Crimes de &amp;quot;Lavagem&amp;quot; ou Ocultação de Bens, Direitos ou Valores</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>15/09/2026 16:53</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>15/09/2026 16:53</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>25/09/2026 09:15</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>0011764-08.2023.8.16.0017</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>27/11/2025</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>16/09/2026 15:43</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>16/09/2026 15:43</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>26/09/2026 05:40</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>0012821-80.2021.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Locação de Imóvel | Obrigação de Fazer / Não Fazer | Indenização por Dano Material | Cobrança de Aluguéis - Sem despejo</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>25/09/2026 17:43</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>25/09/2026 17:43</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>26/09/2026 03:50</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>0013992-22.2014.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Compromisso</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>24/04/2025</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>15/09/2026 17:43</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>15/09/2026 17:43</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>25/09/2026 09:15</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>0014455-75.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Material</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>15/09/2026 17:53</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>15/09/2026 17:53</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>25/09/2026 09:15</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>0015214-66.2025.8.16.0185</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Dívida Ativa (Execução Fiscal)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>17/09/2026 13:33</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>17/09/2026 13:33</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>26/09/2026 04:10</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>0015829-97.2023.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Embargos de Divergência em Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>09/10/2024</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>25/09/2026 16:33</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>25/09/2026 16:33</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>26/09/2026 04:00</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>0016200-33.2025.8.16.0019</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Homicídio Qualificado</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>16/09/2026 15:23</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>16/09/2026 15:23</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>26/09/2026 04:10</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>0017165-68.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Cédula de Crédito Bancário</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>15/09/2026 17:24</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>15/09/2026 17:24</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>25/09/2026 09:15</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>0017322-41.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Alienação Fiduciária</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>15/09/2026 13:33</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>15/09/2026 13:33</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>25/09/2026 05:01</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>0018063-74.2008.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Erro Médico</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>15/09/2026 14:03</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>15/09/2026 14:03</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>25/09/2026 09:15</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>0019158-59.2015.8.16.0013</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Corrupção passiva | Crimes contra a Ordem Tributária</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>31/03/2024</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>24/09/2026 18:41</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:29</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>26/09/2026 04:10</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>0020261-66.2023.8.16.0031</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Compromisso</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>14/09/2026 13:09</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>14/09/2026 13:09</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>25/09/2026 09:15</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>0020605-84.2022.8.16.0030</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Receptação Qualificada</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>22/09/2026 16:35</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>22/09/2026 16:35</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>26/09/2026 03:40</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>0024526-39.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Aquisição | Indenização por Dano Moral | Indenização por Dano Material</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>17/09/2026 14:03</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>17/09/2026 14:03</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>26/09/2026 05:40</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>0024742-68.2019.8.16.0013</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Peculato | Aplicação da Pena | Nulidade | Prevaricação | Concussão</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>22/09/2026 14:33</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>22/09/2026 14:33</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>25/09/2026 09:15</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>0025922-28.2024.8.16.0019</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Adulteração de Sinal Identificador de Veículo Automotor</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>25/09/2026 17:34</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>25/09/2026 17:34</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>26/09/2026 05:50</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>0027742-42.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Práticas Abusivas | Limitação de Juros</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>24/09/2026 15:53</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>24/09/2026 15:53</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>25/09/2026 09:15</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>0032740-19.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Espécies de Títulos de Crédito | Sucumbenciais</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>06/03/2026</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>17/09/2026 14:23</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>17/09/2026 14:23</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>26/09/2026 03:40</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>0033262-14.2023.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Moral</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>24/09/2026 17:43</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>24/09/2026 17:43</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>25/09/2026 09:15</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>0033528-79.2015.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Direitos / Deveres do Condômino</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>15/09/2026 16:13</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>15/09/2026 16:13</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>25/09/2026 09:15</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>0041089-11.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Desconsideração da Personalidade Jurídica</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>24/09/2026 14:53</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>24/09/2026 14:53</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>25/09/2026 05:19</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>0047645-92.2026.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Recurso Ordinário em Habeas Corpus</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Associação para a Produção e Tráfico e Condutas Afins | Prisão Preventiva | Promoção, constituição, financiamento ou integração de Organização Criminosa</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>22/09/2026 15:53</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>22/09/2026 15:53</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>26/09/2026 03:30</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>0052267-88.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Processo Administrativo Disciplinar ou Sindicância</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>25/09/2026 16:23</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>25/09/2026 16:23</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>26/09/2026 04:00</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>0053642-61.2023.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Improbidade Administrativa | Multas e demais Sanções | Dano ao Erário | Violação dos Princípios Administrativos | Cumprimento Provisório de Sentença | Penhora / Depósito/ Avaliação | Ônus da Prova</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>27/01/2026</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>18/09/2026 13:33</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>18/09/2026 13:33</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>26/09/2026 05:50</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>0055070-44.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Dívida Ativa (Execução Fiscal) | ICMS/ Imposto sobre Circulação de Mercadorias</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>16/09/2026 15:43</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>16/09/2026 15:43</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>26/09/2026 05:30</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>0059515-08.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Direitos e Títulos de Crédito</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>10/12/2025</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>18/09/2026 14:23</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>18/09/2026 14:23</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>26/09/2026 05:40</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>0060675-26.2024.8.16.0014</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Moral</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>16/09/2026 14:23</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>16/09/2026 14:23</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>26/09/2026 03:40</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>0072672-48.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Dano ao Erário</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>16/12/2025</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>25/09/2026 15:53</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>25/09/2026 15:53</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>26/09/2026 05:30</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>0075197-66.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Direito de Vizinhança</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>24/09/2026 16:53</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>24/09/2026 16:53</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>25/09/2026 09:15</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>0078935-20.2025.8.16.0014</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>22/09/2026 14:03</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>22/09/2026 14:03</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>26/09/2026 05:40</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>0089720-83.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Recurso Ordinário em Habeas Corpus</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Crimes do Sistema Nacional de Armas</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>09/12/2025</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>25/09/2026 17:13</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>25/09/2026 17:13</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>26/09/2026 05:40</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>0091703-20.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Promessa de Compra e Venda</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>24/09/2026 15:13</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>24/09/2026 15:13</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>25/09/2026 04:59</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>0105473-51.2023.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Esbulho / Turbação / Ameaça | Perdas e Danos</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>09/05/2025</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>24/09/2026 14:43</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>24/09/2026 14:43</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>25/09/2026 09:15</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>0119994-64.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>IPTU/ Imposto Predial e Territorial Urbano</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>16/09/2026 14:23</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>16/09/2026 14:23</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>26/09/2026 04:10</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>0121180-25.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Dívida Ativa (Execução Fiscal)</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>24/09/2026 14:23</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>24/09/2026 14:23</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>25/09/2026 05:20</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>0122256-84.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Enriquecimento ilícito | Dano ao Erário | Violação dos Princípios Administrativos</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>16/09/2026 14:43</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>16/09/2026 14:43</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>26/09/2026 05:00</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>0127161-35.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>PASEP</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>24/09/2026 16:43</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>24/09/2026 16:43</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>25/09/2026 09:15</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>0129144-69.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Despesas Condominiais | Penhora / Depósito/ Avaliação | Prestação de Serviços</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>25/09/2026 18:03</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>25/09/2026 18:03</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>26/09/2026 05:10</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/resultados.xlsx
+++ b/docs/resultados.xlsx
@@ -425,12 +425,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
@@ -486,6 +486,4518 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>0000430-35.2006.8.16.0158</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Seguro | Vícios de Construção | Multa de 10% | Perito</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>09/10/2024</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>28/09/2026 20:03</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>28/09/2026 20:03</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>29/09/2026 07:01</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>0000502-33.1987.8.16.0014</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Nota Promissória</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>16/07/2024</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>28/09/2026 15:23</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>28/09/2026 15:23</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>29/09/2026 07:20</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>0000506-43.2019.8.16.0113</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ICMS/Importação</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>30/12/1899</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>21/09/2026 14:43</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>21/09/2026 14:43</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>29/09/2026 08:40</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>0000507-35.2021.8.16.0185</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Concurso de Credores</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>27/05/2025</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>28/09/2026 16:53</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>28/09/2026 16:53</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>29/09/2026 05:30</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>0000733-34.2024.8.16.0056</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Contratos Bancários</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>28/09/2026 19:33</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>28/09/2026 19:33</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:30</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>0001054-57.2022.8.16.0115</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Promessa de Compra e Venda | Obrigação de Fazer / Não Fazer</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>28/09/2026 14:53</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>28/09/2026 14:53</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:30</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>0001127-42.2008.8.16.0043</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Moral</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>16/12/2025</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>28/09/2026 16:23</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>28/09/2026 16:23</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>29/09/2026 05:40</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>0001238-65.2016.8.16.0004</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços | Rescisão / Resolução | Perdas e Danos</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>26/10/2021</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>28/09/2026 15:43</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>28/09/2026 15:43</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>29/09/2026 07:10</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>0001665-20.2022.8.16.0047</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>23/07/2025</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>28/09/2026 14:03</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>28/09/2026 14:03</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:40</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>0001837-98.2025.8.16.0097</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>22/09/2026 14:53</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>22/09/2026 14:53</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>29/09/2026 05:50</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>0002148-65.2020.8.16.0194</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Produto Impróprio</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>01/10/2025</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>21/09/2026 17:23</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>21/09/2026 17:23</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>29/09/2026 07:01</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>0002202-63.2019.8.16.0130</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Bem de Família (Voluntário)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>28/09/2026 14:53</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>28/09/2026 14:53</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:50</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>0002235-20.2023.8.16.0128</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Bancários</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>03/12/2025</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>21/09/2026 14:03</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>21/09/2026 14:03</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>29/09/2026 07:20</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>0002351-37.2009.8.16.0089</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Seguro</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>28/09/2026 19:23</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>28/09/2026 19:23</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>29/09/2026 05:50</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>0002488-84.2023.8.16.0038</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Alienação Fiduciária</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>21/09/2026 13:33</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>21/09/2026 13:33</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:20</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>0003162-36.2023.8.16.0079</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Práticas Abusivas</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>30/01/2026</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>28/09/2026 19:53</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>28/09/2026 19:53</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>29/09/2026 07:40</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>0003205-60.2025.8.16.0189</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Lesão Cometida em Razão da Condição de Mulher</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>21/09/2026 17:53</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>21/09/2026 17:53</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:00</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>0003306-75.2016.8.16.0072</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Saneamento</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>02/09/2025</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>21/09/2026 13:53</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>21/09/2026 13:53</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:40</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>0003766-51.2023.8.16.0158</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Revisão de Juros Remuneratórios, Capitalização/Anatocismo</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>28/09/2026 19:53</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>28/09/2026 19:53</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:40</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>0003984-61.2020.8.16.0004</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Moral | Indenização por Dano Material</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>21/09/2026 14:53</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>21/09/2026 14:53</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>29/09/2026 07:40</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>0004576-62.2021.8.16.0104</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Parceria Agrícola e/ou pecuária</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>28/09/2026 18:23</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>28/09/2026 18:23</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>29/09/2026 08:00</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>0004635-66.2024.8.16.0194</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Desenho Industrial | Perdas e Danos</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>25/03/2025</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>21/09/2026 15:43</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>21/09/2026 15:43</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>29/09/2026 07:50</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>0004667-84.2009.8.16.0004</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Contratos Bancários | Pagamento em Consignação</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>09/11/2019</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>21/09/2026 17:53</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>21/09/2026 17:53</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:30</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>0004949-76.2025.8.16.0129</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Dívida Ativa (Execução Fiscal)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>21/09/2026 16:23</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>21/09/2026 16:23</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:40</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>0004994-55.2020.8.16.0194</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Material | Prestação de Serviços | Obrigação de Fazer / Não Fazer | Indenização por Dano Moral | Ônus da Prova | Inadimplemento</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>04/02/2026</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>28/09/2026 14:53</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>28/09/2026 14:53</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>29/09/2026 07:00</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>0005035-85.2024.8.16.0160</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Fonte de Custeio</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>23/09/2026 13:23</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>23/09/2026 13:23</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>29/09/2026 07:00</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>0005096-84.2024.8.16.0017</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>23/09/2026 05:23</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>23/09/2026 05:23</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>24/09/2026 16:51</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>0005644-69.2025.8.16.0116</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Recurso Ordinário em Mandado de Segurança</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Moral</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>28/09/2026 18:43</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>28/09/2026 18:43</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>29/09/2026 07:30</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>0005863-05.2022.8.16.0014</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Compra e Venda | Indenização por Dano Moral | Indenização por Dano Material | Defeito, nulidade ou anulação</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>21/09/2026 18:03</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>21/09/2026 18:03</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>29/09/2026 07:10</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>0006563-78.2022.8.16.0014</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Compra e Venda</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>28/01/2026</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>28/09/2026 20:23</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>28/09/2026 20:23</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:50</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>0006648-82.2017.8.16.0194</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Material</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>10/10/2024</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>28/09/2026 13:43</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>28/09/2026 13:43</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>29/09/2026 08:00</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>0008208-80.2021.8.16.0174</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Material</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>21/09/2026 17:33</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>21/09/2026 17:33</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>29/09/2026 07:00</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>0009159-43.2020.8.16.0131</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Adimplemento e Extinção | Bem de Família (Voluntário)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>18/06/2025</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>28/09/2026 18:13</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>28/09/2026 18:13</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:00</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>0009195-17.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Cédula de Crédito Bancário</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>28/09/2026 19:53</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>28/09/2026 19:53</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>29/09/2026 08:20</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>0009337-85.2022.8.16.0045</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Desconsideração da Personalidade Jurídica | Defeito, nulidade ou anulação | Embargos de Terceiro | Penhora / Depósito/ Avaliação</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>05/05/2025</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>28/09/2026 16:33</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>28/09/2026 16:33</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>29/09/2026 07:10</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>0010353-10.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>28/09/2026 17:33</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>28/09/2026 17:33</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:20</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>0011222-02.2024.8.16.0131</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>23/09/2026 13:23</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>23/09/2026 13:23</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:50</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>0011426-17.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Moral | Indenização por Dano Material</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>06/02/2026</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>28/09/2026 20:23</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>28/09/2026 20:23</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>29/09/2026 05:50</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>0011485-52.2015.8.16.0033</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Sustação de Protesto</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>05/09/2025</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>28/09/2026 13:33</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>28/09/2026 13:33</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>29/09/2026 08:20</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>0012346-88.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Despesas Condominiais</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>25/03/2026</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>28/09/2026 20:53</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>28/09/2026 20:53</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:30</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>0012385-53.2017.8.16.0069</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Rescisão / Resolução</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>26/11/2025</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>28/09/2026 16:43</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>28/09/2026 16:43</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>29/09/2026 05:07</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>0012627-78.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Despesas Condominiais | Condomínio em Edifício</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>18/11/2024</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>28/09/2026 21:33</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>28/09/2026 21:33</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:40</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>0014041-70.2018.8.16.0017</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Cobrança de Aluguéis - Sem despejo</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>09/02/2022</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>21/09/2026 17:53</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>21/09/2026 17:53</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>29/09/2026 08:40</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>0014138-79.2022.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Alienação Fiduciária</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>28/09/2026 17:33</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>28/09/2026 17:33</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:00</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>0014457-45.2025.8.16.0194</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Moral | Tutela de Urgência</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>28/09/2026 21:43</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>28/09/2026 21:43</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:50</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>0017353-44.2024.8.16.0017</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Despejo por Inadimplemento | Habitação | Oposição | Penhora / Depósito/ Avaliação</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>28/09/2026 19:53</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>28/09/2026 19:53</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:30</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>0018989-25.2022.8.16.0014</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>25/08/2025</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>21/09/2026 18:13</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>21/09/2026 18:13</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:20</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>0019158-59.2015.8.16.0013</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Corrupção passiva | Crimes contra a Ordem Tributária</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>31/03/2024</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>24/09/2026 18:41</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>09/03/2026 09:29</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>29/09/2026 08:20</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>0019842-08.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Cédula de Crédito Bancário</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>28/09/2026 14:33</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>28/09/2026 14:33</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>29/09/2026 07:40</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>0019843-53.2022.8.16.0035</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Pagamento</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>11/12/2025</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>21/09/2026 17:53</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>21/09/2026 17:53</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>29/09/2026 05:40</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>0019858-22.2022.8.16.0035</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Pagamento</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>23/09/2025</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>28/09/2026 18:03</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>28/09/2026 18:03</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:40</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>0019932-08.2023.8.16.0014</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>11/09/2026 15:33</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>11/09/2026 15:33</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>24/09/2026 16:57</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>0021175-92.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Recuperação judicial e Falência | Concurso de Credores</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>08/12/2025</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>28/09/2026 18:23</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>28/09/2026 18:23</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:40</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>0021838-87.2014.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Moral | Obrigação de Fazer / Não Fazer</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>03/02/2026</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>21/09/2026 13:23</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>21/09/2026 13:23</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:20</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>0023032-64.2020.8.16.0017</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Direitos e Títulos de Crédito</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>04/06/2024</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>21/09/2026 18:33</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>21/09/2026 18:33</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:00</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>0024007-62.2023.8.16.0185</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Dívida Ativa (Execução Fiscal)</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>21/09/2026 17:33</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>21/09/2026 17:33</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>29/09/2026 05:30</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>0025353-57.2025.8.16.0030</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Receptação Qualificada</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>28/09/2026 17:23</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>28/09/2026 17:23</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>29/09/2026 07:40</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>0026626-90.2023.8.16.0014</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Tratamento médico-hospitalar</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>03/12/2025</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>21/09/2026 17:43</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>21/09/2026 17:43</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:40</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>0027654-38.2023.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Restituição ao Erário | Dano ao Erário | Obrigação de Fazer / Não Fazer | Ônus da Prova | Violação dos Princípios Administrativos</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>19/05/2025</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>28/09/2026 16:03</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>28/09/2026 16:03</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>29/09/2026 08:20</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>0028703-46.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Espécies de Títulos de Crédito</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>28/09/2026 17:14</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>28/09/2026 17:14</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>29/09/2026 07:10</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>0028898-92.2016.8.16.0017</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Rescisão / Resolução | Efeito Suspensivo / Impugnação / Embargos à Execução</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>02/06/2025</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>28/09/2026 10:44</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>28/09/2026 10:44</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>29/09/2026 07:00</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>0033203-58.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>PIS/PASEP | Indenização por Dano Material | Práticas Abusivas</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>28/09/2026 17:53</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>28/09/2026 17:53</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>29/09/2026 07:10</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>0033286-91.2013.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Reivindicação | Pagamento</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>09/02/2022</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>28/09/2026 14:33</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>28/09/2026 14:33</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>29/09/2026 07:10</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>0033792-21.2023.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Tratamento médico-hospitalar | Obrigação de Fazer / Não Fazer</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>21/09/2026 17:23</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>21/09/2026 17:23</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:20</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>0034555-58.2019.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Seguro</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>11/03/2025</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>28/09/2026 17:03</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>28/09/2026 17:03</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>29/09/2026 08:20</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>0034821-55.2013.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Cédula de Crédito Bancário</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>10/12/2025</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>21/09/2026 18:13</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>21/09/2026 18:13</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>29/09/2026 05:07</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>0035579-85.2023.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Material</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>11/12/2024</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>28/09/2026 14:33</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>28/09/2026 14:33</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:00</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>0037028-51.2024.8.16.0030</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Crimes do Sistema Nacional de Armas</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>21/09/2026 14:03</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>21/09/2026 14:03</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>29/09/2026 07:10</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>0037065-88.2012.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Compra e Venda | Interpretação / Revisão de Contrato | Abatimento proporcional do preço | Indenização por Dano Material | Indenização por Dano Moral | Espécies de Contratos</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>14/12/2020</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>21/09/2026 13:43</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>21/09/2026 13:43</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:40</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>0039377-54.2024.8.16.0021</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Rescisão / Resolução</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>29/01/2026</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>28/09/2026 21:33</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>28/09/2026 21:33</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:40</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>0041536-33.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Promessa de Compra e Venda</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>17/07/2025</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>21/09/2026 14:23</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>21/09/2026 14:23</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:00</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>0041752-57.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Dívida Ativa (Execução Fiscal)</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>21/09/2026 18:23</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>21/09/2026 18:23</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>29/09/2026 08:30</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>0044419-16.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ingresso e Exclusão dos Sócios na Sociedade</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>21/09/2026 13:33</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>21/09/2026 13:33</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>29/09/2026 08:00</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>0049066-40.2014.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Seguro</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>22/10/2025</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>11/09/2026 13:23</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>11/09/2026 13:23</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>24/09/2026 17:01</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>0058493-75.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Defeito, nulidade ou anulação</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>06/02/2026</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>28/09/2026 16:53</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>28/09/2026 16:53</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>29/09/2026 07:00</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>0064910-44.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Práticas Abusivas</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>28/09/2026 21:23</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>28/09/2026 21:23</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>29/09/2026 04:21</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>0071691-82.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>PIS/PASEP | Indenização por Dano Material</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>23/07/2026</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>28/09/2026 16:03</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>28/09/2026 16:03</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>29/09/2026 07:40</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>0071839-30.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Contratos Bancários | Causas Supervenientes à Sentença</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>07/10/2025</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>28/09/2026 20:23</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>28/09/2026 20:23</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:50</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>0072736-29.2022.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Dano ao Erário | Violação dos Princípios Administrativos | Sobrestamento</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>13/03/2025</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>21/09/2026 19:03</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>21/09/2026 19:03</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>29/09/2026 07:50</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>0074926-28.2023.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Duplicata</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>05/09/2024</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>28/09/2026 18:53</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>28/09/2026 18:53</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:30</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>0075408-05.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços | Efeito Suspensivo / Impugnação / Embargos à Execução | Prescrição e Decadência</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>28/09/2026 16:23</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>28/09/2026 16:23</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>29/09/2026 07:00</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>0077227-74.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Seguro</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>28/09/2026 19:33</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>28/09/2026 19:33</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>29/09/2026 08:20</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>0080070-80.2023.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Cédula de Crédito Bancário | Penhora / Depósito/ Avaliação</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>13/02/2025</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>28/09/2026 17:33</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>28/09/2026 17:33</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:10</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>0080573-04.2023.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Inventário e Partilha</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>13/11/2024</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>28/09/2026 14:13</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>28/09/2026 14:13</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:20</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>0082380-54.2026.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Recurso Ordinário em Habeas Corpus</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins | Prisão Preventiva | Cerceamento de Defesa | Promoção, constituição, financiamento ou integração de Organização Criminosa</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>23/09/2026 13:43</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>23/09/2026 13:43</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>29/09/2026 05:07</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>0089720-83.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Recurso Ordinário em Habeas Corpus</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Crimes do Sistema Nacional de Armas</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>09/12/2025</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>25/09/2026 17:13</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>25/09/2026 17:13</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:40</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>0092890-34.2023.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>24/01/2025</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>28/09/2026 13:33</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>28/09/2026 13:33</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:50</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>0097644-82.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Práticas Abusivas</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>16/12/2025</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>28/09/2026 19:53</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>28/09/2026 19:53</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:40</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>0097671-65.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Espécies de Contratos</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>15/12/2025</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>28/09/2026 16:53</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>28/09/2026 16:53</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>29/09/2026 07:20</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>0099078-09.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Confissão/Composição de Dívida</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>12/11/2025</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>21/09/2026 13:33</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>21/09/2026 13:33</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>29/09/2026 05:07</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>0101751-72.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Concessão</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>30/01/2026</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>28/09/2026 21:23</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>28/09/2026 21:23</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:40</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>0104756-39.2023.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Espécies de Títulos de Crédito</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>28/09/2026 14:33</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>28/09/2026 14:33</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>29/09/2026 07:20</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>0105320-13.2026.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Recurso Ordinário em Habeas Corpus</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>22/09/2026 17:13</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>22/09/2026 17:13</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:30</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>0116528-28.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>21/09/2026 16:55</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>21/09/2026 16:55</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>29/09/2026 08:00</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>0118791-67.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Cobrança | Obrigação de Fazer / Não Fazer</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>21/09/2026 19:03</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>21/09/2026 19:03</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>29/09/2026 08:20</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>0123956-95.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Compromisso</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>28/09/2026 16:53</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>28/09/2026 16:53</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:20</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/resultados.xlsx
+++ b/docs/resultados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I97"/>
+  <dimension ref="A1:I89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -677,7 +677,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0000733-34.2024.8.16.0056</t>
+          <t>0001127-42.2008.8.16.0043</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -687,27 +687,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>28/09/2026 19:33</t>
+          <t>28/09/2026 16:23</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>28/09/2026 19:33</t>
+          <t>28/09/2026 16:23</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>29/09/2026 06:30</t>
+          <t>29/09/2026 05:40</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -724,37 +724,37 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0001054-57.2022.8.16.0115</t>
+          <t>0001238-65.2016.8.16.0004</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Promessa de Compra e Venda | Obrigação de Fazer / Não Fazer</t>
+          <t>Prestação de Serviços | Rescisão / Resolução | Perdas e Danos</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>26/10/2021</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>28/09/2026 14:53</t>
+          <t>28/09/2026 15:43</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>28/09/2026 14:53</t>
+          <t>28/09/2026 15:43</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>29/09/2026 06:30</t>
+          <t>29/09/2026 07:10</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -771,7 +771,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0001127-42.2008.8.16.0043</t>
+          <t>0001665-20.2022.8.16.0047</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -781,27 +781,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>23/07/2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>28/09/2026 16:23</t>
+          <t>28/09/2026 14:03</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>28/09/2026 16:23</t>
+          <t>28/09/2026 14:03</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>29/09/2026 05:40</t>
+          <t>29/09/2026 06:40</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -818,37 +818,37 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0001238-65.2016.8.16.0004</t>
+          <t>0001837-98.2025.8.16.0097</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Prestação de Serviços | Rescisão / Resolução | Perdas e Danos</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>26/10/2021</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>28/09/2026 15:43</t>
+          <t>22/09/2026 14:53</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>28/09/2026 15:43</t>
+          <t>22/09/2026 14:53</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>29/09/2026 07:10</t>
+          <t>29/09/2026 05:50</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -865,7 +865,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0001665-20.2022.8.16.0047</t>
+          <t>0002148-65.2020.8.16.0194</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -875,27 +875,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Produto Impróprio</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>23/07/2025</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>28/09/2026 14:03</t>
+          <t>21/09/2026 17:23</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>28/09/2026 14:03</t>
+          <t>21/09/2026 17:23</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>29/09/2026 06:40</t>
+          <t>29/09/2026 07:01</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -912,7 +912,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0001837-98.2025.8.16.0097</t>
+          <t>0002202-63.2019.8.16.0130</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -922,27 +922,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Bem de Família (Voluntário)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>22/09/2026 14:53</t>
+          <t>28/09/2026 14:53</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>22/09/2026 14:53</t>
+          <t>28/09/2026 14:53</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>29/09/2026 05:50</t>
+          <t>29/09/2026 06:50</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0002148-65.2020.8.16.0194</t>
+          <t>0002235-20.2023.8.16.0128</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -969,27 +969,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Produto Impróprio</t>
+          <t>Bancários</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>01/10/2025</t>
+          <t>03/12/2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>21/09/2026 17:23</t>
+          <t>21/09/2026 14:03</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>21/09/2026 17:23</t>
+          <t>21/09/2026 14:03</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>29/09/2026 07:01</t>
+          <t>29/09/2026 07:20</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1006,7 +1006,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0002202-63.2019.8.16.0130</t>
+          <t>0002351-37.2009.8.16.0089</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1016,27 +1016,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bem de Família (Voluntário)</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>28/09/2026 14:53</t>
+          <t>28/09/2026 19:23</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>28/09/2026 14:53</t>
+          <t>28/09/2026 19:23</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>29/09/2026 06:50</t>
+          <t>29/09/2026 05:50</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1053,7 +1053,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0002235-20.2023.8.16.0128</t>
+          <t>0003162-36.2023.8.16.0079</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1063,27 +1063,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bancários</t>
+          <t>Práticas Abusivas</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>03/12/2025</t>
+          <t>30/01/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>21/09/2026 14:03</t>
+          <t>28/09/2026 19:53</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>21/09/2026 14:03</t>
+          <t>28/09/2026 19:53</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>29/09/2026 07:20</t>
+          <t>29/09/2026 07:40</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0002351-37.2009.8.16.0089</t>
+          <t>0003205-60.2025.8.16.0189</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1110,27 +1110,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Lesão Cometida em Razão da Condição de Mulher</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>28/09/2026 19:23</t>
+          <t>21/09/2026 17:53</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>28/09/2026 19:23</t>
+          <t>21/09/2026 17:53</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>29/09/2026 05:50</t>
+          <t>29/09/2026 06:00</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1147,37 +1147,37 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0002488-84.2023.8.16.0038</t>
+          <t>0003306-75.2016.8.16.0072</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Alienação Fiduciária</t>
+          <t>Saneamento</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>02/09/2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>21/09/2026 13:33</t>
+          <t>21/09/2026 13:53</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>21/09/2026 13:33</t>
+          <t>21/09/2026 13:53</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>29/09/2026 06:20</t>
+          <t>29/09/2026 06:40</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1194,7 +1194,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0003162-36.2023.8.16.0079</t>
+          <t>0003766-51.2023.8.16.0158</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Práticas Abusivas</t>
+          <t>Revisão de Juros Remuneratórios, Capitalização/Anatocismo</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>30/01/2026</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>29/09/2026 07:40</t>
+          <t>29/09/2026 06:40</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1241,7 +1241,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0003205-60.2025.8.16.0189</t>
+          <t>0003812-81.2020.8.16.0146</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1251,27 +1251,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lesão Cometida em Razão da Condição de Mulher</t>
+          <t>Arrendamento Rural | Liminar</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>28/08/2024</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>21/09/2026 17:53</t>
+          <t>11/09/2026 15:13</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>21/09/2026 17:53</t>
+          <t>11/09/2026 15:13</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>29/09/2026 06:00</t>
+          <t>24/09/2026 17:37</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1288,7 +1288,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0003306-75.2016.8.16.0072</t>
+          <t>0003984-61.2020.8.16.0004</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1298,27 +1298,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Saneamento</t>
+          <t>Indenização por Dano Moral | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>02/09/2025</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>21/09/2026 13:53</t>
+          <t>21/09/2026 14:53</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>21/09/2026 13:53</t>
+          <t>21/09/2026 14:53</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>29/09/2026 06:40</t>
+          <t>29/09/2026 07:40</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1335,37 +1335,37 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0003766-51.2023.8.16.0158</t>
+          <t>0004330-27.2024.8.16.0083</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Revisão de Juros Remuneratórios, Capitalização/Anatocismo</t>
+          <t>Furto Qualificado</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>28/09/2026 19:53</t>
+          <t>11/09/2026 14:13</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>28/09/2026 19:53</t>
+          <t>11/09/2026 14:13</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>29/09/2026 06:40</t>
+          <t>24/09/2026 17:10</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1382,7 +1382,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0003984-61.2020.8.16.0004</t>
+          <t>0004576-62.2021.8.16.0104</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1392,27 +1392,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Indenização por Dano Material</t>
+          <t>Parceria Agrícola e/ou pecuária</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>26/01/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>21/09/2026 14:53</t>
+          <t>28/09/2026 18:23</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>21/09/2026 14:53</t>
+          <t>28/09/2026 18:23</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>29/09/2026 07:40</t>
+          <t>29/09/2026 08:00</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1429,7 +1429,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0004576-62.2021.8.16.0104</t>
+          <t>0004635-66.2024.8.16.0194</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1439,27 +1439,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Parceria Agrícola e/ou pecuária</t>
+          <t>Desenho Industrial | Perdas e Danos</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>26/01/2026</t>
+          <t>25/03/2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>28/09/2026 18:23</t>
+          <t>21/09/2026 15:43</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>28/09/2026 18:23</t>
+          <t>21/09/2026 15:43</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>29/09/2026 08:00</t>
+          <t>29/09/2026 07:50</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1476,7 +1476,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0004635-66.2024.8.16.0194</t>
+          <t>0004949-76.2025.8.16.0129</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1486,27 +1486,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Desenho Industrial | Perdas e Danos</t>
+          <t>Dívida Ativa (Execução Fiscal)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>25/03/2025</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>21/09/2026 15:43</t>
+          <t>21/09/2026 16:23</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>21/09/2026 15:43</t>
+          <t>21/09/2026 16:23</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>29/09/2026 07:50</t>
+          <t>29/09/2026 06:40</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1523,7 +1523,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0004667-84.2009.8.16.0004</t>
+          <t>0004994-55.2020.8.16.0194</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1533,27 +1533,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Contratos Bancários | Pagamento em Consignação</t>
+          <t>Indenização por Dano Material | Prestação de Serviços | Obrigação de Fazer / Não Fazer | Indenização por Dano Moral | Ônus da Prova | Inadimplemento</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>09/11/2019</t>
+          <t>04/02/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>21/09/2026 17:53</t>
+          <t>28/09/2026 14:53</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>21/09/2026 17:53</t>
+          <t>28/09/2026 14:53</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>29/09/2026 06:30</t>
+          <t>29/09/2026 07:00</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1570,7 +1570,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0004949-76.2025.8.16.0129</t>
+          <t>0005035-85.2024.8.16.0160</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1580,27 +1580,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>Fonte de Custeio</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>21/09/2026 16:23</t>
+          <t>23/09/2026 13:23</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>21/09/2026 16:23</t>
+          <t>23/09/2026 13:23</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>29/09/2026 06:40</t>
+          <t>29/09/2026 07:00</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1617,7 +1617,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0004994-55.2020.8.16.0194</t>
+          <t>0005096-84.2024.8.16.0017</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1627,27 +1627,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Prestação de Serviços | Obrigação de Fazer / Não Fazer | Indenização por Dano Moral | Ônus da Prova | Inadimplemento</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>04/02/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>28/09/2026 14:53</t>
+          <t>23/09/2026 05:23</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>28/09/2026 14:53</t>
+          <t>23/09/2026 05:23</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>29/09/2026 07:00</t>
+          <t>24/09/2026 16:51</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1664,7 +1664,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0005035-85.2024.8.16.0160</t>
+          <t>0005532-90.2023.8.16.0045</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1674,27 +1674,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fonte de Custeio</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>25/02/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>23/09/2026 13:23</t>
+          <t>14/09/2026 13:23</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>23/09/2026 13:23</t>
+          <t>14/09/2026 13:23</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>29/09/2026 07:00</t>
+          <t>24/09/2026 17:21</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1711,37 +1711,37 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0005096-84.2024.8.16.0017</t>
+          <t>0005644-69.2025.8.16.0116</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Mandado de Segurança</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>23/09/2026 05:23</t>
+          <t>28/09/2026 18:43</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>23/09/2026 05:23</t>
+          <t>28/09/2026 18:43</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>24/09/2026 16:51</t>
+          <t>29/09/2026 07:30</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1758,37 +1758,37 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0005644-69.2025.8.16.0116</t>
+          <t>0005863-05.2022.8.16.0014</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Mandado de Segurança</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Compra e Venda | Indenização por Dano Moral | Indenização por Dano Material | Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>01/12/2025</t>
+          <t>26/01/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>28/09/2026 18:43</t>
+          <t>21/09/2026 18:03</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>28/09/2026 18:43</t>
+          <t>21/09/2026 18:03</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>29/09/2026 07:30</t>
+          <t>29/09/2026 07:10</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1805,7 +1805,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0005863-05.2022.8.16.0014</t>
+          <t>0006563-78.2022.8.16.0014</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1815,27 +1815,27 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Compra e Venda | Indenização por Dano Moral | Indenização por Dano Material | Defeito, nulidade ou anulação</t>
+          <t>Compra e Venda</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>26/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>21/09/2026 18:03</t>
+          <t>28/09/2026 20:23</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>21/09/2026 18:03</t>
+          <t>28/09/2026 20:23</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>29/09/2026 07:10</t>
+          <t>29/09/2026 06:50</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1852,37 +1852,37 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0006563-78.2022.8.16.0014</t>
+          <t>0006648-82.2017.8.16.0194</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Compra e Venda</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>10/10/2024</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>28/09/2026 20:23</t>
+          <t>28/09/2026 13:43</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>28/09/2026 20:23</t>
+          <t>28/09/2026 13:43</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>29/09/2026 06:50</t>
+          <t>29/09/2026 08:00</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1899,37 +1899,37 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0006648-82.2017.8.16.0194</t>
+          <t>0007836-93.2021.8.16.0025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Horas Extras</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>10/10/2024</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>28/09/2026 13:43</t>
+          <t>10/09/2026 17:23</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>28/09/2026 13:43</t>
+          <t>10/09/2026 17:23</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>29/09/2026 08:00</t>
+          <t>24/09/2026 17:21</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2134,37 +2134,37 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0010353-10.2025.8.16.0000</t>
+          <t>0011222-02.2024.8.16.0131</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>28/09/2026 17:33</t>
+          <t>23/09/2026 13:23</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>28/09/2026 17:33</t>
+          <t>23/09/2026 13:23</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>29/09/2026 06:20</t>
+          <t>29/09/2026 06:50</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2181,7 +2181,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0011222-02.2024.8.16.0131</t>
+          <t>0011426-17.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2191,27 +2191,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Indenização por Dano Moral | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>23/09/2026 13:23</t>
+          <t>28/09/2026 20:23</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>23/09/2026 13:23</t>
+          <t>28/09/2026 20:23</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>29/09/2026 06:50</t>
+          <t>29/09/2026 05:50</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2228,7 +2228,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0011426-17.2025.8.16.0000</t>
+          <t>0011485-52.2015.8.16.0033</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2238,27 +2238,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Indenização por Dano Material</t>
+          <t>Sustação de Protesto</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>05/09/2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>28/09/2026 20:23</t>
+          <t>28/09/2026 13:33</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>28/09/2026 20:23</t>
+          <t>28/09/2026 13:33</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>29/09/2026 05:50</t>
+          <t>29/09/2026 08:20</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2275,7 +2275,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0011485-52.2015.8.16.0033</t>
+          <t>0012385-53.2017.8.16.0069</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2285,27 +2285,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sustação de Protesto</t>
+          <t>Rescisão / Resolução</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>05/09/2025</t>
+          <t>26/11/2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>28/09/2026 13:33</t>
+          <t>28/09/2026 16:43</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>28/09/2026 13:33</t>
+          <t>28/09/2026 16:43</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>29/09/2026 08:20</t>
+          <t>29/09/2026 05:07</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2322,7 +2322,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0012346-88.2025.8.16.0000</t>
+          <t>0012511-74.2015.8.16.0069</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2332,27 +2332,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Despesas Condominiais</t>
+          <t>Aposentadoria Especial (Art. 57/8)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>28/09/2026 20:53</t>
+          <t>14/09/2026 13:53</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>28/09/2026 20:53</t>
+          <t>14/09/2026 13:53</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>29/09/2026 06:30</t>
+          <t>24/09/2026 17:10</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2369,37 +2369,37 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0012385-53.2017.8.16.0069</t>
+          <t>0012627-78.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Rescisão / Resolução</t>
+          <t>Despesas Condominiais | Condomínio em Edifício</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>26/11/2025</t>
+          <t>18/11/2024</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>28/09/2026 16:43</t>
+          <t>28/09/2026 21:33</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>28/09/2026 16:43</t>
+          <t>28/09/2026 21:33</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>29/09/2026 05:07</t>
+          <t>29/09/2026 06:40</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2416,7 +2416,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0012627-78.2024.8.16.0000</t>
+          <t>0014041-70.2018.8.16.0017</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2426,27 +2426,27 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Despesas Condominiais | Condomínio em Edifício</t>
+          <t>Cobrança de Aluguéis - Sem despejo</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>18/11/2024</t>
+          <t>09/02/2022</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>28/09/2026 21:33</t>
+          <t>21/09/2026 17:53</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>28/09/2026 21:33</t>
+          <t>21/09/2026 17:53</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>29/09/2026 06:40</t>
+          <t>29/09/2026 08:40</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2463,7 +2463,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0014041-70.2018.8.16.0017</t>
+          <t>0014138-79.2022.8.16.0001</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2473,27 +2473,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Cobrança de Aluguéis - Sem despejo</t>
+          <t>Alienação Fiduciária</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>09/02/2022</t>
+          <t>12/01/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>21/09/2026 17:53</t>
+          <t>28/09/2026 17:33</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>21/09/2026 17:53</t>
+          <t>28/09/2026 17:33</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>29/09/2026 08:40</t>
+          <t>29/09/2026 06:00</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2510,37 +2510,37 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0014138-79.2022.8.16.0001</t>
+          <t>0014457-45.2025.8.16.0194</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Alienação Fiduciária</t>
+          <t>Indenização por Dano Moral | Tutela de Urgência</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>12/01/2026</t>
+          <t>02/02/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>28/09/2026 17:33</t>
+          <t>28/09/2026 21:43</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>28/09/2026 17:33</t>
+          <t>28/09/2026 21:43</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>29/09/2026 06:00</t>
+          <t>29/09/2026 06:50</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2557,37 +2557,37 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0014457-45.2025.8.16.0194</t>
+          <t>0019158-59.2015.8.16.0013</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Tutela de Urgência</t>
+          <t>Corrupção passiva | Crimes contra a Ordem Tributária</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>02/02/2026</t>
+          <t>31/03/2024</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>28/09/2026 21:43</t>
+          <t>24/09/2026 18:41</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>28/09/2026 21:43</t>
+          <t>09/03/2026 09:29</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>29/09/2026 06:50</t>
+          <t>29/09/2026 08:20</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2604,7 +2604,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0017353-44.2024.8.16.0017</t>
+          <t>0019842-08.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2614,27 +2614,27 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Despejo por Inadimplemento | Habitação | Oposição | Penhora / Depósito/ Avaliação</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>28/09/2026 19:53</t>
+          <t>28/09/2026 14:33</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>28/09/2026 19:53</t>
+          <t>28/09/2026 14:33</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>29/09/2026 06:30</t>
+          <t>29/09/2026 07:40</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2651,7 +2651,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0018989-25.2022.8.16.0014</t>
+          <t>0019843-53.2022.8.16.0035</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2661,27 +2661,27 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Pagamento</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>25/08/2025</t>
+          <t>11/12/2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>21/09/2026 18:13</t>
+          <t>21/09/2026 17:53</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>21/09/2026 18:13</t>
+          <t>21/09/2026 17:53</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>29/09/2026 06:20</t>
+          <t>29/09/2026 05:40</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2698,37 +2698,37 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0019158-59.2015.8.16.0013</t>
+          <t>0019858-22.2022.8.16.0035</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Corrupção passiva | Crimes contra a Ordem Tributária</t>
+          <t>Pagamento</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>31/03/2024</t>
+          <t>23/09/2025</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>24/09/2026 18:41</t>
+          <t>28/09/2026 18:03</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>09/03/2026 09:29</t>
+          <t>28/09/2026 18:03</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>29/09/2026 08:20</t>
+          <t>29/09/2026 06:40</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2745,37 +2745,37 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0019842-08.2024.8.16.0000</t>
+          <t>0019932-08.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>28/09/2026 14:33</t>
+          <t>11/09/2026 15:33</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>28/09/2026 14:33</t>
+          <t>11/09/2026 15:33</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>29/09/2026 07:40</t>
+          <t>24/09/2026 16:57</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2792,7 +2792,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0019843-53.2022.8.16.0035</t>
+          <t>0021175-92.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2802,27 +2802,27 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Pagamento</t>
+          <t>Recuperação judicial e Falência | Concurso de Credores</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>11/12/2025</t>
+          <t>08/12/2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>21/09/2026 17:53</t>
+          <t>28/09/2026 18:23</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>21/09/2026 17:53</t>
+          <t>28/09/2026 18:23</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>29/09/2026 05:40</t>
+          <t>29/09/2026 06:40</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2839,7 +2839,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0019858-22.2022.8.16.0035</t>
+          <t>0021838-87.2014.8.16.0001</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2849,27 +2849,27 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Pagamento</t>
+          <t>Indenização por Dano Moral | Obrigação de Fazer / Não Fazer</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>23/09/2025</t>
+          <t>03/02/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>28/09/2026 18:03</t>
+          <t>21/09/2026 13:23</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>28/09/2026 18:03</t>
+          <t>21/09/2026 13:23</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>29/09/2026 06:40</t>
+          <t>29/09/2026 06:20</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2886,37 +2886,37 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0019932-08.2023.8.16.0014</t>
+          <t>0023032-64.2020.8.16.0017</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Direitos e Títulos de Crédito</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>04/06/2024</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>11/09/2026 15:33</t>
+          <t>21/09/2026 18:33</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>11/09/2026 15:33</t>
+          <t>21/09/2026 18:33</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>24/09/2026 16:57</t>
+          <t>29/09/2026 06:00</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2933,7 +2933,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0021175-92.2024.8.16.0000</t>
+          <t>0024007-62.2023.8.16.0185</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2943,27 +2943,27 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Recuperação judicial e Falência | Concurso de Credores</t>
+          <t>Dívida Ativa (Execução Fiscal)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>08/12/2025</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>28/09/2026 18:23</t>
+          <t>21/09/2026 17:33</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>28/09/2026 18:23</t>
+          <t>21/09/2026 17:33</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>29/09/2026 06:40</t>
+          <t>29/09/2026 05:30</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2980,37 +2980,37 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0021838-87.2014.8.16.0001</t>
+          <t>0025353-57.2025.8.16.0030</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Obrigação de Fazer / Não Fazer</t>
+          <t>Receptação Qualificada</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>03/02/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>21/09/2026 13:23</t>
+          <t>28/09/2026 17:23</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>21/09/2026 13:23</t>
+          <t>28/09/2026 17:23</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>29/09/2026 06:20</t>
+          <t>29/09/2026 07:40</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3027,7 +3027,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0023032-64.2020.8.16.0017</t>
+          <t>0026626-90.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3037,27 +3037,27 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Direitos e Títulos de Crédito</t>
+          <t>Tratamento médico-hospitalar</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>04/06/2024</t>
+          <t>03/12/2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>21/09/2026 18:33</t>
+          <t>21/09/2026 17:43</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>21/09/2026 18:33</t>
+          <t>21/09/2026 17:43</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>29/09/2026 06:00</t>
+          <t>29/09/2026 06:40</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3074,7 +3074,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0024007-62.2023.8.16.0185</t>
+          <t>0027654-38.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3084,27 +3084,27 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>Restituição ao Erário | Dano ao Erário | Obrigação de Fazer / Não Fazer | Ônus da Prova | Violação dos Princípios Administrativos</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>19/05/2025</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>21/09/2026 17:33</t>
+          <t>28/09/2026 16:03</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>21/09/2026 17:33</t>
+          <t>28/09/2026 16:03</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>29/09/2026 05:30</t>
+          <t>29/09/2026 08:20</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3121,37 +3121,37 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0025353-57.2025.8.16.0030</t>
+          <t>0028703-46.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Receptação Qualificada</t>
+          <t>Espécies de Títulos de Crédito</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>28/09/2026 17:23</t>
+          <t>28/09/2026 17:14</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>28/09/2026 17:23</t>
+          <t>28/09/2026 17:14</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>29/09/2026 07:40</t>
+          <t>29/09/2026 07:10</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3168,7 +3168,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0026626-90.2023.8.16.0014</t>
+          <t>0028898-92.2016.8.16.0017</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3178,27 +3178,27 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Tratamento médico-hospitalar</t>
+          <t>Rescisão / Resolução | Efeito Suspensivo / Impugnação / Embargos à Execução</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>03/12/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>21/09/2026 17:43</t>
+          <t>28/09/2026 10:44</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>21/09/2026 17:43</t>
+          <t>28/09/2026 10:44</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>29/09/2026 06:40</t>
+          <t>29/09/2026 07:00</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3215,7 +3215,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0027654-38.2023.8.16.0000</t>
+          <t>0033203-58.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3225,27 +3225,27 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Restituição ao Erário | Dano ao Erário | Obrigação de Fazer / Não Fazer | Ônus da Prova | Violação dos Princípios Administrativos</t>
+          <t>PIS/PASEP | Indenização por Dano Material | Práticas Abusivas</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>19/05/2025</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>28/09/2026 16:03</t>
+          <t>28/09/2026 17:53</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>28/09/2026 16:03</t>
+          <t>28/09/2026 17:53</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>29/09/2026 08:20</t>
+          <t>29/09/2026 07:10</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3262,32 +3262,32 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0028703-46.2025.8.16.0000</t>
+          <t>0033286-91.2013.8.16.0001</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Espécies de Títulos de Crédito</t>
+          <t>Reivindicação | Pagamento</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>09/02/2022</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>28/09/2026 17:14</t>
+          <t>28/09/2026 14:33</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>28/09/2026 17:14</t>
+          <t>28/09/2026 14:33</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3309,7 +3309,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0028898-92.2016.8.16.0017</t>
+          <t>0034555-58.2019.8.16.0001</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3319,27 +3319,27 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Rescisão / Resolução | Efeito Suspensivo / Impugnação / Embargos à Execução</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>28/09/2026 10:44</t>
+          <t>28/09/2026 17:03</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>28/09/2026 10:44</t>
+          <t>28/09/2026 17:03</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>29/09/2026 07:00</t>
+          <t>29/09/2026 08:20</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3356,7 +3356,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0033203-58.2025.8.16.0000</t>
+          <t>0034821-55.2013.8.16.0001</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3366,27 +3366,27 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>PIS/PASEP | Indenização por Dano Material | Práticas Abusivas</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>10/12/2025</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>28/09/2026 17:53</t>
+          <t>21/09/2026 18:13</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>28/09/2026 17:53</t>
+          <t>21/09/2026 18:13</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>29/09/2026 07:10</t>
+          <t>29/09/2026 05:07</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3403,7 +3403,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0033286-91.2013.8.16.0001</t>
+          <t>0035579-85.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3413,12 +3413,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Reivindicação | Pagamento</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>09/02/2022</t>
+          <t>11/12/2024</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>29/09/2026 07:10</t>
+          <t>29/09/2026 06:00</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3450,37 +3450,37 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0033792-21.2023.8.16.0000</t>
+          <t>0037028-51.2024.8.16.0030</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tratamento médico-hospitalar | Obrigação de Fazer / Não Fazer</t>
+          <t>Crimes do Sistema Nacional de Armas</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>21/09/2026 17:23</t>
+          <t>21/09/2026 14:03</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>21/09/2026 17:23</t>
+          <t>21/09/2026 14:03</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>29/09/2026 06:20</t>
+          <t>29/09/2026 07:10</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3497,37 +3497,37 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0034555-58.2019.8.16.0001</t>
+          <t>0037065-88.2012.8.16.0001</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Compra e Venda | Interpretação / Revisão de Contrato | Abatimento proporcional do preço | Indenização por Dano Material | Indenização por Dano Moral | Espécies de Contratos</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>14/12/2020</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>28/09/2026 17:03</t>
+          <t>21/09/2026 13:43</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>28/09/2026 17:03</t>
+          <t>21/09/2026 13:43</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>29/09/2026 08:20</t>
+          <t>29/09/2026 06:40</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3544,7 +3544,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0034821-55.2013.8.16.0001</t>
+          <t>0039377-54.2024.8.16.0021</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3554,27 +3554,27 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Rescisão / Resolução</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>10/12/2025</t>
+          <t>29/01/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>21/09/2026 18:13</t>
+          <t>28/09/2026 21:33</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>21/09/2026 18:13</t>
+          <t>28/09/2026 21:33</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>29/09/2026 05:07</t>
+          <t>29/09/2026 06:40</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3591,32 +3591,32 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0035579-85.2023.8.16.0000</t>
+          <t>0041536-33.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Promessa de Compra e Venda</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>11/12/2024</t>
+          <t>17/07/2025</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>28/09/2026 14:33</t>
+          <t>21/09/2026 14:23</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>28/09/2026 14:33</t>
+          <t>21/09/2026 14:23</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -3638,7 +3638,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0037028-51.2024.8.16.0030</t>
+          <t>0041752-57.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3648,27 +3648,27 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Crimes do Sistema Nacional de Armas</t>
+          <t>Dívida Ativa (Execução Fiscal)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>21/09/2026 14:03</t>
+          <t>21/09/2026 18:23</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>21/09/2026 14:03</t>
+          <t>21/09/2026 18:23</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>29/09/2026 07:10</t>
+          <t>29/09/2026 08:30</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3685,37 +3685,37 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0037065-88.2012.8.16.0001</t>
+          <t>0044419-16.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Compra e Venda | Interpretação / Revisão de Contrato | Abatimento proporcional do preço | Indenização por Dano Material | Indenização por Dano Moral | Espécies de Contratos</t>
+          <t>Ingresso e Exclusão dos Sócios na Sociedade</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>14/12/2020</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>21/09/2026 13:43</t>
+          <t>21/09/2026 13:33</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>21/09/2026 13:43</t>
+          <t>21/09/2026 13:33</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>29/09/2026 06:40</t>
+          <t>29/09/2026 08:00</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3732,37 +3732,37 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0039377-54.2024.8.16.0021</t>
+          <t>0049066-40.2014.8.16.0000</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Rescisão / Resolução</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
+          <t>22/10/2025</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>28/09/2026 21:33</t>
+          <t>11/09/2026 13:23</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>28/09/2026 21:33</t>
+          <t>11/09/2026 13:23</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>29/09/2026 06:40</t>
+          <t>24/09/2026 17:01</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3779,7 +3779,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0041536-33.2024.8.16.0000</t>
+          <t>0058493-75.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3789,27 +3789,27 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Promessa de Compra e Venda</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>17/07/2025</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>21/09/2026 14:23</t>
+          <t>28/09/2026 16:53</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>21/09/2026 14:23</t>
+          <t>28/09/2026 16:53</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>29/09/2026 06:00</t>
+          <t>29/09/2026 07:00</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3826,7 +3826,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0041752-57.2025.8.16.0000</t>
+          <t>0064910-44.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3836,27 +3836,27 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>Práticas Abusivas</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>21/09/2026 18:23</t>
+          <t>28/09/2026 21:23</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>21/09/2026 18:23</t>
+          <t>28/09/2026 21:23</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>29/09/2026 08:30</t>
+          <t>29/09/2026 04:21</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3873,7 +3873,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0044419-16.2025.8.16.0000</t>
+          <t>0071691-82.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3883,27 +3883,27 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Ingresso e Exclusão dos Sócios na Sociedade</t>
+          <t>PIS/PASEP | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>21/09/2026 13:33</t>
+          <t>28/09/2026 16:03</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>21/09/2026 13:33</t>
+          <t>28/09/2026 16:03</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>29/09/2026 08:00</t>
+          <t>29/09/2026 07:40</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3920,37 +3920,37 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0049066-40.2014.8.16.0000</t>
+          <t>0071839-30.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Contratos Bancários | Causas Supervenientes à Sentença</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>22/10/2025</t>
+          <t>07/10/2025</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>11/09/2026 13:23</t>
+          <t>28/09/2026 20:23</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>11/09/2026 13:23</t>
+          <t>28/09/2026 20:23</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>24/09/2026 17:01</t>
+          <t>29/09/2026 06:50</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3967,7 +3967,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0058493-75.2025.8.16.0000</t>
+          <t>0072736-29.2022.8.16.0000</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3977,27 +3977,27 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação</t>
+          <t>Dano ao Erário | Violação dos Princípios Administrativos | Sobrestamento</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>13/03/2025</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>28/09/2026 16:53</t>
+          <t>21/09/2026 19:03</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>28/09/2026 16:53</t>
+          <t>21/09/2026 19:03</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>29/09/2026 07:00</t>
+          <t>29/09/2026 07:50</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -4014,7 +4014,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0064910-44.2025.8.16.0000</t>
+          <t>0075408-05.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Práticas Abusivas</t>
+          <t>Prestação de Serviços | Efeito Suspensivo / Impugnação / Embargos à Execução | Prescrição e Decadência</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4034,17 +4034,17 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>28/09/2026 21:23</t>
+          <t>28/09/2026 16:23</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>28/09/2026 21:23</t>
+          <t>28/09/2026 16:23</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>29/09/2026 04:21</t>
+          <t>29/09/2026 07:00</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4061,7 +4061,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0071691-82.2025.8.16.0000</t>
+          <t>0077227-74.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4071,27 +4071,27 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>PIS/PASEP | Indenização por Dano Material</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>28/09/2026 16:03</t>
+          <t>28/09/2026 19:33</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>28/09/2026 16:03</t>
+          <t>28/09/2026 19:33</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>29/09/2026 07:40</t>
+          <t>29/09/2026 08:20</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -4108,7 +4108,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0071839-30.2024.8.16.0000</t>
+          <t>0080070-80.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4118,27 +4118,27 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Contratos Bancários | Causas Supervenientes à Sentença</t>
+          <t>Cédula de Crédito Bancário | Penhora / Depósito/ Avaliação</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>07/10/2025</t>
+          <t>13/02/2025</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>28/09/2026 20:23</t>
+          <t>28/09/2026 17:33</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>28/09/2026 20:23</t>
+          <t>28/09/2026 17:33</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>29/09/2026 06:50</t>
+          <t>29/09/2026 06:10</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4155,37 +4155,37 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0072736-29.2022.8.16.0000</t>
+          <t>0082380-54.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Dano ao Erário | Violação dos Princípios Administrativos | Sobrestamento</t>
+          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins | Prisão Preventiva | Cerceamento de Defesa | Promoção, constituição, financiamento ou integração de Organização Criminosa</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>13/03/2025</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>21/09/2026 19:03</t>
+          <t>23/09/2026 13:43</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>21/09/2026 19:03</t>
+          <t>23/09/2026 13:43</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>29/09/2026 07:50</t>
+          <t>29/09/2026 05:07</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4202,37 +4202,37 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0074926-28.2023.8.16.0000</t>
+          <t>0089720-83.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Duplicata</t>
+          <t>Crimes do Sistema Nacional de Armas</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>05/09/2024</t>
+          <t>09/12/2025</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>28/09/2026 18:53</t>
+          <t>25/09/2026 17:13</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>28/09/2026 18:53</t>
+          <t>25/09/2026 17:13</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>29/09/2026 06:30</t>
+          <t>29/09/2026 06:40</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4249,7 +4249,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0075408-05.2025.8.16.0000</t>
+          <t>0092890-34.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4259,27 +4259,27 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Prestação de Serviços | Efeito Suspensivo / Impugnação / Embargos à Execução | Prescrição e Decadência</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>24/01/2025</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>28/09/2026 16:23</t>
+          <t>28/09/2026 13:33</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>28/09/2026 16:23</t>
+          <t>28/09/2026 13:33</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>29/09/2026 07:00</t>
+          <t>29/09/2026 06:50</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4296,7 +4296,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0077227-74.2025.8.16.0000</t>
+          <t>0097644-82.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4306,27 +4306,27 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Práticas Abusivas</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>28/09/2026 19:33</t>
+          <t>28/09/2026 19:53</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>28/09/2026 19:33</t>
+          <t>28/09/2026 19:53</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>29/09/2026 08:20</t>
+          <t>29/09/2026 06:40</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4343,7 +4343,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0080070-80.2023.8.16.0000</t>
+          <t>0097671-65.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4353,27 +4353,27 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário | Penhora / Depósito/ Avaliação</t>
+          <t>Espécies de Contratos</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>13/02/2025</t>
+          <t>15/12/2025</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>28/09/2026 17:33</t>
+          <t>28/09/2026 16:53</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>28/09/2026 17:33</t>
+          <t>28/09/2026 16:53</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>29/09/2026 06:10</t>
+          <t>29/09/2026 07:20</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4390,7 +4390,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0080573-04.2023.8.16.0000</t>
+          <t>0099078-09.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4400,27 +4400,27 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Inventário e Partilha</t>
+          <t>Confissão/Composição de Dívida</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>13/11/2024</t>
+          <t>12/11/2025</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>28/09/2026 14:13</t>
+          <t>21/09/2026 13:33</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>28/09/2026 14:13</t>
+          <t>21/09/2026 13:33</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>29/09/2026 06:20</t>
+          <t>29/09/2026 05:07</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4437,37 +4437,37 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0082380-54.2026.8.16.0000</t>
+          <t>0101751-72.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins | Prisão Preventiva | Cerceamento de Defesa | Promoção, constituição, financiamento ou integração de Organização Criminosa</t>
+          <t>Concessão</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>30/01/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>23/09/2026 13:43</t>
+          <t>28/09/2026 21:23</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>23/09/2026 13:43</t>
+          <t>28/09/2026 21:23</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>29/09/2026 05:07</t>
+          <t>29/09/2026 06:40</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4484,37 +4484,37 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0089720-83.2025.8.16.0000</t>
+          <t>0104756-39.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Crimes do Sistema Nacional de Armas</t>
+          <t>Espécies de Títulos de Crédito</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>09/12/2025</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>25/09/2026 17:13</t>
+          <t>28/09/2026 14:33</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>25/09/2026 17:13</t>
+          <t>28/09/2026 14:33</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>29/09/2026 06:40</t>
+          <t>29/09/2026 07:20</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4531,7 +4531,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0092890-34.2023.8.16.0000</t>
+          <t>0116528-28.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4541,27 +4541,27 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>24/01/2025</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>28/09/2026 13:33</t>
+          <t>21/09/2026 16:55</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>28/09/2026 13:33</t>
+          <t>21/09/2026 16:55</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>29/09/2026 06:50</t>
+          <t>29/09/2026 08:00</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4578,7 +4578,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0097644-82.2024.8.16.0000</t>
+          <t>0118791-67.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4588,27 +4588,27 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Práticas Abusivas</t>
+          <t>Cobrança | Obrigação de Fazer / Não Fazer</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>28/09/2026 19:53</t>
+          <t>21/09/2026 19:03</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>28/09/2026 19:53</t>
+          <t>21/09/2026 19:03</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>29/09/2026 06:40</t>
+          <t>29/09/2026 08:20</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4617,382 +4617,6 @@
         </is>
       </c>
       <c r="I89" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>0097671-65.2024.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Espécies de Contratos</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>15/12/2025</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>28/09/2026 16:53</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>28/09/2026 16:53</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>29/09/2026 07:20</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>0099078-09.2024.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Confissão/Composição de Dívida</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>12/11/2025</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>21/09/2026 13:33</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>21/09/2026 13:33</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>29/09/2026 05:07</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>0101751-72.2024.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Concessão</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>30/01/2026</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>28/09/2026 21:23</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>28/09/2026 21:23</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>29/09/2026 06:40</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>0104756-39.2023.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Espécies de Títulos de Crédito</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>16/03/2026</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>28/09/2026 14:33</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>28/09/2026 14:33</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>29/09/2026 07:20</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>0105320-13.2026.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>10/09/2026</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>22/09/2026 17:13</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>22/09/2026 17:13</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>29/09/2026 06:30</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>0116528-28.2025.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>11/08/2026</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>21/09/2026 16:55</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>21/09/2026 16:55</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>29/09/2026 08:00</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>0118791-67.2024.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Cobrança | Obrigação de Fazer / Não Fazer</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>27/02/2026</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>21/09/2026 19:03</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>21/09/2026 19:03</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>29/09/2026 08:20</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>0123956-95.2024.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Compromisso</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>09/03/2026</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>28/09/2026 16:53</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>28/09/2026 16:53</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>29/09/2026 06:20</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>

--- a/docs/resultados.xlsx
+++ b/docs/resultados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I89"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -630,37 +630,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0000507-35.2021.8.16.0185</t>
+          <t>0001238-65.2016.8.16.0004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Concurso de Credores</t>
+          <t>Prestação de Serviços | Rescisão / Resolução | Perdas e Danos</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>27/05/2025</t>
+          <t>26/10/2021</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>28/09/2026 16:53</t>
+          <t>28/09/2026 15:43</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>28/09/2026 16:53</t>
+          <t>28/09/2026 15:43</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>29/09/2026 05:30</t>
+          <t>29/09/2026 07:10</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -677,7 +677,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0001127-42.2008.8.16.0043</t>
+          <t>0002148-65.2020.8.16.0194</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -687,27 +687,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Produto Impróprio</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>28/09/2026 16:23</t>
+          <t>21/09/2026 17:23</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>28/09/2026 16:23</t>
+          <t>21/09/2026 17:23</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>29/09/2026 05:40</t>
+          <t>29/09/2026 07:01</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -724,37 +724,37 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0001238-65.2016.8.16.0004</t>
+          <t>0002235-20.2023.8.16.0128</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Prestação de Serviços | Rescisão / Resolução | Perdas e Danos</t>
+          <t>Bancários</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>26/10/2021</t>
+          <t>03/12/2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>28/09/2026 15:43</t>
+          <t>21/09/2026 14:03</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>28/09/2026 15:43</t>
+          <t>21/09/2026 14:03</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>29/09/2026 07:10</t>
+          <t>29/09/2026 07:20</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -771,7 +771,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0001665-20.2022.8.16.0047</t>
+          <t>0003162-36.2023.8.16.0079</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -781,27 +781,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Práticas Abusivas</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>23/07/2025</t>
+          <t>30/01/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>28/09/2026 14:03</t>
+          <t>28/09/2026 19:53</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>28/09/2026 14:03</t>
+          <t>28/09/2026 19:53</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>29/09/2026 06:40</t>
+          <t>29/09/2026 07:40</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -818,7 +818,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0001837-98.2025.8.16.0097</t>
+          <t>0003766-51.2023.8.16.0158</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -828,27 +828,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Revisão de Juros Remuneratórios, Capitalização/Anatocismo</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>22/09/2026 14:53</t>
+          <t>28/09/2026 19:53</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>22/09/2026 14:53</t>
+          <t>28/09/2026 19:53</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>29/09/2026 05:50</t>
+          <t>29/09/2026 06:40</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -865,7 +865,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0002148-65.2020.8.16.0194</t>
+          <t>0003984-61.2020.8.16.0004</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -875,27 +875,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Produto Impróprio</t>
+          <t>Indenização por Dano Moral | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>01/10/2025</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>21/09/2026 17:23</t>
+          <t>21/09/2026 14:53</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>21/09/2026 17:23</t>
+          <t>21/09/2026 14:53</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>29/09/2026 07:01</t>
+          <t>29/09/2026 07:40</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -912,7 +912,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0002202-63.2019.8.16.0130</t>
+          <t>0004576-62.2021.8.16.0104</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -922,27 +922,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bem de Família (Voluntário)</t>
+          <t>Parceria Agrícola e/ou pecuária</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>26/01/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>28/09/2026 14:53</t>
+          <t>28/09/2026 18:23</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>28/09/2026 14:53</t>
+          <t>28/09/2026 18:23</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>29/09/2026 06:50</t>
+          <t>29/09/2026 08:00</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0002235-20.2023.8.16.0128</t>
+          <t>0004635-66.2024.8.16.0194</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -969,27 +969,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bancários</t>
+          <t>Desenho Industrial | Perdas e Danos</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>03/12/2025</t>
+          <t>25/03/2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>21/09/2026 14:03</t>
+          <t>21/09/2026 15:43</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>21/09/2026 14:03</t>
+          <t>21/09/2026 15:43</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>29/09/2026 07:20</t>
+          <t>29/09/2026 07:50</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1006,7 +1006,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0002351-37.2009.8.16.0089</t>
+          <t>0004949-76.2025.8.16.0129</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1016,27 +1016,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Dívida Ativa (Execução Fiscal)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>28/09/2026 19:23</t>
+          <t>21/09/2026 16:23</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>28/09/2026 19:23</t>
+          <t>21/09/2026 16:23</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>29/09/2026 05:50</t>
+          <t>29/09/2026 06:40</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1053,7 +1053,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0003162-36.2023.8.16.0079</t>
+          <t>0004994-55.2020.8.16.0194</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1063,27 +1063,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Práticas Abusivas</t>
+          <t>Indenização por Dano Material | Prestação de Serviços | Obrigação de Fazer / Não Fazer | Indenização por Dano Moral | Ônus da Prova | Inadimplemento</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>30/01/2026</t>
+          <t>04/02/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>28/09/2026 19:53</t>
+          <t>28/09/2026 14:53</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>28/09/2026 19:53</t>
+          <t>28/09/2026 14:53</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>29/09/2026 07:40</t>
+          <t>29/09/2026 07:00</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0003205-60.2025.8.16.0189</t>
+          <t>0005035-85.2024.8.16.0160</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1110,27 +1110,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lesão Cometida em Razão da Condição de Mulher</t>
+          <t>Fonte de Custeio</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>21/09/2026 17:53</t>
+          <t>23/09/2026 13:23</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>21/09/2026 17:53</t>
+          <t>23/09/2026 13:23</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>29/09/2026 06:00</t>
+          <t>29/09/2026 07:00</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1147,37 +1147,37 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0003306-75.2016.8.16.0072</t>
+          <t>0005644-69.2025.8.16.0116</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Mandado de Segurança</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saneamento</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>02/09/2025</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>21/09/2026 13:53</t>
+          <t>28/09/2026 18:43</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>21/09/2026 13:53</t>
+          <t>28/09/2026 18:43</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>29/09/2026 06:40</t>
+          <t>29/09/2026 07:30</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1194,7 +1194,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0003766-51.2023.8.16.0158</t>
+          <t>0005863-05.2022.8.16.0014</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1204,27 +1204,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Revisão de Juros Remuneratórios, Capitalização/Anatocismo</t>
+          <t>Compra e Venda | Indenização por Dano Moral | Indenização por Dano Material | Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>26/01/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>28/09/2026 19:53</t>
+          <t>21/09/2026 18:03</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>28/09/2026 19:53</t>
+          <t>21/09/2026 18:03</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>29/09/2026 06:40</t>
+          <t>29/09/2026 07:10</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1241,37 +1241,37 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0003812-81.2020.8.16.0146</t>
+          <t>0006648-82.2017.8.16.0194</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Arrendamento Rural | Liminar</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>28/08/2024</t>
+          <t>10/10/2024</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>11/09/2026 15:13</t>
+          <t>28/09/2026 13:43</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>11/09/2026 15:13</t>
+          <t>28/09/2026 13:43</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>24/09/2026 17:37</t>
+          <t>29/09/2026 08:00</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1288,7 +1288,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0003984-61.2020.8.16.0004</t>
+          <t>0008208-80.2021.8.16.0174</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1298,27 +1298,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Indenização por Dano Material</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>21/09/2026 14:53</t>
+          <t>21/09/2026 17:33</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>21/09/2026 14:53</t>
+          <t>21/09/2026 17:33</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>29/09/2026 07:40</t>
+          <t>29/09/2026 07:00</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1335,37 +1335,37 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0004330-27.2024.8.16.0083</t>
+          <t>0009195-17.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Furto Qualificado</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>11/09/2026 14:13</t>
+          <t>28/09/2026 19:53</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>11/09/2026 14:13</t>
+          <t>28/09/2026 19:53</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>24/09/2026 17:10</t>
+          <t>29/09/2026 08:20</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1382,7 +1382,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0004576-62.2021.8.16.0104</t>
+          <t>0009337-85.2022.8.16.0045</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1392,27 +1392,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Parceria Agrícola e/ou pecuária</t>
+          <t>Desconsideração da Personalidade Jurídica | Defeito, nulidade ou anulação | Embargos de Terceiro | Penhora / Depósito/ Avaliação</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>26/01/2026</t>
+          <t>05/05/2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>28/09/2026 18:23</t>
+          <t>28/09/2026 16:33</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>28/09/2026 18:23</t>
+          <t>28/09/2026 16:33</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>29/09/2026 08:00</t>
+          <t>29/09/2026 07:10</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1429,7 +1429,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0004635-66.2024.8.16.0194</t>
+          <t>0011222-02.2024.8.16.0131</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1439,27 +1439,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Desenho Industrial | Perdas e Danos</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>25/03/2025</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>21/09/2026 15:43</t>
+          <t>23/09/2026 13:23</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>21/09/2026 15:43</t>
+          <t>23/09/2026 13:23</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>29/09/2026 07:50</t>
+          <t>29/09/2026 06:50</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1476,7 +1476,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0004949-76.2025.8.16.0129</t>
+          <t>0011485-52.2015.8.16.0033</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1486,27 +1486,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>Sustação de Protesto</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>05/09/2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>21/09/2026 16:23</t>
+          <t>28/09/2026 13:33</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>21/09/2026 16:23</t>
+          <t>28/09/2026 13:33</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>29/09/2026 06:40</t>
+          <t>29/09/2026 08:20</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1523,37 +1523,37 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0004994-55.2020.8.16.0194</t>
+          <t>0014041-70.2018.8.16.0017</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Prestação de Serviços | Obrigação de Fazer / Não Fazer | Indenização por Dano Moral | Ônus da Prova | Inadimplemento</t>
+          <t>Cobrança de Aluguéis - Sem despejo</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>04/02/2026</t>
+          <t>09/02/2022</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>28/09/2026 14:53</t>
+          <t>21/09/2026 17:53</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>28/09/2026 14:53</t>
+          <t>21/09/2026 17:53</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>29/09/2026 07:00</t>
+          <t>29/09/2026 08:40</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1570,7 +1570,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0005035-85.2024.8.16.0160</t>
+          <t>0014457-45.2025.8.16.0194</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1580,27 +1580,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Fonte de Custeio</t>
+          <t>Indenização por Dano Moral | Tutela de Urgência</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>02/02/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>23/09/2026 13:23</t>
+          <t>28/09/2026 21:43</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>23/09/2026 13:23</t>
+          <t>28/09/2026 21:43</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>29/09/2026 07:00</t>
+          <t>29/09/2026 06:50</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1617,37 +1617,37 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0005096-84.2024.8.16.0017</t>
+          <t>0019158-59.2015.8.16.0013</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Corrupção passiva | Crimes contra a Ordem Tributária</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>31/03/2024</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>23/09/2026 05:23</t>
+          <t>24/09/2026 18:41</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>23/09/2026 05:23</t>
+          <t>09/03/2026 09:29</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>24/09/2026 16:51</t>
+          <t>29/09/2026 08:20</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1664,7 +1664,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0005532-90.2023.8.16.0045</t>
+          <t>0019842-08.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1674,27 +1674,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>25/02/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>14/09/2026 13:23</t>
+          <t>28/09/2026 14:33</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>14/09/2026 13:23</t>
+          <t>28/09/2026 14:33</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>24/09/2026 17:21</t>
+          <t>29/09/2026 07:40</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1711,37 +1711,37 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0005644-69.2025.8.16.0116</t>
+          <t>0025353-57.2025.8.16.0030</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Mandado de Segurança</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Receptação Qualificada</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>01/12/2025</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>28/09/2026 18:43</t>
+          <t>28/09/2026 17:23</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>28/09/2026 18:43</t>
+          <t>28/09/2026 17:23</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>29/09/2026 07:30</t>
+          <t>29/09/2026 07:40</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1758,7 +1758,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0005863-05.2022.8.16.0014</t>
+          <t>0027654-38.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1768,27 +1768,27 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Compra e Venda | Indenização por Dano Moral | Indenização por Dano Material | Defeito, nulidade ou anulação</t>
+          <t>Restituição ao Erário | Dano ao Erário | Obrigação de Fazer / Não Fazer | Ônus da Prova | Violação dos Princípios Administrativos</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>26/01/2026</t>
+          <t>19/05/2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>21/09/2026 18:03</t>
+          <t>28/09/2026 16:03</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>21/09/2026 18:03</t>
+          <t>28/09/2026 16:03</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>29/09/2026 07:10</t>
+          <t>29/09/2026 08:20</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1805,7 +1805,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0006563-78.2022.8.16.0014</t>
+          <t>0028703-46.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1815,27 +1815,27 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Compra e Venda</t>
+          <t>Espécies de Títulos de Crédito</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>28/09/2026 20:23</t>
+          <t>28/09/2026 17:14</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>28/09/2026 20:23</t>
+          <t>28/09/2026 17:14</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>29/09/2026 06:50</t>
+          <t>29/09/2026 07:10</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1852,37 +1852,37 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0006648-82.2017.8.16.0194</t>
+          <t>0028898-92.2016.8.16.0017</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Rescisão / Resolução | Efeito Suspensivo / Impugnação / Embargos à Execução</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>10/10/2024</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>28/09/2026 13:43</t>
+          <t>28/09/2026 10:44</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>28/09/2026 13:43</t>
+          <t>28/09/2026 10:44</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>29/09/2026 08:00</t>
+          <t>29/09/2026 07:00</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1899,7 +1899,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0007836-93.2021.8.16.0025</t>
+          <t>0033203-58.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1909,27 +1909,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Horas Extras</t>
+          <t>PIS/PASEP | Indenização por Dano Material | Práticas Abusivas</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>10/09/2026 17:23</t>
+          <t>28/09/2026 17:53</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>10/09/2026 17:23</t>
+          <t>28/09/2026 17:53</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>24/09/2026 17:21</t>
+          <t>29/09/2026 07:10</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1946,37 +1946,37 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0008208-80.2021.8.16.0174</t>
+          <t>0033286-91.2013.8.16.0001</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Reivindicação | Pagamento</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/02/2022</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>21/09/2026 17:33</t>
+          <t>28/09/2026 14:33</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>21/09/2026 17:33</t>
+          <t>28/09/2026 14:33</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>29/09/2026 07:00</t>
+          <t>29/09/2026 07:10</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0009159-43.2020.8.16.0131</t>
+          <t>0034555-58.2019.8.16.0001</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2003,27 +2003,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Adimplemento e Extinção | Bem de Família (Voluntário)</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>18/06/2025</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>28/09/2026 18:13</t>
+          <t>28/09/2026 17:03</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>28/09/2026 18:13</t>
+          <t>28/09/2026 17:03</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>29/09/2026 06:00</t>
+          <t>29/09/2026 08:20</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2040,7 +2040,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0009195-17.2025.8.16.0000</t>
+          <t>0037028-51.2024.8.16.0030</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2050,27 +2050,27 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Crimes do Sistema Nacional de Armas</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>28/09/2026 19:53</t>
+          <t>21/09/2026 14:03</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>28/09/2026 19:53</t>
+          <t>21/09/2026 14:03</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>29/09/2026 08:20</t>
+          <t>29/09/2026 07:10</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2087,37 +2087,37 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0009337-85.2022.8.16.0045</t>
+          <t>0037065-88.2012.8.16.0001</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Desconsideração da Personalidade Jurídica | Defeito, nulidade ou anulação | Embargos de Terceiro | Penhora / Depósito/ Avaliação</t>
+          <t>Compra e Venda | Interpretação / Revisão de Contrato | Abatimento proporcional do preço | Indenização por Dano Material | Indenização por Dano Moral | Espécies de Contratos</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>05/05/2025</t>
+          <t>14/12/2020</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>28/09/2026 16:33</t>
+          <t>21/09/2026 13:43</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>28/09/2026 16:33</t>
+          <t>21/09/2026 13:43</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>29/09/2026 07:10</t>
+          <t>29/09/2026 06:40</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2134,7 +2134,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0011222-02.2024.8.16.0131</t>
+          <t>0041752-57.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2144,27 +2144,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Dívida Ativa (Execução Fiscal)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>23/09/2026 13:23</t>
+          <t>21/09/2026 18:23</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>23/09/2026 13:23</t>
+          <t>21/09/2026 18:23</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>29/09/2026 06:50</t>
+          <t>29/09/2026 08:30</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2181,7 +2181,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0011426-17.2025.8.16.0000</t>
+          <t>0044419-16.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2191,27 +2191,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Indenização por Dano Material</t>
+          <t>Ingresso e Exclusão dos Sócios na Sociedade</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>28/09/2026 20:23</t>
+          <t>21/09/2026 13:33</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>28/09/2026 20:23</t>
+          <t>21/09/2026 13:33</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>29/09/2026 05:50</t>
+          <t>29/09/2026 08:00</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2228,7 +2228,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0011485-52.2015.8.16.0033</t>
+          <t>0058493-75.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2238,27 +2238,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sustação de Protesto</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>05/09/2025</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>28/09/2026 13:33</t>
+          <t>28/09/2026 16:53</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>28/09/2026 13:33</t>
+          <t>28/09/2026 16:53</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>29/09/2026 08:20</t>
+          <t>29/09/2026 07:00</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2275,7 +2275,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0012385-53.2017.8.16.0069</t>
+          <t>0071691-82.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2285,27 +2285,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Rescisão / Resolução</t>
+          <t>PIS/PASEP | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>26/11/2025</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>28/09/2026 16:43</t>
+          <t>28/09/2026 16:03</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>28/09/2026 16:43</t>
+          <t>28/09/2026 16:03</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>29/09/2026 05:07</t>
+          <t>29/09/2026 07:40</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2322,7 +2322,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0012511-74.2015.8.16.0069</t>
+          <t>0072736-29.2022.8.16.0000</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2332,27 +2332,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Aposentadoria Especial (Art. 57/8)</t>
+          <t>Dano ao Erário | Violação dos Princípios Administrativos | Sobrestamento</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>13/03/2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>14/09/2026 13:53</t>
+          <t>21/09/2026 19:03</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>14/09/2026 13:53</t>
+          <t>21/09/2026 19:03</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>24/09/2026 17:10</t>
+          <t>29/09/2026 07:50</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2369,37 +2369,37 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0012627-78.2024.8.16.0000</t>
+          <t>0075408-05.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Despesas Condominiais | Condomínio em Edifício</t>
+          <t>Prestação de Serviços | Efeito Suspensivo / Impugnação / Embargos à Execução | Prescrição e Decadência</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>18/11/2024</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>28/09/2026 21:33</t>
+          <t>28/09/2026 16:23</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>28/09/2026 21:33</t>
+          <t>28/09/2026 16:23</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>29/09/2026 06:40</t>
+          <t>29/09/2026 07:00</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2416,37 +2416,37 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0014041-70.2018.8.16.0017</t>
+          <t>0077227-74.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cobrança de Aluguéis - Sem despejo</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>09/02/2022</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>21/09/2026 17:53</t>
+          <t>28/09/2026 19:33</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>21/09/2026 17:53</t>
+          <t>28/09/2026 19:33</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>29/09/2026 08:40</t>
+          <t>29/09/2026 08:20</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2463,37 +2463,37 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0014138-79.2022.8.16.0001</t>
+          <t>0089720-83.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Alienação Fiduciária</t>
+          <t>Crimes do Sistema Nacional de Armas</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>12/01/2026</t>
+          <t>09/12/2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>28/09/2026 17:33</t>
+          <t>25/09/2026 17:13</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>28/09/2026 17:33</t>
+          <t>25/09/2026 17:13</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>29/09/2026 06:00</t>
+          <t>29/09/2026 06:40</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2510,7 +2510,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0014457-45.2025.8.16.0194</t>
+          <t>0097671-65.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2520,27 +2520,27 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Tutela de Urgência</t>
+          <t>Espécies de Contratos</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>02/02/2026</t>
+          <t>15/12/2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>28/09/2026 21:43</t>
+          <t>28/09/2026 16:53</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>28/09/2026 21:43</t>
+          <t>28/09/2026 16:53</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>29/09/2026 06:50</t>
+          <t>29/09/2026 07:20</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2557,37 +2557,37 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0019158-59.2015.8.16.0013</t>
+          <t>0104756-39.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Corrupção passiva | Crimes contra a Ordem Tributária</t>
+          <t>Espécies de Títulos de Crédito</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>31/03/2024</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>24/09/2026 18:41</t>
+          <t>28/09/2026 14:33</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>09/03/2026 09:29</t>
+          <t>28/09/2026 14:33</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>29/09/2026 08:20</t>
+          <t>29/09/2026 07:20</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2604,7 +2604,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0019842-08.2024.8.16.0000</t>
+          <t>0116528-28.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2614,27 +2614,27 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>28/09/2026 14:33</t>
+          <t>21/09/2026 16:55</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>28/09/2026 14:33</t>
+          <t>21/09/2026 16:55</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>29/09/2026 07:40</t>
+          <t>29/09/2026 08:00</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2651,7 +2651,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0019843-53.2022.8.16.0035</t>
+          <t>0118791-67.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2661,27 +2661,27 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Pagamento</t>
+          <t>Cobrança | Obrigação de Fazer / Não Fazer</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>11/12/2025</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>21/09/2026 17:53</t>
+          <t>21/09/2026 19:03</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>21/09/2026 17:53</t>
+          <t>21/09/2026 19:03</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>29/09/2026 05:40</t>
+          <t>29/09/2026 08:20</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2690,1933 +2690,6 @@
         </is>
       </c>
       <c r="I48" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>0019858-22.2022.8.16.0035</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Pagamento</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>23/09/2025</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>28/09/2026 18:03</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>28/09/2026 18:03</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>29/09/2026 06:40</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>0019932-08.2023.8.16.0014</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>11/09/2026 15:33</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>11/09/2026 15:33</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>24/09/2026 16:57</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>0021175-92.2024.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Recuperação judicial e Falência | Concurso de Credores</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>08/12/2025</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>28/09/2026 18:23</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>28/09/2026 18:23</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>29/09/2026 06:40</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>0021838-87.2014.8.16.0001</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Indenização por Dano Moral | Obrigação de Fazer / Não Fazer</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>03/02/2026</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>21/09/2026 13:23</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>21/09/2026 13:23</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>29/09/2026 06:20</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>0023032-64.2020.8.16.0017</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Direitos e Títulos de Crédito</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>04/06/2024</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>21/09/2026 18:33</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>21/09/2026 18:33</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>29/09/2026 06:00</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>0024007-62.2023.8.16.0185</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>21/09/2026 17:33</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>21/09/2026 17:33</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>29/09/2026 05:30</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>0025353-57.2025.8.16.0030</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Receptação Qualificada</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>28/09/2026 17:23</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>28/09/2026 17:23</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>29/09/2026 07:40</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>0026626-90.2023.8.16.0014</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Tratamento médico-hospitalar</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>03/12/2025</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>21/09/2026 17:43</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>21/09/2026 17:43</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>29/09/2026 06:40</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>0027654-38.2023.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Restituição ao Erário | Dano ao Erário | Obrigação de Fazer / Não Fazer | Ônus da Prova | Violação dos Princípios Administrativos</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>19/05/2025</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>28/09/2026 16:03</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>28/09/2026 16:03</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>29/09/2026 08:20</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>0028703-46.2025.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Espécies de Títulos de Crédito</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>26/03/2026</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>28/09/2026 17:14</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>28/09/2026 17:14</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>29/09/2026 07:10</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>0028898-92.2016.8.16.0017</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Rescisão / Resolução | Efeito Suspensivo / Impugnação / Embargos à Execução</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>02/06/2025</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>28/09/2026 10:44</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>28/09/2026 10:44</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>29/09/2026 07:00</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>0033203-58.2025.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>PIS/PASEP | Indenização por Dano Material | Práticas Abusivas</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>11/08/2026</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>28/09/2026 17:53</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>28/09/2026 17:53</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>29/09/2026 07:10</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>0033286-91.2013.8.16.0001</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Reivindicação | Pagamento</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>09/02/2022</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>28/09/2026 14:33</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>28/09/2026 14:33</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>29/09/2026 07:10</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>0034555-58.2019.8.16.0001</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Seguro</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>11/03/2025</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>28/09/2026 17:03</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>28/09/2026 17:03</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>29/09/2026 08:20</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>0034821-55.2013.8.16.0001</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Cédula de Crédito Bancário</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>10/12/2025</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>21/09/2026 18:13</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>21/09/2026 18:13</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>29/09/2026 05:07</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>0035579-85.2023.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Indenização por Dano Material</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>11/12/2024</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>28/09/2026 14:33</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>28/09/2026 14:33</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>29/09/2026 06:00</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>0037028-51.2024.8.16.0030</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Crimes do Sistema Nacional de Armas</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>14/08/2026</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>21/09/2026 14:03</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>21/09/2026 14:03</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>29/09/2026 07:10</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>0037065-88.2012.8.16.0001</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Compra e Venda | Interpretação / Revisão de Contrato | Abatimento proporcional do preço | Indenização por Dano Material | Indenização por Dano Moral | Espécies de Contratos</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>14/12/2020</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>21/09/2026 13:43</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>21/09/2026 13:43</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>29/09/2026 06:40</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>0039377-54.2024.8.16.0021</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Rescisão / Resolução</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>29/01/2026</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>28/09/2026 21:33</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>28/09/2026 21:33</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>29/09/2026 06:40</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>0041536-33.2024.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Promessa de Compra e Venda</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>17/07/2025</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>21/09/2026 14:23</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>21/09/2026 14:23</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>29/09/2026 06:00</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>0041752-57.2025.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>21/09/2026 18:23</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>21/09/2026 18:23</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>29/09/2026 08:30</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>0044419-16.2025.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ingresso e Exclusão dos Sócios na Sociedade</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>21/09/2026 13:33</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>21/09/2026 13:33</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>29/09/2026 08:00</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>0049066-40.2014.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Seguro</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>22/10/2025</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>11/09/2026 13:23</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>11/09/2026 13:23</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>24/09/2026 17:01</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>0058493-75.2025.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Defeito, nulidade ou anulação</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>06/02/2026</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>28/09/2026 16:53</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>28/09/2026 16:53</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>29/09/2026 07:00</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>0064910-44.2025.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Práticas Abusivas</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>28/09/2026 21:23</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>28/09/2026 21:23</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>29/09/2026 04:21</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>0071691-82.2025.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>PIS/PASEP | Indenização por Dano Material</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>23/07/2026</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>28/09/2026 16:03</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>28/09/2026 16:03</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>29/09/2026 07:40</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>0071839-30.2024.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Contratos Bancários | Causas Supervenientes à Sentença</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>07/10/2025</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>28/09/2026 20:23</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>28/09/2026 20:23</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>29/09/2026 06:50</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>0072736-29.2022.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Dano ao Erário | Violação dos Princípios Administrativos | Sobrestamento</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>13/03/2025</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>21/09/2026 19:03</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>21/09/2026 19:03</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>29/09/2026 07:50</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>0075408-05.2025.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Prestação de Serviços | Efeito Suspensivo / Impugnação / Embargos à Execução | Prescrição e Decadência</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>28/09/2026 16:23</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>28/09/2026 16:23</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>29/09/2026 07:00</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>0077227-74.2025.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Seguro</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>28/09/2026 19:33</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>28/09/2026 19:33</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>29/09/2026 08:20</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>0080070-80.2023.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Cédula de Crédito Bancário | Penhora / Depósito/ Avaliação</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>13/02/2025</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>28/09/2026 17:33</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>28/09/2026 17:33</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>29/09/2026 06:10</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>0082380-54.2026.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins | Prisão Preventiva | Cerceamento de Defesa | Promoção, constituição, financiamento ou integração de Organização Criminosa</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>23/09/2026 13:43</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>23/09/2026 13:43</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>29/09/2026 05:07</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>0089720-83.2025.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Crimes do Sistema Nacional de Armas</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>09/12/2025</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>25/09/2026 17:13</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>25/09/2026 17:13</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>29/09/2026 06:40</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>0092890-34.2023.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Prestação de Serviços</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>24/01/2025</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>28/09/2026 13:33</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>28/09/2026 13:33</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>29/09/2026 06:50</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>0097644-82.2024.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Práticas Abusivas</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>16/12/2025</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>28/09/2026 19:53</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>28/09/2026 19:53</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>29/09/2026 06:40</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>0097671-65.2024.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Espécies de Contratos</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>15/12/2025</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>28/09/2026 16:53</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>28/09/2026 16:53</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>29/09/2026 07:20</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>0099078-09.2024.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Confissão/Composição de Dívida</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>12/11/2025</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>21/09/2026 13:33</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>21/09/2026 13:33</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>29/09/2026 05:07</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>0101751-72.2024.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Concessão</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>30/01/2026</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>28/09/2026 21:23</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>28/09/2026 21:23</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>29/09/2026 06:40</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>0104756-39.2023.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Espécies de Títulos de Crédito</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>16/03/2026</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>28/09/2026 14:33</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>28/09/2026 14:33</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>29/09/2026 07:20</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>0116528-28.2025.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>11/08/2026</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>21/09/2026 16:55</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>21/09/2026 16:55</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>29/09/2026 08:00</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>0118791-67.2024.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Cobrança | Obrigação de Fazer / Não Fazer</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>27/02/2026</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>21/09/2026 19:03</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>21/09/2026 19:03</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>29/09/2026 08:20</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>

--- a/docs/resultados.xlsx
+++ b/docs/resultados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -630,37 +630,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0001238-65.2016.8.16.0004</t>
+          <t>0000507-35.2021.8.16.0185</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Prestação de Serviços | Rescisão / Resolução | Perdas e Danos</t>
+          <t>Concurso de Credores</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>26/10/2021</t>
+          <t>27/05/2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>28/09/2026 15:43</t>
+          <t>28/09/2026 16:53</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>28/09/2026 15:43</t>
+          <t>28/09/2026 16:53</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>29/09/2026 07:10</t>
+          <t>29/09/2026 05:30</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -677,7 +677,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0002148-65.2020.8.16.0194</t>
+          <t>0000733-34.2024.8.16.0056</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -687,27 +687,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Produto Impróprio</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>01/10/2025</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>21/09/2026 17:23</t>
+          <t>28/09/2026 19:33</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>21/09/2026 17:23</t>
+          <t>28/09/2026 19:33</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>29/09/2026 07:01</t>
+          <t>29/09/2026 06:30</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -724,7 +724,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0002235-20.2023.8.16.0128</t>
+          <t>0001054-57.2022.8.16.0115</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -734,27 +734,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bancários</t>
+          <t>Promessa de Compra e Venda | Obrigação de Fazer / Não Fazer</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>03/12/2025</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>21/09/2026 14:03</t>
+          <t>28/09/2026 14:53</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>21/09/2026 14:03</t>
+          <t>28/09/2026 14:53</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>29/09/2026 07:20</t>
+          <t>29/09/2026 06:30</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -771,7 +771,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0003162-36.2023.8.16.0079</t>
+          <t>0001127-42.2008.8.16.0043</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -781,27 +781,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Práticas Abusivas</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>30/01/2026</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>28/09/2026 19:53</t>
+          <t>28/09/2026 16:23</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>28/09/2026 19:53</t>
+          <t>28/09/2026 16:23</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>29/09/2026 07:40</t>
+          <t>29/09/2026 05:40</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -818,37 +818,37 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0003766-51.2023.8.16.0158</t>
+          <t>0001238-65.2016.8.16.0004</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Revisão de Juros Remuneratórios, Capitalização/Anatocismo</t>
+          <t>Prestação de Serviços | Rescisão / Resolução | Perdas e Danos</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>26/10/2021</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>28/09/2026 19:53</t>
+          <t>28/09/2026 15:43</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>28/09/2026 19:53</t>
+          <t>28/09/2026 15:43</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>29/09/2026 06:40</t>
+          <t>29/09/2026 07:10</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -865,7 +865,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0003984-61.2020.8.16.0004</t>
+          <t>0001665-20.2022.8.16.0047</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -875,27 +875,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Indenização por Dano Material</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>23/07/2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>21/09/2026 14:53</t>
+          <t>28/09/2026 14:03</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>21/09/2026 14:53</t>
+          <t>28/09/2026 14:03</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>29/09/2026 07:40</t>
+          <t>29/09/2026 06:40</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -912,7 +912,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0004576-62.2021.8.16.0104</t>
+          <t>0001837-98.2025.8.16.0097</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -922,27 +922,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Parceria Agrícola e/ou pecuária</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>26/01/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>28/09/2026 18:23</t>
+          <t>22/09/2026 14:53</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>28/09/2026 18:23</t>
+          <t>22/09/2026 14:53</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>29/09/2026 08:00</t>
+          <t>29/09/2026 05:50</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0004635-66.2024.8.16.0194</t>
+          <t>0002148-65.2020.8.16.0194</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -969,27 +969,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Desenho Industrial | Perdas e Danos</t>
+          <t>Produto Impróprio</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>25/03/2025</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>21/09/2026 15:43</t>
+          <t>21/09/2026 17:23</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>21/09/2026 15:43</t>
+          <t>21/09/2026 17:23</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>29/09/2026 07:50</t>
+          <t>29/09/2026 07:01</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1006,7 +1006,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0004949-76.2025.8.16.0129</t>
+          <t>0002202-63.2019.8.16.0130</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1016,27 +1016,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>Bem de Família (Voluntário)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>21/09/2026 16:23</t>
+          <t>28/09/2026 14:53</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>21/09/2026 16:23</t>
+          <t>28/09/2026 14:53</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>29/09/2026 06:40</t>
+          <t>29/09/2026 06:50</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1053,7 +1053,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0004994-55.2020.8.16.0194</t>
+          <t>0002235-20.2023.8.16.0128</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1063,27 +1063,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Prestação de Serviços | Obrigação de Fazer / Não Fazer | Indenização por Dano Moral | Ônus da Prova | Inadimplemento</t>
+          <t>Bancários</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>04/02/2026</t>
+          <t>03/12/2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>28/09/2026 14:53</t>
+          <t>21/09/2026 14:03</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>28/09/2026 14:53</t>
+          <t>21/09/2026 14:03</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>29/09/2026 07:00</t>
+          <t>29/09/2026 07:20</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0005035-85.2024.8.16.0160</t>
+          <t>0002351-37.2009.8.16.0089</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1110,27 +1110,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Fonte de Custeio</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>23/09/2026 13:23</t>
+          <t>28/09/2026 19:23</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>23/09/2026 13:23</t>
+          <t>28/09/2026 19:23</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>29/09/2026 07:00</t>
+          <t>29/09/2026 05:50</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1147,37 +1147,37 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0005644-69.2025.8.16.0116</t>
+          <t>0002488-84.2023.8.16.0038</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Mandado de Segurança</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Alienação Fiduciária</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>01/12/2025</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>28/09/2026 18:43</t>
+          <t>21/09/2026 13:33</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>28/09/2026 18:43</t>
+          <t>21/09/2026 13:33</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>29/09/2026 07:30</t>
+          <t>29/09/2026 06:20</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1194,7 +1194,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0005863-05.2022.8.16.0014</t>
+          <t>0003162-36.2023.8.16.0079</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1204,27 +1204,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Compra e Venda | Indenização por Dano Moral | Indenização por Dano Material | Defeito, nulidade ou anulação</t>
+          <t>Práticas Abusivas</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>26/01/2026</t>
+          <t>30/01/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>21/09/2026 18:03</t>
+          <t>28/09/2026 19:53</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>21/09/2026 18:03</t>
+          <t>28/09/2026 19:53</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>29/09/2026 07:10</t>
+          <t>29/09/2026 07:40</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1241,37 +1241,37 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0006648-82.2017.8.16.0194</t>
+          <t>0003205-60.2025.8.16.0189</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Lesão Cometida em Razão da Condição de Mulher</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>10/10/2024</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>28/09/2026 13:43</t>
+          <t>21/09/2026 17:53</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>28/09/2026 13:43</t>
+          <t>21/09/2026 17:53</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>29/09/2026 08:00</t>
+          <t>29/09/2026 06:00</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1288,7 +1288,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0008208-80.2021.8.16.0174</t>
+          <t>0003306-75.2016.8.16.0072</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1298,27 +1298,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Saneamento</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>02/09/2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>21/09/2026 17:33</t>
+          <t>21/09/2026 13:53</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>21/09/2026 17:33</t>
+          <t>21/09/2026 13:53</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>29/09/2026 07:00</t>
+          <t>29/09/2026 06:40</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1335,7 +1335,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0009195-17.2025.8.16.0000</t>
+          <t>0003984-61.2020.8.16.0004</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1345,27 +1345,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Indenização por Dano Moral | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>28/09/2026 19:53</t>
+          <t>21/09/2026 14:53</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>28/09/2026 19:53</t>
+          <t>21/09/2026 14:53</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>29/09/2026 08:20</t>
+          <t>29/09/2026 07:40</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1382,37 +1382,37 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0009337-85.2022.8.16.0045</t>
+          <t>0004330-27.2024.8.16.0083</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Desconsideração da Personalidade Jurídica | Defeito, nulidade ou anulação | Embargos de Terceiro | Penhora / Depósito/ Avaliação</t>
+          <t>Furto Qualificado</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>05/05/2025</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>28/09/2026 16:33</t>
+          <t>11/09/2026 14:13</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>28/09/2026 16:33</t>
+          <t>11/09/2026 14:13</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>29/09/2026 07:10</t>
+          <t>24/09/2026 17:10</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1429,7 +1429,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0011222-02.2024.8.16.0131</t>
+          <t>0004576-62.2021.8.16.0104</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1439,27 +1439,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Parceria Agrícola e/ou pecuária</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>26/01/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>23/09/2026 13:23</t>
+          <t>28/09/2026 18:23</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>23/09/2026 13:23</t>
+          <t>28/09/2026 18:23</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>29/09/2026 06:50</t>
+          <t>29/09/2026 08:00</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1476,7 +1476,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0011485-52.2015.8.16.0033</t>
+          <t>0004635-66.2024.8.16.0194</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1486,27 +1486,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sustação de Protesto</t>
+          <t>Desenho Industrial | Perdas e Danos</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>05/09/2025</t>
+          <t>25/03/2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>28/09/2026 13:33</t>
+          <t>21/09/2026 15:43</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>28/09/2026 13:33</t>
+          <t>21/09/2026 15:43</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>29/09/2026 08:20</t>
+          <t>29/09/2026 07:50</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1523,22 +1523,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0014041-70.2018.8.16.0017</t>
+          <t>0004667-84.2009.8.16.0004</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cobrança de Aluguéis - Sem despejo</t>
+          <t>Contratos Bancários | Pagamento em Consignação</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>09/02/2022</t>
+          <t>09/11/2019</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>29/09/2026 08:40</t>
+          <t>29/09/2026 06:30</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1570,7 +1570,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0014457-45.2025.8.16.0194</t>
+          <t>0005096-84.2024.8.16.0017</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1580,27 +1580,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Tutela de Urgência</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>02/02/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>28/09/2026 21:43</t>
+          <t>23/09/2026 05:23</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>28/09/2026 21:43</t>
+          <t>23/09/2026 05:23</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>29/09/2026 06:50</t>
+          <t>24/09/2026 16:51</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1617,37 +1617,37 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0019158-59.2015.8.16.0013</t>
+          <t>0005532-90.2023.8.16.0045</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Corrupção passiva | Crimes contra a Ordem Tributária</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>31/03/2024</t>
+          <t>25/02/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>24/09/2026 18:41</t>
+          <t>14/09/2026 13:23</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>09/03/2026 09:29</t>
+          <t>14/09/2026 13:23</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>29/09/2026 08:20</t>
+          <t>24/09/2026 17:21</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1664,37 +1664,37 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0019842-08.2024.8.16.0000</t>
+          <t>0005644-69.2025.8.16.0116</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Mandado de Segurança</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>28/09/2026 14:33</t>
+          <t>28/09/2026 18:43</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>28/09/2026 14:33</t>
+          <t>28/09/2026 18:43</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>29/09/2026 07:40</t>
+          <t>29/09/2026 07:30</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1711,37 +1711,37 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0025353-57.2025.8.16.0030</t>
+          <t>0005863-05.2022.8.16.0014</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Receptação Qualificada</t>
+          <t>Compra e Venda | Indenização por Dano Moral | Indenização por Dano Material | Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>26/01/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>28/09/2026 17:23</t>
+          <t>21/09/2026 18:03</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>28/09/2026 17:23</t>
+          <t>21/09/2026 18:03</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>29/09/2026 07:40</t>
+          <t>29/09/2026 07:10</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1758,7 +1758,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0027654-38.2023.8.16.0000</t>
+          <t>0006563-78.2022.8.16.0014</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1768,27 +1768,27 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Restituição ao Erário | Dano ao Erário | Obrigação de Fazer / Não Fazer | Ônus da Prova | Violação dos Princípios Administrativos</t>
+          <t>Compra e Venda</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>19/05/2025</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>28/09/2026 16:03</t>
+          <t>28/09/2026 20:23</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>28/09/2026 16:03</t>
+          <t>28/09/2026 20:23</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>29/09/2026 08:20</t>
+          <t>29/09/2026 06:50</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1805,37 +1805,37 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0028703-46.2025.8.16.0000</t>
+          <t>0006648-82.2017.8.16.0194</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Espécies de Títulos de Crédito</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>10/10/2024</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>28/09/2026 17:14</t>
+          <t>28/09/2026 13:43</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>28/09/2026 17:14</t>
+          <t>28/09/2026 13:43</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>29/09/2026 07:10</t>
+          <t>29/09/2026 08:00</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1852,7 +1852,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0028898-92.2016.8.16.0017</t>
+          <t>0009159-43.2020.8.16.0131</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1862,27 +1862,27 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Rescisão / Resolução | Efeito Suspensivo / Impugnação / Embargos à Execução</t>
+          <t>Adimplemento e Extinção | Bem de Família (Voluntário)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>18/06/2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>28/09/2026 10:44</t>
+          <t>28/09/2026 18:13</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>28/09/2026 10:44</t>
+          <t>28/09/2026 18:13</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>29/09/2026 07:00</t>
+          <t>29/09/2026 06:00</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1899,7 +1899,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0033203-58.2025.8.16.0000</t>
+          <t>0009195-17.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1909,27 +1909,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>PIS/PASEP | Indenização por Dano Material | Práticas Abusivas</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>28/09/2026 17:53</t>
+          <t>28/09/2026 19:53</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>28/09/2026 17:53</t>
+          <t>28/09/2026 19:53</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>29/09/2026 07:10</t>
+          <t>29/09/2026 08:20</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1946,32 +1946,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0033286-91.2013.8.16.0001</t>
+          <t>0009337-85.2022.8.16.0045</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Reivindicação | Pagamento</t>
+          <t>Desconsideração da Personalidade Jurídica | Defeito, nulidade ou anulação | Embargos de Terceiro | Penhora / Depósito/ Avaliação</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>09/02/2022</t>
+          <t>05/05/2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>28/09/2026 14:33</t>
+          <t>28/09/2026 16:33</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>28/09/2026 14:33</t>
+          <t>28/09/2026 16:33</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1993,37 +1993,37 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0034555-58.2019.8.16.0001</t>
+          <t>0010353-10.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>28/09/2026 17:03</t>
+          <t>28/09/2026 17:33</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>28/09/2026 17:03</t>
+          <t>28/09/2026 17:33</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>29/09/2026 08:20</t>
+          <t>29/09/2026 06:20</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2040,7 +2040,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0037028-51.2024.8.16.0030</t>
+          <t>0011426-17.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2050,27 +2050,27 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Crimes do Sistema Nacional de Armas</t>
+          <t>Indenização por Dano Moral | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>21/09/2026 14:03</t>
+          <t>28/09/2026 20:23</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>21/09/2026 14:03</t>
+          <t>28/09/2026 20:23</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>29/09/2026 07:10</t>
+          <t>29/09/2026 05:50</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2087,37 +2087,37 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0037065-88.2012.8.16.0001</t>
+          <t>0011485-52.2015.8.16.0033</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Compra e Venda | Interpretação / Revisão de Contrato | Abatimento proporcional do preço | Indenização por Dano Material | Indenização por Dano Moral | Espécies de Contratos</t>
+          <t>Sustação de Protesto</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>14/12/2020</t>
+          <t>05/09/2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>21/09/2026 13:43</t>
+          <t>28/09/2026 13:33</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>21/09/2026 13:43</t>
+          <t>28/09/2026 13:33</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>29/09/2026 06:40</t>
+          <t>29/09/2026 08:20</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2134,7 +2134,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0041752-57.2025.8.16.0000</t>
+          <t>0012346-88.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2144,27 +2144,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>Despesas Condominiais</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>21/09/2026 18:23</t>
+          <t>28/09/2026 20:53</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>21/09/2026 18:23</t>
+          <t>28/09/2026 20:53</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>29/09/2026 08:30</t>
+          <t>29/09/2026 06:30</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2181,7 +2181,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0044419-16.2025.8.16.0000</t>
+          <t>0012385-53.2017.8.16.0069</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2191,27 +2191,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ingresso e Exclusão dos Sócios na Sociedade</t>
+          <t>Rescisão / Resolução</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>26/11/2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>21/09/2026 13:33</t>
+          <t>28/09/2026 16:43</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>21/09/2026 13:33</t>
+          <t>28/09/2026 16:43</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>29/09/2026 08:00</t>
+          <t>29/09/2026 05:07</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2228,7 +2228,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0058493-75.2025.8.16.0000</t>
+          <t>0012511-74.2015.8.16.0069</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2238,27 +2238,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação</t>
+          <t>Aposentadoria Especial (Art. 57/8)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>28/09/2026 16:53</t>
+          <t>14/09/2026 13:53</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>28/09/2026 16:53</t>
+          <t>14/09/2026 13:53</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>29/09/2026 07:00</t>
+          <t>24/09/2026 17:10</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2275,37 +2275,37 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0071691-82.2025.8.16.0000</t>
+          <t>0012627-78.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>PIS/PASEP | Indenização por Dano Material</t>
+          <t>Despesas Condominiais | Condomínio em Edifício</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>18/11/2024</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>28/09/2026 16:03</t>
+          <t>28/09/2026 21:33</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>28/09/2026 16:03</t>
+          <t>28/09/2026 21:33</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>29/09/2026 07:40</t>
+          <t>29/09/2026 06:40</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2322,37 +2322,37 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0072736-29.2022.8.16.0000</t>
+          <t>0014041-70.2018.8.16.0017</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dano ao Erário | Violação dos Princípios Administrativos | Sobrestamento</t>
+          <t>Cobrança de Aluguéis - Sem despejo</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>13/03/2025</t>
+          <t>09/02/2022</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>21/09/2026 19:03</t>
+          <t>21/09/2026 17:53</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>21/09/2026 19:03</t>
+          <t>21/09/2026 17:53</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>29/09/2026 07:50</t>
+          <t>29/09/2026 08:40</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2369,37 +2369,37 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0075408-05.2025.8.16.0000</t>
+          <t>0014138-79.2022.8.16.0001</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Prestação de Serviços | Efeito Suspensivo / Impugnação / Embargos à Execução | Prescrição e Decadência</t>
+          <t>Alienação Fiduciária</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>12/01/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>28/09/2026 16:23</t>
+          <t>28/09/2026 17:33</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>28/09/2026 16:23</t>
+          <t>28/09/2026 17:33</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>29/09/2026 07:00</t>
+          <t>29/09/2026 06:00</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2416,7 +2416,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0077227-74.2025.8.16.0000</t>
+          <t>0017353-44.2024.8.16.0017</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2426,27 +2426,27 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Despejo por Inadimplemento | Habitação | Oposição | Penhora / Depósito/ Avaliação</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>28/09/2026 19:33</t>
+          <t>28/09/2026 19:53</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>28/09/2026 19:33</t>
+          <t>28/09/2026 19:53</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>29/09/2026 08:20</t>
+          <t>29/09/2026 06:30</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2463,37 +2463,37 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0089720-83.2025.8.16.0000</t>
+          <t>0018989-25.2022.8.16.0014</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Crimes do Sistema Nacional de Armas</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>09/12/2025</t>
+          <t>25/08/2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>25/09/2026 17:13</t>
+          <t>21/09/2026 18:13</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>25/09/2026 17:13</t>
+          <t>21/09/2026 18:13</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>29/09/2026 06:40</t>
+          <t>29/09/2026 06:20</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2510,37 +2510,37 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0097671-65.2024.8.16.0000</t>
+          <t>0019158-59.2015.8.16.0013</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Espécies de Contratos</t>
+          <t>Corrupção passiva | Crimes contra a Ordem Tributária</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>15/12/2025</t>
+          <t>31/03/2024</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>28/09/2026 16:53</t>
+          <t>24/09/2026 18:41</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>28/09/2026 16:53</t>
+          <t>09/03/2026 09:29</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>29/09/2026 07:20</t>
+          <t>29/09/2026 08:20</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2557,7 +2557,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0104756-39.2023.8.16.0000</t>
+          <t>0019842-08.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Espécies de Títulos de Crédito</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>29/09/2026 07:20</t>
+          <t>29/09/2026 07:40</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2604,7 +2604,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0116528-28.2025.8.16.0000</t>
+          <t>0019843-53.2022.8.16.0035</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2614,27 +2614,27 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Pagamento</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>11/12/2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>21/09/2026 16:55</t>
+          <t>21/09/2026 17:53</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>21/09/2026 16:55</t>
+          <t>21/09/2026 17:53</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>29/09/2026 08:00</t>
+          <t>29/09/2026 05:40</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2651,45 +2651,1925 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>0019858-22.2022.8.16.0035</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Pagamento</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>23/09/2025</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>28/09/2026 18:03</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>28/09/2026 18:03</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:40</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>0019932-08.2023.8.16.0014</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>11/09/2026 15:33</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>11/09/2026 15:33</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>24/09/2026 16:57</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>0021175-92.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Recuperação judicial e Falência | Concurso de Credores</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>08/12/2025</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>28/09/2026 18:23</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>28/09/2026 18:23</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:40</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>0021838-87.2014.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Moral | Obrigação de Fazer / Não Fazer</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>03/02/2026</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>21/09/2026 13:23</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>21/09/2026 13:23</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:20</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>0023032-64.2020.8.16.0017</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Direitos e Títulos de Crédito</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>04/06/2024</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>21/09/2026 18:33</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>21/09/2026 18:33</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:00</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>0024007-62.2023.8.16.0185</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Dívida Ativa (Execução Fiscal)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>21/09/2026 17:33</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>21/09/2026 17:33</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>29/09/2026 05:30</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>0025353-57.2025.8.16.0030</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Receptação Qualificada</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>28/09/2026 17:23</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>28/09/2026 17:23</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>29/09/2026 07:40</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>0026626-90.2023.8.16.0014</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Tratamento médico-hospitalar</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>03/12/2025</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>21/09/2026 17:43</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>21/09/2026 17:43</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:40</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>0027654-38.2023.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Restituição ao Erário | Dano ao Erário | Obrigação de Fazer / Não Fazer | Ônus da Prova | Violação dos Princípios Administrativos</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>19/05/2025</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>28/09/2026 16:03</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>28/09/2026 16:03</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>29/09/2026 08:20</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>0028703-46.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Espécies de Títulos de Crédito</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>28/09/2026 17:14</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>28/09/2026 17:14</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>29/09/2026 07:10</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>0033203-58.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>PIS/PASEP | Indenização por Dano Material | Práticas Abusivas</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>28/09/2026 17:53</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>28/09/2026 17:53</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>29/09/2026 07:10</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>0033286-91.2013.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Reivindicação | Pagamento</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>09/02/2022</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>28/09/2026 14:33</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>28/09/2026 14:33</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>29/09/2026 07:10</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>0033792-21.2023.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Tratamento médico-hospitalar | Obrigação de Fazer / Não Fazer</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>21/09/2026 17:23</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>21/09/2026 17:23</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:20</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>0034555-58.2019.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Seguro</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>11/03/2025</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>28/09/2026 17:03</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>28/09/2026 17:03</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>29/09/2026 08:20</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>0034821-55.2013.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Cédula de Crédito Bancário</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>10/12/2025</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>21/09/2026 18:13</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>21/09/2026 18:13</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>29/09/2026 05:07</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>0035579-85.2023.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Material</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>11/12/2024</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>28/09/2026 14:33</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>28/09/2026 14:33</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:00</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>0037028-51.2024.8.16.0030</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Crimes do Sistema Nacional de Armas</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>21/09/2026 14:03</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>21/09/2026 14:03</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>29/09/2026 07:10</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>0039377-54.2024.8.16.0021</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Rescisão / Resolução</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>29/01/2026</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>28/09/2026 21:33</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>28/09/2026 21:33</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:40</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>0041536-33.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Promessa de Compra e Venda</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>17/07/2025</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>21/09/2026 14:23</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>21/09/2026 14:23</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:00</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>0041752-57.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Dívida Ativa (Execução Fiscal)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>21/09/2026 18:23</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>21/09/2026 18:23</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>29/09/2026 08:30</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>0044419-16.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ingresso e Exclusão dos Sócios na Sociedade</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>21/09/2026 13:33</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>21/09/2026 13:33</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>29/09/2026 08:00</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>0049066-40.2014.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Seguro</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>22/10/2025</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>11/09/2026 13:23</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>11/09/2026 13:23</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>24/09/2026 17:01</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>0064910-44.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Práticas Abusivas</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>28/09/2026 21:23</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>28/09/2026 21:23</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>29/09/2026 04:21</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>0071691-82.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>PIS/PASEP | Indenização por Dano Material</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>23/07/2026</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>28/09/2026 16:03</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>28/09/2026 16:03</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>29/09/2026 07:40</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>0071839-30.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Contratos Bancários | Causas Supervenientes à Sentença</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>07/10/2025</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>28/09/2026 20:23</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>28/09/2026 20:23</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:50</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>0072736-29.2022.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Dano ao Erário | Violação dos Princípios Administrativos | Sobrestamento</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>13/03/2025</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>21/09/2026 19:03</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>21/09/2026 19:03</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>29/09/2026 07:50</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>0074926-28.2023.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Duplicata</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>05/09/2024</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>28/09/2026 18:53</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>28/09/2026 18:53</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:30</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>0077227-74.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Seguro</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>28/09/2026 19:33</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>28/09/2026 19:33</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>29/09/2026 08:20</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>0080070-80.2023.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Cédula de Crédito Bancário | Penhora / Depósito/ Avaliação</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>13/02/2025</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>28/09/2026 17:33</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>28/09/2026 17:33</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:10</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>0080573-04.2023.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Inventário e Partilha</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>13/11/2024</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>28/09/2026 14:13</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>28/09/2026 14:13</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:20</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>0082380-54.2026.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Recurso Ordinário em Habeas Corpus</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins | Prisão Preventiva | Cerceamento de Defesa | Promoção, constituição, financiamento ou integração de Organização Criminosa</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>23/09/2026 13:43</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>23/09/2026 13:43</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>29/09/2026 05:07</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>0092890-34.2023.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>24/01/2025</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>28/09/2026 13:33</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>28/09/2026 13:33</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:50</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>0097644-82.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Práticas Abusivas</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>16/12/2025</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>28/09/2026 19:53</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>28/09/2026 19:53</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:40</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>0097671-65.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Espécies de Contratos</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>15/12/2025</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>28/09/2026 16:53</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>28/09/2026 16:53</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>29/09/2026 07:20</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>0099078-09.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Confissão/Composição de Dívida</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>12/11/2025</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>21/09/2026 13:33</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>21/09/2026 13:33</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>29/09/2026 05:07</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>0101751-72.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Concessão</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>30/01/2026</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>28/09/2026 21:23</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>28/09/2026 21:23</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:40</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>0104756-39.2023.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Espécies de Títulos de Crédito</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>28/09/2026 14:33</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>28/09/2026 14:33</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>29/09/2026 07:20</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>0105320-13.2026.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Recurso Ordinário em Habeas Corpus</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>22/09/2026 17:13</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>22/09/2026 17:13</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:30</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>0116528-28.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>21/09/2026 16:55</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>21/09/2026 16:55</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>29/09/2026 08:00</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
           <t>0118791-67.2024.8.16.0000</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
         <is>
           <t>Cobrança | Obrigação de Fazer / Não Fazer</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>27/02/2026</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>21/09/2026 19:03</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>21/09/2026 19:03</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>29/09/2026 08:20</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>0123956-95.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Compromisso</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>28/09/2026 16:53</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>28/09/2026 16:53</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>29/09/2026 06:20</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>

--- a/docs/resultados.xlsx
+++ b/docs/resultados.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I88"/>
+  <dimension ref="A1:I101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
@@ -489,37 +489,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0000430-35.2006.8.16.0158</t>
+          <t>0007548-08.2009.8.16.0045</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Seguro | Vícios de Construção | Multa de 10% | Perito</t>
+          <t>Vícios de Construção | Seguro | Obrigação de Fazer / Não Fazer | Ônus da Prova | Legitimidade Ativa e Passiva</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>09/10/2024</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>28/09/2026 20:03</t>
+          <t>29/09/2026 14:53</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>28/09/2026 20:03</t>
+          <t>29/09/2026 14:53</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>29/09/2026 07:01</t>
+          <t>07/10/2026 06:19</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -536,7 +536,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0000502-33.1987.8.16.0014</t>
+          <t>0116457-60.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -546,27 +546,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Nota Promissória</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>16/07/2024</t>
+          <t>05/03/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>28/09/2026 15:23</t>
+          <t>28/09/2026 18:03</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>28/09/2026 15:23</t>
+          <t>28/09/2026 18:03</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>29/09/2026 07:20</t>
+          <t>07/10/2026 06:22</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -583,7 +583,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0000506-43.2019.8.16.0113</t>
+          <t>0005352-88.2017.8.16.0173</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -593,27 +593,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ICMS/Importação</t>
+          <t>Furto</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>30/12/1899</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>21/09/2026 14:43</t>
+          <t>06/10/2026 14:03</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>21/09/2026 14:43</t>
+          <t>06/10/2026 14:03</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>29/09/2026 08:40</t>
+          <t>07/10/2026 06:22</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,7 +630,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0000507-35.2021.8.16.0185</t>
+          <t>0001384-29.2018.8.16.0104</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -640,27 +640,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Concurso de Credores</t>
+          <t>Execução Contratual</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>27/05/2025</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>28/09/2026 16:53</t>
+          <t>06/10/2026 16:03</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>28/09/2026 16:53</t>
+          <t>06/10/2026 16:03</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>29/09/2026 05:30</t>
+          <t>07/10/2026 06:22</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -677,7 +677,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0000733-34.2024.8.16.0056</t>
+          <t>0012385-53.2017.8.16.0069</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -687,27 +687,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Rescisão / Resolução</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/11/2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>28/09/2026 19:33</t>
+          <t>28/09/2026 16:43</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>28/09/2026 19:33</t>
+          <t>28/09/2026 16:43</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>29/09/2026 06:30</t>
+          <t>07/10/2026 06:22</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -724,7 +724,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0001054-57.2022.8.16.0115</t>
+          <t>0001357-42.2021.8.16.0136</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -734,27 +734,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Promessa de Compra e Venda | Obrigação de Fazer / Não Fazer</t>
+          <t>Receptação</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>28/09/2026 14:53</t>
+          <t>06/10/2026 15:23</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>28/09/2026 14:53</t>
+          <t>06/10/2026 15:23</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>29/09/2026 06:30</t>
+          <t>07/10/2026 06:32</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -771,37 +771,37 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0001127-42.2008.8.16.0043</t>
+          <t>0001036-16.2024.8.16.0196</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Tráfico de Drogas e Condutas Afins | Aplicação da Pena</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>28/09/2026 16:23</t>
+          <t>02/10/2026 07:12</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>28/09/2026 16:23</t>
+          <t>02/10/2026 07:12</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>29/09/2026 05:40</t>
+          <t>07/10/2026 06:32</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -818,37 +818,37 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0001238-65.2016.8.16.0004</t>
+          <t>0123956-95.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Prestação de Serviços | Rescisão / Resolução | Perdas e Danos</t>
+          <t>Compromisso</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>26/10/2021</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>28/09/2026 15:43</t>
+          <t>28/09/2026 16:53</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>28/09/2026 15:43</t>
+          <t>28/09/2026 16:53</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>29/09/2026 07:10</t>
+          <t>07/10/2026 06:09</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -865,37 +865,37 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0001665-20.2022.8.16.0047</t>
+          <t>0014138-79.2022.8.16.0001</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Alienação Fiduciária</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>23/07/2025</t>
+          <t>12/01/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>28/09/2026 14:03</t>
+          <t>28/09/2026 17:33</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>28/09/2026 14:03</t>
+          <t>28/09/2026 17:33</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>29/09/2026 06:40</t>
+          <t>07/10/2026 06:09</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -912,7 +912,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0001837-98.2025.8.16.0097</t>
+          <t>0009159-43.2020.8.16.0131</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -922,27 +922,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Adimplemento e Extinção | Bem de Família (Voluntário)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>18/06/2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>22/09/2026 14:53</t>
+          <t>28/09/2026 18:13</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>22/09/2026 14:53</t>
+          <t>28/09/2026 18:13</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>29/09/2026 05:50</t>
+          <t>07/10/2026 06:09</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0002148-65.2020.8.16.0194</t>
+          <t>0003416-16.2024.8.16.0033</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -969,27 +969,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Produto Impróprio</t>
+          <t>Práticas Abusivas</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>01/10/2025</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>21/09/2026 17:23</t>
+          <t>06/10/2026 16:03</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>21/09/2026 17:23</t>
+          <t>06/10/2026 16:03</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>29/09/2026 07:01</t>
+          <t>07/10/2026 06:11</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1006,37 +1006,37 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0002202-63.2019.8.16.0130</t>
+          <t>0033286-91.2013.8.16.0001</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bem de Família (Voluntário)</t>
+          <t>Reivindicação | Pagamento</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/02/2022</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>28/09/2026 14:53</t>
+          <t>28/09/2026 14:33</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>28/09/2026 14:53</t>
+          <t>28/09/2026 14:33</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>29/09/2026 06:50</t>
+          <t>07/10/2026 05:40</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1053,7 +1053,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0002235-20.2023.8.16.0128</t>
+          <t>0048696-67.2024.8.16.0014</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1063,27 +1063,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bancários</t>
+          <t>Cessão de Crédito | Causas Supervenientes à Sentença</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>03/12/2025</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>21/09/2026 14:03</t>
+          <t>02/10/2026 15:23</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>21/09/2026 14:03</t>
+          <t>02/10/2026 15:23</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>29/09/2026 07:20</t>
+          <t>07/10/2026 05:43</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0002351-37.2009.8.16.0089</t>
+          <t>0001127-42.2008.8.16.0043</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1110,27 +1110,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>28/09/2026 19:23</t>
+          <t>28/09/2026 16:23</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>28/09/2026 19:23</t>
+          <t>28/09/2026 16:23</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>29/09/2026 05:50</t>
+          <t>07/10/2026 05:43</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1147,37 +1147,37 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0002488-84.2023.8.16.0038</t>
+          <t>0001866-46.2025.8.16.0131</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Alienação Fiduciária</t>
+          <t>Restituição de Coisas Apreendidas | Crimes do Sistema Nacional de Armas | Receptação | Adulteração de Sinal Identificador de Veículo Automotor</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>21/09/2026 13:33</t>
+          <t>06/10/2026 13:13</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>21/09/2026 13:33</t>
+          <t>06/10/2026 13:13</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>29/09/2026 06:20</t>
+          <t>07/10/2026 05:43</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1194,37 +1194,37 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0003162-36.2023.8.16.0079</t>
+          <t>0035579-85.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Práticas Abusivas</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>30/01/2026</t>
+          <t>11/12/2024</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>28/09/2026 19:53</t>
+          <t>28/09/2026 14:33</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>28/09/2026 19:53</t>
+          <t>28/09/2026 14:33</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>29/09/2026 07:40</t>
+          <t>07/10/2026 05:43</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1241,37 +1241,37 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0003205-60.2025.8.16.0189</t>
+          <t>0010353-10.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lesão Cometida em Razão da Condição de Mulher</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>21/09/2026 17:53</t>
+          <t>28/09/2026 17:33</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>21/09/2026 17:53</t>
+          <t>28/09/2026 17:33</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>29/09/2026 06:00</t>
+          <t>07/10/2026 05:43</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1288,7 +1288,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0003306-75.2016.8.16.0072</t>
+          <t>4001568-46.2025.8.16.0014</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1298,27 +1298,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Saneamento</t>
+          <t>Falta Grave | Roubo Majorado</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>02/09/2025</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>21/09/2026 13:53</t>
+          <t>06/10/2026 16:23</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>21/09/2026 13:53</t>
+          <t>06/10/2026 16:23</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>29/09/2026 06:40</t>
+          <t>07/10/2026 05:52</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1335,7 +1335,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0003984-61.2020.8.16.0004</t>
+          <t>0071691-82.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1345,27 +1345,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Indenização por Dano Material</t>
+          <t>PIS/PASEP | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>21/09/2026 14:53</t>
+          <t>28/09/2026 16:03</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>21/09/2026 14:53</t>
+          <t>28/09/2026 16:03</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>29/09/2026 07:40</t>
+          <t>07/10/2026 05:52</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1382,37 +1382,37 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0004330-27.2024.8.16.0083</t>
+          <t>0087707-77.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Furto Qualificado</t>
+          <t>Tráfico de Drogas e Condutas Afins | Adulteração de Sinal Identificador de Veículo Automotor</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>11/09/2026 14:13</t>
+          <t>06/10/2026 13:03</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>11/09/2026 14:13</t>
+          <t>06/10/2026 13:03</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>24/09/2026 17:10</t>
+          <t>07/10/2026 05:52</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1429,7 +1429,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0004576-62.2021.8.16.0104</t>
+          <t>0007498-89.2023.8.16.0174</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1439,27 +1439,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Parceria Agrícola e/ou pecuária</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>26/01/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>28/09/2026 18:23</t>
+          <t>06/10/2026 13:13</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>28/09/2026 18:23</t>
+          <t>06/10/2026 13:13</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>29/09/2026 08:00</t>
+          <t>07/10/2026 05:52</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1476,7 +1476,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0004635-66.2024.8.16.0194</t>
+          <t>0027654-38.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1486,27 +1486,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Desenho Industrial | Perdas e Danos</t>
+          <t>Restituição ao Erário | Dano ao Erário | Obrigação de Fazer / Não Fazer | Ônus da Prova | Violação dos Princípios Administrativos</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>25/03/2025</t>
+          <t>19/05/2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>21/09/2026 15:43</t>
+          <t>28/09/2026 16:03</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>21/09/2026 15:43</t>
+          <t>28/09/2026 16:03</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>29/09/2026 07:50</t>
+          <t>07/10/2026 05:52</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1523,7 +1523,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0004667-84.2009.8.16.0004</t>
+          <t>0011485-52.2015.8.16.0033</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1533,27 +1533,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Contratos Bancários | Pagamento em Consignação</t>
+          <t>Sustação de Protesto</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>09/11/2019</t>
+          <t>05/09/2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>21/09/2026 17:53</t>
+          <t>28/09/2026 13:33</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>21/09/2026 17:53</t>
+          <t>28/09/2026 13:33</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>29/09/2026 06:30</t>
+          <t>07/10/2026 05:52</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1570,7 +1570,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0005096-84.2024.8.16.0017</t>
+          <t>0001665-20.2022.8.16.0047</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1580,27 +1580,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>23/07/2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>23/09/2026 05:23</t>
+          <t>28/09/2026 14:03</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>23/09/2026 05:23</t>
+          <t>28/09/2026 14:03</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>24/09/2026 16:51</t>
+          <t>07/10/2026 05:55</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1617,7 +1617,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0005532-90.2023.8.16.0045</t>
+          <t>0016917-05.2024.8.16.0173</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1632,22 +1632,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>25/02/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>14/09/2026 13:23</t>
+          <t>06/10/2026 14:43</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>14/09/2026 13:23</t>
+          <t>06/10/2026 14:43</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>24/09/2026 17:21</t>
+          <t>07/10/2026 06:03</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1664,37 +1664,37 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0005644-69.2025.8.16.0116</t>
+          <t>0065426-64.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Mandado de Segurança</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Compra e Venda</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>01/12/2025</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>28/09/2026 18:43</t>
+          <t>05/10/2026 14:03</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>28/09/2026 18:43</t>
+          <t>05/10/2026 14:03</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>29/09/2026 07:30</t>
+          <t>07/10/2026 04:43</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0005863-05.2022.8.16.0014</t>
+          <t>0006182-72.2025.8.16.0044</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1721,27 +1721,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Compra e Venda | Indenização por Dano Moral | Indenização por Dano Material | Defeito, nulidade ou anulação</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>26/01/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>21/09/2026 18:03</t>
+          <t>06/10/2026 15:03</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>21/09/2026 18:03</t>
+          <t>06/10/2026 15:03</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>29/09/2026 07:10</t>
+          <t>07/10/2026 04:43</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1758,37 +1758,37 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0006563-78.2022.8.16.0014</t>
+          <t>0000563-56.2024.8.16.0155</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Compra e Venda</t>
+          <t>Adulteração de Sinal Identificador de Veículo Automotor</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>28/09/2026 20:23</t>
+          <t>06/10/2026 14:03</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>28/09/2026 20:23</t>
+          <t>06/10/2026 14:03</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>29/09/2026 06:50</t>
+          <t>07/10/2026 04:46</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1805,7 +1805,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0006648-82.2017.8.16.0194</t>
+          <t>0001238-65.2016.8.16.0004</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1815,27 +1815,27 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Prestação de Serviços | Rescisão / Resolução | Perdas e Danos</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>10/10/2024</t>
+          <t>26/10/2021</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>28/09/2026 13:43</t>
+          <t>28/09/2026 15:43</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>28/09/2026 13:43</t>
+          <t>28/09/2026 15:43</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>29/09/2026 08:00</t>
+          <t>07/10/2026 04:46</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1852,7 +1852,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0009159-43.2020.8.16.0131</t>
+          <t>0010005-48.2023.8.16.0004</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1862,27 +1862,27 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Adimplemento e Extinção | Bem de Família (Voluntário)</t>
+          <t>Servidores Inativos</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>18/06/2025</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>28/09/2026 18:13</t>
+          <t>02/10/2026 13:33</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>28/09/2026 18:13</t>
+          <t>02/10/2026 13:33</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>29/09/2026 06:00</t>
+          <t>07/10/2026 04:32</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1899,7 +1899,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0009195-17.2025.8.16.0000</t>
+          <t>0004994-55.2020.8.16.0194</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1909,27 +1909,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Indenização por Dano Material | Prestação de Serviços | Obrigação de Fazer / Não Fazer | Indenização por Dano Moral | Ônus da Prova | Inadimplemento</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>04/02/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>28/09/2026 19:53</t>
+          <t>28/09/2026 14:53</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>28/09/2026 19:53</t>
+          <t>28/09/2026 14:53</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>29/09/2026 08:20</t>
+          <t>07/10/2026 04:32</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1946,7 +1946,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0009337-85.2022.8.16.0045</t>
+          <t>0058493-75.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1956,27 +1956,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Desconsideração da Personalidade Jurídica | Defeito, nulidade ou anulação | Embargos de Terceiro | Penhora / Depósito/ Avaliação</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>05/05/2025</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>28/09/2026 16:33</t>
+          <t>28/09/2026 16:53</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>28/09/2026 16:33</t>
+          <t>28/09/2026 16:53</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>29/09/2026 07:10</t>
+          <t>07/10/2026 04:32</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0010353-10.2025.8.16.0000</t>
+          <t>0002467-70.2023.8.16.0083</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2003,27 +2003,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Homicídio Qualificado | Promoção, constituição, financiamento ou integração de Organização Criminosa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>28/09/2026 17:33</t>
+          <t>06/10/2026 16:03</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>28/09/2026 17:33</t>
+          <t>06/10/2026 16:03</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>29/09/2026 06:20</t>
+          <t>07/10/2026 04:32</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2040,7 +2040,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0011426-17.2025.8.16.0000</t>
+          <t>0000502-33.1987.8.16.0014</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2050,27 +2050,27 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Indenização por Dano Material</t>
+          <t>Nota Promissória</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>16/07/2024</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>28/09/2026 20:23</t>
+          <t>28/09/2026 15:23</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>28/09/2026 20:23</t>
+          <t>28/09/2026 15:23</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>29/09/2026 05:50</t>
+          <t>07/10/2026 04:32</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2087,37 +2087,37 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0011485-52.2015.8.16.0033</t>
+          <t>0025353-57.2025.8.16.0030</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sustação de Protesto</t>
+          <t>Receptação Qualificada</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>05/09/2025</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>28/09/2026 13:33</t>
+          <t>28/09/2026 17:23</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>28/09/2026 13:33</t>
+          <t>28/09/2026 17:23</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>29/09/2026 08:20</t>
+          <t>07/10/2026 04:32</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2134,7 +2134,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0012346-88.2025.8.16.0000</t>
+          <t>0080070-80.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2144,27 +2144,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Despesas Condominiais</t>
+          <t>Cédula de Crédito Bancário | Penhora / Depósito/ Avaliação</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>13/02/2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>28/09/2026 20:53</t>
+          <t>28/09/2026 17:33</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>28/09/2026 20:53</t>
+          <t>28/09/2026 17:33</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>29/09/2026 06:30</t>
+          <t>07/10/2026 04:34</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2181,7 +2181,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0012385-53.2017.8.16.0069</t>
+          <t>0001054-57.2022.8.16.0115</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2191,27 +2191,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Rescisão / Resolução</t>
+          <t>Promessa de Compra e Venda | Obrigação de Fazer / Não Fazer</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>26/11/2025</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>28/09/2026 16:43</t>
+          <t>28/09/2026 14:53</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>28/09/2026 16:43</t>
+          <t>28/09/2026 14:53</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>29/09/2026 05:07</t>
+          <t>07/10/2026 04:34</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2228,37 +2228,37 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0012511-74.2015.8.16.0069</t>
+          <t>0005561-08.2025.8.16.0131</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Aposentadoria Especial (Art. 57/8)</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>14/09/2026 13:53</t>
+          <t>06/10/2026 13:03</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>14/09/2026 13:53</t>
+          <t>06/10/2026 13:03</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>24/09/2026 17:10</t>
+          <t>07/10/2026 04:01</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2275,37 +2275,37 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0012627-78.2024.8.16.0000</t>
+          <t>0000733-34.2024.8.16.0056</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Despesas Condominiais | Condomínio em Edifício</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>18/11/2024</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>28/09/2026 21:33</t>
+          <t>28/09/2026 19:33</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>28/09/2026 21:33</t>
+          <t>28/09/2026 19:33</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>29/09/2026 06:40</t>
+          <t>07/10/2026 04:04</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2322,37 +2322,37 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0014041-70.2018.8.16.0017</t>
+          <t>0007491-72.2022.8.16.0129</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Cobrança de Aluguéis - Sem despejo</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>09/02/2022</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>21/09/2026 17:53</t>
+          <t>06/10/2026 10:07</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>21/09/2026 17:53</t>
+          <t>06/10/2026 10:07</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>29/09/2026 08:40</t>
+          <t>07/10/2026 04:04</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2369,37 +2369,37 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0014138-79.2022.8.16.0001</t>
+          <t>0075408-05.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Alienação Fiduciária</t>
+          <t>Prestação de Serviços | Efeito Suspensivo / Impugnação / Embargos à Execução | Prescrição e Decadência</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>12/01/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>28/09/2026 17:33</t>
+          <t>28/09/2026 16:23</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>28/09/2026 17:33</t>
+          <t>28/09/2026 16:23</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>29/09/2026 06:00</t>
+          <t>07/10/2026 04:04</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2416,7 +2416,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0017353-44.2024.8.16.0017</t>
+          <t>0104756-39.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2426,27 +2426,27 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Despejo por Inadimplemento | Habitação | Oposição | Penhora / Depósito/ Avaliação</t>
+          <t>Espécies de Títulos de Crédito</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>28/09/2026 19:53</t>
+          <t>28/09/2026 14:33</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>28/09/2026 19:53</t>
+          <t>28/09/2026 14:33</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>29/09/2026 06:30</t>
+          <t>07/10/2026 04:04</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2463,7 +2463,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0018989-25.2022.8.16.0014</t>
+          <t>0097671-65.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2473,27 +2473,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Espécies de Contratos</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>25/08/2025</t>
+          <t>15/12/2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>21/09/2026 18:13</t>
+          <t>28/09/2026 16:53</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>21/09/2026 18:13</t>
+          <t>28/09/2026 16:53</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>29/09/2026 06:20</t>
+          <t>07/10/2026 04:04</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2510,7 +2510,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0019158-59.2015.8.16.0013</t>
+          <t>0006648-82.2017.8.16.0194</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2520,27 +2520,27 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Corrupção passiva | Crimes contra a Ordem Tributária</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>31/03/2024</t>
+          <t>10/10/2024</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>24/09/2026 18:41</t>
+          <t>28/09/2026 13:43</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>09/03/2026 09:29</t>
+          <t>28/09/2026 13:43</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>29/09/2026 08:20</t>
+          <t>07/10/2026 04:17</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2557,7 +2557,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0019842-08.2024.8.16.0000</t>
+          <t>0004576-62.2021.8.16.0104</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2567,27 +2567,27 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Parceria Agrícola e/ou pecuária</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>26/01/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>28/09/2026 14:33</t>
+          <t>28/09/2026 18:23</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>28/09/2026 14:33</t>
+          <t>28/09/2026 18:23</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>29/09/2026 07:40</t>
+          <t>07/10/2026 04:17</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2604,7 +2604,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0019843-53.2022.8.16.0035</t>
+          <t>0000240-03.2021.8.16.0108</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2614,27 +2614,27 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Pagamento</t>
+          <t>Apropriação indébita</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>11/12/2025</t>
+          <t>20/01/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>21/09/2026 17:53</t>
+          <t>06/10/2026 16:03</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>21/09/2026 17:53</t>
+          <t>06/10/2026 16:03</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>29/09/2026 05:40</t>
+          <t>07/10/2026 04:17</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2651,7 +2651,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0019858-22.2022.8.16.0035</t>
+          <t>0043698-98.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2661,27 +2661,27 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Pagamento</t>
+          <t>Crimes da Lei de licitações</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>23/09/2025</t>
+          <t>02/10/2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>28/09/2026 18:03</t>
+          <t>06/10/2026 13:03</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>28/09/2026 18:03</t>
+          <t>06/10/2026 13:03</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>29/09/2026 06:40</t>
+          <t>07/10/2026 04:20</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2698,37 +2698,37 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0019932-08.2023.8.16.0014</t>
+          <t>0080573-04.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Inventário e Partilha</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>13/11/2024</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>11/09/2026 15:33</t>
+          <t>28/09/2026 14:13</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>11/09/2026 15:33</t>
+          <t>28/09/2026 14:13</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>24/09/2026 16:57</t>
+          <t>07/10/2026 04:20</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2745,37 +2745,37 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0021175-92.2024.8.16.0000</t>
+          <t>0019221-37.2022.8.16.0014</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Recuperação judicial e Falência | Concurso de Credores</t>
+          <t>ICMS/ Imposto sobre Circulação de Mercadorias</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>08/12/2025</t>
+          <t>25/09/2024</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>28/09/2026 18:23</t>
+          <t>09/09/2026 14:42</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>28/09/2026 18:23</t>
+          <t>09/09/2026 14:42</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>29/09/2026 06:40</t>
+          <t>23/09/2026 03:40</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2792,7 +2792,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0021838-87.2014.8.16.0001</t>
+          <t>0113231-47.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2802,27 +2802,27 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Obrigação de Fazer / Não Fazer</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>03/02/2026</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>21/09/2026 13:23</t>
+          <t>09/09/2026 21:03</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>21/09/2026 13:23</t>
+          <t>09/09/2026 21:03</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>29/09/2026 06:20</t>
+          <t>23/09/2026 04:30</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2839,7 +2839,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0023032-64.2020.8.16.0017</t>
+          <t>0000431-42.2024.8.16.0173</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2849,27 +2849,27 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Direitos e Títulos de Crédito</t>
+          <t>Inclusão Indevida em Cadastro de Inadimplentes</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>04/06/2024</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>21/09/2026 18:33</t>
+          <t>10/09/2026 13:43</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>21/09/2026 18:33</t>
+          <t>10/09/2026 13:43</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>29/09/2026 06:00</t>
+          <t>23/09/2026 04:50</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2886,37 +2886,37 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0024007-62.2023.8.16.0185</t>
+          <t>0004811-97.2020.8.16.0028</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>21/09/2026 17:33</t>
+          <t>09/09/2026 20:23</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>21/09/2026 17:33</t>
+          <t>09/09/2026 20:23</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>29/09/2026 05:30</t>
+          <t>23/09/2026 05:00</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2933,37 +2933,37 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0025353-57.2025.8.16.0030</t>
+          <t>0000517-06.2019.8.16.0038</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Receptação Qualificada</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>28/09/2026 17:23</t>
+          <t>10/09/2026 14:33</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>28/09/2026 17:23</t>
+          <t>10/09/2026 14:33</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>29/09/2026 07:40</t>
+          <t>23/09/2026 05:30</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2980,7 +2980,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0026626-90.2023.8.16.0014</t>
+          <t>0008741-35.2019.8.16.0004</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2990,27 +2990,27 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Tratamento médico-hospitalar</t>
+          <t>Enriquecimento ilícito | Dano ao Erário | Violação dos Princípios Administrativos | Obrigação de Fazer / Não Fazer | Ônus da Prova</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>03/12/2025</t>
+          <t>07/10/2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>21/09/2026 17:43</t>
+          <t>10/09/2026 13:13</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>21/09/2026 17:43</t>
+          <t>10/09/2026 13:13</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>29/09/2026 06:40</t>
+          <t>23/09/2026 06:10</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3027,7 +3027,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0027654-38.2023.8.16.0000</t>
+          <t>0058476-39.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3037,27 +3037,27 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Restituição ao Erário | Dano ao Erário | Obrigação de Fazer / Não Fazer | Ônus da Prova | Violação dos Princípios Administrativos</t>
+          <t>Cobrança | Legitimidade</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>19/05/2025</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>28/09/2026 16:03</t>
+          <t>10/09/2026 13:33</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>28/09/2026 16:03</t>
+          <t>10/09/2026 13:33</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>29/09/2026 08:20</t>
+          <t>23/09/2026 06:10</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3074,37 +3074,37 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0028703-46.2025.8.16.0000</t>
+          <t>0010091-86.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Pedido de Uniformização de Interpretação de Lei Criminal</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Espécies de Títulos de Crédito</t>
+          <t>Adicional de Periculosidade</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>28/09/2026 17:14</t>
+          <t>14/09/2026 14:43</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>28/09/2026 17:14</t>
+          <t>14/09/2026 14:43</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>29/09/2026 07:10</t>
+          <t>23/09/2026 06:20</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3121,37 +3121,37 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0033203-58.2025.8.16.0000</t>
+          <t>0017381-10.2017.8.16.0000</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>PIS/PASEP | Indenização por Dano Material | Práticas Abusivas</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>13/08/2018</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>28/09/2026 17:53</t>
+          <t>09/09/2026 21:23</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>28/09/2026 17:53</t>
+          <t>09/09/2026 21:23</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>29/09/2026 07:10</t>
+          <t>23/09/2026 06:20</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3168,7 +3168,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0033286-91.2013.8.16.0001</t>
+          <t>0001990-08.2020.8.16.0033</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3178,27 +3178,27 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Reivindicação | Pagamento</t>
+          <t>Consórcio</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>09/02/2022</t>
+          <t>12/03/2025</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>28/09/2026 14:33</t>
+          <t>09/09/2026 20:23</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>28/09/2026 14:33</t>
+          <t>09/09/2026 20:23</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>29/09/2026 07:10</t>
+          <t>23/09/2026 06:30</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3215,37 +3215,37 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0033792-21.2023.8.16.0000</t>
+          <t>0005631-18.2021.8.16.0017</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Tratamento médico-hospitalar | Obrigação de Fazer / Não Fazer</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>21/08/2024</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>21/09/2026 17:23</t>
+          <t>09/09/2026 20:23</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>21/09/2026 17:23</t>
+          <t>09/09/2026 20:23</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>29/09/2026 06:20</t>
+          <t>23/09/2026 06:50</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3262,37 +3262,37 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0034555-58.2019.8.16.0001</t>
+          <t>0013451-44.2014.8.16.0014</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Acidente de Trânsito | Acidente de Trânsito</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>29/06/2022</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>28/09/2026 17:03</t>
+          <t>10/09/2026 13:33</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>28/09/2026 17:03</t>
+          <t>10/09/2026 13:33</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>29/09/2026 08:20</t>
+          <t>23/09/2026 07:00</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3309,7 +3309,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0034821-55.2013.8.16.0001</t>
+          <t>0009379-59.2011.8.16.0033</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3319,27 +3319,27 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Compra e Venda</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>10/12/2025</t>
+          <t>17/07/2023</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>21/09/2026 18:13</t>
+          <t>09/09/2026 20:23</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>21/09/2026 18:13</t>
+          <t>09/09/2026 20:23</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>29/09/2026 05:07</t>
+          <t>23/09/2026 07:30</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3356,37 +3356,37 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0035579-85.2023.8.16.0000</t>
+          <t>0005532-20.2009.8.16.0130</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Dano ao Erário</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>11/12/2024</t>
+          <t>29/06/2021</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>28/09/2026 14:33</t>
+          <t>09/09/2026 14:43</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>28/09/2026 14:33</t>
+          <t>09/09/2026 14:43</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>29/09/2026 06:00</t>
+          <t>23/09/2026 07:50</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3403,37 +3403,37 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0037028-51.2024.8.16.0030</t>
+          <t>0019932-08.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Crimes do Sistema Nacional de Armas</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>21/09/2026 14:03</t>
+          <t>11/09/2026 15:33</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>21/09/2026 14:03</t>
+          <t>11/09/2026 15:33</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>29/09/2026 07:10</t>
+          <t>24/09/2026 16:57</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3450,37 +3450,37 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0039377-54.2024.8.16.0021</t>
+          <t>0049066-40.2014.8.16.0000</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Rescisão / Resolução</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
+          <t>22/10/2025</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>28/09/2026 21:33</t>
+          <t>11/09/2026 13:23</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>28/09/2026 21:33</t>
+          <t>11/09/2026 13:23</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>29/09/2026 06:40</t>
+          <t>24/09/2026 17:01</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3497,7 +3497,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0041536-33.2024.8.16.0000</t>
+          <t>0012511-74.2015.8.16.0069</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3507,27 +3507,27 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Promessa de Compra e Venda</t>
+          <t>Aposentadoria Especial (Art. 57/8)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>17/07/2025</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>21/09/2026 14:23</t>
+          <t>14/09/2026 13:53</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>21/09/2026 14:23</t>
+          <t>14/09/2026 13:53</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>29/09/2026 06:00</t>
+          <t>24/09/2026 17:10</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3544,37 +3544,37 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0041752-57.2025.8.16.0000</t>
+          <t>0004330-27.2024.8.16.0083</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>Furto Qualificado</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>21/09/2026 18:23</t>
+          <t>11/09/2026 14:13</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>21/09/2026 18:23</t>
+          <t>11/09/2026 14:13</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>29/09/2026 08:30</t>
+          <t>24/09/2026 17:10</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3591,7 +3591,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0044419-16.2025.8.16.0000</t>
+          <t>0005532-90.2023.8.16.0045</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3601,27 +3601,27 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ingresso e Exclusão dos Sócios na Sociedade</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>25/02/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>21/09/2026 13:33</t>
+          <t>14/09/2026 13:23</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>21/09/2026 13:33</t>
+          <t>14/09/2026 13:23</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>29/09/2026 08:00</t>
+          <t>24/09/2026 17:21</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3638,37 +3638,37 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0049066-40.2014.8.16.0000</t>
+          <t>0007836-93.2021.8.16.0025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Horas Extras</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>22/10/2025</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>11/09/2026 13:23</t>
+          <t>10/09/2026 17:23</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>11/09/2026 13:23</t>
+          <t>10/09/2026 17:23</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>24/09/2026 17:01</t>
+          <t>24/09/2026 17:21</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3685,7 +3685,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0064910-44.2025.8.16.0000</t>
+          <t>0003812-81.2020.8.16.0146</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3695,27 +3695,27 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Práticas Abusivas</t>
+          <t>Arrendamento Rural | Liminar</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>28/08/2024</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>28/09/2026 21:23</t>
+          <t>11/09/2026 15:13</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>28/09/2026 21:23</t>
+          <t>11/09/2026 15:13</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>29/09/2026 04:21</t>
+          <t>24/09/2026 17:37</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3732,37 +3732,37 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0071691-82.2025.8.16.0000</t>
+          <t>0013782-02.2023.8.16.0017</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>PIS/PASEP | Indenização por Dano Material</t>
+          <t>Receptação | Adulteração de Sinal Identificador de Veículo Automotor | Crimes do Sistema Nacional de Armas</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>28/09/2026 16:03</t>
+          <t>11/09/2026 14:53</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>28/09/2026 16:03</t>
+          <t>11/09/2026 14:53</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>29/09/2026 07:40</t>
+          <t>24/09/2026 17:37</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3779,7 +3779,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0071839-30.2024.8.16.0000</t>
+          <t>0007613-79.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3789,27 +3789,27 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Contratos Bancários | Causas Supervenientes à Sentença</t>
+          <t>Indenização por Dano Moral | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>07/10/2025</t>
+          <t>05/03/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>28/09/2026 20:23</t>
+          <t>11/09/2026 13:13</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>28/09/2026 20:23</t>
+          <t>11/09/2026 13:13</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>29/09/2026 06:50</t>
+          <t>24/09/2026 17:39</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3826,7 +3826,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0072736-29.2022.8.16.0000</t>
+          <t>0053296-42.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3836,27 +3836,27 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dano ao Erário | Violação dos Princípios Administrativos | Sobrestamento</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>13/03/2025</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>21/09/2026 19:03</t>
+          <t>10/09/2026 15:43</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>21/09/2026 19:03</t>
+          <t>10/09/2026 15:43</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>29/09/2026 07:50</t>
+          <t>24/09/2026 17:44</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3873,37 +3873,37 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0074926-28.2023.8.16.0000</t>
+          <t>0027375-64.2010.8.16.0014</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Duplicata</t>
+          <t>Exclusão - ICMS</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>05/09/2024</t>
+          <t>22/03/2024</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>28/09/2026 18:53</t>
+          <t>10/09/2026 16:43</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>28/09/2026 18:53</t>
+          <t>10/09/2026 16:43</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>29/09/2026 06:30</t>
+          <t>24/09/2026 17:44</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3920,7 +3920,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0077227-74.2025.8.16.0000</t>
+          <t>0000318-92.2023.8.16.0086</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3930,27 +3930,27 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>28/09/2026 19:33</t>
+          <t>11/09/2026 15:13</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>28/09/2026 19:33</t>
+          <t>11/09/2026 15:13</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>29/09/2026 08:20</t>
+          <t>24/09/2026 17:45</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3967,7 +3967,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0080070-80.2023.8.16.0000</t>
+          <t>0028232-46.2020.8.16.0019</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3977,27 +3977,27 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário | Penhora / Depósito/ Avaliação</t>
+          <t>Homicídio Qualificado</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>13/02/2025</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>28/09/2026 17:33</t>
+          <t>14/09/2026 14:23</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>28/09/2026 17:33</t>
+          <t>14/09/2026 14:23</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>29/09/2026 06:10</t>
+          <t>24/09/2026 17:45</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -4014,37 +4014,37 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0080573-04.2023.8.16.0000</t>
+          <t>0050674-53.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Inventário e Partilha</t>
+          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>13/11/2024</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>28/09/2026 14:13</t>
+          <t>22/09/2026 14:33</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>28/09/2026 14:13</t>
+          <t>22/09/2026 14:33</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>29/09/2026 06:20</t>
+          <t>24/09/2026 17:45</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4061,37 +4061,37 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0082380-54.2026.8.16.0000</t>
+          <t>0001251-11.2022.8.16.0180</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins | Prisão Preventiva | Cerceamento de Defesa | Promoção, constituição, financiamento ou integração de Organização Criminosa</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>23/09/2026 13:43</t>
+          <t>10/09/2026 17:33</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>23/09/2026 13:43</t>
+          <t>10/09/2026 17:33</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>29/09/2026 05:07</t>
+          <t>24/09/2026 17:56</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -4108,7 +4108,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0092890-34.2023.8.16.0000</t>
+          <t>0002655-82.2023.8.16.0109</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4118,27 +4118,27 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Espécies de Contratos</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>24/01/2025</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>28/09/2026 13:33</t>
+          <t>10/09/2026 16:03</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>28/09/2026 13:33</t>
+          <t>10/09/2026 16:03</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>29/09/2026 06:50</t>
+          <t>24/09/2026 17:58</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4155,7 +4155,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0097644-82.2024.8.16.0000</t>
+          <t>0001243-96.2023.8.16.0148</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4165,27 +4165,27 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Práticas Abusivas</t>
+          <t>Indenização por Dano Moral | Liminar | Indenização por Dano Material | Obrigação de Fazer / Não Fazer</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>28/09/2026 19:53</t>
+          <t>14/09/2026 13:23</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>28/09/2026 19:53</t>
+          <t>14/09/2026 13:23</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>29/09/2026 06:40</t>
+          <t>24/09/2026 18:03</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4202,7 +4202,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0097671-65.2024.8.16.0000</t>
+          <t>0006358-21.2024.8.16.0130</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4212,27 +4212,27 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Espécies de Contratos</t>
+          <t>Práticas Abusivas</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>15/12/2025</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>28/09/2026 16:53</t>
+          <t>10/09/2026 16:13</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>28/09/2026 16:53</t>
+          <t>10/09/2026 16:13</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>29/09/2026 07:20</t>
+          <t>24/09/2026 18:03</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4249,7 +4249,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0099078-09.2024.8.16.0000</t>
+          <t>0049197-29.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4259,27 +4259,27 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Confissão/Composição de Dívida</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>21/09/2026 13:33</t>
+          <t>10/09/2026 16:33</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>21/09/2026 13:33</t>
+          <t>10/09/2026 16:33</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>29/09/2026 05:07</t>
+          <t>24/09/2026 18:03</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4296,7 +4296,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0101751-72.2024.8.16.0000</t>
+          <t>0087191-28.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4306,27 +4306,27 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Concessão</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>30/01/2026</t>
+          <t>09/02/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>28/09/2026 21:23</t>
+          <t>11/09/2026 14:33</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>28/09/2026 21:23</t>
+          <t>11/09/2026 14:33</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>29/09/2026 06:40</t>
+          <t>24/09/2026 18:07</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4343,7 +4343,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0104756-39.2023.8.16.0000</t>
+          <t>0040364-56.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4353,27 +4353,27 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Espécies de Títulos de Crédito</t>
+          <t>Dano ao Erário | Nulidade - Intimação Sem Observância das Prescrições Legais | Violação dos Princípios Administrativos</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>15/05/2025</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>28/09/2026 14:33</t>
+          <t>14/09/2026 13:13</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>28/09/2026 14:33</t>
+          <t>14/09/2026 13:13</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>29/09/2026 07:20</t>
+          <t>24/09/2026 18:07</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4390,37 +4390,37 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0105320-13.2026.8.16.0000</t>
+          <t>0025625-17.2020.8.16.0001</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins</t>
+          <t>Prestação de Serviços | Contratos Bancários | Honorários Advocatícios</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>16/09/2025</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>22/09/2026 17:13</t>
+          <t>14/09/2026 14:33</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>22/09/2026 17:13</t>
+          <t>14/09/2026 14:33</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>29/09/2026 06:30</t>
+          <t>24/09/2026 18:17</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4437,7 +4437,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0116528-28.2025.8.16.0000</t>
+          <t>0001508-80.2024.8.16.0175</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4447,27 +4447,27 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>21/09/2026 16:55</t>
+          <t>14/09/2026 13:43</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>21/09/2026 16:55</t>
+          <t>14/09/2026 13:43</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>29/09/2026 08:00</t>
+          <t>24/09/2026 18:17</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4484,7 +4484,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0118791-67.2024.8.16.0000</t>
+          <t>0003891-27.2023.8.16.0026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4494,27 +4494,27 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Cobrança | Obrigação de Fazer / Não Fazer</t>
+          <t>Compra e Venda | Tutela de Urgência | Divisão e Demarcação</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>21/09/2026 19:03</t>
+          <t>10/09/2026 15:13</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>21/09/2026 19:03</t>
+          <t>10/09/2026 15:13</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>29/09/2026 08:20</t>
+          <t>24/09/2026 18:20</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4531,7 +4531,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0123956-95.2024.8.16.0000</t>
+          <t>0148376-33.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4541,27 +4541,27 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Compromisso</t>
+          <t>PIS/PASEP | PASEP</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>28/09/2026 16:53</t>
+          <t>14/09/2026 14:03</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>28/09/2026 16:53</t>
+          <t>14/09/2026 14:03</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>29/09/2026 06:20</t>
+          <t>24/09/2026 18:20</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4570,6 +4570,617 @@
         </is>
       </c>
       <c r="I88" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>0010112-36.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Duplicata</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>10/09/2026 17:13</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>10/09/2026 17:13</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>24/09/2026 18:20</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>0003517-82.2020.8.16.0004</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Previdência privada</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>11/09/2026 14:23</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>11/09/2026 14:23</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>24/09/2026 18:23</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>0097585-94.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Telefonia</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>26/11/2025</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>14/09/2026 13:43</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>14/09/2026 13:43</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>24/09/2026 18:25</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>0003787-45.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Desconsideração da Personalidade Jurídica</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>11/03/2026</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>10/09/2026 16:43</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>10/09/2026 16:43</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>24/09/2026 18:28</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>0059031-56.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Limitação de Juros</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>10/09/2026 16:53</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>10/09/2026 16:53</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>24/09/2026 18:28</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>0024754-06.2024.8.16.0014</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Práticas Abusivas</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>12/03/2026</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>11/09/2026 13:43</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>11/09/2026 13:43</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>24/09/2026 18:31</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>0096817-71.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>15/10/2025</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>11/09/2026 15:13</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>11/09/2026 15:13</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>24/09/2026 18:31</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>0007976-66.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Contratos Bancários</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>05/10/2026 14:33</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>05/10/2026 14:33</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>06/10/2026 04:06</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>0076622-57.2023.8.16.0014</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Cédula de Crédito Bancário</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>25/09/2026 18:33</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>25/09/2026 18:33</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>06/10/2026 04:09</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>0000063-25.2024.8.16.0014</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Transporte de Coisas</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>25/02/2026</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>25/09/2026 18:23</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>25/09/2026 18:23</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>06/10/2026 04:09</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>0009971-90.2012.8.16.0026</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Rescisão / Resolução</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>25/08/2025</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>25/09/2026 18:33</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>25/09/2026 18:33</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>06/10/2026 04:09</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>0012473-91.2023.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Rescisão / Resolução</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>25/09/2026 15:33</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>25/09/2026 15:33</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>06/10/2026 04:09</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>0009558-98.2008.8.16.0129</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Moral</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>25/09/2026 16:23</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>25/09/2026 16:23</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>06/10/2026 04:09</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>

--- a/docs/resultados.xlsx
+++ b/docs/resultados.xlsx
@@ -425,12 +425,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
@@ -486,6 +486,4706 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>0016917-05.2024.8.16.0173</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>06/10/2026 14:43</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>06/10/2026 14:43</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>07/10/2026 06:03</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>0123956-95.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Compromisso</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>28/09/2026 16:53</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>28/09/2026 16:53</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>07/10/2026 06:09</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>0014138-79.2022.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Alienação Fiduciária</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>28/09/2026 17:33</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>28/09/2026 17:33</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>07/10/2026 06:09</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>0009159-43.2020.8.16.0131</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Adimplemento e Extinção | Bem de Família (Voluntário)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>18/06/2025</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>28/09/2026 18:13</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>28/09/2026 18:13</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>07/10/2026 06:09</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>0003416-16.2024.8.16.0033</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Práticas Abusivas</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>06/10/2026 16:03</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>06/10/2026 16:03</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>07/10/2026 06:11</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>0007548-08.2009.8.16.0045</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Vícios de Construção | Seguro | Obrigação de Fazer / Não Fazer | Ônus da Prova | Legitimidade Ativa e Passiva</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>09/09/2025</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>29/09/2026 14:53</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>29/09/2026 14:53</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>07/10/2026 06:19</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>0116457-60.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Contratos Bancários</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>28/09/2026 18:03</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>28/09/2026 18:03</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>07/10/2026 06:22</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>0005352-88.2017.8.16.0173</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Furto</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>06/10/2026 14:03</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>06/10/2026 14:03</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>07/10/2026 06:22</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>0001384-29.2018.8.16.0104</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Execução Contratual</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>06/10/2026 16:03</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>06/10/2026 16:03</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>07/10/2026 06:22</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>0012385-53.2017.8.16.0069</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Rescisão / Resolução</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>26/11/2025</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>28/09/2026 16:43</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>28/09/2026 16:43</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>07/10/2026 06:22</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>0001357-42.2021.8.16.0136</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Receptação</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>06/10/2026 15:23</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>06/10/2026 15:23</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>07/10/2026 06:32</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>0001036-16.2024.8.16.0196</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins | Aplicação da Pena</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>05/08/2026</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>02/10/2026 07:12</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>02/10/2026 07:12</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>07/10/2026 06:32</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>0027654-38.2023.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Restituição ao Erário | Dano ao Erário | Obrigação de Fazer / Não Fazer | Ônus da Prova | Violação dos Princípios Administrativos</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>19/05/2025</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>28/09/2026 16:03</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>28/09/2026 16:03</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>07/10/2026 05:52</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>0011485-52.2015.8.16.0033</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Sustação de Protesto</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>05/09/2025</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>28/09/2026 13:33</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>28/09/2026 13:33</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>07/10/2026 05:52</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>0001665-20.2022.8.16.0047</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>23/07/2025</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>28/09/2026 14:03</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>28/09/2026 14:03</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>07/10/2026 05:55</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>0033286-91.2013.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Reivindicação | Pagamento</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>09/02/2022</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>28/09/2026 14:33</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>28/09/2026 14:33</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>07/10/2026 05:40</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>0048696-67.2024.8.16.0014</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Cessão de Crédito | Causas Supervenientes à Sentença</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>02/10/2026 15:23</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>02/10/2026 15:23</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>07/10/2026 05:43</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>0001127-42.2008.8.16.0043</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Moral</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>16/12/2025</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>28/09/2026 16:23</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>28/09/2026 16:23</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>07/10/2026 05:43</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>0001866-46.2025.8.16.0131</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Restituição de Coisas Apreendidas | Crimes do Sistema Nacional de Armas | Receptação | Adulteração de Sinal Identificador de Veículo Automotor</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>06/10/2026 13:13</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>06/10/2026 13:13</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>07/10/2026 05:43</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>0035579-85.2023.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Material</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>11/12/2024</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>28/09/2026 14:33</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>28/09/2026 14:33</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>07/10/2026 05:43</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>0010353-10.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>28/09/2026 17:33</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>28/09/2026 17:33</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>07/10/2026 05:43</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>4001568-46.2025.8.16.0014</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Falta Grave | Roubo Majorado</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>06/10/2026 16:23</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>06/10/2026 16:23</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>07/10/2026 05:52</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>0071691-82.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>PIS/PASEP | Indenização por Dano Material</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>23/07/2026</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>28/09/2026 16:03</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>28/09/2026 16:03</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>07/10/2026 05:52</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>0087707-77.2026.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Recurso Ordinário em Habeas Corpus</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins | Adulteração de Sinal Identificador de Veículo Automotor</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>06/10/2026 13:03</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>06/10/2026 13:03</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>07/10/2026 05:52</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>0007498-89.2023.8.16.0174</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>06/10/2026 13:13</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>06/10/2026 13:13</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>07/10/2026 05:52</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>0007532-69.2021.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Condomínio</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>27/05/2024</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>29/09/2026 11:18</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>29/09/2026 11:18</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>07/10/2026 04:20</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>0021175-92.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Recuperação judicial e Falência | Concurso de Credores</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>08/12/2025</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>28/09/2026 18:23</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>28/09/2026 18:23</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>07/10/2026 04:20</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>0019858-22.2022.8.16.0035</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Pagamento</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>23/09/2025</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>28/09/2026 18:03</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>28/09/2026 18:03</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>07/10/2026 04:20</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>0002351-37.2009.8.16.0089</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Seguro</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>28/09/2026 19:23</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>28/09/2026 19:23</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>07/10/2026 04:23</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>0017883-91.2024.8.16.0035</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>04/04/2025</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>05/10/2026 17:12</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>06/10/2026 15:48</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>07/10/2026 04:23</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>0000507-35.2021.8.16.0185</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Concurso de Credores</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>27/05/2025</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>28/09/2026 16:53</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>28/09/2026 16:53</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>07/10/2026 04:23</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>0010005-48.2023.8.16.0004</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Servidores Inativos</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>02/10/2026 13:33</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>02/10/2026 13:33</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>07/10/2026 04:32</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>0004994-55.2020.8.16.0194</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Material | Prestação de Serviços | Obrigação de Fazer / Não Fazer | Indenização por Dano Moral | Ônus da Prova | Inadimplemento</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>04/02/2026</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>28/09/2026 14:53</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>28/09/2026 14:53</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>07/10/2026 04:32</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>0058493-75.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Defeito, nulidade ou anulação</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>06/02/2026</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>28/09/2026 16:53</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>28/09/2026 16:53</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>07/10/2026 04:32</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>0002467-70.2023.8.16.0083</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Homicídio Qualificado | Promoção, constituição, financiamento ou integração de Organização Criminosa</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>06/10/2026 16:03</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>06/10/2026 16:03</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>07/10/2026 04:32</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>0000502-33.1987.8.16.0014</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Nota Promissória</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>16/07/2024</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>28/09/2026 15:23</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>28/09/2026 15:23</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>07/10/2026 04:32</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>0025353-57.2025.8.16.0030</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Receptação Qualificada</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>28/09/2026 17:23</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>28/09/2026 17:23</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>07/10/2026 04:32</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>0080070-80.2023.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Cédula de Crédito Bancário | Penhora / Depósito/ Avaliação</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>13/02/2025</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>28/09/2026 17:33</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>28/09/2026 17:33</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>07/10/2026 04:34</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>0001054-57.2022.8.16.0115</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Promessa de Compra e Venda | Obrigação de Fazer / Não Fazer</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>28/09/2026 14:53</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>28/09/2026 14:53</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>07/10/2026 04:34</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>0065426-64.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Compra e Venda</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>05/10/2026 14:03</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>05/10/2026 14:03</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>07/10/2026 04:43</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>0006182-72.2025.8.16.0044</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>06/10/2026 15:03</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>06/10/2026 15:03</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>07/10/2026 04:43</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>0000563-56.2024.8.16.0155</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Adulteração de Sinal Identificador de Veículo Automotor</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>06/10/2026 14:03</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>06/10/2026 14:03</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>07/10/2026 04:46</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>0001238-65.2016.8.16.0004</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços | Rescisão / Resolução | Perdas e Danos</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>26/10/2021</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>28/09/2026 15:43</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>28/09/2026 15:43</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>07/10/2026 04:46</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>0006648-82.2017.8.16.0194</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Material</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>10/10/2024</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>28/09/2026 13:43</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>28/09/2026 13:43</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>07/10/2026 04:17</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>0004576-62.2021.8.16.0104</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Parceria Agrícola e/ou pecuária</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>28/09/2026 18:23</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>28/09/2026 18:23</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>07/10/2026 04:17</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>0000240-03.2021.8.16.0108</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Apropriação indébita</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>20/01/2026</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>06/10/2026 16:03</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>06/10/2026 16:03</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>07/10/2026 04:17</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>0043698-98.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Crimes da Lei de licitações</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>02/10/2025</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>06/10/2026 13:03</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>06/10/2026 13:03</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>07/10/2026 04:20</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>0080573-04.2023.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Inventário e Partilha</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>13/11/2024</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>28/09/2026 14:13</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>28/09/2026 14:13</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>07/10/2026 04:20</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>0010091-86.2023.8.16.0014</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Pedido de Uniformização de Interpretação de Lei Criminal</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Adicional de Periculosidade</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>14/09/2026 14:43</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>14/09/2026 14:43</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>23/09/2026 06:20</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>0012511-74.2015.8.16.0069</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Aposentadoria Especial (Art. 57/8)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>14/09/2026 13:53</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>14/09/2026 13:53</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>24/09/2026 17:10</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>0005532-90.2023.8.16.0045</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>25/02/2026</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>14/09/2026 13:23</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>14/09/2026 13:23</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>24/09/2026 17:21</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>0028232-46.2020.8.16.0019</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Homicídio Qualificado</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>14/09/2026 14:23</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>14/09/2026 14:23</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>24/09/2026 17:45</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>0050674-53.2026.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Recurso Ordinário em Habeas Corpus</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>22/09/2026 14:33</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>22/09/2026 14:33</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>24/09/2026 17:45</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>0001243-96.2023.8.16.0148</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Moral | Liminar | Indenização por Dano Material | Obrigação de Fazer / Não Fazer</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>14/09/2026 13:23</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>14/09/2026 13:23</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>24/09/2026 18:03</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>0040364-56.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Dano ao Erário | Nulidade - Intimação Sem Observância das Prescrições Legais | Violação dos Princípios Administrativos</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>15/05/2025</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>14/09/2026 13:13</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>14/09/2026 13:13</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>24/09/2026 18:07</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>0025625-17.2020.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços | Contratos Bancários | Honorários Advocatícios</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>16/09/2025</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>14/09/2026 14:33</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>14/09/2026 14:33</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>24/09/2026 18:17</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>0001508-80.2024.8.16.0175</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Moral</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>14/09/2026 13:43</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>14/09/2026 13:43</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>24/09/2026 18:17</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>0148376-33.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>PIS/PASEP | PASEP</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>23/07/2026</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>14/09/2026 14:03</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>14/09/2026 14:03</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>24/09/2026 18:20</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>0097585-94.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Telefonia</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>26/11/2025</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>14/09/2026 13:43</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>14/09/2026 13:43</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>24/09/2026 18:25</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>0000674-91.2024.8.16.0138</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Sustação de Protesto</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>14/09/2026 14:23</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>14/09/2026 14:23</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>24/09/2026 18:32</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>0001565-54.2024.8.16.0028</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Roubo Majorado | Crime Tentado</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>15/08/2025</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>14/09/2026 14:03</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>14/09/2026 14:03</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>24/09/2026 18:32</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>0058340-76.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Dívida Ativa (Execução Fiscal)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>14/09/2026 14:23</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>14/09/2026 14:23</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>24/09/2026 18:36</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>0003548-40.2022.8.16.0196</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>16/09/2026 13:33</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>16/09/2026 13:33</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>25/09/2026 04:40</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>0003769-86.2023.8.16.0196</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>15/09/2026 14:53</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>15/09/2026 14:53</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>25/09/2026 04:44</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>0002122-28.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Dívida Ativa (Execução Fiscal)</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>25/08/2025</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>16/09/2026 12:06</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>16/09/2026 12:06</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>25/09/2026 04:44</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>0013125-21.2023.8.16.0030</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Fiscalização</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>15/09/2026 15:43</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>15/09/2026 15:43</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>25/09/2026 04:47</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>0081451-89.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços | Honorários Advocatícios</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>15/09/2026 14:03</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>15/09/2026 14:03</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>25/09/2026 04:49</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>0098757-71.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Revisão de Juros Remuneratórios, Capitalização/Anatocismo</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>15/09/2026 13:53</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>15/09/2026 13:53</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>25/09/2026 04:49</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>0017322-41.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Alienação Fiduciária</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>15/09/2026 13:33</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>15/09/2026 13:33</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>25/09/2026 05:01</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>0005030-07.2025.8.16.0038</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>15/09/2026 17:23</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>15/09/2026 17:23</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>25/09/2026 05:10</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>0040684-14.2022.8.16.0021</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ICMS/ Imposto sobre Circulação de Mercadorias</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>14/08/2025</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>16/09/2026 07:28</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>16/09/2026 07:28</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>25/09/2026 05:10</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>0109824-62.2026.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Recurso Ordinário em Habeas Corpus</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ameaça | Desobediência | Crimes do Sistema Nacional de Armas</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>22/09/2026 16:13</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>22/09/2026 16:13</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>25/09/2026 05:12</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>0024154-27.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Contratos Bancários</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>15/09/2026 17:03</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>15/09/2026 17:03</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>25/09/2026 05:12</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>0000908-97.2024.8.16.0033</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>15/09/2026 17:03</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>15/09/2026 17:03</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>25/09/2026 05:15</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>0009896-40.2025.8.16.0044</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Associação para a Produção e Tráfico e Condutas Afins</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>15/09/2026 15:03</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>15/09/2026 15:03</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>25/09/2026 05:19</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>0010154-54.2021.8.16.0185</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Dívida Ativa (Execução Fiscal)</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>16/09/2026 14:03</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>16/09/2026 14:03</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>25/09/2026 05:20</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>0003013-71.2020.8.16.0038</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Nota Promissória</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>30/01/2026</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>16/09/2026 13:53</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>16/09/2026 13:53</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>25/09/2026 05:34</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>0011262-51.2024.8.16.0044</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Associação para a Produção e Tráfico e Condutas Afins | Promoção, constituição, financiamento ou integração de Organização Criminosa | Crimes de &amp;quot;Lavagem&amp;quot; ou Ocultação de Bens, Direitos ou Valores</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>15/09/2026 16:53</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>15/09/2026 16:53</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>25/09/2026 09:15</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>0020261-66.2023.8.16.0031</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Compromisso</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>14/09/2026 13:09</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>14/09/2026 13:09</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>25/09/2026 09:15</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>0002809-68.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>16/09/2026 13:23</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>16/09/2026 13:23</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>25/09/2026 09:15</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>0004317-38.2018.8.16.0083</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Erro Médico</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>20/01/2026</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>16/09/2026 13:53</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>16/09/2026 13:53</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>25/09/2026 09:15</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>0017165-68.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Cédula de Crédito Bancário</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>15/09/2026 17:24</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>15/09/2026 17:24</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>25/09/2026 09:15</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>0033528-79.2015.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Direitos / Deveres do Condômino</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>15/09/2026 16:13</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>15/09/2026 16:13</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>25/09/2026 09:15</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>0014455-75.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Material</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>15/09/2026 17:53</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>15/09/2026 17:53</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>25/09/2026 09:15</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>0005298-13.2024.8.16.0033</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Superendividamento</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>16/09/2026 13:43</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>16/09/2026 13:43</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>25/09/2026 09:15</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>0013992-22.2014.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Compromisso</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>24/04/2025</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>15/09/2026 17:43</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>15/09/2026 17:43</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>25/09/2026 09:15</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>0018063-74.2008.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Erro Médico</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>15/09/2026 14:03</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>15/09/2026 14:03</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>25/09/2026 09:15</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>0047645-92.2026.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Recurso Ordinário em Habeas Corpus</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Associação para a Produção e Tráfico e Condutas Afins | Prisão Preventiva | Promoção, constituição, financiamento ou integração de Organização Criminosa</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>22/09/2026 15:53</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>22/09/2026 15:53</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>26/09/2026 03:30</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>0060675-26.2024.8.16.0014</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Moral</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>16/09/2026 14:23</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>16/09/2026 14:23</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>26/09/2026 03:40</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>0032740-19.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Espécies de Títulos de Crédito | Sucumbenciais</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>06/03/2026</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>17/09/2026 14:23</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>17/09/2026 14:23</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>26/09/2026 03:40</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>0012821-80.2021.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Locação de Imóvel | Obrigação de Fazer / Não Fazer | Indenização por Dano Material | Cobrança de Aluguéis - Sem despejo</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>25/09/2026 17:43</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>25/09/2026 17:43</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>26/09/2026 03:50</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>0052267-88.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Processo Administrativo Disciplinar ou Sindicância</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>25/09/2026 16:23</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>25/09/2026 16:23</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>26/09/2026 04:00</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>0119994-64.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>IPTU/ Imposto Predial e Territorial Urbano</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>16/09/2026 14:23</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>16/09/2026 14:23</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>26/09/2026 04:10</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>0015214-66.2025.8.16.0185</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Dívida Ativa (Execução Fiscal)</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>17/09/2026 13:33</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>17/09/2026 13:33</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>26/09/2026 04:10</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>0016200-33.2025.8.16.0019</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Homicídio Qualificado</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>16/09/2026 15:23</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>16/09/2026 15:23</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>26/09/2026 04:10</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>0122256-84.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Enriquecimento ilícito | Dano ao Erário | Violação dos Princípios Administrativos</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>16/09/2026 14:43</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>16/09/2026 14:43</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>26/09/2026 05:00</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>0000963-09.2022.8.16.0004</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Ato Normativo | Defeito, nulidade ou anulação</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>10/06/2025</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>17/09/2026 14:33</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>17/09/2026 14:33</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>26/09/2026 05:00</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>0000486-51.2023.8.16.0165</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Revisão de Juros Remuneratórios, Capitalização/Anatocismo</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>16/09/2026 14:13</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>16/09/2026 14:13</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>26/09/2026 05:20</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>0055070-44.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Dívida Ativa (Execução Fiscal) | ICMS/ Imposto sobre Circulação de Mercadorias</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>16/09/2026 15:43</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>16/09/2026 15:43</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>26/09/2026 05:30</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>0027456-37.2015.8.16.0014</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Alienação Fiduciária</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>22/09/2026 15:33</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>22/09/2026 15:33</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>30/09/2026 05:00</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/resultados.xlsx
+++ b/docs/resultados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I101"/>
+  <dimension ref="A1:I95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -489,7 +489,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0016917-05.2024.8.16.0173</t>
+          <t>0000043-07.2025.8.16.0044</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -504,22 +504,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>10/12/2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>06/10/2026 14:43</t>
+          <t>30/09/2026 14:13</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>06/10/2026 14:43</t>
+          <t>30/09/2026 14:13</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>07/10/2026 06:03</t>
+          <t>06/10/2026 04:33</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -536,7 +536,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0123956-95.2024.8.16.0000</t>
+          <t>0000240-03.2021.8.16.0108</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -546,27 +546,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Compromisso</t>
+          <t>Apropriação indébita</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>20/01/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>28/09/2026 16:53</t>
+          <t>06/10/2026 16:03</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>28/09/2026 16:53</t>
+          <t>06/10/2026 16:03</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>07/10/2026 06:09</t>
+          <t>07/10/2026 04:17</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -583,37 +583,37 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0014138-79.2022.8.16.0001</t>
+          <t>0000502-33.1987.8.16.0014</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Alienação Fiduciária</t>
+          <t>Nota Promissória</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>12/01/2026</t>
+          <t>16/07/2024</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>28/09/2026 17:33</t>
+          <t>28/09/2026 15:23</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>28/09/2026 17:33</t>
+          <t>28/09/2026 15:23</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>07/10/2026 06:09</t>
+          <t>07/10/2026 04:32</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,7 +630,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0009159-43.2020.8.16.0131</t>
+          <t>0000507-35.2021.8.16.0185</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -640,27 +640,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Adimplemento e Extinção | Bem de Família (Voluntário)</t>
+          <t>Concurso de Credores</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>18/06/2025</t>
+          <t>27/05/2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>28/09/2026 18:13</t>
+          <t>28/09/2026 16:53</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>28/09/2026 18:13</t>
+          <t>28/09/2026 16:53</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>07/10/2026 06:09</t>
+          <t>07/10/2026 04:23</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -677,37 +677,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0003416-16.2024.8.16.0033</t>
+          <t>0000563-56.2024.8.16.0155</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Práticas Abusivas</t>
+          <t>Adulteração de Sinal Identificador de Veículo Automotor</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>06/10/2026 16:03</t>
+          <t>06/10/2026 14:03</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>06/10/2026 16:03</t>
+          <t>06/10/2026 14:03</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>07/10/2026 06:11</t>
+          <t>07/10/2026 04:46</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -724,7 +724,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0007548-08.2009.8.16.0045</t>
+          <t>0000823-87.2016.8.16.0164</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -734,27 +734,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Vícios de Construção | Seguro | Obrigação de Fazer / Não Fazer | Ônus da Prova | Legitimidade Ativa e Passiva</t>
+          <t>Inventário e Partilha</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>29/09/2026 14:53</t>
+          <t>25/09/2026 16:03</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>29/09/2026 14:53</t>
+          <t>25/09/2026 16:03</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>07/10/2026 06:19</t>
+          <t>06/10/2026 04:33</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -771,7 +771,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0116457-60.2024.8.16.0000</t>
+          <t>0000963-09.2022.8.16.0004</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -781,27 +781,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Ato Normativo | Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>05/03/2026</t>
+          <t>10/06/2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>28/09/2026 18:03</t>
+          <t>17/09/2026 14:33</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>28/09/2026 18:03</t>
+          <t>17/09/2026 14:33</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>07/10/2026 06:22</t>
+          <t>26/09/2026 05:00</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -818,37 +818,37 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0005352-88.2017.8.16.0173</t>
+          <t>0001036-16.2024.8.16.0196</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Furto</t>
+          <t>Tráfico de Drogas e Condutas Afins | Aplicação da Pena</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>06/10/2026 14:03</t>
+          <t>02/10/2026 07:12</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>06/10/2026 14:03</t>
+          <t>02/10/2026 07:12</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>07/10/2026 06:22</t>
+          <t>07/10/2026 06:32</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -865,7 +865,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0001384-29.2018.8.16.0104</t>
+          <t>0001053-77.2023.8.16.0102</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -875,27 +875,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Execução Contratual</t>
+          <t>Contratos Bancários | Indenização por Dano Moral | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>06/10/2026 16:03</t>
+          <t>25/09/2026 17:44</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>06/10/2026 16:03</t>
+          <t>25/09/2026 17:44</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>07/10/2026 06:22</t>
+          <t>06/10/2026 04:57</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -912,7 +912,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0012385-53.2017.8.16.0069</t>
+          <t>0001054-57.2022.8.16.0115</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -922,27 +922,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Rescisão / Resolução</t>
+          <t>Promessa de Compra e Venda | Obrigação de Fazer / Não Fazer</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>26/11/2025</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>28/09/2026 16:43</t>
+          <t>28/09/2026 14:53</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>28/09/2026 16:43</t>
+          <t>28/09/2026 14:53</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>07/10/2026 06:22</t>
+          <t>07/10/2026 04:34</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0001357-42.2021.8.16.0136</t>
+          <t>0001127-42.2008.8.16.0043</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -969,27 +969,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Receptação</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>06/10/2026 15:23</t>
+          <t>28/09/2026 16:23</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>06/10/2026 15:23</t>
+          <t>28/09/2026 16:23</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>07/10/2026 06:32</t>
+          <t>07/10/2026 05:43</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1006,7 +1006,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0001036-16.2024.8.16.0196</t>
+          <t>0001238-65.2016.8.16.0004</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1016,27 +1016,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Aplicação da Pena</t>
+          <t>Prestação de Serviços | Rescisão / Resolução | Perdas e Danos</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>26/10/2021</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>02/10/2026 07:12</t>
+          <t>28/09/2026 15:43</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>02/10/2026 07:12</t>
+          <t>28/09/2026 15:43</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>07/10/2026 06:32</t>
+          <t>07/10/2026 04:46</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1053,7 +1053,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0027654-38.2023.8.16.0000</t>
+          <t>0001357-42.2021.8.16.0136</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1063,27 +1063,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Restituição ao Erário | Dano ao Erário | Obrigação de Fazer / Não Fazer | Ônus da Prova | Violação dos Princípios Administrativos</t>
+          <t>Receptação</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>19/05/2025</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>28/09/2026 16:03</t>
+          <t>06/10/2026 15:23</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>28/09/2026 16:03</t>
+          <t>06/10/2026 15:23</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>07/10/2026 05:52</t>
+          <t>07/10/2026 06:32</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0011485-52.2015.8.16.0033</t>
+          <t>0001384-29.2018.8.16.0104</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1110,27 +1110,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sustação de Protesto</t>
+          <t>Execução Contratual</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>05/09/2025</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>28/09/2026 13:33</t>
+          <t>06/10/2026 16:03</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>28/09/2026 13:33</t>
+          <t>06/10/2026 16:03</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>07/10/2026 05:52</t>
+          <t>07/10/2026 06:22</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1194,37 +1194,37 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0033286-91.2013.8.16.0001</t>
+          <t>0001866-46.2025.8.16.0131</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Reivindicação | Pagamento</t>
+          <t>Restituição de Coisas Apreendidas | Crimes do Sistema Nacional de Armas | Receptação | Adulteração de Sinal Identificador de Veículo Automotor</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>09/02/2022</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>28/09/2026 14:33</t>
+          <t>06/10/2026 13:13</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>28/09/2026 14:33</t>
+          <t>06/10/2026 13:13</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>07/10/2026 05:40</t>
+          <t>07/10/2026 05:43</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1241,7 +1241,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0048696-67.2024.8.16.0014</t>
+          <t>0002202-63.2019.8.16.0130</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1251,27 +1251,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cessão de Crédito | Causas Supervenientes à Sentença</t>
+          <t>Bem de Família (Voluntário)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>02/10/2026 15:23</t>
+          <t>28/09/2026 14:53</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>02/10/2026 15:23</t>
+          <t>28/09/2026 14:53</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>07/10/2026 05:43</t>
+          <t>07/10/2026 03:31</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1288,7 +1288,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0001127-42.2008.8.16.0043</t>
+          <t>0002351-37.2009.8.16.0089</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1298,27 +1298,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>28/09/2026 16:23</t>
+          <t>28/09/2026 19:23</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>28/09/2026 16:23</t>
+          <t>28/09/2026 19:23</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>07/10/2026 05:43</t>
+          <t>07/10/2026 04:23</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1335,37 +1335,37 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0001866-46.2025.8.16.0131</t>
+          <t>0002467-70.2023.8.16.0083</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Restituição de Coisas Apreendidas | Crimes do Sistema Nacional de Armas | Receptação | Adulteração de Sinal Identificador de Veículo Automotor</t>
+          <t>Homicídio Qualificado | Promoção, constituição, financiamento ou integração de Organização Criminosa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>06/10/2026 13:13</t>
+          <t>06/10/2026 16:03</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>06/10/2026 13:13</t>
+          <t>06/10/2026 16:03</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>07/10/2026 05:43</t>
+          <t>07/10/2026 04:32</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1382,37 +1382,37 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0035579-85.2023.8.16.0000</t>
+          <t>0002613-46.2022.8.16.0116</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>11/12/2024</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>28/09/2026 14:33</t>
+          <t>05/10/2026 16:03</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>28/09/2026 14:33</t>
+          <t>05/10/2026 16:03</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>07/10/2026 05:43</t>
+          <t>06/10/2026 04:42</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1429,37 +1429,37 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0010353-10.2025.8.16.0000</t>
+          <t>0002787-13.2022.8.16.0033</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Compra e Venda</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>28/09/2026 17:33</t>
+          <t>05/10/2026 13:03</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>28/09/2026 17:33</t>
+          <t>05/10/2026 13:03</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>07/10/2026 05:43</t>
+          <t>06/10/2026 04:35</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1476,7 +1476,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>4001568-46.2025.8.16.0014</t>
+          <t>0003416-16.2024.8.16.0033</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1486,27 +1486,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Falta Grave | Roubo Majorado</t>
+          <t>Práticas Abusivas</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>06/10/2026 16:23</t>
+          <t>06/10/2026 16:03</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>06/10/2026 16:23</t>
+          <t>06/10/2026 16:03</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>07/10/2026 05:52</t>
+          <t>07/10/2026 06:11</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1523,7 +1523,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0071691-82.2025.8.16.0000</t>
+          <t>0004195-67.2023.8.16.0174</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1533,27 +1533,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PIS/PASEP | Indenização por Dano Material</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>28/09/2026 16:03</t>
+          <t>05/10/2026 16:03</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>28/09/2026 16:03</t>
+          <t>05/10/2026 16:03</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>07/10/2026 05:52</t>
+          <t>06/10/2026 04:49</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1570,37 +1570,37 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0087707-77.2026.8.16.0000</t>
+          <t>0004318-17.2024.8.16.0017</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Adulteração de Sinal Identificador de Veículo Automotor</t>
+          <t>Pagamento</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>06/10/2026 13:03</t>
+          <t>05/10/2026 15:33</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>06/10/2026 13:03</t>
+          <t>05/10/2026 15:33</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>07/10/2026 05:52</t>
+          <t>06/10/2026 04:42</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1617,7 +1617,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0007498-89.2023.8.16.0174</t>
+          <t>0004576-62.2021.8.16.0104</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1627,27 +1627,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Parceria Agrícola e/ou pecuária</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>26/01/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>06/10/2026 13:13</t>
+          <t>28/09/2026 18:23</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>06/10/2026 13:13</t>
+          <t>28/09/2026 18:23</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>07/10/2026 05:52</t>
+          <t>07/10/2026 04:17</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1664,37 +1664,37 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0007532-69.2021.8.16.0001</t>
+          <t>0004994-55.2020.8.16.0194</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Condomínio</t>
+          <t>Indenização por Dano Material | Prestação de Serviços | Obrigação de Fazer / Não Fazer | Indenização por Dano Moral | Ônus da Prova | Inadimplemento</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>27/05/2024</t>
+          <t>04/02/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>29/09/2026 11:18</t>
+          <t>28/09/2026 14:53</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>29/09/2026 11:18</t>
+          <t>28/09/2026 14:53</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>07/10/2026 04:20</t>
+          <t>07/10/2026 04:32</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0021175-92.2024.8.16.0000</t>
+          <t>0005352-88.2017.8.16.0173</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1721,27 +1721,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Recuperação judicial e Falência | Concurso de Credores</t>
+          <t>Furto</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>08/12/2025</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>28/09/2026 18:23</t>
+          <t>06/10/2026 14:03</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>28/09/2026 18:23</t>
+          <t>06/10/2026 14:03</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>07/10/2026 04:20</t>
+          <t>07/10/2026 06:22</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1758,7 +1758,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0019858-22.2022.8.16.0035</t>
+          <t>0005630-14.2023.8.16.0130</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1768,27 +1768,27 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Pagamento</t>
+          <t>Confissão/Composição de Dívida | Efeito Suspensivo / Impugnação / Embargos à Execução</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>23/09/2025</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>28/09/2026 18:03</t>
+          <t>25/09/2026 17:13</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>28/09/2026 18:03</t>
+          <t>25/09/2026 17:13</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>07/10/2026 04:20</t>
+          <t>06/10/2026 04:38</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1805,7 +1805,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0002351-37.2009.8.16.0089</t>
+          <t>0005780-15.2020.8.16.0028</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1815,27 +1815,27 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Direito de Vizinhança</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>28/09/2026 19:23</t>
+          <t>05/10/2026 13:43</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>28/09/2026 19:23</t>
+          <t>05/10/2026 13:43</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>07/10/2026 04:23</t>
+          <t>06/10/2026 04:42</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1852,7 +1852,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0017883-91.2024.8.16.0035</t>
+          <t>0006182-72.2025.8.16.0044</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1867,22 +1867,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>04/04/2025</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>05/10/2026 17:12</t>
+          <t>06/10/2026 15:03</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>06/10/2026 15:48</t>
+          <t>06/10/2026 15:03</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>07/10/2026 04:23</t>
+          <t>07/10/2026 04:43</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1899,37 +1899,37 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0000507-35.2021.8.16.0185</t>
+          <t>0006648-82.2017.8.16.0194</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Concurso de Credores</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>27/05/2025</t>
+          <t>10/10/2024</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>28/09/2026 16:53</t>
+          <t>28/09/2026 13:43</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>28/09/2026 16:53</t>
+          <t>28/09/2026 13:43</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>07/10/2026 04:23</t>
+          <t>07/10/2026 04:17</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1946,7 +1946,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0010005-48.2023.8.16.0004</t>
+          <t>0007498-89.2023.8.16.0174</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1956,27 +1956,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Servidores Inativos</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>02/10/2026 13:33</t>
+          <t>06/10/2026 13:13</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>02/10/2026 13:33</t>
+          <t>06/10/2026 13:13</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>07/10/2026 04:32</t>
+          <t>07/10/2026 05:52</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1993,37 +1993,37 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0004994-55.2020.8.16.0194</t>
+          <t>0007532-69.2021.8.16.0001</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Prestação de Serviços | Obrigação de Fazer / Não Fazer | Indenização por Dano Moral | Ônus da Prova | Inadimplemento</t>
+          <t>Condomínio</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>04/02/2026</t>
+          <t>27/05/2024</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>28/09/2026 14:53</t>
+          <t>29/09/2026 11:18</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>28/09/2026 14:53</t>
+          <t>29/09/2026 11:18</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>07/10/2026 04:32</t>
+          <t>07/10/2026 04:20</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2040,7 +2040,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0058493-75.2025.8.16.0000</t>
+          <t>0007548-08.2009.8.16.0045</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2050,27 +2050,27 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação</t>
+          <t>Vícios de Construção | Seguro | Obrigação de Fazer / Não Fazer | Ônus da Prova | Legitimidade Ativa e Passiva</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>28/09/2026 16:53</t>
+          <t>29/09/2026 14:53</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>28/09/2026 16:53</t>
+          <t>29/09/2026 14:53</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>07/10/2026 04:32</t>
+          <t>07/10/2026 06:19</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2087,37 +2087,37 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0002467-70.2023.8.16.0083</t>
+          <t>0009159-43.2020.8.16.0131</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Homicídio Qualificado | Promoção, constituição, financiamento ou integração de Organização Criminosa</t>
+          <t>Adimplemento e Extinção | Bem de Família (Voluntário)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>18/06/2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>06/10/2026 16:03</t>
+          <t>28/09/2026 18:13</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>06/10/2026 16:03</t>
+          <t>28/09/2026 18:13</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>07/10/2026 04:32</t>
+          <t>07/10/2026 06:09</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2134,7 +2134,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0000502-33.1987.8.16.0014</t>
+          <t>0009337-85.2022.8.16.0045</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2144,27 +2144,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Nota Promissória</t>
+          <t>Desconsideração da Personalidade Jurídica | Defeito, nulidade ou anulação | Embargos de Terceiro | Penhora / Depósito/ Avaliação</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>16/07/2024</t>
+          <t>05/05/2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>28/09/2026 15:23</t>
+          <t>28/09/2026 16:33</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>28/09/2026 15:23</t>
+          <t>28/09/2026 16:33</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>07/10/2026 04:32</t>
+          <t>07/10/2026 03:31</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2181,37 +2181,37 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0025353-57.2025.8.16.0030</t>
+          <t>0009528-05.2021.8.16.0001</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Receptação Qualificada</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>28/09/2026 17:23</t>
+          <t>05/10/2026 15:33</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>28/09/2026 17:23</t>
+          <t>05/10/2026 15:33</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>07/10/2026 04:32</t>
+          <t>06/10/2026 04:49</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2228,7 +2228,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0080070-80.2023.8.16.0000</t>
+          <t>0009839-97.2025.8.16.0019</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2238,27 +2238,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário | Penhora / Depósito/ Avaliação</t>
+          <t>Seqüestro e cárcere privado | Dano | Grave</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>13/02/2025</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>28/09/2026 17:33</t>
+          <t>05/10/2026 20:33</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>28/09/2026 17:33</t>
+          <t>05/10/2026 20:33</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>07/10/2026 04:34</t>
+          <t>06/10/2026 04:38</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2275,7 +2275,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0001054-57.2022.8.16.0115</t>
+          <t>0010005-48.2023.8.16.0004</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2285,27 +2285,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Promessa de Compra e Venda | Obrigação de Fazer / Não Fazer</t>
+          <t>Servidores Inativos</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>28/09/2026 14:53</t>
+          <t>02/10/2026 13:33</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>28/09/2026 14:53</t>
+          <t>02/10/2026 13:33</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>07/10/2026 04:34</t>
+          <t>07/10/2026 04:32</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2322,37 +2322,37 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0065426-64.2025.8.16.0000</t>
+          <t>0010353-10.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Compra e Venda</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>05/10/2026 14:03</t>
+          <t>28/09/2026 17:33</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>05/10/2026 14:03</t>
+          <t>28/09/2026 17:33</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>07/10/2026 04:43</t>
+          <t>07/10/2026 05:43</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2369,7 +2369,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0006182-72.2025.8.16.0044</t>
+          <t>0010901-86.2022.8.16.0017</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2379,27 +2379,27 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Incorporação Imobiliária</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>06/10/2026 15:03</t>
+          <t>05/10/2026 13:23</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>06/10/2026 15:03</t>
+          <t>05/10/2026 13:23</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>07/10/2026 04:43</t>
+          <t>06/10/2026 04:53</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2416,37 +2416,37 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0000563-56.2024.8.16.0155</t>
+          <t>0011027-98.2016.8.16.0033</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Adulteração de Sinal Identificador de Veículo Automotor</t>
+          <t>Mensalidades</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>06/10/2026 14:03</t>
+          <t>05/10/2026 15:13</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>06/10/2026 14:03</t>
+          <t>05/10/2026 15:13</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>07/10/2026 04:46</t>
+          <t>06/10/2026 04:35</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2463,37 +2463,37 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0001238-65.2016.8.16.0004</t>
+          <t>0011485-52.2015.8.16.0033</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Prestação de Serviços | Rescisão / Resolução | Perdas e Danos</t>
+          <t>Sustação de Protesto</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>26/10/2021</t>
+          <t>05/09/2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>28/09/2026 15:43</t>
+          <t>28/09/2026 13:33</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>28/09/2026 15:43</t>
+          <t>28/09/2026 13:33</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>07/10/2026 04:46</t>
+          <t>07/10/2026 05:52</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2510,37 +2510,37 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0006648-82.2017.8.16.0194</t>
+          <t>0012385-53.2017.8.16.0069</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Rescisão / Resolução</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>10/10/2024</t>
+          <t>26/11/2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>28/09/2026 13:43</t>
+          <t>28/09/2026 16:43</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>28/09/2026 13:43</t>
+          <t>28/09/2026 16:43</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>07/10/2026 04:17</t>
+          <t>07/10/2026 06:22</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2557,37 +2557,37 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0004576-62.2021.8.16.0104</t>
+          <t>0013673-47.2017.8.16.0130</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Embargos de Divergência em Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Parceria Agrícola e/ou pecuária</t>
+          <t>Promessa de Compra e Venda | Rescisão / Resolução</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>26/01/2026</t>
+          <t>26/03/2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>28/09/2026 18:23</t>
+          <t>06/10/2026 14:53</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>28/09/2026 18:23</t>
+          <t>06/10/2026 14:53</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>07/10/2026 04:17</t>
+          <t>07/10/2026 03:49</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2604,7 +2604,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0000240-03.2021.8.16.0108</t>
+          <t>0014093-66.2023.8.16.0025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2614,27 +2614,27 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Apropriação indébita</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>20/01/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>06/10/2026 16:03</t>
+          <t>05/10/2026 15:53</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>06/10/2026 16:03</t>
+          <t>05/10/2026 15:53</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>07/10/2026 04:17</t>
+          <t>06/10/2026 04:35</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2651,37 +2651,37 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0043698-98.2024.8.16.0000</t>
+          <t>0014138-79.2022.8.16.0001</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Crimes da Lei de licitações</t>
+          <t>Alienação Fiduciária</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>02/10/2025</t>
+          <t>12/01/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>06/10/2026 13:03</t>
+          <t>28/09/2026 17:33</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>06/10/2026 13:03</t>
+          <t>28/09/2026 17:33</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>07/10/2026 04:20</t>
+          <t>07/10/2026 06:09</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2698,7 +2698,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0080573-04.2023.8.16.0000</t>
+          <t>0014381-21.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2708,27 +2708,27 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Inventário e Partilha</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>13/11/2024</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>28/09/2026 14:13</t>
+          <t>05/10/2026 14:13</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>28/09/2026 14:13</t>
+          <t>05/10/2026 14:13</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>07/10/2026 04:20</t>
+          <t>06/10/2026 04:38</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2745,37 +2745,37 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0010091-86.2023.8.16.0014</t>
+          <t>0015214-66.2025.8.16.0185</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Pedido de Uniformização de Interpretação de Lei Criminal</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Adicional de Periculosidade</t>
+          <t>Dívida Ativa (Execução Fiscal)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>14/09/2026 14:43</t>
+          <t>17/09/2026 13:33</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>14/09/2026 14:43</t>
+          <t>17/09/2026 13:33</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>23/09/2026 06:20</t>
+          <t>26/09/2026 04:10</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2792,7 +2792,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0012511-74.2015.8.16.0069</t>
+          <t>0016200-33.2025.8.16.0019</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2802,27 +2802,27 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Aposentadoria Especial (Art. 57/8)</t>
+          <t>Homicídio Qualificado</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>14/09/2026 13:53</t>
+          <t>16/09/2026 15:23</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>14/09/2026 13:53</t>
+          <t>16/09/2026 15:23</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>24/09/2026 17:10</t>
+          <t>26/09/2026 04:10</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2839,7 +2839,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0005532-90.2023.8.16.0045</t>
+          <t>0016524-48.2023.8.16.0001</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2849,27 +2849,27 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Rescisão / Resolução</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>25/02/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>14/09/2026 13:23</t>
+          <t>05/10/2026 14:03</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>14/09/2026 13:23</t>
+          <t>05/10/2026 14:03</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>24/09/2026 17:21</t>
+          <t>06/10/2026 04:49</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2886,7 +2886,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0028232-46.2020.8.16.0019</t>
+          <t>0016917-05.2024.8.16.0173</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2896,27 +2896,27 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Homicídio Qualificado</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>14/09/2026 14:23</t>
+          <t>06/10/2026 14:43</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>14/09/2026 14:23</t>
+          <t>06/10/2026 14:43</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>24/09/2026 17:45</t>
+          <t>07/10/2026 06:03</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2933,37 +2933,37 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0050674-53.2026.8.16.0000</t>
+          <t>0017883-91.2024.8.16.0035</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>04/04/2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>22/09/2026 14:33</t>
+          <t>05/10/2026 17:12</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>22/09/2026 14:33</t>
+          <t>06/10/2026 15:48</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>24/09/2026 17:45</t>
+          <t>07/10/2026 04:23</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2980,7 +2980,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0001243-96.2023.8.16.0148</t>
+          <t>0019842-08.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2990,27 +2990,27 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Liminar | Indenização por Dano Material | Obrigação de Fazer / Não Fazer</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>14/09/2026 13:23</t>
+          <t>28/09/2026 14:33</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>14/09/2026 13:23</t>
+          <t>28/09/2026 14:33</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>24/09/2026 18:03</t>
+          <t>07/10/2026 03:45</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3027,7 +3027,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0040364-56.2024.8.16.0000</t>
+          <t>0019858-22.2022.8.16.0035</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3037,27 +3037,27 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dano ao Erário | Nulidade - Intimação Sem Observância das Prescrições Legais | Violação dos Princípios Administrativos</t>
+          <t>Pagamento</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>15/05/2025</t>
+          <t>23/09/2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>14/09/2026 13:13</t>
+          <t>28/09/2026 18:03</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>14/09/2026 13:13</t>
+          <t>28/09/2026 18:03</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>24/09/2026 18:07</t>
+          <t>07/10/2026 04:20</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3074,7 +3074,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0025625-17.2020.8.16.0001</t>
+          <t>0021175-92.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3084,27 +3084,27 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Prestação de Serviços | Contratos Bancários | Honorários Advocatícios</t>
+          <t>Recuperação judicial e Falência | Concurso de Credores</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>16/09/2025</t>
+          <t>08/12/2025</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>14/09/2026 14:33</t>
+          <t>28/09/2026 18:23</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>14/09/2026 14:33</t>
+          <t>28/09/2026 18:23</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>24/09/2026 18:17</t>
+          <t>07/10/2026 04:20</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3121,7 +3121,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0001508-80.2024.8.16.0175</t>
+          <t>0023521-76.2021.8.16.0014</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3131,27 +3131,27 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Defeito, nulidade ou anulação | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>14/09/2026 13:43</t>
+          <t>05/10/2026 16:03</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>14/09/2026 13:43</t>
+          <t>05/10/2026 16:03</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>24/09/2026 18:17</t>
+          <t>06/10/2026 04:49</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3168,7 +3168,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0148376-33.2025.8.16.0000</t>
+          <t>0023941-38.2022.8.16.0017</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3178,27 +3178,27 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>PIS/PASEP | PASEP</t>
+          <t>Rescisão do contrato e devolução do dinheiro</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>14/09/2026 14:03</t>
+          <t>05/10/2026 15:43</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>14/09/2026 14:03</t>
+          <t>05/10/2026 15:43</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>24/09/2026 18:20</t>
+          <t>06/10/2026 04:35</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3215,37 +3215,37 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0097585-94.2024.8.16.0000</t>
+          <t>0025353-57.2025.8.16.0030</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Telefonia</t>
+          <t>Receptação Qualificada</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>26/11/2025</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>14/09/2026 13:43</t>
+          <t>28/09/2026 17:23</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>14/09/2026 13:43</t>
+          <t>28/09/2026 17:23</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>24/09/2026 18:25</t>
+          <t>07/10/2026 04:32</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3262,7 +3262,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0000674-91.2024.8.16.0138</t>
+          <t>0027654-38.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3272,27 +3272,27 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sustação de Protesto</t>
+          <t>Restituição ao Erário | Dano ao Erário | Obrigação de Fazer / Não Fazer | Ônus da Prova | Violação dos Princípios Administrativos</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>19/05/2025</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>14/09/2026 14:23</t>
+          <t>28/09/2026 16:03</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>14/09/2026 14:23</t>
+          <t>28/09/2026 16:03</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>24/09/2026 18:32</t>
+          <t>07/10/2026 05:52</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3309,7 +3309,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0001565-54.2024.8.16.0028</t>
+          <t>0028703-46.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3319,27 +3319,27 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Roubo Majorado | Crime Tentado</t>
+          <t>Espécies de Títulos de Crédito</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>15/08/2025</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>14/09/2026 14:03</t>
+          <t>28/09/2026 17:14</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>14/09/2026 14:03</t>
+          <t>28/09/2026 17:14</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>24/09/2026 18:32</t>
+          <t>07/10/2026 03:31</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3356,7 +3356,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0058340-76.2024.8.16.0000</t>
+          <t>0033203-58.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3366,27 +3366,27 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>PIS/PASEP | Indenização por Dano Material | Práticas Abusivas</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>14/09/2026 14:23</t>
+          <t>28/09/2026 17:53</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>14/09/2026 14:23</t>
+          <t>28/09/2026 17:53</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>24/09/2026 18:36</t>
+          <t>07/10/2026 03:31</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3403,37 +3403,37 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0003548-40.2022.8.16.0196</t>
+          <t>0033286-91.2013.8.16.0001</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Reivindicação | Pagamento</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>09/02/2022</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>16/09/2026 13:33</t>
+          <t>28/09/2026 14:33</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>16/09/2026 13:33</t>
+          <t>28/09/2026 14:33</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>25/09/2026 04:40</t>
+          <t>07/10/2026 05:40</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3450,7 +3450,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0003769-86.2023.8.16.0196</t>
+          <t>0034555-58.2019.8.16.0001</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3460,27 +3460,27 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>15/09/2026 14:53</t>
+          <t>28/09/2026 17:03</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>15/09/2026 14:53</t>
+          <t>28/09/2026 17:03</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>25/09/2026 04:44</t>
+          <t>07/10/2026 03:46</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3497,37 +3497,37 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0002122-28.2024.8.16.0000</t>
+          <t>0035579-85.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>25/08/2025</t>
+          <t>11/12/2024</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>16/09/2026 12:06</t>
+          <t>28/09/2026 14:33</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>16/09/2026 12:06</t>
+          <t>28/09/2026 14:33</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>25/09/2026 04:44</t>
+          <t>07/10/2026 05:43</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3544,7 +3544,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0013125-21.2023.8.16.0030</t>
+          <t>0038273-56.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3554,27 +3554,27 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Fiscalização</t>
+          <t>Práticas Abusivas</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>15/09/2026 15:43</t>
+          <t>05/10/2026 14:23</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>15/09/2026 15:43</t>
+          <t>05/10/2026 14:23</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>25/09/2026 04:47</t>
+          <t>06/10/2026 04:35</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3591,7 +3591,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0081451-89.2024.8.16.0000</t>
+          <t>0043698-98.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3601,27 +3601,27 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Prestação de Serviços | Honorários Advocatícios</t>
+          <t>Crimes da Lei de licitações</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>02/10/2025</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>15/09/2026 14:03</t>
+          <t>06/10/2026 13:03</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>15/09/2026 14:03</t>
+          <t>06/10/2026 13:03</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>25/09/2026 04:49</t>
+          <t>07/10/2026 04:20</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3638,7 +3638,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0098757-71.2024.8.16.0000</t>
+          <t>0046220-64.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3648,27 +3648,27 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Revisão de Juros Remuneratórios, Capitalização/Anatocismo</t>
+          <t>Reintegração de Posse</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>15/09/2026 13:53</t>
+          <t>05/10/2026 15:33</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>15/09/2026 13:53</t>
+          <t>05/10/2026 15:33</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>25/09/2026 04:49</t>
+          <t>06/10/2026 04:35</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3685,7 +3685,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0017322-41.2025.8.16.0000</t>
+          <t>0048696-67.2024.8.16.0014</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3695,27 +3695,27 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Alienação Fiduciária</t>
+          <t>Cessão de Crédito | Causas Supervenientes à Sentença</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>15/09/2026 13:33</t>
+          <t>02/10/2026 15:23</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>15/09/2026 13:33</t>
+          <t>02/10/2026 15:23</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>25/09/2026 05:01</t>
+          <t>07/10/2026 05:43</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3732,7 +3732,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0005030-07.2025.8.16.0038</t>
+          <t>0056802-26.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3742,27 +3742,27 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Contratos Bancários | Tutela de Urgência</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>15/09/2026 17:23</t>
+          <t>05/10/2026 14:23</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>15/09/2026 17:23</t>
+          <t>05/10/2026 14:23</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>25/09/2026 05:10</t>
+          <t>06/10/2026 04:35</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3779,7 +3779,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0040684-14.2022.8.16.0021</t>
+          <t>0058493-75.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3789,27 +3789,27 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ICMS/ Imposto sobre Circulação de Mercadorias</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>14/08/2025</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>16/09/2026 07:28</t>
+          <t>28/09/2026 16:53</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>16/09/2026 07:28</t>
+          <t>28/09/2026 16:53</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>25/09/2026 05:10</t>
+          <t>07/10/2026 04:32</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3826,37 +3826,37 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0109824-62.2026.8.16.0000</t>
+          <t>0064056-50.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Ameaça | Desobediência | Crimes do Sistema Nacional de Armas</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>22/09/2026 16:13</t>
+          <t>05/10/2026 15:23</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>22/09/2026 16:13</t>
+          <t>05/10/2026 15:23</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>25/09/2026 05:12</t>
+          <t>06/10/2026 04:49</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3873,7 +3873,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0024154-27.2024.8.16.0000</t>
+          <t>0065426-64.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3883,27 +3883,27 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Compra e Venda</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>15/09/2026 17:03</t>
+          <t>05/10/2026 14:03</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>15/09/2026 17:03</t>
+          <t>05/10/2026 14:03</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>25/09/2026 05:12</t>
+          <t>07/10/2026 04:43</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3920,7 +3920,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0000908-97.2024.8.16.0033</t>
+          <t>0070752-05.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3930,27 +3930,27 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Compra e Venda | Assistência Judiciária Gratuita</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>15/09/2026 17:03</t>
+          <t>05/10/2026 14:33</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>15/09/2026 17:03</t>
+          <t>05/10/2026 14:33</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>25/09/2026 05:15</t>
+          <t>06/10/2026 04:53</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3967,7 +3967,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0009896-40.2025.8.16.0044</t>
+          <t>0071100-57.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3977,27 +3977,27 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Associação para a Produção e Tráfico e Condutas Afins</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>17/09/2025</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>15/09/2026 15:03</t>
+          <t>05/10/2026 14:53</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>15/09/2026 15:03</t>
+          <t>05/10/2026 14:53</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>25/09/2026 05:19</t>
+          <t>06/10/2026 04:35</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -4014,7 +4014,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0010154-54.2021.8.16.0185</t>
+          <t>0071691-82.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4024,27 +4024,27 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>PIS/PASEP | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>16/09/2026 14:03</t>
+          <t>28/09/2026 16:03</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>16/09/2026 14:03</t>
+          <t>28/09/2026 16:03</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>25/09/2026 05:20</t>
+          <t>07/10/2026 05:52</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4061,7 +4061,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0003013-71.2020.8.16.0038</t>
+          <t>0074926-28.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4071,27 +4071,27 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Nota Promissória</t>
+          <t>Duplicata</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>30/01/2026</t>
+          <t>05/09/2024</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>16/09/2026 13:53</t>
+          <t>28/09/2026 18:53</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>16/09/2026 13:53</t>
+          <t>28/09/2026 18:53</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>25/09/2026 05:34</t>
+          <t>07/10/2026 03:48</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -4108,7 +4108,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0011262-51.2024.8.16.0044</t>
+          <t>0077227-74.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4118,27 +4118,27 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Associação para a Produção e Tráfico e Condutas Afins | Promoção, constituição, financiamento ou integração de Organização Criminosa | Crimes de &amp;quot;Lavagem&amp;quot; ou Ocultação de Bens, Direitos ou Valores</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>15/09/2026 16:53</t>
+          <t>28/09/2026 19:33</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>15/09/2026 16:53</t>
+          <t>28/09/2026 19:33</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>25/09/2026 09:15</t>
+          <t>07/10/2026 03:45</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4155,7 +4155,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0020261-66.2023.8.16.0031</t>
+          <t>0080070-80.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4165,27 +4165,27 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Compromisso</t>
+          <t>Cédula de Crédito Bancário | Penhora / Depósito/ Avaliação</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/02/2025</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>14/09/2026 13:09</t>
+          <t>28/09/2026 17:33</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>14/09/2026 13:09</t>
+          <t>28/09/2026 17:33</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>25/09/2026 09:15</t>
+          <t>07/10/2026 04:34</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4202,7 +4202,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0002809-68.2025.8.16.0000</t>
+          <t>0080573-04.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4212,27 +4212,27 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Inventário e Partilha</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>13/11/2024</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>16/09/2026 13:23</t>
+          <t>28/09/2026 14:13</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>16/09/2026 13:23</t>
+          <t>28/09/2026 14:13</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>25/09/2026 09:15</t>
+          <t>07/10/2026 04:20</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4249,37 +4249,37 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0004317-38.2018.8.16.0083</t>
+          <t>0086164-39.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Erro Médico</t>
+          <t>Associação Criminosa | Furto Qualificado</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>20/01/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>16/09/2026 13:53</t>
+          <t>06/10/2026 14:33</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>16/09/2026 13:53</t>
+          <t>06/10/2026 14:33</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>25/09/2026 09:15</t>
+          <t>07/10/2026 03:45</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4296,37 +4296,37 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0017165-68.2025.8.16.0000</t>
+          <t>0087707-77.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Tráfico de Drogas e Condutas Afins | Adulteração de Sinal Identificador de Veículo Automotor</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>15/09/2026 17:24</t>
+          <t>06/10/2026 13:03</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>15/09/2026 17:24</t>
+          <t>06/10/2026 13:03</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>25/09/2026 09:15</t>
+          <t>07/10/2026 05:52</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4343,7 +4343,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0033528-79.2015.8.16.0001</t>
+          <t>0088053-62.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4353,27 +4353,27 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Direitos / Deveres do Condômino</t>
+          <t>Direito de Vizinhança | Assistência Judiciária Gratuita</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>15/09/2026 16:13</t>
+          <t>05/10/2026 14:33</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>15/09/2026 16:13</t>
+          <t>05/10/2026 14:33</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>25/09/2026 09:15</t>
+          <t>06/10/2026 04:53</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4390,37 +4390,37 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0014455-75.2025.8.16.0000</t>
+          <t>0089765-53.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>15/09/2026 17:53</t>
+          <t>29/09/2026 16:23</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>15/09/2026 17:53</t>
+          <t>29/09/2026 16:23</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>25/09/2026 09:15</t>
+          <t>06/10/2026 04:38</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4437,7 +4437,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0005298-13.2024.8.16.0033</t>
+          <t>0089862-87.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4447,27 +4447,27 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Superendividamento</t>
+          <t>Rescisão / Resolução</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>16/09/2026 13:43</t>
+          <t>05/10/2026 13:53</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>16/09/2026 13:43</t>
+          <t>05/10/2026 13:53</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>25/09/2026 09:15</t>
+          <t>06/10/2026 04:53</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4484,37 +4484,37 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0013992-22.2014.8.16.0000</t>
+          <t>0092890-34.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Compromisso</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>24/04/2025</t>
+          <t>24/01/2025</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>15/09/2026 17:43</t>
+          <t>28/09/2026 13:33</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>15/09/2026 17:43</t>
+          <t>28/09/2026 13:33</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>25/09/2026 09:15</t>
+          <t>07/10/2026 03:31</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4531,7 +4531,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0018063-74.2008.8.16.0001</t>
+          <t>0116457-60.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4541,27 +4541,27 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Erro Médico</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>05/03/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>15/09/2026 14:03</t>
+          <t>28/09/2026 18:03</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>15/09/2026 14:03</t>
+          <t>28/09/2026 18:03</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>25/09/2026 09:15</t>
+          <t>07/10/2026 06:22</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4578,37 +4578,37 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0047645-92.2026.8.16.0000</t>
+          <t>0119994-64.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Associação para a Produção e Tráfico e Condutas Afins | Prisão Preventiva | Promoção, constituição, financiamento ou integração de Organização Criminosa</t>
+          <t>IPTU/ Imposto Predial e Territorial Urbano</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>22/09/2026 15:53</t>
+          <t>16/09/2026 14:23</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>22/09/2026 15:53</t>
+          <t>16/09/2026 14:23</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>26/09/2026 03:30</t>
+          <t>26/09/2026 04:10</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4625,7 +4625,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0060675-26.2024.8.16.0014</t>
+          <t>0122256-84.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4635,27 +4635,27 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Enriquecimento ilícito | Dano ao Erário | Violação dos Princípios Administrativos</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>16/09/2026 14:23</t>
+          <t>16/09/2026 14:43</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>16/09/2026 14:23</t>
+          <t>16/09/2026 14:43</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>26/09/2026 03:40</t>
+          <t>26/09/2026 05:00</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4672,7 +4672,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0032740-19.2025.8.16.0000</t>
+          <t>0123956-95.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4682,27 +4682,27 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Espécies de Títulos de Crédito | Sucumbenciais</t>
+          <t>Compromisso</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>17/09/2026 14:23</t>
+          <t>28/09/2026 16:53</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>17/09/2026 14:23</t>
+          <t>28/09/2026 16:53</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>26/09/2026 03:40</t>
+          <t>07/10/2026 06:09</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4719,37 +4719,37 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0012821-80.2021.8.16.0001</t>
+          <t>0127645-50.2